--- a/output/2024-07-26.xlsx
+++ b/output/2024-07-26.xlsx
@@ -625,34 +625,34 @@
         <v>1</v>
       </c>
       <c r="E14" t="n">
-        <v>1.99</v>
+        <v>2.26</v>
       </c>
       <c r="F14" t="n">
-        <v>8.08</v>
+        <v>9.16</v>
       </c>
       <c r="G14" t="n">
-        <v>66.09999999999999</v>
+        <v>68.8</v>
       </c>
       <c r="H14" t="n">
-        <v>30.3</v>
+        <v>30.4</v>
       </c>
       <c r="I14" t="n">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="J14" t="n">
-        <v>-14.9</v>
+        <v>48.78</v>
       </c>
       <c r="K14" t="n">
-        <v>81.48</v>
+        <v>49.82</v>
       </c>
       <c r="L14" t="n">
-        <v>82.84</v>
+        <v>69.72</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>05:11:20</t>
+          <t>05:09:53</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -667,34 +667,34 @@
         <v>2</v>
       </c>
       <c r="E15" t="n">
-        <v>1.74</v>
+        <v>1.64</v>
       </c>
       <c r="F15" t="n">
-        <v>9.24</v>
+        <v>8</v>
       </c>
       <c r="G15" t="n">
-        <v>77.90000000000001</v>
+        <v>88.7</v>
       </c>
       <c r="H15" t="n">
-        <v>37.1</v>
+        <v>30.7</v>
       </c>
       <c r="I15" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="J15" t="n">
-        <v>2.55</v>
+        <v>24.64</v>
       </c>
       <c r="K15" t="n">
-        <v>-33.01</v>
+        <v>-19.78</v>
       </c>
       <c r="L15" t="n">
-        <v>33.11</v>
+        <v>31.59</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>05:13:43</t>
+          <t>05:11:09</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -709,34 +709,34 @@
         <v>3</v>
       </c>
       <c r="E16" t="n">
-        <v>1.66</v>
+        <v>1.7</v>
       </c>
       <c r="F16" t="n">
-        <v>9.35</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="G16" t="n">
-        <v>76.5</v>
+        <v>67.40000000000001</v>
       </c>
       <c r="H16" t="n">
-        <v>25.7</v>
+        <v>29.3</v>
       </c>
       <c r="I16" t="n">
         <v>23</v>
       </c>
       <c r="J16" t="n">
-        <v>127.21</v>
+        <v>-19.64</v>
       </c>
       <c r="K16" t="n">
-        <v>48.06</v>
+        <v>46.91</v>
       </c>
       <c r="L16" t="n">
-        <v>135.99</v>
+        <v>50.86</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>05:19:11</t>
+          <t>05:17:56</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -751,34 +751,34 @@
         <v>1</v>
       </c>
       <c r="E17" t="n">
-        <v>2.35</v>
+        <v>1.58</v>
       </c>
       <c r="F17" t="n">
-        <v>9.18</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="G17" t="n">
-        <v>59</v>
+        <v>57.4</v>
       </c>
       <c r="H17" t="n">
-        <v>32.9</v>
+        <v>32</v>
       </c>
       <c r="I17" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J17" t="n">
-        <v>24.2</v>
+        <v>-74.70999999999999</v>
       </c>
       <c r="K17" t="n">
-        <v>-183.17</v>
+        <v>65.14</v>
       </c>
       <c r="L17" t="n">
-        <v>184.76</v>
+        <v>99.12</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>05:21:19</t>
+          <t>05:18:46</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -793,34 +793,34 @@
         <v>2</v>
       </c>
       <c r="E18" t="n">
-        <v>1.27</v>
+        <v>1.5</v>
       </c>
       <c r="F18" t="n">
-        <v>9.630000000000001</v>
+        <v>8.720000000000001</v>
       </c>
       <c r="G18" t="n">
-        <v>69.90000000000001</v>
+        <v>57.9</v>
       </c>
       <c r="H18" t="n">
-        <v>32.3</v>
+        <v>27.6</v>
       </c>
       <c r="I18" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="J18" t="n">
-        <v>-32.06</v>
+        <v>48.78</v>
       </c>
       <c r="K18" t="n">
-        <v>51.28</v>
+        <v>9.19</v>
       </c>
       <c r="L18" t="n">
-        <v>60.48</v>
+        <v>49.64</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>05:23:28</t>
+          <t>05:21:11</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -835,34 +835,34 @@
         <v>3</v>
       </c>
       <c r="E19" t="n">
-        <v>2</v>
+        <v>1.47</v>
       </c>
       <c r="F19" t="n">
-        <v>9.550000000000001</v>
+        <v>8.99</v>
       </c>
       <c r="G19" t="n">
-        <v>66.2</v>
+        <v>72.2</v>
       </c>
       <c r="H19" t="n">
-        <v>35.4</v>
+        <v>32.9</v>
       </c>
       <c r="I19" t="n">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="J19" t="n">
-        <v>72.64</v>
+        <v>148.82</v>
       </c>
       <c r="K19" t="n">
-        <v>-95.29000000000001</v>
+        <v>-12.79</v>
       </c>
       <c r="L19" t="n">
-        <v>119.82</v>
+        <v>149.37</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>05:28:21</t>
+          <t>05:25:27</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -877,34 +877,34 @@
         <v>1</v>
       </c>
       <c r="E20" t="n">
-        <v>1.7</v>
+        <v>1.52</v>
       </c>
       <c r="F20" t="n">
-        <v>9.359999999999999</v>
+        <v>8.76</v>
       </c>
       <c r="G20" t="n">
-        <v>75.59999999999999</v>
+        <v>63.9</v>
       </c>
       <c r="H20" t="n">
-        <v>32.7</v>
+        <v>25.8</v>
       </c>
       <c r="I20" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="J20" t="n">
-        <v>85.86</v>
+        <v>-30.87</v>
       </c>
       <c r="K20" t="n">
-        <v>93.11</v>
+        <v>130.68</v>
       </c>
       <c r="L20" t="n">
-        <v>126.65</v>
+        <v>134.28</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>05:30:27</t>
+          <t>05:27:43</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -919,34 +919,34 @@
         <v>2</v>
       </c>
       <c r="E21" t="n">
-        <v>1.61</v>
+        <v>2.11</v>
       </c>
       <c r="F21" t="n">
-        <v>8.51</v>
+        <v>9.15</v>
       </c>
       <c r="G21" t="n">
-        <v>53.1</v>
+        <v>46.7</v>
       </c>
       <c r="H21" t="n">
-        <v>29</v>
+        <v>29.3</v>
       </c>
       <c r="I21" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="J21" t="n">
-        <v>303.51</v>
+        <v>-290.45</v>
       </c>
       <c r="K21" t="n">
-        <v>-99.01000000000001</v>
+        <v>-19.42</v>
       </c>
       <c r="L21" t="n">
-        <v>319.26</v>
+        <v>291.1</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>05:31:29</t>
+          <t>05:28:12</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -961,34 +961,34 @@
         <v>3</v>
       </c>
       <c r="E22" t="n">
-        <v>1.93</v>
+        <v>1.87</v>
       </c>
       <c r="F22" t="n">
-        <v>9.43</v>
+        <v>8.9</v>
       </c>
       <c r="G22" t="n">
-        <v>70.8</v>
+        <v>69.3</v>
       </c>
       <c r="H22" t="n">
-        <v>34.6</v>
+        <v>36.4</v>
       </c>
       <c r="I22" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="J22" t="n">
-        <v>-112.38</v>
+        <v>248.51</v>
       </c>
       <c r="K22" t="n">
-        <v>56.67</v>
+        <v>81.72</v>
       </c>
       <c r="L22" t="n">
-        <v>125.86</v>
+        <v>261.6</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>05:37:54</t>
+          <t>05:33:07</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1003,34 +1003,34 @@
         <v>1</v>
       </c>
       <c r="E23" t="n">
-        <v>1.37</v>
+        <v>1.58</v>
       </c>
       <c r="F23" t="n">
-        <v>8.26</v>
+        <v>8.869999999999999</v>
       </c>
       <c r="G23" t="n">
-        <v>64.7</v>
+        <v>57.2</v>
       </c>
       <c r="H23" t="n">
-        <v>35.7</v>
+        <v>30.1</v>
       </c>
       <c r="I23" t="n">
         <v>23</v>
       </c>
       <c r="J23" t="n">
-        <v>199.82</v>
+        <v>-325.97</v>
       </c>
       <c r="K23" t="n">
-        <v>343.9</v>
+        <v>-207.6</v>
       </c>
       <c r="L23" t="n">
-        <v>397.74</v>
+        <v>386.46</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>05:39:33</t>
+          <t>05:34:12</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1045,34 +1045,34 @@
         <v>2</v>
       </c>
       <c r="E24" t="n">
-        <v>2.92</v>
+        <v>1.66</v>
       </c>
       <c r="F24" t="n">
-        <v>9.710000000000001</v>
+        <v>8.720000000000001</v>
       </c>
       <c r="G24" t="n">
-        <v>60.1</v>
+        <v>63.4</v>
       </c>
       <c r="H24" t="n">
-        <v>25.9</v>
+        <v>28.3</v>
       </c>
       <c r="I24" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="J24" t="n">
-        <v>279.1</v>
+        <v>-103.19</v>
       </c>
       <c r="K24" t="n">
-        <v>-539.12</v>
+        <v>-39.93</v>
       </c>
       <c r="L24" t="n">
-        <v>607.08</v>
+        <v>110.65</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>05:40:46</t>
+          <t>05:35:23</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1087,34 +1087,34 @@
         <v>3</v>
       </c>
       <c r="E25" t="n">
-        <v>1.89</v>
+        <v>1.72</v>
       </c>
       <c r="F25" t="n">
-        <v>9.52</v>
+        <v>8.369999999999999</v>
       </c>
       <c r="G25" t="n">
-        <v>76.09999999999999</v>
+        <v>60.5</v>
       </c>
       <c r="H25" t="n">
-        <v>32.6</v>
+        <v>33</v>
       </c>
       <c r="I25" t="n">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="J25" t="n">
-        <v>-245.33</v>
+        <v>76.53</v>
       </c>
       <c r="K25" t="n">
-        <v>134.65</v>
+        <v>-160.34</v>
       </c>
       <c r="L25" t="n">
-        <v>279.85</v>
+        <v>177.67</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>05:45:09</t>
+          <t>05:39:59</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1129,34 +1129,34 @@
         <v>1</v>
       </c>
       <c r="E26" t="n">
-        <v>1.93</v>
+        <v>1.9</v>
       </c>
       <c r="F26" t="n">
-        <v>9.130000000000001</v>
+        <v>9.42</v>
       </c>
       <c r="G26" t="n">
-        <v>67.5</v>
+        <v>67.59999999999999</v>
       </c>
       <c r="H26" t="n">
-        <v>30.4</v>
+        <v>37.2</v>
       </c>
       <c r="I26" t="n">
         <v>22</v>
       </c>
       <c r="J26" t="n">
-        <v>-214.99</v>
+        <v>21.4</v>
       </c>
       <c r="K26" t="n">
-        <v>-126.93</v>
+        <v>-126.65</v>
       </c>
       <c r="L26" t="n">
-        <v>249.66</v>
+        <v>128.45</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>05:47:08</t>
+          <t>05:41:58</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1171,34 +1171,34 @@
         <v>2</v>
       </c>
       <c r="E27" t="n">
-        <v>1.9</v>
+        <v>1.92</v>
       </c>
       <c r="F27" t="n">
-        <v>8.74</v>
+        <v>9.66</v>
       </c>
       <c r="G27" t="n">
-        <v>74.7</v>
+        <v>55.5</v>
       </c>
       <c r="H27" t="n">
-        <v>32</v>
+        <v>26.5</v>
       </c>
       <c r="I27" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="J27" t="n">
-        <v>-37.36</v>
+        <v>170.66</v>
       </c>
       <c r="K27" t="n">
-        <v>184.55</v>
+        <v>-94.16</v>
       </c>
       <c r="L27" t="n">
-        <v>188.29</v>
+        <v>194.91</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>05:48:23</t>
+          <t>05:43:40</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1213,34 +1213,34 @@
         <v>3</v>
       </c>
       <c r="E28" t="n">
-        <v>2.02</v>
+        <v>1.9</v>
       </c>
       <c r="F28" t="n">
-        <v>9.68</v>
+        <v>8.859999999999999</v>
       </c>
       <c r="G28" t="n">
-        <v>62.3</v>
+        <v>56.2</v>
       </c>
       <c r="H28" t="n">
-        <v>35.8</v>
+        <v>31.8</v>
       </c>
       <c r="I28" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J28" t="n">
-        <v>-569.98</v>
+        <v>-928.35</v>
       </c>
       <c r="K28" t="n">
-        <v>189.38</v>
+        <v>-86.05</v>
       </c>
       <c r="L28" t="n">
-        <v>600.62</v>
+        <v>932.33</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>05:58:01</t>
+          <t>05:53:38</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1255,34 +1255,34 @@
         <v>1</v>
       </c>
       <c r="E29" t="n">
-        <v>1.3</v>
+        <v>1.58</v>
       </c>
       <c r="F29" t="n">
-        <v>9.32</v>
+        <v>9.130000000000001</v>
       </c>
       <c r="G29" t="n">
-        <v>58.4</v>
+        <v>68</v>
       </c>
       <c r="H29" t="n">
-        <v>28.2</v>
+        <v>37.4</v>
       </c>
       <c r="I29" t="n">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="J29" t="n">
-        <v>-82.5</v>
+        <v>59.28</v>
       </c>
       <c r="K29" t="n">
-        <v>-27.48</v>
+        <v>30.8</v>
       </c>
       <c r="L29" t="n">
-        <v>86.95999999999999</v>
+        <v>66.8</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>05:58:53</t>
+          <t>05:54:58</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1297,34 +1297,34 @@
         <v>2</v>
       </c>
       <c r="E30" t="n">
-        <v>2.1</v>
+        <v>1.93</v>
       </c>
       <c r="F30" t="n">
-        <v>9.35</v>
+        <v>9.640000000000001</v>
       </c>
       <c r="G30" t="n">
-        <v>63.9</v>
+        <v>82.3</v>
       </c>
       <c r="H30" t="n">
-        <v>37.4</v>
+        <v>20.6</v>
       </c>
       <c r="I30" t="n">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="J30" t="n">
-        <v>-3.76</v>
+        <v>-106.92</v>
       </c>
       <c r="K30" t="n">
-        <v>52.84</v>
+        <v>92.66</v>
       </c>
       <c r="L30" t="n">
-        <v>52.97</v>
+        <v>141.48</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>05:59:52</t>
+          <t>05:56:07</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1339,34 +1339,34 @@
         <v>3</v>
       </c>
       <c r="E31" t="n">
-        <v>1.57</v>
+        <v>1.65</v>
       </c>
       <c r="F31" t="n">
-        <v>8.92</v>
+        <v>9.029999999999999</v>
       </c>
       <c r="G31" t="n">
-        <v>68.40000000000001</v>
+        <v>54.1</v>
       </c>
       <c r="H31" t="n">
-        <v>27.4</v>
+        <v>39.2</v>
       </c>
       <c r="I31" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="J31" t="n">
-        <v>-19.16</v>
+        <v>-2.82</v>
       </c>
       <c r="K31" t="n">
-        <v>-18.45</v>
+        <v>-37.65</v>
       </c>
       <c r="L31" t="n">
-        <v>26.6</v>
+        <v>37.75</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>06:03:20</t>
+          <t>05:59:58</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1381,34 +1381,34 @@
         <v>1</v>
       </c>
       <c r="E32" t="n">
-        <v>1.71</v>
+        <v>2.18</v>
       </c>
       <c r="F32" t="n">
-        <v>9.279999999999999</v>
+        <v>8.890000000000001</v>
       </c>
       <c r="G32" t="n">
-        <v>78.90000000000001</v>
+        <v>57.4</v>
       </c>
       <c r="H32" t="n">
-        <v>28.3</v>
+        <v>34.9</v>
       </c>
       <c r="I32" t="n">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="J32" t="n">
-        <v>106</v>
+        <v>58.15</v>
       </c>
       <c r="K32" t="n">
-        <v>90.34999999999999</v>
+        <v>42.96</v>
       </c>
       <c r="L32" t="n">
-        <v>139.28</v>
+        <v>72.3</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>06:05:14</t>
+          <t>06:01:32</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1423,34 +1423,34 @@
         <v>2</v>
       </c>
       <c r="E33" t="n">
-        <v>2.51</v>
+        <v>2.06</v>
       </c>
       <c r="F33" t="n">
-        <v>8.84</v>
+        <v>9.640000000000001</v>
       </c>
       <c r="G33" t="n">
-        <v>60.6</v>
+        <v>68.7</v>
       </c>
       <c r="H33" t="n">
-        <v>35.5</v>
+        <v>26.7</v>
       </c>
       <c r="I33" t="n">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="J33" t="n">
-        <v>-101.39</v>
+        <v>55.5</v>
       </c>
       <c r="K33" t="n">
-        <v>22.15</v>
+        <v>74.27</v>
       </c>
       <c r="L33" t="n">
-        <v>103.78</v>
+        <v>92.72</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>06:06:26</t>
+          <t>06:03:53</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1465,34 +1465,34 @@
         <v>3</v>
       </c>
       <c r="E34" t="n">
-        <v>2.07</v>
+        <v>2.28</v>
       </c>
       <c r="F34" t="n">
-        <v>9.48</v>
+        <v>8.710000000000001</v>
       </c>
       <c r="G34" t="n">
-        <v>76.5</v>
+        <v>69</v>
       </c>
       <c r="H34" t="n">
-        <v>33</v>
+        <v>30.7</v>
       </c>
       <c r="I34" t="n">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="J34" t="n">
-        <v>1.17</v>
+        <v>-133.25</v>
       </c>
       <c r="K34" t="n">
-        <v>91.23999999999999</v>
+        <v>152.33</v>
       </c>
       <c r="L34" t="n">
-        <v>91.25</v>
+        <v>202.38</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>06:12:09</t>
+          <t>06:09:24</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1507,34 +1507,34 @@
         <v>1</v>
       </c>
       <c r="E35" t="n">
-        <v>2.44</v>
+        <v>2</v>
       </c>
       <c r="F35" t="n">
-        <v>9.279999999999999</v>
+        <v>8.630000000000001</v>
       </c>
       <c r="G35" t="n">
-        <v>63.2</v>
+        <v>73.5</v>
       </c>
       <c r="H35" t="n">
-        <v>25.3</v>
+        <v>34.9</v>
       </c>
       <c r="I35" t="n">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="J35" t="n">
-        <v>-37.67</v>
+        <v>171.03</v>
       </c>
       <c r="K35" t="n">
-        <v>-194.88</v>
+        <v>65.84</v>
       </c>
       <c r="L35" t="n">
-        <v>198.48</v>
+        <v>183.27</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>06:14:21</t>
+          <t>06:11:27</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1549,34 +1549,34 @@
         <v>2</v>
       </c>
       <c r="E36" t="n">
-        <v>2.22</v>
+        <v>1.62</v>
       </c>
       <c r="F36" t="n">
-        <v>8.6</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="G36" t="n">
-        <v>65.8</v>
+        <v>74.5</v>
       </c>
       <c r="H36" t="n">
-        <v>24.3</v>
+        <v>34.1</v>
       </c>
       <c r="I36" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="J36" t="n">
-        <v>-64.28</v>
+        <v>218.69</v>
       </c>
       <c r="K36" t="n">
-        <v>-104.61</v>
+        <v>169.98</v>
       </c>
       <c r="L36" t="n">
-        <v>122.78</v>
+        <v>276.98</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>06:16:09</t>
+          <t>06:14:02</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1591,34 +1591,34 @@
         <v>3</v>
       </c>
       <c r="E37" t="n">
-        <v>1.68</v>
+        <v>2.3</v>
       </c>
       <c r="F37" t="n">
-        <v>9.08</v>
+        <v>9.49</v>
       </c>
       <c r="G37" t="n">
-        <v>70.3</v>
+        <v>66.09999999999999</v>
       </c>
       <c r="H37" t="n">
-        <v>26.7</v>
+        <v>40.2</v>
       </c>
       <c r="I37" t="n">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="J37" t="n">
-        <v>76.09999999999999</v>
+        <v>162.19</v>
       </c>
       <c r="K37" t="n">
-        <v>107.98</v>
+        <v>-386.75</v>
       </c>
       <c r="L37" t="n">
-        <v>132.1</v>
+        <v>419.38</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>06:19:34</t>
+          <t>06:19:23</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1633,34 +1633,34 @@
         <v>1</v>
       </c>
       <c r="E38" t="n">
-        <v>2.02</v>
+        <v>1.77</v>
       </c>
       <c r="F38" t="n">
-        <v>9.34</v>
+        <v>8.56</v>
       </c>
       <c r="G38" t="n">
-        <v>57.4</v>
+        <v>74.2</v>
       </c>
       <c r="H38" t="n">
-        <v>30.2</v>
+        <v>32.2</v>
       </c>
       <c r="I38" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="J38" t="n">
-        <v>-120.15</v>
+        <v>224.74</v>
       </c>
       <c r="K38" t="n">
-        <v>282.08</v>
+        <v>411.94</v>
       </c>
       <c r="L38" t="n">
-        <v>306.6</v>
+        <v>469.26</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>06:21:22</t>
+          <t>06:21:24</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1675,34 +1675,34 @@
         <v>2</v>
       </c>
       <c r="E39" t="n">
-        <v>1.15</v>
+        <v>2.1</v>
       </c>
       <c r="F39" t="n">
-        <v>9.449999999999999</v>
+        <v>8.99</v>
       </c>
       <c r="G39" t="n">
-        <v>69</v>
+        <v>71.5</v>
       </c>
       <c r="H39" t="n">
-        <v>32.3</v>
+        <v>37.6</v>
       </c>
       <c r="I39" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="J39" t="n">
-        <v>-61.88</v>
+        <v>-177.06</v>
       </c>
       <c r="K39" t="n">
-        <v>-393.46</v>
+        <v>135.41</v>
       </c>
       <c r="L39" t="n">
-        <v>398.3</v>
+        <v>222.9</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>06:22:21</t>
+          <t>06:23:30</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1717,34 +1717,34 @@
         <v>3</v>
       </c>
       <c r="E40" t="n">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="F40" t="n">
-        <v>9.779999999999999</v>
+        <v>9.539999999999999</v>
       </c>
       <c r="G40" t="n">
-        <v>63.6</v>
+        <v>53.1</v>
       </c>
       <c r="H40" t="n">
-        <v>32.9</v>
+        <v>32.8</v>
       </c>
       <c r="I40" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="J40" t="n">
-        <v>-322.38</v>
+        <v>-78.54000000000001</v>
       </c>
       <c r="K40" t="n">
-        <v>-43.16</v>
+        <v>200.92</v>
       </c>
       <c r="L40" t="n">
-        <v>325.26</v>
+        <v>215.73</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>06:27:54</t>
+          <t>06:27:51</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1759,34 +1759,34 @@
         <v>1</v>
       </c>
       <c r="E41" t="n">
-        <v>2.12</v>
+        <v>2</v>
       </c>
       <c r="F41" t="n">
-        <v>9.17</v>
+        <v>9.109999999999999</v>
       </c>
       <c r="G41" t="n">
-        <v>70.8</v>
+        <v>63.3</v>
       </c>
       <c r="H41" t="n">
-        <v>24.5</v>
+        <v>30.9</v>
       </c>
       <c r="I41" t="n">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="J41" t="n">
-        <v>160.04</v>
+        <v>-132.96</v>
       </c>
       <c r="K41" t="n">
-        <v>-28.31</v>
+        <v>221.88</v>
       </c>
       <c r="L41" t="n">
-        <v>162.53</v>
+        <v>258.67</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>06:30:24</t>
+          <t>06:29:10</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -1801,34 +1801,34 @@
         <v>2</v>
       </c>
       <c r="E42" t="n">
-        <v>2.31</v>
+        <v>1.65</v>
       </c>
       <c r="F42" t="n">
-        <v>8.76</v>
+        <v>8.960000000000001</v>
       </c>
       <c r="G42" t="n">
-        <v>68.90000000000001</v>
+        <v>68.59999999999999</v>
       </c>
       <c r="H42" t="n">
-        <v>30.1</v>
+        <v>31.1</v>
       </c>
       <c r="I42" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="J42" t="n">
-        <v>-68.22</v>
+        <v>130.75</v>
       </c>
       <c r="K42" t="n">
-        <v>559.35</v>
+        <v>101.85</v>
       </c>
       <c r="L42" t="n">
-        <v>563.5</v>
+        <v>165.74</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>06:31:22</t>
+          <t>06:30:17</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -1843,34 +1843,34 @@
         <v>3</v>
       </c>
       <c r="E43" t="n">
-        <v>2.21</v>
+        <v>1.65</v>
       </c>
       <c r="F43" t="n">
-        <v>8.82</v>
+        <v>8.65</v>
       </c>
       <c r="G43" t="n">
-        <v>85.5</v>
+        <v>68.90000000000001</v>
       </c>
       <c r="H43" t="n">
-        <v>27</v>
+        <v>32.9</v>
       </c>
       <c r="I43" t="n">
         <v>22</v>
       </c>
       <c r="J43" t="n">
-        <v>450.8</v>
+        <v>266.21</v>
       </c>
       <c r="K43" t="n">
-        <v>-106.61</v>
+        <v>-316.12</v>
       </c>
       <c r="L43" t="n">
-        <v>463.24</v>
+        <v>413.28</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>06:40:47</t>
+          <t>06:41:01</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -1885,34 +1885,34 @@
         <v>1</v>
       </c>
       <c r="E44" t="n">
-        <v>1.76</v>
+        <v>1.94</v>
       </c>
       <c r="F44" t="n">
-        <v>8.619999999999999</v>
+        <v>9.65</v>
       </c>
       <c r="G44" t="n">
-        <v>69.59999999999999</v>
+        <v>74.8</v>
       </c>
       <c r="H44" t="n">
-        <v>26.3</v>
+        <v>25.2</v>
       </c>
       <c r="I44" t="n">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="J44" t="n">
-        <v>-24.63</v>
+        <v>-25.09</v>
       </c>
       <c r="K44" t="n">
-        <v>47.36</v>
+        <v>79.02</v>
       </c>
       <c r="L44" t="n">
-        <v>53.39</v>
+        <v>82.91</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>06:41:44</t>
+          <t>06:42:40</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -1927,34 +1927,34 @@
         <v>2</v>
       </c>
       <c r="E45" t="n">
-        <v>1.52</v>
+        <v>1.88</v>
       </c>
       <c r="F45" t="n">
-        <v>9.210000000000001</v>
+        <v>8.65</v>
       </c>
       <c r="G45" t="n">
-        <v>68.8</v>
+        <v>71.5</v>
       </c>
       <c r="H45" t="n">
-        <v>33.4</v>
+        <v>32.2</v>
       </c>
       <c r="I45" t="n">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="J45" t="n">
-        <v>-53.32</v>
+        <v>76.37</v>
       </c>
       <c r="K45" t="n">
-        <v>35.78</v>
+        <v>-4.29</v>
       </c>
       <c r="L45" t="n">
-        <v>64.20999999999999</v>
+        <v>76.48999999999999</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>06:42:39</t>
+          <t>06:43:46</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -1969,34 +1969,34 @@
         <v>3</v>
       </c>
       <c r="E46" t="n">
-        <v>1.9</v>
+        <v>1.49</v>
       </c>
       <c r="F46" t="n">
-        <v>9.550000000000001</v>
+        <v>8.44</v>
       </c>
       <c r="G46" t="n">
-        <v>74</v>
+        <v>74.3</v>
       </c>
       <c r="H46" t="n">
-        <v>27.9</v>
+        <v>29.4</v>
       </c>
       <c r="I46" t="n">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="J46" t="n">
-        <v>211.15</v>
+        <v>40.16</v>
       </c>
       <c r="K46" t="n">
-        <v>-75.54000000000001</v>
+        <v>-6.5</v>
       </c>
       <c r="L46" t="n">
-        <v>224.26</v>
+        <v>40.68</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>06:47:17</t>
+          <t>06:48:37</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -2011,34 +2011,34 @@
         <v>1</v>
       </c>
       <c r="E47" t="n">
-        <v>3.07</v>
+        <v>1.6</v>
       </c>
       <c r="F47" t="n">
-        <v>9.130000000000001</v>
+        <v>9.369999999999999</v>
       </c>
       <c r="G47" t="n">
-        <v>69</v>
+        <v>74.90000000000001</v>
       </c>
       <c r="H47" t="n">
-        <v>28.3</v>
+        <v>31.3</v>
       </c>
       <c r="I47" t="n">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="J47" t="n">
-        <v>81.06999999999999</v>
+        <v>-33.28</v>
       </c>
       <c r="K47" t="n">
-        <v>239.65</v>
+        <v>54.48</v>
       </c>
       <c r="L47" t="n">
-        <v>252.99</v>
+        <v>63.84</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>06:48:43</t>
+          <t>06:49:27</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2053,34 +2053,34 @@
         <v>2</v>
       </c>
       <c r="E48" t="n">
-        <v>2.32</v>
+        <v>2.35</v>
       </c>
       <c r="F48" t="n">
-        <v>8.6</v>
+        <v>8.359999999999999</v>
       </c>
       <c r="G48" t="n">
-        <v>72.40000000000001</v>
+        <v>53.6</v>
       </c>
       <c r="H48" t="n">
-        <v>32.5</v>
+        <v>37.9</v>
       </c>
       <c r="I48" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J48" t="n">
-        <v>8.460000000000001</v>
+        <v>-96.2</v>
       </c>
       <c r="K48" t="n">
-        <v>155.4</v>
+        <v>249.18</v>
       </c>
       <c r="L48" t="n">
-        <v>155.63</v>
+        <v>267.1</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>06:50:53</t>
+          <t>06:50:25</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2095,34 +2095,34 @@
         <v>3</v>
       </c>
       <c r="E49" t="n">
-        <v>1.7</v>
+        <v>2.33</v>
       </c>
       <c r="F49" t="n">
-        <v>9.24</v>
+        <v>9.6</v>
       </c>
       <c r="G49" t="n">
-        <v>70.09999999999999</v>
+        <v>52.3</v>
       </c>
       <c r="H49" t="n">
-        <v>34.6</v>
+        <v>26.6</v>
       </c>
       <c r="I49" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="J49" t="n">
-        <v>-11.56</v>
+        <v>192.41</v>
       </c>
       <c r="K49" t="n">
-        <v>-13.4</v>
+        <v>82.23999999999999</v>
       </c>
       <c r="L49" t="n">
-        <v>17.69</v>
+        <v>209.25</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>06:56:05</t>
+          <t>06:55:40</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -2137,34 +2137,34 @@
         <v>1</v>
       </c>
       <c r="E50" t="n">
-        <v>2.34</v>
+        <v>1.93</v>
       </c>
       <c r="F50" t="n">
-        <v>10.01</v>
+        <v>9.57</v>
       </c>
       <c r="G50" t="n">
-        <v>59.8</v>
+        <v>64</v>
       </c>
       <c r="H50" t="n">
-        <v>31.6</v>
+        <v>32.2</v>
       </c>
       <c r="I50" t="n">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="J50" t="n">
-        <v>0.35</v>
+        <v>33.43</v>
       </c>
       <c r="K50" t="n">
-        <v>-54.11</v>
+        <v>-97.61</v>
       </c>
       <c r="L50" t="n">
-        <v>54.11</v>
+        <v>103.17</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>06:58:21</t>
+          <t>06:56:38</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -2179,34 +2179,34 @@
         <v>2</v>
       </c>
       <c r="E51" t="n">
-        <v>1.99</v>
+        <v>2.33</v>
       </c>
       <c r="F51" t="n">
-        <v>9.119999999999999</v>
+        <v>9.390000000000001</v>
       </c>
       <c r="G51" t="n">
-        <v>65.3</v>
+        <v>59</v>
       </c>
       <c r="H51" t="n">
-        <v>31.4</v>
+        <v>33.3</v>
       </c>
       <c r="I51" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="J51" t="n">
-        <v>61.29</v>
+        <v>-109.74</v>
       </c>
       <c r="K51" t="n">
-        <v>170.46</v>
+        <v>219.41</v>
       </c>
       <c r="L51" t="n">
-        <v>181.14</v>
+        <v>245.33</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>06:59:08</t>
+          <t>06:58:40</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -2221,34 +2221,34 @@
         <v>3</v>
       </c>
       <c r="E52" t="n">
-        <v>2.1</v>
+        <v>1.64</v>
       </c>
       <c r="F52" t="n">
-        <v>9.84</v>
+        <v>9.02</v>
       </c>
       <c r="G52" t="n">
-        <v>49.8</v>
+        <v>67.90000000000001</v>
       </c>
       <c r="H52" t="n">
-        <v>32.8</v>
+        <v>22.4</v>
       </c>
       <c r="I52" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="J52" t="n">
-        <v>-124.75</v>
+        <v>78.17</v>
       </c>
       <c r="K52" t="n">
-        <v>40.25</v>
+        <v>-11.79</v>
       </c>
       <c r="L52" t="n">
-        <v>131.08</v>
+        <v>79.06</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>07:05:17</t>
+          <t>07:03:15</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -2263,34 +2263,34 @@
         <v>1</v>
       </c>
       <c r="E53" t="n">
-        <v>2.07</v>
+        <v>2.27</v>
       </c>
       <c r="F53" t="n">
-        <v>9.109999999999999</v>
+        <v>8.880000000000001</v>
       </c>
       <c r="G53" t="n">
-        <v>53.7</v>
+        <v>61.8</v>
       </c>
       <c r="H53" t="n">
-        <v>27.8</v>
+        <v>31.5</v>
       </c>
       <c r="I53" t="n">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="J53" t="n">
-        <v>88.23999999999999</v>
+        <v>-22.82</v>
       </c>
       <c r="K53" t="n">
-        <v>477.79</v>
+        <v>264.05</v>
       </c>
       <c r="L53" t="n">
-        <v>485.87</v>
+        <v>265.04</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>07:06:15</t>
+          <t>07:05:50</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -2305,34 +2305,34 @@
         <v>2</v>
       </c>
       <c r="E54" t="n">
-        <v>2.25</v>
+        <v>2</v>
       </c>
       <c r="F54" t="n">
-        <v>10</v>
+        <v>8.77</v>
       </c>
       <c r="G54" t="n">
-        <v>68.5</v>
+        <v>73.09999999999999</v>
       </c>
       <c r="H54" t="n">
-        <v>32.9</v>
+        <v>24.7</v>
       </c>
       <c r="I54" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J54" t="n">
-        <v>195.66</v>
+        <v>344.38</v>
       </c>
       <c r="K54" t="n">
-        <v>-222.18</v>
+        <v>144.24</v>
       </c>
       <c r="L54" t="n">
-        <v>296.05</v>
+        <v>373.37</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>07:08:02</t>
+          <t>07:07:48</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -2347,34 +2347,34 @@
         <v>3</v>
       </c>
       <c r="E55" t="n">
-        <v>2.19</v>
+        <v>2.25</v>
       </c>
       <c r="F55" t="n">
-        <v>9.32</v>
+        <v>9.449999999999999</v>
       </c>
       <c r="G55" t="n">
-        <v>72.09999999999999</v>
+        <v>71.8</v>
       </c>
       <c r="H55" t="n">
-        <v>32.5</v>
+        <v>29.2</v>
       </c>
       <c r="I55" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="J55" t="n">
-        <v>-179.57</v>
+        <v>483.7</v>
       </c>
       <c r="K55" t="n">
-        <v>-228.58</v>
+        <v>-38.53</v>
       </c>
       <c r="L55" t="n">
-        <v>290.68</v>
+        <v>485.23</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>07:11:55</t>
+          <t>07:12:45</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -2389,34 +2389,34 @@
         <v>1</v>
       </c>
       <c r="E56" t="n">
-        <v>2.49</v>
+        <v>1.58</v>
       </c>
       <c r="F56" t="n">
-        <v>9.470000000000001</v>
+        <v>8.91</v>
       </c>
       <c r="G56" t="n">
-        <v>69.8</v>
+        <v>62.3</v>
       </c>
       <c r="H56" t="n">
-        <v>32.9</v>
+        <v>23.5</v>
       </c>
       <c r="I56" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="J56" t="n">
-        <v>-183.08</v>
+        <v>11.58</v>
       </c>
       <c r="K56" t="n">
-        <v>-83.73</v>
+        <v>252.94</v>
       </c>
       <c r="L56" t="n">
-        <v>201.32</v>
+        <v>253.2</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>07:13:00</t>
+          <t>07:14:17</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -2431,34 +2431,34 @@
         <v>2</v>
       </c>
       <c r="E57" t="n">
-        <v>2.28</v>
+        <v>2</v>
       </c>
       <c r="F57" t="n">
-        <v>9.300000000000001</v>
+        <v>9.119999999999999</v>
       </c>
       <c r="G57" t="n">
-        <v>57.1</v>
+        <v>53.3</v>
       </c>
       <c r="H57" t="n">
-        <v>25.7</v>
+        <v>36</v>
       </c>
       <c r="I57" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="J57" t="n">
-        <v>144.36</v>
+        <v>276.38</v>
       </c>
       <c r="K57" t="n">
-        <v>277.86</v>
+        <v>12.21</v>
       </c>
       <c r="L57" t="n">
-        <v>313.12</v>
+        <v>276.65</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>07:14:39</t>
+          <t>07:15:15</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -2473,34 +2473,34 @@
         <v>3</v>
       </c>
       <c r="E58" t="n">
-        <v>1.68</v>
+        <v>1.99</v>
       </c>
       <c r="F58" t="n">
-        <v>9.470000000000001</v>
+        <v>9.789999999999999</v>
       </c>
       <c r="G58" t="n">
-        <v>63.3</v>
+        <v>65.59999999999999</v>
       </c>
       <c r="H58" t="n">
-        <v>33.5</v>
+        <v>35.9</v>
       </c>
       <c r="I58" t="n">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="J58" t="n">
-        <v>166.97</v>
+        <v>64.44</v>
       </c>
       <c r="K58" t="n">
-        <v>-239.67</v>
+        <v>-60.89</v>
       </c>
       <c r="L58" t="n">
-        <v>292.1</v>
+        <v>88.66</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>07:27:18</t>
+          <t>07:26:40</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -2515,34 +2515,34 @@
         <v>1</v>
       </c>
       <c r="E59" t="n">
-        <v>2.33</v>
+        <v>2.16</v>
       </c>
       <c r="F59" t="n">
-        <v>9.539999999999999</v>
+        <v>9.140000000000001</v>
       </c>
       <c r="G59" t="n">
-        <v>77.40000000000001</v>
+        <v>68.2</v>
       </c>
       <c r="H59" t="n">
-        <v>29.4</v>
+        <v>30.3</v>
       </c>
       <c r="I59" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="J59" t="n">
-        <v>-5.55</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="K59" t="n">
-        <v>25.29</v>
+        <v>140.71</v>
       </c>
       <c r="L59" t="n">
-        <v>25.89</v>
+        <v>141.05</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>07:29:09</t>
+          <t>07:28:12</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -2557,34 +2557,34 @@
         <v>2</v>
       </c>
       <c r="E60" t="n">
-        <v>2.33</v>
+        <v>2.13</v>
       </c>
       <c r="F60" t="n">
-        <v>9.52</v>
+        <v>8.710000000000001</v>
       </c>
       <c r="G60" t="n">
-        <v>63.8</v>
+        <v>73.3</v>
       </c>
       <c r="H60" t="n">
-        <v>26.9</v>
+        <v>30.5</v>
       </c>
       <c r="I60" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="J60" t="n">
-        <v>80.31999999999999</v>
+        <v>-69.5</v>
       </c>
       <c r="K60" t="n">
-        <v>-3.38</v>
+        <v>46.42</v>
       </c>
       <c r="L60" t="n">
-        <v>80.39</v>
+        <v>83.58</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>07:31:10</t>
+          <t>07:30:09</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -2599,34 +2599,34 @@
         <v>3</v>
       </c>
       <c r="E61" t="n">
-        <v>2.2</v>
+        <v>1.93</v>
       </c>
       <c r="F61" t="n">
-        <v>9.56</v>
+        <v>9.619999999999999</v>
       </c>
       <c r="G61" t="n">
-        <v>63.5</v>
+        <v>63.4</v>
       </c>
       <c r="H61" t="n">
-        <v>30.5</v>
+        <v>27.1</v>
       </c>
       <c r="I61" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="J61" t="n">
-        <v>104.53</v>
+        <v>-110.18</v>
       </c>
       <c r="K61" t="n">
-        <v>-128.11</v>
+        <v>95.13</v>
       </c>
       <c r="L61" t="n">
-        <v>165.34</v>
+        <v>145.56</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>07:34:05</t>
+          <t>07:34:48</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -2641,34 +2641,34 @@
         <v>1</v>
       </c>
       <c r="E62" t="n">
-        <v>1.56</v>
+        <v>1.76</v>
       </c>
       <c r="F62" t="n">
-        <v>9.09</v>
+        <v>9.74</v>
       </c>
       <c r="G62" t="n">
-        <v>57.1</v>
+        <v>70.5</v>
       </c>
       <c r="H62" t="n">
-        <v>30.7</v>
+        <v>32.5</v>
       </c>
       <c r="I62" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="J62" t="n">
-        <v>35.17</v>
+        <v>68.48999999999999</v>
       </c>
       <c r="K62" t="n">
-        <v>106.3</v>
+        <v>137.45</v>
       </c>
       <c r="L62" t="n">
-        <v>111.97</v>
+        <v>153.57</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>07:36:42</t>
+          <t>07:35:54</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -2683,34 +2683,34 @@
         <v>2</v>
       </c>
       <c r="E63" t="n">
-        <v>1.6</v>
+        <v>1.83</v>
       </c>
       <c r="F63" t="n">
-        <v>9.06</v>
+        <v>9.220000000000001</v>
       </c>
       <c r="G63" t="n">
-        <v>57.5</v>
+        <v>54.3</v>
       </c>
       <c r="H63" t="n">
-        <v>37.7</v>
+        <v>31.6</v>
       </c>
       <c r="I63" t="n">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="J63" t="n">
-        <v>-43.66</v>
+        <v>128.66</v>
       </c>
       <c r="K63" t="n">
-        <v>-107.29</v>
+        <v>51.69</v>
       </c>
       <c r="L63" t="n">
-        <v>115.83</v>
+        <v>138.65</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>07:37:58</t>
+          <t>07:37:10</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -2725,34 +2725,34 @@
         <v>3</v>
       </c>
       <c r="E64" t="n">
-        <v>1.64</v>
+        <v>2.57</v>
       </c>
       <c r="F64" t="n">
-        <v>9.24</v>
+        <v>9.1</v>
       </c>
       <c r="G64" t="n">
-        <v>70.40000000000001</v>
+        <v>59.2</v>
       </c>
       <c r="H64" t="n">
-        <v>32.2</v>
+        <v>29.1</v>
       </c>
       <c r="I64" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="J64" t="n">
-        <v>4.94</v>
+        <v>201.79</v>
       </c>
       <c r="K64" t="n">
-        <v>-10.04</v>
+        <v>-151.75</v>
       </c>
       <c r="L64" t="n">
-        <v>11.19</v>
+        <v>252.48</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>07:42:41</t>
+          <t>07:42:00</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -2767,34 +2767,34 @@
         <v>1</v>
       </c>
       <c r="E65" t="n">
-        <v>1.84</v>
+        <v>2.61</v>
       </c>
       <c r="F65" t="n">
-        <v>9.220000000000001</v>
+        <v>9.08</v>
       </c>
       <c r="G65" t="n">
-        <v>63.6</v>
+        <v>59.3</v>
       </c>
       <c r="H65" t="n">
-        <v>34.9</v>
+        <v>37.5</v>
       </c>
       <c r="I65" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J65" t="n">
-        <v>84.23</v>
+        <v>355.49</v>
       </c>
       <c r="K65" t="n">
-        <v>338.11</v>
+        <v>-301.8</v>
       </c>
       <c r="L65" t="n">
-        <v>348.45</v>
+        <v>466.32</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>07:44:18</t>
+          <t>07:42:55</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -2809,34 +2809,34 @@
         <v>2</v>
       </c>
       <c r="E66" t="n">
-        <v>1.87</v>
+        <v>1.61</v>
       </c>
       <c r="F66" t="n">
-        <v>8.68</v>
+        <v>9.050000000000001</v>
       </c>
       <c r="G66" t="n">
-        <v>59.6</v>
+        <v>73.2</v>
       </c>
       <c r="H66" t="n">
-        <v>32.3</v>
+        <v>35.6</v>
       </c>
       <c r="I66" t="n">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="J66" t="n">
-        <v>-25.44</v>
+        <v>-12.68</v>
       </c>
       <c r="K66" t="n">
-        <v>58.18</v>
+        <v>71.01000000000001</v>
       </c>
       <c r="L66" t="n">
-        <v>63.5</v>
+        <v>72.13</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>07:46:23</t>
+          <t>07:43:47</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -2851,34 +2851,34 @@
         <v>3</v>
       </c>
       <c r="E67" t="n">
-        <v>2.03</v>
+        <v>2.5</v>
       </c>
       <c r="F67" t="n">
-        <v>8.970000000000001</v>
+        <v>9.039999999999999</v>
       </c>
       <c r="G67" t="n">
-        <v>70.8</v>
+        <v>71.5</v>
       </c>
       <c r="H67" t="n">
-        <v>25.8</v>
+        <v>32.2</v>
       </c>
       <c r="I67" t="n">
         <v>23</v>
       </c>
       <c r="J67" t="n">
-        <v>-275.36</v>
+        <v>-44.46</v>
       </c>
       <c r="K67" t="n">
-        <v>18.19</v>
+        <v>45.75</v>
       </c>
       <c r="L67" t="n">
-        <v>275.96</v>
+        <v>63.8</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>07:52:45</t>
+          <t>07:47:30</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -2893,34 +2893,34 @@
         <v>1</v>
       </c>
       <c r="E68" t="n">
-        <v>2</v>
+        <v>2.14</v>
       </c>
       <c r="F68" t="n">
-        <v>9.19</v>
+        <v>9.15</v>
       </c>
       <c r="G68" t="n">
-        <v>81</v>
+        <v>78.5</v>
       </c>
       <c r="H68" t="n">
-        <v>23.5</v>
+        <v>29.1</v>
       </c>
       <c r="I68" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J68" t="n">
-        <v>414.33</v>
+        <v>143.48</v>
       </c>
       <c r="K68" t="n">
-        <v>-248.46</v>
+        <v>242.82</v>
       </c>
       <c r="L68" t="n">
-        <v>483.12</v>
+        <v>282.04</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>07:54:28</t>
+          <t>07:49:58</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -2935,34 +2935,34 @@
         <v>2</v>
       </c>
       <c r="E69" t="n">
-        <v>1.69</v>
+        <v>2.26</v>
       </c>
       <c r="F69" t="n">
-        <v>9.279999999999999</v>
+        <v>9.18</v>
       </c>
       <c r="G69" t="n">
-        <v>52.6</v>
+        <v>75.8</v>
       </c>
       <c r="H69" t="n">
-        <v>35.3</v>
+        <v>20.3</v>
       </c>
       <c r="I69" t="n">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="J69" t="n">
-        <v>111.97</v>
+        <v>155.08</v>
       </c>
       <c r="K69" t="n">
-        <v>-156.76</v>
+        <v>389.66</v>
       </c>
       <c r="L69" t="n">
-        <v>192.64</v>
+        <v>419.38</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>07:56:11</t>
+          <t>07:52:32</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -2977,34 +2977,34 @@
         <v>3</v>
       </c>
       <c r="E70" t="n">
-        <v>1.96</v>
+        <v>2.45</v>
       </c>
       <c r="F70" t="n">
-        <v>8.800000000000001</v>
+        <v>8.050000000000001</v>
       </c>
       <c r="G70" t="n">
-        <v>63.7</v>
+        <v>59.5</v>
       </c>
       <c r="H70" t="n">
-        <v>27.3</v>
+        <v>26.8</v>
       </c>
       <c r="I70" t="n">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="J70" t="n">
-        <v>-134.89</v>
+        <v>262.14</v>
       </c>
       <c r="K70" t="n">
-        <v>102.75</v>
+        <v>273.08</v>
       </c>
       <c r="L70" t="n">
-        <v>169.57</v>
+        <v>378.54</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>08:00:47</t>
+          <t>07:55:54</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -3019,34 +3019,34 @@
         <v>1</v>
       </c>
       <c r="E71" t="n">
-        <v>1.55</v>
+        <v>3.98</v>
       </c>
       <c r="F71" t="n">
-        <v>9.35</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="G71" t="n">
-        <v>62.1</v>
+        <v>57.8</v>
       </c>
       <c r="H71" t="n">
-        <v>28.5</v>
+        <v>29.6</v>
       </c>
       <c r="I71" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="J71" t="n">
-        <v>-46.34</v>
+        <v>-13.58</v>
       </c>
       <c r="K71" t="n">
-        <v>682.3200000000001</v>
+        <v>-795.8</v>
       </c>
       <c r="L71" t="n">
-        <v>683.89</v>
+        <v>795.91</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>08:02:00</t>
+          <t>07:58:02</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -3061,34 +3061,34 @@
         <v>2</v>
       </c>
       <c r="E72" t="n">
-        <v>1.96</v>
+        <v>2.14</v>
       </c>
       <c r="F72" t="n">
-        <v>8.73</v>
+        <v>9</v>
       </c>
       <c r="G72" t="n">
-        <v>71</v>
+        <v>58.1</v>
       </c>
       <c r="H72" t="n">
-        <v>37.5</v>
+        <v>28.9</v>
       </c>
       <c r="I72" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="J72" t="n">
-        <v>157.7</v>
+        <v>-15.77</v>
       </c>
       <c r="K72" t="n">
-        <v>354.34</v>
+        <v>669.27</v>
       </c>
       <c r="L72" t="n">
-        <v>387.84</v>
+        <v>669.45</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>08:03:59</t>
+          <t>07:58:59</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -3103,34 +3103,34 @@
         <v>3</v>
       </c>
       <c r="E73" t="n">
-        <v>2.81</v>
+        <v>2.1</v>
       </c>
       <c r="F73" t="n">
-        <v>8.9</v>
+        <v>10</v>
       </c>
       <c r="G73" t="n">
-        <v>76.59999999999999</v>
+        <v>65.40000000000001</v>
       </c>
       <c r="H73" t="n">
-        <v>30.5</v>
+        <v>27.2</v>
       </c>
       <c r="I73" t="n">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="J73" t="n">
-        <v>-116.91</v>
+        <v>141.35</v>
       </c>
       <c r="K73" t="n">
-        <v>59</v>
+        <v>-243.75</v>
       </c>
       <c r="L73" t="n">
-        <v>130.96</v>
+        <v>281.77</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>08:15:48</t>
+          <t>08:10:03</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -3145,34 +3145,34 @@
         <v>1</v>
       </c>
       <c r="E74" t="n">
-        <v>2.14</v>
+        <v>1.27</v>
       </c>
       <c r="F74" t="n">
-        <v>8.84</v>
+        <v>9.66</v>
       </c>
       <c r="G74" t="n">
-        <v>55.7</v>
+        <v>70.40000000000001</v>
       </c>
       <c r="H74" t="n">
-        <v>28.5</v>
+        <v>39.8</v>
       </c>
       <c r="I74" t="n">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="J74" t="n">
-        <v>45.12</v>
+        <v>-125.22</v>
       </c>
       <c r="K74" t="n">
-        <v>-89.56</v>
+        <v>-58.96</v>
       </c>
       <c r="L74" t="n">
-        <v>100.28</v>
+        <v>138.41</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>08:17:29</t>
+          <t>08:11:28</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -3187,34 +3187,34 @@
         <v>2</v>
       </c>
       <c r="E75" t="n">
-        <v>2.05</v>
+        <v>2.18</v>
       </c>
       <c r="F75" t="n">
-        <v>9.19</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="G75" t="n">
-        <v>73.5</v>
+        <v>73.09999999999999</v>
       </c>
       <c r="H75" t="n">
-        <v>32.9</v>
+        <v>28.2</v>
       </c>
       <c r="I75" t="n">
         <v>23</v>
       </c>
       <c r="J75" t="n">
-        <v>52.44</v>
+        <v>23.16</v>
       </c>
       <c r="K75" t="n">
-        <v>52.84</v>
+        <v>-39.98</v>
       </c>
       <c r="L75" t="n">
-        <v>74.44</v>
+        <v>46.2</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>08:19:01</t>
+          <t>08:13:14</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -3229,34 +3229,34 @@
         <v>3</v>
       </c>
       <c r="E76" t="n">
-        <v>1.93</v>
+        <v>1.82</v>
       </c>
       <c r="F76" t="n">
-        <v>9.18</v>
+        <v>9.41</v>
       </c>
       <c r="G76" t="n">
-        <v>49.5</v>
+        <v>74.5</v>
       </c>
       <c r="H76" t="n">
-        <v>29.1</v>
+        <v>37.8</v>
       </c>
       <c r="I76" t="n">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="J76" t="n">
-        <v>-50.79</v>
+        <v>-106.36</v>
       </c>
       <c r="K76" t="n">
-        <v>-36.85</v>
+        <v>82.12</v>
       </c>
       <c r="L76" t="n">
-        <v>62.75</v>
+        <v>134.38</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>08:23:46</t>
+          <t>08:17:57</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -3271,34 +3271,34 @@
         <v>1</v>
       </c>
       <c r="E77" t="n">
-        <v>2.43</v>
+        <v>2.34</v>
       </c>
       <c r="F77" t="n">
-        <v>9.32</v>
+        <v>9.470000000000001</v>
       </c>
       <c r="G77" t="n">
-        <v>63.9</v>
+        <v>72.5</v>
       </c>
       <c r="H77" t="n">
-        <v>31.8</v>
+        <v>24.4</v>
       </c>
       <c r="I77" t="n">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="J77" t="n">
-        <v>-26.07</v>
+        <v>-86.67</v>
       </c>
       <c r="K77" t="n">
-        <v>35.75</v>
+        <v>147.34</v>
       </c>
       <c r="L77" t="n">
-        <v>44.25</v>
+        <v>170.95</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>08:25:47</t>
+          <t>08:18:53</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -3313,34 +3313,34 @@
         <v>2</v>
       </c>
       <c r="E78" t="n">
-        <v>1.61</v>
+        <v>1.9</v>
       </c>
       <c r="F78" t="n">
-        <v>9.25</v>
+        <v>9.02</v>
       </c>
       <c r="G78" t="n">
-        <v>63</v>
+        <v>62.5</v>
       </c>
       <c r="H78" t="n">
-        <v>32.1</v>
+        <v>29.9</v>
       </c>
       <c r="I78" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="J78" t="n">
-        <v>-109.64</v>
+        <v>47.57</v>
       </c>
       <c r="K78" t="n">
-        <v>-59.84</v>
+        <v>-42.11</v>
       </c>
       <c r="L78" t="n">
-        <v>124.91</v>
+        <v>63.54</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>08:28:06</t>
+          <t>08:19:59</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -3355,34 +3355,34 @@
         <v>3</v>
       </c>
       <c r="E79" t="n">
-        <v>2.16</v>
+        <v>2.41</v>
       </c>
       <c r="F79" t="n">
-        <v>9.26</v>
+        <v>9</v>
       </c>
       <c r="G79" t="n">
-        <v>66.8</v>
+        <v>61.9</v>
       </c>
       <c r="H79" t="n">
-        <v>30.9</v>
+        <v>31</v>
       </c>
       <c r="I79" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="J79" t="n">
-        <v>112.46</v>
+        <v>163.11</v>
       </c>
       <c r="K79" t="n">
-        <v>157.28</v>
+        <v>111.04</v>
       </c>
       <c r="L79" t="n">
-        <v>193.35</v>
+        <v>197.32</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>08:32:49</t>
+          <t>08:25:53</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -3397,34 +3397,34 @@
         <v>1</v>
       </c>
       <c r="E80" t="n">
-        <v>2.24</v>
+        <v>2.06</v>
       </c>
       <c r="F80" t="n">
-        <v>8.890000000000001</v>
+        <v>8.949999999999999</v>
       </c>
       <c r="G80" t="n">
-        <v>53.9</v>
+        <v>66.7</v>
       </c>
       <c r="H80" t="n">
-        <v>28.4</v>
+        <v>36.5</v>
       </c>
       <c r="I80" t="n">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="J80" t="n">
-        <v>90.13</v>
+        <v>-76.38</v>
       </c>
       <c r="K80" t="n">
-        <v>-201.14</v>
+        <v>-49.26</v>
       </c>
       <c r="L80" t="n">
-        <v>220.41</v>
+        <v>90.89</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>08:33:21</t>
+          <t>08:28:03</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -3439,34 +3439,34 @@
         <v>2</v>
       </c>
       <c r="E81" t="n">
-        <v>2.05</v>
+        <v>2.03</v>
       </c>
       <c r="F81" t="n">
-        <v>8.85</v>
+        <v>8.720000000000001</v>
       </c>
       <c r="G81" t="n">
-        <v>68.7</v>
+        <v>61</v>
       </c>
       <c r="H81" t="n">
-        <v>32.8</v>
+        <v>27.3</v>
       </c>
       <c r="I81" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="J81" t="n">
-        <v>-36.43</v>
+        <v>-138.59</v>
       </c>
       <c r="K81" t="n">
-        <v>-15.18</v>
+        <v>47.31</v>
       </c>
       <c r="L81" t="n">
-        <v>39.47</v>
+        <v>146.44</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>08:35:16</t>
+          <t>08:30:08</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -3481,34 +3481,34 @@
         <v>3</v>
       </c>
       <c r="E82" t="n">
-        <v>1.97</v>
+        <v>2.05</v>
       </c>
       <c r="F82" t="n">
-        <v>8.630000000000001</v>
+        <v>9.24</v>
       </c>
       <c r="G82" t="n">
-        <v>73.90000000000001</v>
+        <v>64.40000000000001</v>
       </c>
       <c r="H82" t="n">
-        <v>37.6</v>
+        <v>39.7</v>
       </c>
       <c r="I82" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J82" t="n">
-        <v>8.609999999999999</v>
+        <v>-3.9</v>
       </c>
       <c r="K82" t="n">
-        <v>118.02</v>
+        <v>66.38</v>
       </c>
       <c r="L82" t="n">
-        <v>118.34</v>
+        <v>66.48999999999999</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>08:40:31</t>
+          <t>08:33:49</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -3523,34 +3523,34 @@
         <v>1</v>
       </c>
       <c r="E83" t="n">
-        <v>1.94</v>
+        <v>2.11</v>
       </c>
       <c r="F83" t="n">
-        <v>8.59</v>
+        <v>8.210000000000001</v>
       </c>
       <c r="G83" t="n">
-        <v>63.4</v>
+        <v>65.7</v>
       </c>
       <c r="H83" t="n">
-        <v>25.9</v>
+        <v>28.3</v>
       </c>
       <c r="I83" t="n">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="J83" t="n">
-        <v>-343.88</v>
+        <v>419.4</v>
       </c>
       <c r="K83" t="n">
-        <v>-268.16</v>
+        <v>38.04</v>
       </c>
       <c r="L83" t="n">
-        <v>436.08</v>
+        <v>421.12</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>08:41:18</t>
+          <t>08:34:33</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -3565,34 +3565,34 @@
         <v>2</v>
       </c>
       <c r="E84" t="n">
-        <v>1.77</v>
+        <v>2.29</v>
       </c>
       <c r="F84" t="n">
-        <v>8.289999999999999</v>
+        <v>8.83</v>
       </c>
       <c r="G84" t="n">
-        <v>68.5</v>
+        <v>73</v>
       </c>
       <c r="H84" t="n">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="I84" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="J84" t="n">
-        <v>-55.71</v>
+        <v>-25.82</v>
       </c>
       <c r="K84" t="n">
-        <v>-9.77</v>
+        <v>224.28</v>
       </c>
       <c r="L84" t="n">
-        <v>56.56</v>
+        <v>225.76</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>08:43:31</t>
+          <t>08:36:24</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -3607,34 +3607,34 @@
         <v>3</v>
       </c>
       <c r="E85" t="n">
-        <v>1.9</v>
+        <v>2.05</v>
       </c>
       <c r="F85" t="n">
-        <v>8.9</v>
+        <v>9.16</v>
       </c>
       <c r="G85" t="n">
-        <v>66.5</v>
+        <v>70.59999999999999</v>
       </c>
       <c r="H85" t="n">
-        <v>28.7</v>
+        <v>35</v>
       </c>
       <c r="I85" t="n">
         <v>22</v>
       </c>
       <c r="J85" t="n">
-        <v>-207.47</v>
+        <v>-117.04</v>
       </c>
       <c r="K85" t="n">
-        <v>326.02</v>
+        <v>-503.21</v>
       </c>
       <c r="L85" t="n">
-        <v>386.44</v>
+        <v>516.64</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>08:47:10</t>
+          <t>08:41:47</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -3649,34 +3649,34 @@
         <v>1</v>
       </c>
       <c r="E86" t="n">
-        <v>2.77</v>
+        <v>2.42</v>
       </c>
       <c r="F86" t="n">
-        <v>8.609999999999999</v>
+        <v>9.48</v>
       </c>
       <c r="G86" t="n">
-        <v>71.5</v>
+        <v>68.40000000000001</v>
       </c>
       <c r="H86" t="n">
-        <v>24.7</v>
+        <v>35</v>
       </c>
       <c r="I86" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="J86" t="n">
-        <v>-130.61</v>
+        <v>-735.95</v>
       </c>
       <c r="K86" t="n">
-        <v>-456.01</v>
+        <v>205.96</v>
       </c>
       <c r="L86" t="n">
-        <v>474.34</v>
+        <v>764.23</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>08:48:52</t>
+          <t>08:43:47</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -3691,34 +3691,34 @@
         <v>2</v>
       </c>
       <c r="E87" t="n">
-        <v>1.92</v>
+        <v>2.02</v>
       </c>
       <c r="F87" t="n">
-        <v>9.380000000000001</v>
+        <v>8.630000000000001</v>
       </c>
       <c r="G87" t="n">
-        <v>47.7</v>
+        <v>63.4</v>
       </c>
       <c r="H87" t="n">
-        <v>30.8</v>
+        <v>32.7</v>
       </c>
       <c r="I87" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="J87" t="n">
-        <v>-129.67</v>
+        <v>-462.38</v>
       </c>
       <c r="K87" t="n">
-        <v>-429.48</v>
+        <v>-147.5</v>
       </c>
       <c r="L87" t="n">
-        <v>448.63</v>
+        <v>485.34</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>08:50:59</t>
+          <t>08:46:18</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -3733,28 +3733,28 @@
         <v>3</v>
       </c>
       <c r="E88" t="n">
-        <v>2.75</v>
+        <v>1.7</v>
       </c>
       <c r="F88" t="n">
-        <v>9.09</v>
+        <v>8.99</v>
       </c>
       <c r="G88" t="n">
-        <v>80.2</v>
+        <v>69.90000000000001</v>
       </c>
       <c r="H88" t="n">
-        <v>33.8</v>
+        <v>30.8</v>
       </c>
       <c r="I88" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="J88" t="n">
-        <v>-209.99</v>
+        <v>-265.74</v>
       </c>
       <c r="K88" t="n">
-        <v>-150.52</v>
+        <v>-88.22</v>
       </c>
       <c r="L88" t="n">
-        <v>258.37</v>
+        <v>280</v>
       </c>
     </row>
   </sheetData>

--- a/output/2024-07-26.xlsx
+++ b/output/2024-07-26.xlsx
@@ -640,13 +640,13 @@
         <v>27</v>
       </c>
       <c r="J14" t="n">
-        <v>48.78</v>
+        <v>41.05</v>
       </c>
       <c r="K14" t="n">
-        <v>49.82</v>
+        <v>41.92</v>
       </c>
       <c r="L14" t="n">
-        <v>69.72</v>
+        <v>58.67</v>
       </c>
     </row>
     <row r="15">
@@ -682,13 +682,13 @@
         <v>25</v>
       </c>
       <c r="J15" t="n">
-        <v>24.64</v>
+        <v>33.19</v>
       </c>
       <c r="K15" t="n">
-        <v>-19.78</v>
+        <v>-26.65</v>
       </c>
       <c r="L15" t="n">
-        <v>31.59</v>
+        <v>42.56</v>
       </c>
     </row>
     <row r="16">
@@ -724,13 +724,13 @@
         <v>23</v>
       </c>
       <c r="J16" t="n">
-        <v>-19.64</v>
+        <v>-21.89</v>
       </c>
       <c r="K16" t="n">
-        <v>46.91</v>
+        <v>52.29</v>
       </c>
       <c r="L16" t="n">
-        <v>50.86</v>
+        <v>56.69</v>
       </c>
     </row>
     <row r="17">
@@ -766,13 +766,13 @@
         <v>22</v>
       </c>
       <c r="J17" t="n">
-        <v>-74.70999999999999</v>
+        <v>-75.22</v>
       </c>
       <c r="K17" t="n">
-        <v>65.14</v>
+        <v>65.58</v>
       </c>
       <c r="L17" t="n">
-        <v>99.12</v>
+        <v>99.79000000000001</v>
       </c>
     </row>
     <row r="18">
@@ -808,13 +808,13 @@
         <v>22</v>
       </c>
       <c r="J18" t="n">
-        <v>48.78</v>
+        <v>68.39</v>
       </c>
       <c r="K18" t="n">
-        <v>9.19</v>
+        <v>12.89</v>
       </c>
       <c r="L18" t="n">
-        <v>49.64</v>
+        <v>69.59</v>
       </c>
     </row>
     <row r="19">
@@ -850,13 +850,13 @@
         <v>25</v>
       </c>
       <c r="J19" t="n">
-        <v>148.82</v>
+        <v>117.94</v>
       </c>
       <c r="K19" t="n">
-        <v>-12.79</v>
+        <v>-10.14</v>
       </c>
       <c r="L19" t="n">
-        <v>149.37</v>
+        <v>118.37</v>
       </c>
     </row>
     <row r="20">
@@ -892,13 +892,13 @@
         <v>22</v>
       </c>
       <c r="J20" t="n">
-        <v>-30.87</v>
+        <v>-35.47</v>
       </c>
       <c r="K20" t="n">
-        <v>130.68</v>
+        <v>150.15</v>
       </c>
       <c r="L20" t="n">
-        <v>134.28</v>
+        <v>154.28</v>
       </c>
     </row>
     <row r="21">
@@ -934,13 +934,13 @@
         <v>24</v>
       </c>
       <c r="J21" t="n">
-        <v>-290.45</v>
+        <v>-231.53</v>
       </c>
       <c r="K21" t="n">
-        <v>-19.42</v>
+        <v>-15.48</v>
       </c>
       <c r="L21" t="n">
-        <v>291.1</v>
+        <v>232.05</v>
       </c>
     </row>
     <row r="22">
@@ -976,13 +976,13 @@
         <v>21</v>
       </c>
       <c r="J22" t="n">
-        <v>248.51</v>
+        <v>227.09</v>
       </c>
       <c r="K22" t="n">
-        <v>81.72</v>
+        <v>74.68000000000001</v>
       </c>
       <c r="L22" t="n">
-        <v>261.6</v>
+        <v>239.06</v>
       </c>
     </row>
     <row r="23">
@@ -1018,13 +1018,13 @@
         <v>23</v>
       </c>
       <c r="J23" t="n">
-        <v>-325.97</v>
+        <v>-323.44</v>
       </c>
       <c r="K23" t="n">
-        <v>-207.6</v>
+        <v>-205.99</v>
       </c>
       <c r="L23" t="n">
-        <v>386.46</v>
+        <v>383.46</v>
       </c>
     </row>
     <row r="24">
@@ -1060,13 +1060,13 @@
         <v>23</v>
       </c>
       <c r="J24" t="n">
-        <v>-103.19</v>
+        <v>-161.86</v>
       </c>
       <c r="K24" t="n">
-        <v>-39.93</v>
+        <v>-62.63</v>
       </c>
       <c r="L24" t="n">
-        <v>110.65</v>
+        <v>173.56</v>
       </c>
     </row>
     <row r="25">
@@ -1102,13 +1102,13 @@
         <v>27</v>
       </c>
       <c r="J25" t="n">
-        <v>76.53</v>
+        <v>81.84999999999999</v>
       </c>
       <c r="K25" t="n">
-        <v>-160.34</v>
+        <v>-171.48</v>
       </c>
       <c r="L25" t="n">
-        <v>177.67</v>
+        <v>190.02</v>
       </c>
     </row>
     <row r="26">
@@ -1144,13 +1144,13 @@
         <v>22</v>
       </c>
       <c r="J26" t="n">
-        <v>21.4</v>
+        <v>42.74</v>
       </c>
       <c r="K26" t="n">
-        <v>-126.65</v>
+        <v>-252.99</v>
       </c>
       <c r="L26" t="n">
-        <v>128.45</v>
+        <v>256.58</v>
       </c>
     </row>
     <row r="27">
@@ -1186,13 +1186,13 @@
         <v>25</v>
       </c>
       <c r="J27" t="n">
-        <v>170.66</v>
+        <v>240.6</v>
       </c>
       <c r="K27" t="n">
-        <v>-94.16</v>
+        <v>-132.74</v>
       </c>
       <c r="L27" t="n">
-        <v>194.91</v>
+        <v>274.79</v>
       </c>
     </row>
     <row r="28">
@@ -1228,13 +1228,13 @@
         <v>21</v>
       </c>
       <c r="J28" t="n">
-        <v>-928.35</v>
+        <v>-884.96</v>
       </c>
       <c r="K28" t="n">
-        <v>-86.05</v>
+        <v>-82.03</v>
       </c>
       <c r="L28" t="n">
-        <v>932.33</v>
+        <v>888.76</v>
       </c>
     </row>
     <row r="29">
@@ -1270,13 +1270,13 @@
         <v>24</v>
       </c>
       <c r="J29" t="n">
-        <v>59.28</v>
+        <v>57.44</v>
       </c>
       <c r="K29" t="n">
-        <v>30.8</v>
+        <v>29.85</v>
       </c>
       <c r="L29" t="n">
-        <v>66.8</v>
+        <v>64.73</v>
       </c>
     </row>
     <row r="30">
@@ -1312,13 +1312,13 @@
         <v>23</v>
       </c>
       <c r="J30" t="n">
-        <v>-106.92</v>
+        <v>-76.72</v>
       </c>
       <c r="K30" t="n">
-        <v>92.66</v>
+        <v>66.48999999999999</v>
       </c>
       <c r="L30" t="n">
-        <v>141.48</v>
+        <v>101.53</v>
       </c>
     </row>
     <row r="31">
@@ -1354,13 +1354,13 @@
         <v>21</v>
       </c>
       <c r="J31" t="n">
-        <v>-2.82</v>
+        <v>-3.94</v>
       </c>
       <c r="K31" t="n">
-        <v>-37.65</v>
+        <v>-52.6</v>
       </c>
       <c r="L31" t="n">
-        <v>37.75</v>
+        <v>52.75</v>
       </c>
     </row>
     <row r="32">
@@ -1396,13 +1396,13 @@
         <v>27</v>
       </c>
       <c r="J32" t="n">
-        <v>58.15</v>
+        <v>57.31</v>
       </c>
       <c r="K32" t="n">
-        <v>42.96</v>
+        <v>42.34</v>
       </c>
       <c r="L32" t="n">
-        <v>72.3</v>
+        <v>71.25</v>
       </c>
     </row>
     <row r="33">
@@ -1438,13 +1438,13 @@
         <v>25</v>
       </c>
       <c r="J33" t="n">
-        <v>55.5</v>
+        <v>51.73</v>
       </c>
       <c r="K33" t="n">
-        <v>74.27</v>
+        <v>69.22</v>
       </c>
       <c r="L33" t="n">
-        <v>92.72</v>
+        <v>86.41</v>
       </c>
     </row>
     <row r="34">
@@ -1480,13 +1480,13 @@
         <v>26</v>
       </c>
       <c r="J34" t="n">
-        <v>-133.25</v>
+        <v>-96.59999999999999</v>
       </c>
       <c r="K34" t="n">
-        <v>152.33</v>
+        <v>110.43</v>
       </c>
       <c r="L34" t="n">
-        <v>202.38</v>
+        <v>146.72</v>
       </c>
     </row>
     <row r="35">
@@ -1522,13 +1522,13 @@
         <v>22</v>
       </c>
       <c r="J35" t="n">
-        <v>171.03</v>
+        <v>168.94</v>
       </c>
       <c r="K35" t="n">
-        <v>65.84</v>
+        <v>65.04000000000001</v>
       </c>
       <c r="L35" t="n">
-        <v>183.27</v>
+        <v>181.03</v>
       </c>
     </row>
     <row r="36">
@@ -1564,13 +1564,13 @@
         <v>25</v>
       </c>
       <c r="J36" t="n">
-        <v>218.69</v>
+        <v>178.61</v>
       </c>
       <c r="K36" t="n">
-        <v>169.98</v>
+        <v>138.83</v>
       </c>
       <c r="L36" t="n">
-        <v>276.98</v>
+        <v>226.22</v>
       </c>
     </row>
     <row r="37">
@@ -1606,13 +1606,13 @@
         <v>23</v>
       </c>
       <c r="J37" t="n">
-        <v>162.19</v>
+        <v>129.34</v>
       </c>
       <c r="K37" t="n">
-        <v>-386.75</v>
+        <v>-308.42</v>
       </c>
       <c r="L37" t="n">
-        <v>419.38</v>
+        <v>334.45</v>
       </c>
     </row>
     <row r="38">
@@ -1648,13 +1648,13 @@
         <v>23</v>
       </c>
       <c r="J38" t="n">
-        <v>224.74</v>
+        <v>204.36</v>
       </c>
       <c r="K38" t="n">
-        <v>411.94</v>
+        <v>374.58</v>
       </c>
       <c r="L38" t="n">
-        <v>469.26</v>
+        <v>426.7</v>
       </c>
     </row>
     <row r="39">
@@ -1690,13 +1690,13 @@
         <v>24</v>
       </c>
       <c r="J39" t="n">
-        <v>-177.06</v>
+        <v>-182.73</v>
       </c>
       <c r="K39" t="n">
-        <v>135.41</v>
+        <v>139.75</v>
       </c>
       <c r="L39" t="n">
-        <v>222.9</v>
+        <v>230.04</v>
       </c>
     </row>
     <row r="40">
@@ -1732,13 +1732,13 @@
         <v>25</v>
       </c>
       <c r="J40" t="n">
-        <v>-78.54000000000001</v>
+        <v>-80.37</v>
       </c>
       <c r="K40" t="n">
-        <v>200.92</v>
+        <v>205.61</v>
       </c>
       <c r="L40" t="n">
-        <v>215.73</v>
+        <v>220.76</v>
       </c>
     </row>
     <row r="41">
@@ -1774,13 +1774,13 @@
         <v>23</v>
       </c>
       <c r="J41" t="n">
-        <v>-132.96</v>
+        <v>-174.91</v>
       </c>
       <c r="K41" t="n">
-        <v>221.88</v>
+        <v>291.88</v>
       </c>
       <c r="L41" t="n">
-        <v>258.67</v>
+        <v>340.28</v>
       </c>
     </row>
     <row r="42">
@@ -1816,13 +1816,13 @@
         <v>21</v>
       </c>
       <c r="J42" t="n">
-        <v>130.75</v>
+        <v>231.72</v>
       </c>
       <c r="K42" t="n">
-        <v>101.85</v>
+        <v>180.51</v>
       </c>
       <c r="L42" t="n">
-        <v>165.74</v>
+        <v>293.73</v>
       </c>
     </row>
     <row r="43">
@@ -1858,13 +1858,13 @@
         <v>22</v>
       </c>
       <c r="J43" t="n">
-        <v>266.21</v>
+        <v>309.48</v>
       </c>
       <c r="K43" t="n">
-        <v>-316.12</v>
+        <v>-367.5</v>
       </c>
       <c r="L43" t="n">
-        <v>413.28</v>
+        <v>480.46</v>
       </c>
     </row>
     <row r="44">
@@ -1900,13 +1900,13 @@
         <v>27</v>
       </c>
       <c r="J44" t="n">
-        <v>-25.09</v>
+        <v>-18.66</v>
       </c>
       <c r="K44" t="n">
-        <v>79.02</v>
+        <v>58.77</v>
       </c>
       <c r="L44" t="n">
-        <v>82.91</v>
+        <v>61.66</v>
       </c>
     </row>
     <row r="45">
@@ -1942,13 +1942,13 @@
         <v>26</v>
       </c>
       <c r="J45" t="n">
-        <v>76.37</v>
+        <v>61.73</v>
       </c>
       <c r="K45" t="n">
-        <v>-4.29</v>
+        <v>-3.47</v>
       </c>
       <c r="L45" t="n">
-        <v>76.48999999999999</v>
+        <v>61.83</v>
       </c>
     </row>
     <row r="46">
@@ -1984,13 +1984,13 @@
         <v>23</v>
       </c>
       <c r="J46" t="n">
-        <v>40.16</v>
+        <v>52</v>
       </c>
       <c r="K46" t="n">
-        <v>-6.5</v>
+        <v>-8.41</v>
       </c>
       <c r="L46" t="n">
-        <v>40.68</v>
+        <v>52.68</v>
       </c>
     </row>
     <row r="47">
@@ -2026,13 +2026,13 @@
         <v>23</v>
       </c>
       <c r="J47" t="n">
-        <v>-33.28</v>
+        <v>-39.72</v>
       </c>
       <c r="K47" t="n">
-        <v>54.48</v>
+        <v>65.02</v>
       </c>
       <c r="L47" t="n">
-        <v>63.84</v>
+        <v>76.2</v>
       </c>
     </row>
     <row r="48">
@@ -2068,13 +2068,13 @@
         <v>21</v>
       </c>
       <c r="J48" t="n">
-        <v>-96.2</v>
+        <v>-77.48</v>
       </c>
       <c r="K48" t="n">
-        <v>249.18</v>
+        <v>200.69</v>
       </c>
       <c r="L48" t="n">
-        <v>267.1</v>
+        <v>215.13</v>
       </c>
     </row>
     <row r="49">
@@ -2110,13 +2110,13 @@
         <v>22</v>
       </c>
       <c r="J49" t="n">
-        <v>192.41</v>
+        <v>160</v>
       </c>
       <c r="K49" t="n">
-        <v>82.23999999999999</v>
+        <v>68.39</v>
       </c>
       <c r="L49" t="n">
-        <v>209.25</v>
+        <v>174</v>
       </c>
     </row>
     <row r="50">
@@ -2152,13 +2152,13 @@
         <v>25</v>
       </c>
       <c r="J50" t="n">
-        <v>33.43</v>
+        <v>38.58</v>
       </c>
       <c r="K50" t="n">
-        <v>-97.61</v>
+        <v>-112.65</v>
       </c>
       <c r="L50" t="n">
-        <v>103.17</v>
+        <v>119.07</v>
       </c>
     </row>
     <row r="51">
@@ -2194,13 +2194,13 @@
         <v>24</v>
       </c>
       <c r="J51" t="n">
-        <v>-109.74</v>
+        <v>-103.09</v>
       </c>
       <c r="K51" t="n">
-        <v>219.41</v>
+        <v>206.11</v>
       </c>
       <c r="L51" t="n">
-        <v>245.33</v>
+        <v>230.45</v>
       </c>
     </row>
     <row r="52">
@@ -2236,13 +2236,13 @@
         <v>21</v>
       </c>
       <c r="J52" t="n">
-        <v>78.17</v>
+        <v>120.17</v>
       </c>
       <c r="K52" t="n">
-        <v>-11.79</v>
+        <v>-18.12</v>
       </c>
       <c r="L52" t="n">
-        <v>79.06</v>
+        <v>121.53</v>
       </c>
     </row>
     <row r="53">
@@ -2278,13 +2278,13 @@
         <v>23</v>
       </c>
       <c r="J53" t="n">
-        <v>-22.82</v>
+        <v>-24.16</v>
       </c>
       <c r="K53" t="n">
-        <v>264.05</v>
+        <v>279.57</v>
       </c>
       <c r="L53" t="n">
-        <v>265.04</v>
+        <v>280.61</v>
       </c>
     </row>
     <row r="54">
@@ -2320,13 +2320,13 @@
         <v>23</v>
       </c>
       <c r="J54" t="n">
-        <v>344.38</v>
+        <v>316.68</v>
       </c>
       <c r="K54" t="n">
-        <v>144.24</v>
+        <v>132.64</v>
       </c>
       <c r="L54" t="n">
-        <v>373.37</v>
+        <v>343.33</v>
       </c>
     </row>
     <row r="55">
@@ -2362,13 +2362,13 @@
         <v>21</v>
       </c>
       <c r="J55" t="n">
-        <v>483.7</v>
+        <v>447.83</v>
       </c>
       <c r="K55" t="n">
-        <v>-38.53</v>
+        <v>-35.67</v>
       </c>
       <c r="L55" t="n">
-        <v>485.23</v>
+        <v>449.25</v>
       </c>
     </row>
     <row r="56">
@@ -2404,13 +2404,13 @@
         <v>24</v>
       </c>
       <c r="J56" t="n">
-        <v>11.58</v>
+        <v>15.3</v>
       </c>
       <c r="K56" t="n">
-        <v>252.94</v>
+        <v>334.3</v>
       </c>
       <c r="L56" t="n">
-        <v>253.2</v>
+        <v>334.65</v>
       </c>
     </row>
     <row r="57">
@@ -2446,13 +2446,13 @@
         <v>24</v>
       </c>
       <c r="J57" t="n">
-        <v>276.38</v>
+        <v>344.15</v>
       </c>
       <c r="K57" t="n">
-        <v>12.21</v>
+        <v>15.2</v>
       </c>
       <c r="L57" t="n">
-        <v>276.65</v>
+        <v>344.48</v>
       </c>
     </row>
     <row r="58">
@@ -2488,13 +2488,13 @@
         <v>23</v>
       </c>
       <c r="J58" t="n">
-        <v>64.44</v>
+        <v>159.63</v>
       </c>
       <c r="K58" t="n">
-        <v>-60.89</v>
+        <v>-150.82</v>
       </c>
       <c r="L58" t="n">
-        <v>88.66</v>
+        <v>219.61</v>
       </c>
     </row>
     <row r="59">
@@ -2530,13 +2530,13 @@
         <v>24</v>
       </c>
       <c r="J59" t="n">
-        <v>9.800000000000001</v>
+        <v>6.75</v>
       </c>
       <c r="K59" t="n">
-        <v>140.71</v>
+        <v>96.84999999999999</v>
       </c>
       <c r="L59" t="n">
-        <v>141.05</v>
+        <v>97.08</v>
       </c>
     </row>
     <row r="60">
@@ -2572,13 +2572,13 @@
         <v>22</v>
       </c>
       <c r="J60" t="n">
-        <v>-69.5</v>
+        <v>-60.82</v>
       </c>
       <c r="K60" t="n">
-        <v>46.42</v>
+        <v>40.63</v>
       </c>
       <c r="L60" t="n">
-        <v>83.58</v>
+        <v>73.14</v>
       </c>
     </row>
     <row r="61">
@@ -2614,13 +2614,13 @@
         <v>21</v>
       </c>
       <c r="J61" t="n">
-        <v>-110.18</v>
+        <v>-83.55</v>
       </c>
       <c r="K61" t="n">
-        <v>95.13</v>
+        <v>72.14</v>
       </c>
       <c r="L61" t="n">
-        <v>145.56</v>
+        <v>110.38</v>
       </c>
     </row>
     <row r="62">
@@ -2656,13 +2656,13 @@
         <v>21</v>
       </c>
       <c r="J62" t="n">
-        <v>68.48999999999999</v>
+        <v>60.88</v>
       </c>
       <c r="K62" t="n">
-        <v>137.45</v>
+        <v>122.17</v>
       </c>
       <c r="L62" t="n">
-        <v>153.57</v>
+        <v>136.5</v>
       </c>
     </row>
     <row r="63">
@@ -2698,13 +2698,13 @@
         <v>26</v>
       </c>
       <c r="J63" t="n">
-        <v>128.66</v>
+        <v>100.42</v>
       </c>
       <c r="K63" t="n">
-        <v>51.69</v>
+        <v>40.34</v>
       </c>
       <c r="L63" t="n">
-        <v>138.65</v>
+        <v>108.22</v>
       </c>
     </row>
     <row r="64">
@@ -2740,13 +2740,13 @@
         <v>22</v>
       </c>
       <c r="J64" t="n">
-        <v>201.79</v>
+        <v>174.79</v>
       </c>
       <c r="K64" t="n">
-        <v>-151.75</v>
+        <v>-131.45</v>
       </c>
       <c r="L64" t="n">
-        <v>252.48</v>
+        <v>218.7</v>
       </c>
     </row>
     <row r="65">
@@ -2782,13 +2782,13 @@
         <v>23</v>
       </c>
       <c r="J65" t="n">
-        <v>355.49</v>
+        <v>302.96</v>
       </c>
       <c r="K65" t="n">
-        <v>-301.8</v>
+        <v>-257.2</v>
       </c>
       <c r="L65" t="n">
-        <v>466.32</v>
+        <v>397.41</v>
       </c>
     </row>
     <row r="66">
@@ -2824,13 +2824,13 @@
         <v>26</v>
       </c>
       <c r="J66" t="n">
-        <v>-12.68</v>
+        <v>-17.13</v>
       </c>
       <c r="K66" t="n">
-        <v>71.01000000000001</v>
+        <v>95.95999999999999</v>
       </c>
       <c r="L66" t="n">
-        <v>72.13</v>
+        <v>97.47</v>
       </c>
     </row>
     <row r="67">
@@ -2866,13 +2866,13 @@
         <v>23</v>
       </c>
       <c r="J67" t="n">
-        <v>-44.46</v>
+        <v>-87.86</v>
       </c>
       <c r="K67" t="n">
-        <v>45.75</v>
+        <v>90.42</v>
       </c>
       <c r="L67" t="n">
-        <v>63.8</v>
+        <v>126.07</v>
       </c>
     </row>
     <row r="68">
@@ -2908,13 +2908,13 @@
         <v>21</v>
       </c>
       <c r="J68" t="n">
-        <v>143.48</v>
+        <v>151.49</v>
       </c>
       <c r="K68" t="n">
-        <v>242.82</v>
+        <v>256.38</v>
       </c>
       <c r="L68" t="n">
-        <v>282.04</v>
+        <v>297.8</v>
       </c>
     </row>
     <row r="69">
@@ -2950,13 +2950,13 @@
         <v>27</v>
       </c>
       <c r="J69" t="n">
-        <v>155.08</v>
+        <v>123.81</v>
       </c>
       <c r="K69" t="n">
-        <v>389.66</v>
+        <v>311.08</v>
       </c>
       <c r="L69" t="n">
-        <v>419.38</v>
+        <v>334.81</v>
       </c>
     </row>
     <row r="70">
@@ -2992,13 +2992,13 @@
         <v>26</v>
       </c>
       <c r="J70" t="n">
-        <v>262.14</v>
+        <v>236.37</v>
       </c>
       <c r="K70" t="n">
-        <v>273.08</v>
+        <v>246.23</v>
       </c>
       <c r="L70" t="n">
-        <v>378.54</v>
+        <v>341.32</v>
       </c>
     </row>
     <row r="71">
@@ -3034,13 +3034,13 @@
         <v>25</v>
       </c>
       <c r="J71" t="n">
-        <v>-13.58</v>
+        <v>-15.52</v>
       </c>
       <c r="K71" t="n">
-        <v>-795.8</v>
+        <v>-909.45</v>
       </c>
       <c r="L71" t="n">
-        <v>795.91</v>
+        <v>909.59</v>
       </c>
     </row>
     <row r="72">
@@ -3076,13 +3076,13 @@
         <v>21</v>
       </c>
       <c r="J72" t="n">
-        <v>-15.77</v>
+        <v>-15.93</v>
       </c>
       <c r="K72" t="n">
-        <v>669.27</v>
+        <v>676.33</v>
       </c>
       <c r="L72" t="n">
-        <v>669.45</v>
+        <v>676.52</v>
       </c>
     </row>
     <row r="73">
@@ -3118,13 +3118,13 @@
         <v>27</v>
       </c>
       <c r="J73" t="n">
-        <v>141.35</v>
+        <v>155.6</v>
       </c>
       <c r="K73" t="n">
-        <v>-243.75</v>
+        <v>-268.32</v>
       </c>
       <c r="L73" t="n">
-        <v>281.77</v>
+        <v>310.17</v>
       </c>
     </row>
     <row r="74">
@@ -3160,13 +3160,13 @@
         <v>27</v>
       </c>
       <c r="J74" t="n">
-        <v>-125.22</v>
+        <v>-88.04000000000001</v>
       </c>
       <c r="K74" t="n">
-        <v>-58.96</v>
+        <v>-41.45</v>
       </c>
       <c r="L74" t="n">
-        <v>138.41</v>
+        <v>97.31</v>
       </c>
     </row>
     <row r="75">
@@ -3202,13 +3202,13 @@
         <v>23</v>
       </c>
       <c r="J75" t="n">
-        <v>23.16</v>
+        <v>26.69</v>
       </c>
       <c r="K75" t="n">
-        <v>-39.98</v>
+        <v>-46.08</v>
       </c>
       <c r="L75" t="n">
-        <v>46.2</v>
+        <v>53.25</v>
       </c>
     </row>
     <row r="76">
@@ -3244,13 +3244,13 @@
         <v>22</v>
       </c>
       <c r="J76" t="n">
-        <v>-106.36</v>
+        <v>-81.84999999999999</v>
       </c>
       <c r="K76" t="n">
-        <v>82.12</v>
+        <v>63.2</v>
       </c>
       <c r="L76" t="n">
-        <v>134.38</v>
+        <v>103.41</v>
       </c>
     </row>
     <row r="77">
@@ -3286,13 +3286,13 @@
         <v>22</v>
       </c>
       <c r="J77" t="n">
-        <v>-86.67</v>
+        <v>-76.58</v>
       </c>
       <c r="K77" t="n">
-        <v>147.34</v>
+        <v>130.19</v>
       </c>
       <c r="L77" t="n">
-        <v>170.95</v>
+        <v>151.04</v>
       </c>
     </row>
     <row r="78">
@@ -3328,13 +3328,13 @@
         <v>25</v>
       </c>
       <c r="J78" t="n">
-        <v>47.57</v>
+        <v>52.76</v>
       </c>
       <c r="K78" t="n">
-        <v>-42.11</v>
+        <v>-46.71</v>
       </c>
       <c r="L78" t="n">
-        <v>63.54</v>
+        <v>70.47</v>
       </c>
     </row>
     <row r="79">
@@ -3370,13 +3370,13 @@
         <v>25</v>
       </c>
       <c r="J79" t="n">
-        <v>163.11</v>
+        <v>128.14</v>
       </c>
       <c r="K79" t="n">
-        <v>111.04</v>
+        <v>87.23</v>
       </c>
       <c r="L79" t="n">
-        <v>197.32</v>
+        <v>155.01</v>
       </c>
     </row>
     <row r="80">
@@ -3412,13 +3412,13 @@
         <v>27</v>
       </c>
       <c r="J80" t="n">
-        <v>-76.38</v>
+        <v>-85.31</v>
       </c>
       <c r="K80" t="n">
-        <v>-49.26</v>
+        <v>-55.03</v>
       </c>
       <c r="L80" t="n">
-        <v>90.89</v>
+        <v>101.52</v>
       </c>
     </row>
     <row r="81">
@@ -3454,13 +3454,13 @@
         <v>21</v>
       </c>
       <c r="J81" t="n">
-        <v>-138.59</v>
+        <v>-154.33</v>
       </c>
       <c r="K81" t="n">
-        <v>47.31</v>
+        <v>52.68</v>
       </c>
       <c r="L81" t="n">
-        <v>146.44</v>
+        <v>163.07</v>
       </c>
     </row>
     <row r="82">
@@ -3496,13 +3496,13 @@
         <v>22</v>
       </c>
       <c r="J82" t="n">
-        <v>-3.9</v>
+        <v>-6.37</v>
       </c>
       <c r="K82" t="n">
-        <v>66.38</v>
+        <v>108.61</v>
       </c>
       <c r="L82" t="n">
-        <v>66.48999999999999</v>
+        <v>108.8</v>
       </c>
     </row>
     <row r="83">
@@ -3538,13 +3538,13 @@
         <v>25</v>
       </c>
       <c r="J83" t="n">
-        <v>419.4</v>
+        <v>343.05</v>
       </c>
       <c r="K83" t="n">
-        <v>38.04</v>
+        <v>31.11</v>
       </c>
       <c r="L83" t="n">
-        <v>421.12</v>
+        <v>344.46</v>
       </c>
     </row>
     <row r="84">
@@ -3580,13 +3580,13 @@
         <v>21</v>
       </c>
       <c r="J84" t="n">
-        <v>-25.82</v>
+        <v>-30.95</v>
       </c>
       <c r="K84" t="n">
-        <v>224.28</v>
+        <v>268.85</v>
       </c>
       <c r="L84" t="n">
-        <v>225.76</v>
+        <v>270.62</v>
       </c>
     </row>
     <row r="85">
@@ -3622,13 +3622,13 @@
         <v>22</v>
       </c>
       <c r="J85" t="n">
-        <v>-117.04</v>
+        <v>-101.06</v>
       </c>
       <c r="K85" t="n">
-        <v>-503.21</v>
+        <v>-434.51</v>
       </c>
       <c r="L85" t="n">
-        <v>516.64</v>
+        <v>446.11</v>
       </c>
     </row>
     <row r="86">
@@ -3664,13 +3664,13 @@
         <v>23</v>
       </c>
       <c r="J86" t="n">
-        <v>-735.95</v>
+        <v>-720.33</v>
       </c>
       <c r="K86" t="n">
-        <v>205.96</v>
+        <v>201.59</v>
       </c>
       <c r="L86" t="n">
-        <v>764.23</v>
+        <v>748.01</v>
       </c>
     </row>
     <row r="87">
@@ -3706,13 +3706,13 @@
         <v>26</v>
       </c>
       <c r="J87" t="n">
-        <v>-462.38</v>
+        <v>-436.06</v>
       </c>
       <c r="K87" t="n">
-        <v>-147.5</v>
+        <v>-139.11</v>
       </c>
       <c r="L87" t="n">
-        <v>485.34</v>
+        <v>457.71</v>
       </c>
     </row>
     <row r="88">
@@ -3748,13 +3748,13 @@
         <v>21</v>
       </c>
       <c r="J88" t="n">
-        <v>-265.74</v>
+        <v>-365.72</v>
       </c>
       <c r="K88" t="n">
-        <v>-88.22</v>
+        <v>-121.41</v>
       </c>
       <c r="L88" t="n">
-        <v>280</v>
+        <v>385.34</v>
       </c>
     </row>
   </sheetData>

--- a/output/2024-07-26.xlsx
+++ b/output/2024-07-26.xlsx
@@ -640,13 +640,13 @@
         <v>27</v>
       </c>
       <c r="J14" t="n">
-        <v>41.05</v>
+        <v>42.47</v>
       </c>
       <c r="K14" t="n">
-        <v>41.92</v>
+        <v>43.37</v>
       </c>
       <c r="L14" t="n">
-        <v>58.67</v>
+        <v>60.71</v>
       </c>
     </row>
     <row r="15">
@@ -682,13 +682,13 @@
         <v>25</v>
       </c>
       <c r="J15" t="n">
-        <v>33.19</v>
+        <v>28.41</v>
       </c>
       <c r="K15" t="n">
-        <v>-26.65</v>
+        <v>-22.81</v>
       </c>
       <c r="L15" t="n">
-        <v>42.56</v>
+        <v>36.44</v>
       </c>
     </row>
     <row r="16">
@@ -724,13 +724,13 @@
         <v>23</v>
       </c>
       <c r="J16" t="n">
-        <v>-21.89</v>
+        <v>-17.45</v>
       </c>
       <c r="K16" t="n">
-        <v>52.29</v>
+        <v>41.68</v>
       </c>
       <c r="L16" t="n">
-        <v>56.69</v>
+        <v>45.19</v>
       </c>
     </row>
     <row r="17">
@@ -766,13 +766,13 @@
         <v>22</v>
       </c>
       <c r="J17" t="n">
-        <v>-75.22</v>
+        <v>-57.34</v>
       </c>
       <c r="K17" t="n">
-        <v>65.58</v>
+        <v>49.99</v>
       </c>
       <c r="L17" t="n">
-        <v>99.79000000000001</v>
+        <v>76.06999999999999</v>
       </c>
     </row>
     <row r="18">
@@ -808,13 +808,13 @@
         <v>22</v>
       </c>
       <c r="J18" t="n">
-        <v>68.39</v>
+        <v>52.35</v>
       </c>
       <c r="K18" t="n">
-        <v>12.89</v>
+        <v>9.859999999999999</v>
       </c>
       <c r="L18" t="n">
-        <v>69.59</v>
+        <v>53.27</v>
       </c>
     </row>
     <row r="19">
@@ -850,13 +850,13 @@
         <v>25</v>
       </c>
       <c r="J19" t="n">
-        <v>117.94</v>
+        <v>100.11</v>
       </c>
       <c r="K19" t="n">
-        <v>-10.14</v>
+        <v>-8.6</v>
       </c>
       <c r="L19" t="n">
-        <v>118.37</v>
+        <v>100.48</v>
       </c>
     </row>
     <row r="20">
@@ -892,13 +892,13 @@
         <v>22</v>
       </c>
       <c r="J20" t="n">
-        <v>-35.47</v>
+        <v>-23.18</v>
       </c>
       <c r="K20" t="n">
-        <v>150.15</v>
+        <v>98.11</v>
       </c>
       <c r="L20" t="n">
-        <v>154.28</v>
+        <v>100.81</v>
       </c>
     </row>
     <row r="21">
@@ -934,13 +934,13 @@
         <v>24</v>
       </c>
       <c r="J21" t="n">
-        <v>-231.53</v>
+        <v>-172.5</v>
       </c>
       <c r="K21" t="n">
-        <v>-15.48</v>
+        <v>-11.53</v>
       </c>
       <c r="L21" t="n">
-        <v>232.05</v>
+        <v>172.89</v>
       </c>
     </row>
     <row r="22">
@@ -976,13 +976,13 @@
         <v>21</v>
       </c>
       <c r="J22" t="n">
-        <v>227.09</v>
+        <v>143.09</v>
       </c>
       <c r="K22" t="n">
-        <v>74.68000000000001</v>
+        <v>47.05</v>
       </c>
       <c r="L22" t="n">
-        <v>239.06</v>
+        <v>150.63</v>
       </c>
     </row>
     <row r="23">
@@ -1018,13 +1018,13 @@
         <v>23</v>
       </c>
       <c r="J23" t="n">
-        <v>-323.44</v>
+        <v>-184.5</v>
       </c>
       <c r="K23" t="n">
-        <v>-205.99</v>
+        <v>-117.5</v>
       </c>
       <c r="L23" t="n">
-        <v>383.46</v>
+        <v>218.74</v>
       </c>
     </row>
     <row r="24">
@@ -1060,13 +1060,13 @@
         <v>23</v>
       </c>
       <c r="J24" t="n">
-        <v>-161.86</v>
+        <v>-92.29000000000001</v>
       </c>
       <c r="K24" t="n">
-        <v>-62.63</v>
+        <v>-35.71</v>
       </c>
       <c r="L24" t="n">
-        <v>173.56</v>
+        <v>98.95999999999999</v>
       </c>
     </row>
     <row r="25">
@@ -1102,13 +1102,13 @@
         <v>27</v>
       </c>
       <c r="J25" t="n">
-        <v>81.84999999999999</v>
+        <v>54.22</v>
       </c>
       <c r="K25" t="n">
-        <v>-171.48</v>
+        <v>-113.6</v>
       </c>
       <c r="L25" t="n">
-        <v>190.02</v>
+        <v>125.88</v>
       </c>
     </row>
     <row r="26">
@@ -1144,13 +1144,13 @@
         <v>22</v>
       </c>
       <c r="J26" t="n">
-        <v>42.74</v>
+        <v>22.01</v>
       </c>
       <c r="K26" t="n">
-        <v>-252.99</v>
+        <v>-130.3</v>
       </c>
       <c r="L26" t="n">
-        <v>256.58</v>
+        <v>132.15</v>
       </c>
     </row>
     <row r="27">
@@ -1186,13 +1186,13 @@
         <v>25</v>
       </c>
       <c r="J27" t="n">
-        <v>240.6</v>
+        <v>137.86</v>
       </c>
       <c r="K27" t="n">
-        <v>-132.74</v>
+        <v>-76.06</v>
       </c>
       <c r="L27" t="n">
-        <v>274.79</v>
+        <v>157.45</v>
       </c>
     </row>
     <row r="28">
@@ -1228,13 +1228,13 @@
         <v>21</v>
       </c>
       <c r="J28" t="n">
-        <v>-884.96</v>
+        <v>-442.32</v>
       </c>
       <c r="K28" t="n">
-        <v>-82.03</v>
+        <v>-41</v>
       </c>
       <c r="L28" t="n">
-        <v>888.76</v>
+        <v>444.22</v>
       </c>
     </row>
     <row r="29">
@@ -1270,13 +1270,13 @@
         <v>24</v>
       </c>
       <c r="J29" t="n">
-        <v>57.44</v>
+        <v>47.5</v>
       </c>
       <c r="K29" t="n">
-        <v>29.85</v>
+        <v>24.68</v>
       </c>
       <c r="L29" t="n">
-        <v>64.73</v>
+        <v>53.53</v>
       </c>
     </row>
     <row r="30">
@@ -1312,13 +1312,13 @@
         <v>23</v>
       </c>
       <c r="J30" t="n">
-        <v>-76.72</v>
+        <v>-63.93</v>
       </c>
       <c r="K30" t="n">
-        <v>66.48999999999999</v>
+        <v>55.4</v>
       </c>
       <c r="L30" t="n">
-        <v>101.53</v>
+        <v>84.59</v>
       </c>
     </row>
     <row r="31">
@@ -1354,13 +1354,13 @@
         <v>21</v>
       </c>
       <c r="J31" t="n">
-        <v>-3.94</v>
+        <v>-2.96</v>
       </c>
       <c r="K31" t="n">
-        <v>-52.6</v>
+        <v>-39.46</v>
       </c>
       <c r="L31" t="n">
-        <v>52.75</v>
+        <v>39.57</v>
       </c>
     </row>
     <row r="32">
@@ -1396,13 +1396,13 @@
         <v>27</v>
       </c>
       <c r="J32" t="n">
-        <v>57.31</v>
+        <v>54.62</v>
       </c>
       <c r="K32" t="n">
-        <v>42.34</v>
+        <v>40.35</v>
       </c>
       <c r="L32" t="n">
-        <v>71.25</v>
+        <v>67.91</v>
       </c>
     </row>
     <row r="33">
@@ -1438,13 +1438,13 @@
         <v>25</v>
       </c>
       <c r="J33" t="n">
-        <v>51.73</v>
+        <v>45.3</v>
       </c>
       <c r="K33" t="n">
-        <v>69.22</v>
+        <v>60.62</v>
       </c>
       <c r="L33" t="n">
-        <v>86.41</v>
+        <v>75.68000000000001</v>
       </c>
     </row>
     <row r="34">
@@ -1480,13 +1480,13 @@
         <v>26</v>
       </c>
       <c r="J34" t="n">
-        <v>-96.59999999999999</v>
+        <v>-87.08</v>
       </c>
       <c r="K34" t="n">
-        <v>110.43</v>
+        <v>99.56</v>
       </c>
       <c r="L34" t="n">
-        <v>146.72</v>
+        <v>132.27</v>
       </c>
     </row>
     <row r="35">
@@ -1522,13 +1522,13 @@
         <v>22</v>
       </c>
       <c r="J35" t="n">
-        <v>168.94</v>
+        <v>114.2</v>
       </c>
       <c r="K35" t="n">
-        <v>65.04000000000001</v>
+        <v>43.96</v>
       </c>
       <c r="L35" t="n">
-        <v>181.03</v>
+        <v>122.36</v>
       </c>
     </row>
     <row r="36">
@@ -1564,13 +1564,13 @@
         <v>25</v>
       </c>
       <c r="J36" t="n">
-        <v>178.61</v>
+        <v>128.71</v>
       </c>
       <c r="K36" t="n">
-        <v>138.83</v>
+        <v>100.04</v>
       </c>
       <c r="L36" t="n">
-        <v>226.22</v>
+        <v>163.02</v>
       </c>
     </row>
     <row r="37">
@@ -1606,13 +1606,13 @@
         <v>23</v>
       </c>
       <c r="J37" t="n">
-        <v>129.34</v>
+        <v>90.8</v>
       </c>
       <c r="K37" t="n">
-        <v>-308.42</v>
+        <v>-216.53</v>
       </c>
       <c r="L37" t="n">
-        <v>334.45</v>
+        <v>234.8</v>
       </c>
     </row>
     <row r="38">
@@ -1648,13 +1648,13 @@
         <v>23</v>
       </c>
       <c r="J38" t="n">
-        <v>204.36</v>
+        <v>116.45</v>
       </c>
       <c r="K38" t="n">
-        <v>374.58</v>
+        <v>213.44</v>
       </c>
       <c r="L38" t="n">
-        <v>426.7</v>
+        <v>243.14</v>
       </c>
     </row>
     <row r="39">
@@ -1690,13 +1690,13 @@
         <v>24</v>
       </c>
       <c r="J39" t="n">
-        <v>-182.73</v>
+        <v>-118.72</v>
       </c>
       <c r="K39" t="n">
-        <v>139.75</v>
+        <v>90.8</v>
       </c>
       <c r="L39" t="n">
-        <v>230.04</v>
+        <v>149.46</v>
       </c>
     </row>
     <row r="40">
@@ -1732,13 +1732,13 @@
         <v>25</v>
       </c>
       <c r="J40" t="n">
-        <v>-80.37</v>
+        <v>-52.13</v>
       </c>
       <c r="K40" t="n">
-        <v>205.61</v>
+        <v>133.37</v>
       </c>
       <c r="L40" t="n">
-        <v>220.76</v>
+        <v>143.2</v>
       </c>
     </row>
     <row r="41">
@@ -1774,13 +1774,13 @@
         <v>23</v>
       </c>
       <c r="J41" t="n">
-        <v>-174.91</v>
+        <v>-95.17</v>
       </c>
       <c r="K41" t="n">
-        <v>291.88</v>
+        <v>158.81</v>
       </c>
       <c r="L41" t="n">
-        <v>340.28</v>
+        <v>185.14</v>
       </c>
     </row>
     <row r="42">
@@ -1816,13 +1816,13 @@
         <v>21</v>
       </c>
       <c r="J42" t="n">
-        <v>231.72</v>
+        <v>114.8</v>
       </c>
       <c r="K42" t="n">
-        <v>180.51</v>
+        <v>89.43000000000001</v>
       </c>
       <c r="L42" t="n">
-        <v>293.73</v>
+        <v>145.52</v>
       </c>
     </row>
     <row r="43">
@@ -1858,13 +1858,13 @@
         <v>22</v>
       </c>
       <c r="J43" t="n">
-        <v>309.48</v>
+        <v>157.99</v>
       </c>
       <c r="K43" t="n">
-        <v>-367.5</v>
+        <v>-187.61</v>
       </c>
       <c r="L43" t="n">
-        <v>480.46</v>
+        <v>245.27</v>
       </c>
     </row>
     <row r="44">
@@ -1900,13 +1900,13 @@
         <v>27</v>
       </c>
       <c r="J44" t="n">
-        <v>-18.66</v>
+        <v>-18.17</v>
       </c>
       <c r="K44" t="n">
-        <v>58.77</v>
+        <v>57.24</v>
       </c>
       <c r="L44" t="n">
-        <v>61.66</v>
+        <v>60.06</v>
       </c>
     </row>
     <row r="45">
@@ -1942,13 +1942,13 @@
         <v>26</v>
       </c>
       <c r="J45" t="n">
-        <v>61.73</v>
+        <v>55.69</v>
       </c>
       <c r="K45" t="n">
-        <v>-3.47</v>
+        <v>-3.13</v>
       </c>
       <c r="L45" t="n">
-        <v>61.83</v>
+        <v>55.78</v>
       </c>
     </row>
     <row r="46">
@@ -1984,13 +1984,13 @@
         <v>23</v>
       </c>
       <c r="J46" t="n">
-        <v>52</v>
+        <v>41.65</v>
       </c>
       <c r="K46" t="n">
-        <v>-8.41</v>
+        <v>-6.74</v>
       </c>
       <c r="L46" t="n">
-        <v>52.68</v>
+        <v>42.2</v>
       </c>
     </row>
     <row r="47">
@@ -2026,13 +2026,13 @@
         <v>23</v>
       </c>
       <c r="J47" t="n">
-        <v>-39.72</v>
+        <v>-31.23</v>
       </c>
       <c r="K47" t="n">
-        <v>65.02</v>
+        <v>51.12</v>
       </c>
       <c r="L47" t="n">
-        <v>76.2</v>
+        <v>59.91</v>
       </c>
     </row>
     <row r="48">
@@ -2068,13 +2068,13 @@
         <v>21</v>
       </c>
       <c r="J48" t="n">
-        <v>-77.48</v>
+        <v>-58.36</v>
       </c>
       <c r="K48" t="n">
-        <v>200.69</v>
+        <v>151.16</v>
       </c>
       <c r="L48" t="n">
-        <v>215.13</v>
+        <v>162.04</v>
       </c>
     </row>
     <row r="49">
@@ -2110,13 +2110,13 @@
         <v>22</v>
       </c>
       <c r="J49" t="n">
-        <v>160</v>
+        <v>124.5</v>
       </c>
       <c r="K49" t="n">
-        <v>68.39</v>
+        <v>53.22</v>
       </c>
       <c r="L49" t="n">
-        <v>174</v>
+        <v>135.39</v>
       </c>
     </row>
     <row r="50">
@@ -2152,13 +2152,13 @@
         <v>25</v>
       </c>
       <c r="J50" t="n">
-        <v>38.58</v>
+        <v>28.27</v>
       </c>
       <c r="K50" t="n">
-        <v>-112.65</v>
+        <v>-82.54000000000001</v>
       </c>
       <c r="L50" t="n">
-        <v>119.07</v>
+        <v>87.25</v>
       </c>
     </row>
     <row r="51">
@@ -2194,13 +2194,13 @@
         <v>24</v>
       </c>
       <c r="J51" t="n">
-        <v>-103.09</v>
+        <v>-74.55</v>
       </c>
       <c r="K51" t="n">
-        <v>206.11</v>
+        <v>149.05</v>
       </c>
       <c r="L51" t="n">
-        <v>230.45</v>
+        <v>166.65</v>
       </c>
     </row>
     <row r="52">
@@ -2236,13 +2236,13 @@
         <v>21</v>
       </c>
       <c r="J52" t="n">
-        <v>120.17</v>
+        <v>75.83</v>
       </c>
       <c r="K52" t="n">
-        <v>-18.12</v>
+        <v>-11.43</v>
       </c>
       <c r="L52" t="n">
-        <v>121.53</v>
+        <v>76.69</v>
       </c>
     </row>
     <row r="53">
@@ -2278,13 +2278,13 @@
         <v>23</v>
       </c>
       <c r="J53" t="n">
-        <v>-24.16</v>
+        <v>-14.97</v>
       </c>
       <c r="K53" t="n">
-        <v>279.57</v>
+        <v>173.21</v>
       </c>
       <c r="L53" t="n">
-        <v>280.61</v>
+        <v>173.86</v>
       </c>
     </row>
     <row r="54">
@@ -2320,13 +2320,13 @@
         <v>23</v>
       </c>
       <c r="J54" t="n">
-        <v>316.68</v>
+        <v>191.51</v>
       </c>
       <c r="K54" t="n">
-        <v>132.64</v>
+        <v>80.20999999999999</v>
       </c>
       <c r="L54" t="n">
-        <v>343.33</v>
+        <v>207.63</v>
       </c>
     </row>
     <row r="55">
@@ -2362,13 +2362,13 @@
         <v>21</v>
       </c>
       <c r="J55" t="n">
-        <v>447.83</v>
+        <v>261.53</v>
       </c>
       <c r="K55" t="n">
-        <v>-35.67</v>
+        <v>-20.83</v>
       </c>
       <c r="L55" t="n">
-        <v>449.25</v>
+        <v>262.35</v>
       </c>
     </row>
     <row r="56">
@@ -2404,13 +2404,13 @@
         <v>24</v>
       </c>
       <c r="J56" t="n">
-        <v>15.3</v>
+        <v>8.35</v>
       </c>
       <c r="K56" t="n">
-        <v>334.3</v>
+        <v>182.45</v>
       </c>
       <c r="L56" t="n">
-        <v>334.65</v>
+        <v>182.65</v>
       </c>
     </row>
     <row r="57">
@@ -2446,13 +2446,13 @@
         <v>24</v>
       </c>
       <c r="J57" t="n">
-        <v>344.15</v>
+        <v>193.7</v>
       </c>
       <c r="K57" t="n">
-        <v>15.2</v>
+        <v>8.56</v>
       </c>
       <c r="L57" t="n">
-        <v>344.48</v>
+        <v>193.89</v>
       </c>
     </row>
     <row r="58">
@@ -2488,13 +2488,13 @@
         <v>23</v>
       </c>
       <c r="J58" t="n">
-        <v>159.63</v>
+        <v>86.66</v>
       </c>
       <c r="K58" t="n">
-        <v>-150.82</v>
+        <v>-81.88</v>
       </c>
       <c r="L58" t="n">
-        <v>219.61</v>
+        <v>119.22</v>
       </c>
     </row>
     <row r="59">
@@ -2530,13 +2530,13 @@
         <v>24</v>
       </c>
       <c r="J59" t="n">
-        <v>6.75</v>
+        <v>6.37</v>
       </c>
       <c r="K59" t="n">
-        <v>96.84999999999999</v>
+        <v>91.47</v>
       </c>
       <c r="L59" t="n">
-        <v>97.08</v>
+        <v>91.69</v>
       </c>
     </row>
     <row r="60">
@@ -2572,13 +2572,13 @@
         <v>22</v>
       </c>
       <c r="J60" t="n">
-        <v>-60.82</v>
+        <v>-54.24</v>
       </c>
       <c r="K60" t="n">
-        <v>40.63</v>
+        <v>36.23</v>
       </c>
       <c r="L60" t="n">
-        <v>73.14</v>
+        <v>65.22</v>
       </c>
     </row>
     <row r="61">
@@ -2614,13 +2614,13 @@
         <v>21</v>
       </c>
       <c r="J61" t="n">
-        <v>-83.55</v>
+        <v>-65.44</v>
       </c>
       <c r="K61" t="n">
-        <v>72.14</v>
+        <v>56.5</v>
       </c>
       <c r="L61" t="n">
-        <v>110.38</v>
+        <v>86.45</v>
       </c>
     </row>
     <row r="62">
@@ -2656,13 +2656,13 @@
         <v>21</v>
       </c>
       <c r="J62" t="n">
-        <v>60.88</v>
+        <v>44.65</v>
       </c>
       <c r="K62" t="n">
-        <v>122.17</v>
+        <v>89.59999999999999</v>
       </c>
       <c r="L62" t="n">
-        <v>136.5</v>
+        <v>100.11</v>
       </c>
     </row>
     <row r="63">
@@ -2698,13 +2698,13 @@
         <v>26</v>
       </c>
       <c r="J63" t="n">
-        <v>100.42</v>
+        <v>87.06999999999999</v>
       </c>
       <c r="K63" t="n">
-        <v>40.34</v>
+        <v>34.98</v>
       </c>
       <c r="L63" t="n">
-        <v>108.22</v>
+        <v>93.83</v>
       </c>
     </row>
     <row r="64">
@@ -2740,13 +2740,13 @@
         <v>22</v>
       </c>
       <c r="J64" t="n">
-        <v>174.79</v>
+        <v>132.26</v>
       </c>
       <c r="K64" t="n">
-        <v>-131.45</v>
+        <v>-99.45999999999999</v>
       </c>
       <c r="L64" t="n">
-        <v>218.7</v>
+        <v>165.49</v>
       </c>
     </row>
     <row r="65">
@@ -2782,13 +2782,13 @@
         <v>23</v>
       </c>
       <c r="J65" t="n">
-        <v>302.96</v>
+        <v>204.46</v>
       </c>
       <c r="K65" t="n">
-        <v>-257.2</v>
+        <v>-173.58</v>
       </c>
       <c r="L65" t="n">
-        <v>397.41</v>
+        <v>268.21</v>
       </c>
     </row>
     <row r="66">
@@ -2824,13 +2824,13 @@
         <v>26</v>
       </c>
       <c r="J66" t="n">
-        <v>-17.13</v>
+        <v>-12.84</v>
       </c>
       <c r="K66" t="n">
-        <v>95.95999999999999</v>
+        <v>71.91</v>
       </c>
       <c r="L66" t="n">
-        <v>97.47</v>
+        <v>73.04000000000001</v>
       </c>
     </row>
     <row r="67">
@@ -2866,13 +2866,13 @@
         <v>23</v>
       </c>
       <c r="J67" t="n">
-        <v>-87.86</v>
+        <v>-60.06</v>
       </c>
       <c r="K67" t="n">
-        <v>90.42</v>
+        <v>61.81</v>
       </c>
       <c r="L67" t="n">
-        <v>126.07</v>
+        <v>86.18000000000001</v>
       </c>
     </row>
     <row r="68">
@@ -2908,13 +2908,13 @@
         <v>21</v>
       </c>
       <c r="J68" t="n">
-        <v>151.49</v>
+        <v>89.87</v>
       </c>
       <c r="K68" t="n">
-        <v>256.38</v>
+        <v>152.1</v>
       </c>
       <c r="L68" t="n">
-        <v>297.8</v>
+        <v>176.67</v>
       </c>
     </row>
     <row r="69">
@@ -2950,13 +2950,13 @@
         <v>27</v>
       </c>
       <c r="J69" t="n">
-        <v>123.81</v>
+        <v>89.27</v>
       </c>
       <c r="K69" t="n">
-        <v>311.08</v>
+        <v>224.31</v>
       </c>
       <c r="L69" t="n">
-        <v>334.81</v>
+        <v>241.42</v>
       </c>
     </row>
     <row r="70">
@@ -2992,13 +2992,13 @@
         <v>26</v>
       </c>
       <c r="J70" t="n">
-        <v>236.37</v>
+        <v>159.67</v>
       </c>
       <c r="K70" t="n">
-        <v>246.23</v>
+        <v>166.33</v>
       </c>
       <c r="L70" t="n">
-        <v>341.32</v>
+        <v>230.56</v>
       </c>
     </row>
     <row r="71">
@@ -3034,13 +3034,13 @@
         <v>25</v>
       </c>
       <c r="J71" t="n">
-        <v>-15.52</v>
+        <v>-8.34</v>
       </c>
       <c r="K71" t="n">
-        <v>-909.45</v>
+        <v>-488.75</v>
       </c>
       <c r="L71" t="n">
-        <v>909.59</v>
+        <v>488.83</v>
       </c>
     </row>
     <row r="72">
@@ -3076,13 +3076,13 @@
         <v>21</v>
       </c>
       <c r="J72" t="n">
-        <v>-15.93</v>
+        <v>-8.35</v>
       </c>
       <c r="K72" t="n">
-        <v>676.33</v>
+        <v>354.64</v>
       </c>
       <c r="L72" t="n">
-        <v>676.52</v>
+        <v>354.74</v>
       </c>
     </row>
     <row r="73">
@@ -3118,13 +3118,13 @@
         <v>27</v>
       </c>
       <c r="J73" t="n">
-        <v>155.6</v>
+        <v>100.61</v>
       </c>
       <c r="K73" t="n">
-        <v>-268.32</v>
+        <v>-173.49</v>
       </c>
       <c r="L73" t="n">
-        <v>310.17</v>
+        <v>200.55</v>
       </c>
     </row>
     <row r="74">
@@ -3160,13 +3160,13 @@
         <v>27</v>
       </c>
       <c r="J74" t="n">
-        <v>-88.04000000000001</v>
+        <v>-82.39</v>
       </c>
       <c r="K74" t="n">
-        <v>-41.45</v>
+        <v>-38.79</v>
       </c>
       <c r="L74" t="n">
-        <v>97.31</v>
+        <v>91.06</v>
       </c>
     </row>
     <row r="75">
@@ -3202,13 +3202,13 @@
         <v>23</v>
       </c>
       <c r="J75" t="n">
-        <v>26.69</v>
+        <v>24.24</v>
       </c>
       <c r="K75" t="n">
-        <v>-46.08</v>
+        <v>-41.85</v>
       </c>
       <c r="L75" t="n">
-        <v>53.25</v>
+        <v>48.36</v>
       </c>
     </row>
     <row r="76">
@@ -3244,13 +3244,13 @@
         <v>22</v>
       </c>
       <c r="J76" t="n">
-        <v>-81.84999999999999</v>
+        <v>-63.04</v>
       </c>
       <c r="K76" t="n">
-        <v>63.2</v>
+        <v>48.67</v>
       </c>
       <c r="L76" t="n">
-        <v>103.41</v>
+        <v>79.64</v>
       </c>
     </row>
     <row r="77">
@@ -3286,13 +3286,13 @@
         <v>22</v>
       </c>
       <c r="J77" t="n">
-        <v>-76.58</v>
+        <v>-59.51</v>
       </c>
       <c r="K77" t="n">
-        <v>130.19</v>
+        <v>101.17</v>
       </c>
       <c r="L77" t="n">
-        <v>151.04</v>
+        <v>117.38</v>
       </c>
     </row>
     <row r="78">
@@ -3328,13 +3328,13 @@
         <v>25</v>
       </c>
       <c r="J78" t="n">
-        <v>52.76</v>
+        <v>44.52</v>
       </c>
       <c r="K78" t="n">
-        <v>-46.71</v>
+        <v>-39.41</v>
       </c>
       <c r="L78" t="n">
-        <v>70.47</v>
+        <v>59.45</v>
       </c>
     </row>
     <row r="79">
@@ -3370,13 +3370,13 @@
         <v>25</v>
       </c>
       <c r="J79" t="n">
-        <v>128.14</v>
+        <v>109.31</v>
       </c>
       <c r="K79" t="n">
-        <v>87.23</v>
+        <v>74.42</v>
       </c>
       <c r="L79" t="n">
-        <v>155.01</v>
+        <v>132.24</v>
       </c>
     </row>
     <row r="80">
@@ -3412,13 +3412,13 @@
         <v>27</v>
       </c>
       <c r="J80" t="n">
-        <v>-85.31</v>
+        <v>-70.41</v>
       </c>
       <c r="K80" t="n">
-        <v>-55.03</v>
+        <v>-45.42</v>
       </c>
       <c r="L80" t="n">
-        <v>101.52</v>
+        <v>83.79000000000001</v>
       </c>
     </row>
     <row r="81">
@@ -3454,13 +3454,13 @@
         <v>21</v>
       </c>
       <c r="J81" t="n">
-        <v>-154.33</v>
+        <v>-102.13</v>
       </c>
       <c r="K81" t="n">
-        <v>52.68</v>
+        <v>34.86</v>
       </c>
       <c r="L81" t="n">
-        <v>163.07</v>
+        <v>107.92</v>
       </c>
     </row>
     <row r="82">
@@ -3496,13 +3496,13 @@
         <v>22</v>
       </c>
       <c r="J82" t="n">
-        <v>-6.37</v>
+        <v>-4.37</v>
       </c>
       <c r="K82" t="n">
-        <v>108.61</v>
+        <v>74.5</v>
       </c>
       <c r="L82" t="n">
-        <v>108.8</v>
+        <v>74.63</v>
       </c>
     </row>
     <row r="83">
@@ -3538,13 +3538,13 @@
         <v>25</v>
       </c>
       <c r="J83" t="n">
-        <v>343.05</v>
+        <v>231.96</v>
       </c>
       <c r="K83" t="n">
-        <v>31.11</v>
+        <v>21.04</v>
       </c>
       <c r="L83" t="n">
-        <v>344.46</v>
+        <v>232.91</v>
       </c>
     </row>
     <row r="84">
@@ -3580,13 +3580,13 @@
         <v>21</v>
       </c>
       <c r="J84" t="n">
-        <v>-30.95</v>
+        <v>-17.98</v>
       </c>
       <c r="K84" t="n">
-        <v>268.85</v>
+        <v>156.16</v>
       </c>
       <c r="L84" t="n">
-        <v>270.62</v>
+        <v>157.2</v>
       </c>
     </row>
     <row r="85">
@@ -3622,13 +3622,13 @@
         <v>22</v>
       </c>
       <c r="J85" t="n">
-        <v>-101.06</v>
+        <v>-60.34</v>
       </c>
       <c r="K85" t="n">
-        <v>-434.51</v>
+        <v>-259.45</v>
       </c>
       <c r="L85" t="n">
-        <v>446.11</v>
+        <v>266.38</v>
       </c>
     </row>
     <row r="86">
@@ -3664,13 +3664,13 @@
         <v>23</v>
       </c>
       <c r="J86" t="n">
-        <v>-720.33</v>
+        <v>-391.93</v>
       </c>
       <c r="K86" t="n">
-        <v>201.59</v>
+        <v>109.68</v>
       </c>
       <c r="L86" t="n">
-        <v>748.01</v>
+        <v>406.99</v>
       </c>
     </row>
     <row r="87">
@@ -3706,13 +3706,13 @@
         <v>26</v>
       </c>
       <c r="J87" t="n">
-        <v>-436.06</v>
+        <v>-265.72</v>
       </c>
       <c r="K87" t="n">
-        <v>-139.11</v>
+        <v>-84.77</v>
       </c>
       <c r="L87" t="n">
-        <v>457.71</v>
+        <v>278.91</v>
       </c>
     </row>
     <row r="88">
@@ -3748,13 +3748,13 @@
         <v>21</v>
       </c>
       <c r="J88" t="n">
-        <v>-365.72</v>
+        <v>-181.05</v>
       </c>
       <c r="K88" t="n">
-        <v>-121.41</v>
+        <v>-60.1</v>
       </c>
       <c r="L88" t="n">
-        <v>385.34</v>
+        <v>190.76</v>
       </c>
     </row>
   </sheetData>

--- a/output/2024-07-26.xlsx
+++ b/output/2024-07-26.xlsx
@@ -640,13 +640,13 @@
         <v>27</v>
       </c>
       <c r="J14" t="n">
-        <v>42.47</v>
+        <v>40.06</v>
       </c>
       <c r="K14" t="n">
-        <v>43.37</v>
+        <v>40.91</v>
       </c>
       <c r="L14" t="n">
-        <v>60.71</v>
+        <v>57.26</v>
       </c>
     </row>
     <row r="15">
@@ -682,13 +682,13 @@
         <v>25</v>
       </c>
       <c r="J15" t="n">
-        <v>28.41</v>
+        <v>26.81</v>
       </c>
       <c r="K15" t="n">
-        <v>-22.81</v>
+        <v>-21.53</v>
       </c>
       <c r="L15" t="n">
-        <v>36.44</v>
+        <v>34.38</v>
       </c>
     </row>
     <row r="16">
@@ -724,13 +724,13 @@
         <v>23</v>
       </c>
       <c r="J16" t="n">
-        <v>-17.45</v>
+        <v>-16.65</v>
       </c>
       <c r="K16" t="n">
-        <v>41.68</v>
+        <v>39.77</v>
       </c>
       <c r="L16" t="n">
-        <v>45.19</v>
+        <v>43.12</v>
       </c>
     </row>
     <row r="17">
@@ -766,13 +766,13 @@
         <v>22</v>
       </c>
       <c r="J17" t="n">
-        <v>-57.34</v>
+        <v>-56.54</v>
       </c>
       <c r="K17" t="n">
-        <v>49.99</v>
+        <v>49.3</v>
       </c>
       <c r="L17" t="n">
-        <v>76.06999999999999</v>
+        <v>75.02</v>
       </c>
     </row>
     <row r="18">
@@ -808,13 +808,13 @@
         <v>22</v>
       </c>
       <c r="J18" t="n">
-        <v>52.35</v>
+        <v>51.25</v>
       </c>
       <c r="K18" t="n">
-        <v>9.859999999999999</v>
+        <v>9.66</v>
       </c>
       <c r="L18" t="n">
-        <v>53.27</v>
+        <v>52.16</v>
       </c>
     </row>
     <row r="19">
@@ -850,13 +850,13 @@
         <v>25</v>
       </c>
       <c r="J19" t="n">
-        <v>100.11</v>
+        <v>97.29000000000001</v>
       </c>
       <c r="K19" t="n">
-        <v>-8.6</v>
+        <v>-8.359999999999999</v>
       </c>
       <c r="L19" t="n">
-        <v>100.48</v>
+        <v>97.65000000000001</v>
       </c>
     </row>
     <row r="20">
@@ -892,13 +892,13 @@
         <v>22</v>
       </c>
       <c r="J20" t="n">
-        <v>-23.18</v>
+        <v>-23.98</v>
       </c>
       <c r="K20" t="n">
-        <v>98.11</v>
+        <v>101.52</v>
       </c>
       <c r="L20" t="n">
-        <v>100.81</v>
+        <v>104.31</v>
       </c>
     </row>
     <row r="21">
@@ -934,13 +934,13 @@
         <v>24</v>
       </c>
       <c r="J21" t="n">
-        <v>-172.5</v>
+        <v>-177.67</v>
       </c>
       <c r="K21" t="n">
-        <v>-11.53</v>
+        <v>-11.88</v>
       </c>
       <c r="L21" t="n">
-        <v>172.89</v>
+        <v>178.07</v>
       </c>
     </row>
     <row r="22">
@@ -976,13 +976,13 @@
         <v>21</v>
       </c>
       <c r="J22" t="n">
-        <v>143.09</v>
+        <v>151.02</v>
       </c>
       <c r="K22" t="n">
-        <v>47.05</v>
+        <v>49.66</v>
       </c>
       <c r="L22" t="n">
-        <v>150.63</v>
+        <v>158.97</v>
       </c>
     </row>
     <row r="23">
@@ -1018,13 +1018,13 @@
         <v>23</v>
       </c>
       <c r="J23" t="n">
-        <v>-184.5</v>
+        <v>-198.36</v>
       </c>
       <c r="K23" t="n">
-        <v>-117.5</v>
+        <v>-126.33</v>
       </c>
       <c r="L23" t="n">
-        <v>218.74</v>
+        <v>235.17</v>
       </c>
     </row>
     <row r="24">
@@ -1060,13 +1060,13 @@
         <v>23</v>
       </c>
       <c r="J24" t="n">
-        <v>-92.29000000000001</v>
+        <v>-98.95999999999999</v>
       </c>
       <c r="K24" t="n">
-        <v>-35.71</v>
+        <v>-38.29</v>
       </c>
       <c r="L24" t="n">
-        <v>98.95999999999999</v>
+        <v>106.11</v>
       </c>
     </row>
     <row r="25">
@@ -1102,13 +1102,13 @@
         <v>27</v>
       </c>
       <c r="J25" t="n">
-        <v>54.22</v>
+        <v>57.33</v>
       </c>
       <c r="K25" t="n">
-        <v>-113.6</v>
+        <v>-120.11</v>
       </c>
       <c r="L25" t="n">
-        <v>125.88</v>
+        <v>133.09</v>
       </c>
     </row>
     <row r="26">
@@ -1144,13 +1144,13 @@
         <v>22</v>
       </c>
       <c r="J26" t="n">
-        <v>22.01</v>
+        <v>24.22</v>
       </c>
       <c r="K26" t="n">
-        <v>-130.3</v>
+        <v>-143.34</v>
       </c>
       <c r="L26" t="n">
-        <v>132.15</v>
+        <v>145.37</v>
       </c>
     </row>
     <row r="27">
@@ -1186,13 +1186,13 @@
         <v>25</v>
       </c>
       <c r="J27" t="n">
-        <v>137.86</v>
+        <v>147.13</v>
       </c>
       <c r="K27" t="n">
-        <v>-76.06</v>
+        <v>-81.18000000000001</v>
       </c>
       <c r="L27" t="n">
-        <v>157.45</v>
+        <v>168.04</v>
       </c>
     </row>
     <row r="28">
@@ -1228,13 +1228,13 @@
         <v>21</v>
       </c>
       <c r="J28" t="n">
-        <v>-442.32</v>
+        <v>-485.1</v>
       </c>
       <c r="K28" t="n">
-        <v>-41</v>
+        <v>-44.97</v>
       </c>
       <c r="L28" t="n">
-        <v>444.22</v>
+        <v>487.18</v>
       </c>
     </row>
     <row r="29">
@@ -1270,13 +1270,13 @@
         <v>24</v>
       </c>
       <c r="J29" t="n">
-        <v>47.5</v>
+        <v>45.33</v>
       </c>
       <c r="K29" t="n">
-        <v>24.68</v>
+        <v>23.56</v>
       </c>
       <c r="L29" t="n">
-        <v>53.53</v>
+        <v>51.09</v>
       </c>
     </row>
     <row r="30">
@@ -1312,13 +1312,13 @@
         <v>23</v>
       </c>
       <c r="J30" t="n">
-        <v>-63.93</v>
+        <v>-60.7</v>
       </c>
       <c r="K30" t="n">
-        <v>55.4</v>
+        <v>52.6</v>
       </c>
       <c r="L30" t="n">
-        <v>84.59</v>
+        <v>80.31999999999999</v>
       </c>
     </row>
     <row r="31">
@@ -1354,13 +1354,13 @@
         <v>21</v>
       </c>
       <c r="J31" t="n">
-        <v>-2.96</v>
+        <v>-2.88</v>
       </c>
       <c r="K31" t="n">
-        <v>-39.46</v>
+        <v>-38.44</v>
       </c>
       <c r="L31" t="n">
-        <v>39.57</v>
+        <v>38.55</v>
       </c>
     </row>
     <row r="32">
@@ -1396,13 +1396,13 @@
         <v>27</v>
       </c>
       <c r="J32" t="n">
-        <v>54.62</v>
+        <v>53.32</v>
       </c>
       <c r="K32" t="n">
-        <v>40.35</v>
+        <v>39.4</v>
       </c>
       <c r="L32" t="n">
-        <v>67.91</v>
+        <v>66.3</v>
       </c>
     </row>
     <row r="33">
@@ -1438,13 +1438,13 @@
         <v>25</v>
       </c>
       <c r="J33" t="n">
-        <v>45.3</v>
+        <v>44.06</v>
       </c>
       <c r="K33" t="n">
-        <v>60.62</v>
+        <v>58.96</v>
       </c>
       <c r="L33" t="n">
-        <v>75.68000000000001</v>
+        <v>73.59999999999999</v>
       </c>
     </row>
     <row r="34">
@@ -1480,13 +1480,13 @@
         <v>26</v>
       </c>
       <c r="J34" t="n">
-        <v>-87.08</v>
+        <v>-85.16</v>
       </c>
       <c r="K34" t="n">
-        <v>99.56</v>
+        <v>97.36</v>
       </c>
       <c r="L34" t="n">
-        <v>132.27</v>
+        <v>129.35</v>
       </c>
     </row>
     <row r="35">
@@ -1522,13 +1522,13 @@
         <v>22</v>
       </c>
       <c r="J35" t="n">
-        <v>114.2</v>
+        <v>119.71</v>
       </c>
       <c r="K35" t="n">
-        <v>43.96</v>
+        <v>46.08</v>
       </c>
       <c r="L35" t="n">
-        <v>122.36</v>
+        <v>128.27</v>
       </c>
     </row>
     <row r="36">
@@ -1564,13 +1564,13 @@
         <v>25</v>
       </c>
       <c r="J36" t="n">
-        <v>128.71</v>
+        <v>132.8</v>
       </c>
       <c r="K36" t="n">
-        <v>100.04</v>
+        <v>103.22</v>
       </c>
       <c r="L36" t="n">
-        <v>163.02</v>
+        <v>168.2</v>
       </c>
     </row>
     <row r="37">
@@ -1606,13 +1606,13 @@
         <v>23</v>
       </c>
       <c r="J37" t="n">
-        <v>90.8</v>
+        <v>95.45</v>
       </c>
       <c r="K37" t="n">
-        <v>-216.53</v>
+        <v>-227.61</v>
       </c>
       <c r="L37" t="n">
-        <v>234.8</v>
+        <v>246.82</v>
       </c>
     </row>
     <row r="38">
@@ -1648,13 +1648,13 @@
         <v>23</v>
       </c>
       <c r="J38" t="n">
-        <v>116.45</v>
+        <v>125.55</v>
       </c>
       <c r="K38" t="n">
-        <v>213.44</v>
+        <v>230.12</v>
       </c>
       <c r="L38" t="n">
-        <v>243.14</v>
+        <v>262.14</v>
       </c>
     </row>
     <row r="39">
@@ -1690,13 +1690,13 @@
         <v>24</v>
       </c>
       <c r="J39" t="n">
-        <v>-118.72</v>
+        <v>-127.76</v>
       </c>
       <c r="K39" t="n">
-        <v>90.8</v>
+        <v>97.70999999999999</v>
       </c>
       <c r="L39" t="n">
-        <v>149.46</v>
+        <v>160.84</v>
       </c>
     </row>
     <row r="40">
@@ -1732,13 +1732,13 @@
         <v>25</v>
       </c>
       <c r="J40" t="n">
-        <v>-52.13</v>
+        <v>-55.53</v>
       </c>
       <c r="K40" t="n">
-        <v>133.37</v>
+        <v>142.07</v>
       </c>
       <c r="L40" t="n">
-        <v>143.2</v>
+        <v>152.54</v>
       </c>
     </row>
     <row r="41">
@@ -1774,13 +1774,13 @@
         <v>23</v>
       </c>
       <c r="J41" t="n">
-        <v>-95.17</v>
+        <v>-103.13</v>
       </c>
       <c r="K41" t="n">
-        <v>158.81</v>
+        <v>172.1</v>
       </c>
       <c r="L41" t="n">
-        <v>185.14</v>
+        <v>200.63</v>
       </c>
     </row>
     <row r="42">
@@ -1816,13 +1816,13 @@
         <v>21</v>
       </c>
       <c r="J42" t="n">
-        <v>114.8</v>
+        <v>126.04</v>
       </c>
       <c r="K42" t="n">
-        <v>89.43000000000001</v>
+        <v>98.18000000000001</v>
       </c>
       <c r="L42" t="n">
-        <v>145.52</v>
+        <v>159.76</v>
       </c>
     </row>
     <row r="43">
@@ -1858,13 +1858,13 @@
         <v>22</v>
       </c>
       <c r="J43" t="n">
-        <v>157.99</v>
+        <v>173.11</v>
       </c>
       <c r="K43" t="n">
-        <v>-187.61</v>
+        <v>-205.56</v>
       </c>
       <c r="L43" t="n">
-        <v>245.27</v>
+        <v>268.74</v>
       </c>
     </row>
     <row r="44">
@@ -1900,13 +1900,13 @@
         <v>27</v>
       </c>
       <c r="J44" t="n">
-        <v>-18.17</v>
+        <v>-17.02</v>
       </c>
       <c r="K44" t="n">
-        <v>57.24</v>
+        <v>53.59</v>
       </c>
       <c r="L44" t="n">
-        <v>60.06</v>
+        <v>56.23</v>
       </c>
     </row>
     <row r="45">
@@ -1942,13 +1942,13 @@
         <v>26</v>
       </c>
       <c r="J45" t="n">
-        <v>55.69</v>
+        <v>52.95</v>
       </c>
       <c r="K45" t="n">
-        <v>-3.13</v>
+        <v>-2.97</v>
       </c>
       <c r="L45" t="n">
-        <v>55.78</v>
+        <v>53.04</v>
       </c>
     </row>
     <row r="46">
@@ -1984,13 +1984,13 @@
         <v>23</v>
       </c>
       <c r="J46" t="n">
-        <v>41.65</v>
+        <v>39.31</v>
       </c>
       <c r="K46" t="n">
-        <v>-6.74</v>
+        <v>-6.36</v>
       </c>
       <c r="L46" t="n">
-        <v>42.2</v>
+        <v>39.82</v>
       </c>
     </row>
     <row r="47">
@@ -2026,13 +2026,13 @@
         <v>23</v>
       </c>
       <c r="J47" t="n">
-        <v>-31.23</v>
+        <v>-30.63</v>
       </c>
       <c r="K47" t="n">
-        <v>51.12</v>
+        <v>50.14</v>
       </c>
       <c r="L47" t="n">
-        <v>59.91</v>
+        <v>58.75</v>
       </c>
     </row>
     <row r="48">
@@ -2068,13 +2068,13 @@
         <v>21</v>
       </c>
       <c r="J48" t="n">
-        <v>-58.36</v>
+        <v>-59.18</v>
       </c>
       <c r="K48" t="n">
-        <v>151.16</v>
+        <v>153.28</v>
       </c>
       <c r="L48" t="n">
-        <v>162.04</v>
+        <v>164.31</v>
       </c>
     </row>
     <row r="49">
@@ -2110,13 +2110,13 @@
         <v>22</v>
       </c>
       <c r="J49" t="n">
-        <v>124.5</v>
+        <v>123.61</v>
       </c>
       <c r="K49" t="n">
-        <v>53.22</v>
+        <v>52.84</v>
       </c>
       <c r="L49" t="n">
-        <v>135.39</v>
+        <v>134.43</v>
       </c>
     </row>
     <row r="50">
@@ -2152,13 +2152,13 @@
         <v>25</v>
       </c>
       <c r="J50" t="n">
-        <v>28.27</v>
+        <v>29.09</v>
       </c>
       <c r="K50" t="n">
-        <v>-82.54000000000001</v>
+        <v>-84.93000000000001</v>
       </c>
       <c r="L50" t="n">
-        <v>87.25</v>
+        <v>89.78</v>
       </c>
     </row>
     <row r="51">
@@ -2194,13 +2194,13 @@
         <v>24</v>
       </c>
       <c r="J51" t="n">
-        <v>-74.55</v>
+        <v>-77.22</v>
       </c>
       <c r="K51" t="n">
-        <v>149.05</v>
+        <v>154.39</v>
       </c>
       <c r="L51" t="n">
-        <v>166.65</v>
+        <v>172.63</v>
       </c>
     </row>
     <row r="52">
@@ -2236,13 +2236,13 @@
         <v>21</v>
       </c>
       <c r="J52" t="n">
-        <v>75.83</v>
+        <v>78.44</v>
       </c>
       <c r="K52" t="n">
-        <v>-11.43</v>
+        <v>-11.83</v>
       </c>
       <c r="L52" t="n">
-        <v>76.69</v>
+        <v>79.33</v>
       </c>
     </row>
     <row r="53">
@@ -2278,13 +2278,13 @@
         <v>23</v>
       </c>
       <c r="J53" t="n">
-        <v>-14.97</v>
+        <v>-16.01</v>
       </c>
       <c r="K53" t="n">
-        <v>173.21</v>
+        <v>185.22</v>
       </c>
       <c r="L53" t="n">
-        <v>173.86</v>
+        <v>185.91</v>
       </c>
     </row>
     <row r="54">
@@ -2320,13 +2320,13 @@
         <v>23</v>
       </c>
       <c r="J54" t="n">
-        <v>191.51</v>
+        <v>203.68</v>
       </c>
       <c r="K54" t="n">
-        <v>80.20999999999999</v>
+        <v>85.31</v>
       </c>
       <c r="L54" t="n">
-        <v>207.63</v>
+        <v>220.82</v>
       </c>
     </row>
     <row r="55">
@@ -2362,13 +2362,13 @@
         <v>21</v>
       </c>
       <c r="J55" t="n">
-        <v>261.53</v>
+        <v>281.43</v>
       </c>
       <c r="K55" t="n">
-        <v>-20.83</v>
+        <v>-22.42</v>
       </c>
       <c r="L55" t="n">
-        <v>262.35</v>
+        <v>282.32</v>
       </c>
     </row>
     <row r="56">
@@ -2404,13 +2404,13 @@
         <v>24</v>
       </c>
       <c r="J56" t="n">
-        <v>8.35</v>
+        <v>8.949999999999999</v>
       </c>
       <c r="K56" t="n">
-        <v>182.45</v>
+        <v>195.43</v>
       </c>
       <c r="L56" t="n">
-        <v>182.65</v>
+        <v>195.64</v>
       </c>
     </row>
     <row r="57">
@@ -2446,13 +2446,13 @@
         <v>24</v>
       </c>
       <c r="J57" t="n">
-        <v>193.7</v>
+        <v>210.4</v>
       </c>
       <c r="K57" t="n">
-        <v>8.56</v>
+        <v>9.289999999999999</v>
       </c>
       <c r="L57" t="n">
-        <v>193.89</v>
+        <v>210.61</v>
       </c>
     </row>
     <row r="58">
@@ -2488,13 +2488,13 @@
         <v>23</v>
       </c>
       <c r="J58" t="n">
-        <v>86.66</v>
+        <v>94.59</v>
       </c>
       <c r="K58" t="n">
-        <v>-81.88</v>
+        <v>-89.37</v>
       </c>
       <c r="L58" t="n">
-        <v>119.22</v>
+        <v>130.13</v>
       </c>
     </row>
     <row r="59">
@@ -2530,13 +2530,13 @@
         <v>24</v>
       </c>
       <c r="J59" t="n">
-        <v>6.37</v>
+        <v>6.11</v>
       </c>
       <c r="K59" t="n">
-        <v>91.47</v>
+        <v>87.65000000000001</v>
       </c>
       <c r="L59" t="n">
-        <v>91.69</v>
+        <v>87.86</v>
       </c>
     </row>
     <row r="60">
@@ -2572,13 +2572,13 @@
         <v>22</v>
       </c>
       <c r="J60" t="n">
-        <v>-54.24</v>
+        <v>-52.49</v>
       </c>
       <c r="K60" t="n">
-        <v>36.23</v>
+        <v>35.06</v>
       </c>
       <c r="L60" t="n">
-        <v>65.22</v>
+        <v>63.12</v>
       </c>
     </row>
     <row r="61">
@@ -2614,13 +2614,13 @@
         <v>21</v>
       </c>
       <c r="J61" t="n">
-        <v>-65.44</v>
+        <v>-63.31</v>
       </c>
       <c r="K61" t="n">
-        <v>56.5</v>
+        <v>54.66</v>
       </c>
       <c r="L61" t="n">
-        <v>86.45</v>
+        <v>83.64</v>
       </c>
     </row>
     <row r="62">
@@ -2656,13 +2656,13 @@
         <v>21</v>
       </c>
       <c r="J62" t="n">
-        <v>44.65</v>
+        <v>44.34</v>
       </c>
       <c r="K62" t="n">
-        <v>89.59999999999999</v>
+        <v>89</v>
       </c>
       <c r="L62" t="n">
-        <v>100.11</v>
+        <v>99.43000000000001</v>
       </c>
     </row>
     <row r="63">
@@ -2698,13 +2698,13 @@
         <v>26</v>
       </c>
       <c r="J63" t="n">
-        <v>87.06999999999999</v>
+        <v>84.33</v>
       </c>
       <c r="K63" t="n">
-        <v>34.98</v>
+        <v>33.88</v>
       </c>
       <c r="L63" t="n">
-        <v>93.83</v>
+        <v>90.88</v>
       </c>
     </row>
     <row r="64">
@@ -2740,13 +2740,13 @@
         <v>22</v>
       </c>
       <c r="J64" t="n">
-        <v>132.26</v>
+        <v>132.37</v>
       </c>
       <c r="K64" t="n">
-        <v>-99.45999999999999</v>
+        <v>-99.54000000000001</v>
       </c>
       <c r="L64" t="n">
-        <v>165.49</v>
+        <v>165.62</v>
       </c>
     </row>
     <row r="65">
@@ -2782,13 +2782,13 @@
         <v>23</v>
       </c>
       <c r="J65" t="n">
-        <v>204.46</v>
+        <v>214.11</v>
       </c>
       <c r="K65" t="n">
-        <v>-173.58</v>
+        <v>-181.77</v>
       </c>
       <c r="L65" t="n">
-        <v>268.21</v>
+        <v>280.86</v>
       </c>
     </row>
     <row r="66">
@@ -2824,13 +2824,13 @@
         <v>26</v>
       </c>
       <c r="J66" t="n">
-        <v>-12.84</v>
+        <v>-13.21</v>
       </c>
       <c r="K66" t="n">
-        <v>71.91</v>
+        <v>73.95999999999999</v>
       </c>
       <c r="L66" t="n">
-        <v>73.04000000000001</v>
+        <v>75.13</v>
       </c>
     </row>
     <row r="67">
@@ -2866,13 +2866,13 @@
         <v>23</v>
       </c>
       <c r="J67" t="n">
-        <v>-60.06</v>
+        <v>-62.42</v>
       </c>
       <c r="K67" t="n">
-        <v>61.81</v>
+        <v>64.23999999999999</v>
       </c>
       <c r="L67" t="n">
-        <v>86.18000000000001</v>
+        <v>89.56999999999999</v>
       </c>
     </row>
     <row r="68">
@@ -2908,13 +2908,13 @@
         <v>21</v>
       </c>
       <c r="J68" t="n">
-        <v>89.87</v>
+        <v>96.86</v>
       </c>
       <c r="K68" t="n">
-        <v>152.1</v>
+        <v>163.93</v>
       </c>
       <c r="L68" t="n">
-        <v>176.67</v>
+        <v>190.41</v>
       </c>
     </row>
     <row r="69">
@@ -2950,13 +2950,13 @@
         <v>27</v>
       </c>
       <c r="J69" t="n">
-        <v>89.27</v>
+        <v>92.02</v>
       </c>
       <c r="K69" t="n">
-        <v>224.31</v>
+        <v>231.21</v>
       </c>
       <c r="L69" t="n">
-        <v>241.42</v>
+        <v>248.85</v>
       </c>
     </row>
     <row r="70">
@@ -2992,13 +2992,13 @@
         <v>26</v>
       </c>
       <c r="J70" t="n">
-        <v>159.67</v>
+        <v>166.61</v>
       </c>
       <c r="K70" t="n">
-        <v>166.33</v>
+        <v>173.57</v>
       </c>
       <c r="L70" t="n">
-        <v>230.56</v>
+        <v>240.59</v>
       </c>
     </row>
     <row r="71">
@@ -3034,13 +3034,13 @@
         <v>25</v>
       </c>
       <c r="J71" t="n">
-        <v>-8.34</v>
+        <v>-8.960000000000001</v>
       </c>
       <c r="K71" t="n">
-        <v>-488.75</v>
+        <v>-524.9</v>
       </c>
       <c r="L71" t="n">
-        <v>488.83</v>
+        <v>524.97</v>
       </c>
     </row>
     <row r="72">
@@ -3076,13 +3076,13 @@
         <v>21</v>
       </c>
       <c r="J72" t="n">
-        <v>-8.35</v>
+        <v>-9.1</v>
       </c>
       <c r="K72" t="n">
-        <v>354.64</v>
+        <v>386.12</v>
       </c>
       <c r="L72" t="n">
-        <v>354.74</v>
+        <v>386.23</v>
       </c>
     </row>
     <row r="73">
@@ -3118,13 +3118,13 @@
         <v>27</v>
       </c>
       <c r="J73" t="n">
-        <v>100.61</v>
+        <v>106.09</v>
       </c>
       <c r="K73" t="n">
-        <v>-173.49</v>
+        <v>-182.94</v>
       </c>
       <c r="L73" t="n">
-        <v>200.55</v>
+        <v>211.47</v>
       </c>
     </row>
     <row r="74">
@@ -3160,13 +3160,13 @@
         <v>27</v>
       </c>
       <c r="J74" t="n">
-        <v>-82.39</v>
+        <v>-76.34</v>
       </c>
       <c r="K74" t="n">
-        <v>-38.79</v>
+        <v>-35.94</v>
       </c>
       <c r="L74" t="n">
-        <v>91.06</v>
+        <v>84.38</v>
       </c>
     </row>
     <row r="75">
@@ -3202,13 +3202,13 @@
         <v>23</v>
       </c>
       <c r="J75" t="n">
-        <v>24.24</v>
+        <v>23.27</v>
       </c>
       <c r="K75" t="n">
-        <v>-41.85</v>
+        <v>-40.17</v>
       </c>
       <c r="L75" t="n">
-        <v>48.36</v>
+        <v>46.43</v>
       </c>
     </row>
     <row r="76">
@@ -3244,13 +3244,13 @@
         <v>22</v>
       </c>
       <c r="J76" t="n">
-        <v>-63.04</v>
+        <v>-61.55</v>
       </c>
       <c r="K76" t="n">
-        <v>48.67</v>
+        <v>47.52</v>
       </c>
       <c r="L76" t="n">
-        <v>79.64</v>
+        <v>77.76000000000001</v>
       </c>
     </row>
     <row r="77">
@@ -3286,13 +3286,13 @@
         <v>22</v>
       </c>
       <c r="J77" t="n">
-        <v>-59.51</v>
+        <v>-58.91</v>
       </c>
       <c r="K77" t="n">
-        <v>101.17</v>
+        <v>100.15</v>
       </c>
       <c r="L77" t="n">
-        <v>117.38</v>
+        <v>116.19</v>
       </c>
     </row>
     <row r="78">
@@ -3328,13 +3328,13 @@
         <v>25</v>
       </c>
       <c r="J78" t="n">
-        <v>44.52</v>
+        <v>43.31</v>
       </c>
       <c r="K78" t="n">
-        <v>-39.41</v>
+        <v>-38.34</v>
       </c>
       <c r="L78" t="n">
-        <v>59.45</v>
+        <v>57.85</v>
       </c>
     </row>
     <row r="79">
@@ -3370,13 +3370,13 @@
         <v>25</v>
       </c>
       <c r="J79" t="n">
-        <v>109.31</v>
+        <v>107.78</v>
       </c>
       <c r="K79" t="n">
-        <v>74.42</v>
+        <v>73.38</v>
       </c>
       <c r="L79" t="n">
-        <v>132.24</v>
+        <v>130.39</v>
       </c>
     </row>
     <row r="80">
@@ -3412,13 +3412,13 @@
         <v>27</v>
       </c>
       <c r="J80" t="n">
-        <v>-70.41</v>
+        <v>-72.12</v>
       </c>
       <c r="K80" t="n">
-        <v>-45.42</v>
+        <v>-46.52</v>
       </c>
       <c r="L80" t="n">
-        <v>83.79000000000001</v>
+        <v>85.81999999999999</v>
       </c>
     </row>
     <row r="81">
@@ -3454,13 +3454,13 @@
         <v>21</v>
       </c>
       <c r="J81" t="n">
-        <v>-102.13</v>
+        <v>-106.4</v>
       </c>
       <c r="K81" t="n">
-        <v>34.86</v>
+        <v>36.32</v>
       </c>
       <c r="L81" t="n">
-        <v>107.92</v>
+        <v>112.43</v>
       </c>
     </row>
     <row r="82">
@@ -3496,13 +3496,13 @@
         <v>22</v>
       </c>
       <c r="J82" t="n">
-        <v>-4.37</v>
+        <v>-4.61</v>
       </c>
       <c r="K82" t="n">
-        <v>74.5</v>
+        <v>78.63</v>
       </c>
       <c r="L82" t="n">
-        <v>74.63</v>
+        <v>78.76000000000001</v>
       </c>
     </row>
     <row r="83">
@@ -3538,13 +3538,13 @@
         <v>25</v>
       </c>
       <c r="J83" t="n">
-        <v>231.96</v>
+        <v>245.04</v>
       </c>
       <c r="K83" t="n">
-        <v>21.04</v>
+        <v>22.22</v>
       </c>
       <c r="L83" t="n">
-        <v>232.91</v>
+        <v>246.05</v>
       </c>
     </row>
     <row r="84">
@@ -3580,13 +3580,13 @@
         <v>21</v>
       </c>
       <c r="J84" t="n">
-        <v>-17.98</v>
+        <v>-19.22</v>
       </c>
       <c r="K84" t="n">
-        <v>156.16</v>
+        <v>166.94</v>
       </c>
       <c r="L84" t="n">
-        <v>157.2</v>
+        <v>168.05</v>
       </c>
     </row>
     <row r="85">
@@ -3622,13 +3622,13 @@
         <v>22</v>
       </c>
       <c r="J85" t="n">
-        <v>-60.34</v>
+        <v>-65.38</v>
       </c>
       <c r="K85" t="n">
-        <v>-259.45</v>
+        <v>-281.11</v>
       </c>
       <c r="L85" t="n">
-        <v>266.38</v>
+        <v>288.62</v>
       </c>
     </row>
     <row r="86">
@@ -3664,13 +3664,13 @@
         <v>23</v>
       </c>
       <c r="J86" t="n">
-        <v>-391.93</v>
+        <v>-425.12</v>
       </c>
       <c r="K86" t="n">
-        <v>109.68</v>
+        <v>118.97</v>
       </c>
       <c r="L86" t="n">
-        <v>406.99</v>
+        <v>441.45</v>
       </c>
     </row>
     <row r="87">
@@ -3706,13 +3706,13 @@
         <v>26</v>
       </c>
       <c r="J87" t="n">
-        <v>-265.72</v>
+        <v>-284.24</v>
       </c>
       <c r="K87" t="n">
-        <v>-84.77</v>
+        <v>-90.68000000000001</v>
       </c>
       <c r="L87" t="n">
-        <v>278.91</v>
+        <v>298.35</v>
       </c>
     </row>
     <row r="88">
@@ -3748,13 +3748,13 @@
         <v>21</v>
       </c>
       <c r="J88" t="n">
-        <v>-181.05</v>
+        <v>-198.61</v>
       </c>
       <c r="K88" t="n">
-        <v>-60.1</v>
+        <v>-65.94</v>
       </c>
       <c r="L88" t="n">
-        <v>190.76</v>
+        <v>209.27</v>
       </c>
     </row>
   </sheetData>

--- a/output/2024-07-26.xlsx
+++ b/output/2024-07-26.xlsx
@@ -640,13 +640,13 @@
         <v>27</v>
       </c>
       <c r="J14" t="n">
-        <v>40.06</v>
+        <v>26.33</v>
       </c>
       <c r="K14" t="n">
-        <v>40.91</v>
+        <v>26.89</v>
       </c>
       <c r="L14" t="n">
-        <v>57.26</v>
+        <v>37.64</v>
       </c>
     </row>
     <row r="15">
@@ -682,13 +682,13 @@
         <v>25</v>
       </c>
       <c r="J15" t="n">
-        <v>26.81</v>
+        <v>20.11</v>
       </c>
       <c r="K15" t="n">
-        <v>-21.53</v>
+        <v>-16.14</v>
       </c>
       <c r="L15" t="n">
-        <v>34.38</v>
+        <v>25.79</v>
       </c>
     </row>
     <row r="16">
@@ -724,13 +724,13 @@
         <v>23</v>
       </c>
       <c r="J16" t="n">
-        <v>-16.65</v>
+        <v>-12.48</v>
       </c>
       <c r="K16" t="n">
-        <v>39.77</v>
+        <v>29.83</v>
       </c>
       <c r="L16" t="n">
-        <v>43.12</v>
+        <v>32.34</v>
       </c>
     </row>
     <row r="17">
@@ -766,13 +766,13 @@
         <v>22</v>
       </c>
       <c r="J17" t="n">
-        <v>-56.54</v>
+        <v>-42.41</v>
       </c>
       <c r="K17" t="n">
-        <v>49.3</v>
+        <v>36.98</v>
       </c>
       <c r="L17" t="n">
-        <v>75.02</v>
+        <v>56.26</v>
       </c>
     </row>
     <row r="18">
@@ -808,13 +808,13 @@
         <v>22</v>
       </c>
       <c r="J18" t="n">
-        <v>51.25</v>
+        <v>38.44</v>
       </c>
       <c r="K18" t="n">
-        <v>9.66</v>
+        <v>7.24</v>
       </c>
       <c r="L18" t="n">
-        <v>52.16</v>
+        <v>39.12</v>
       </c>
     </row>
     <row r="19">
@@ -850,13 +850,13 @@
         <v>25</v>
       </c>
       <c r="J19" t="n">
-        <v>97.29000000000001</v>
+        <v>72.97</v>
       </c>
       <c r="K19" t="n">
-        <v>-8.359999999999999</v>
+        <v>-6.27</v>
       </c>
       <c r="L19" t="n">
-        <v>97.65000000000001</v>
+        <v>73.23</v>
       </c>
     </row>
     <row r="20">
@@ -892,13 +892,13 @@
         <v>22</v>
       </c>
       <c r="J20" t="n">
-        <v>-23.98</v>
+        <v>-17.99</v>
       </c>
       <c r="K20" t="n">
-        <v>101.52</v>
+        <v>76.14</v>
       </c>
       <c r="L20" t="n">
-        <v>104.31</v>
+        <v>78.23</v>
       </c>
     </row>
     <row r="21">
@@ -934,13 +934,13 @@
         <v>24</v>
       </c>
       <c r="J21" t="n">
-        <v>-177.67</v>
+        <v>-121.7</v>
       </c>
       <c r="K21" t="n">
-        <v>-11.88</v>
+        <v>-8.140000000000001</v>
       </c>
       <c r="L21" t="n">
-        <v>178.07</v>
+        <v>121.97</v>
       </c>
     </row>
     <row r="22">
@@ -976,13 +976,13 @@
         <v>21</v>
       </c>
       <c r="J22" t="n">
-        <v>151.02</v>
+        <v>112.42</v>
       </c>
       <c r="K22" t="n">
-        <v>49.66</v>
+        <v>36.97</v>
       </c>
       <c r="L22" t="n">
-        <v>158.97</v>
+        <v>118.34</v>
       </c>
     </row>
     <row r="23">
@@ -1018,13 +1018,13 @@
         <v>23</v>
       </c>
       <c r="J23" t="n">
-        <v>-198.36</v>
+        <v>-148.77</v>
       </c>
       <c r="K23" t="n">
-        <v>-126.33</v>
+        <v>-94.75</v>
       </c>
       <c r="L23" t="n">
-        <v>235.17</v>
+        <v>176.38</v>
       </c>
     </row>
     <row r="24">
@@ -1060,13 +1060,13 @@
         <v>23</v>
       </c>
       <c r="J24" t="n">
-        <v>-98.95999999999999</v>
+        <v>-74.22</v>
       </c>
       <c r="K24" t="n">
-        <v>-38.29</v>
+        <v>-28.72</v>
       </c>
       <c r="L24" t="n">
-        <v>106.11</v>
+        <v>79.58</v>
       </c>
     </row>
     <row r="25">
@@ -1102,13 +1102,13 @@
         <v>27</v>
       </c>
       <c r="J25" t="n">
-        <v>57.33</v>
+        <v>42.99</v>
       </c>
       <c r="K25" t="n">
-        <v>-120.11</v>
+        <v>-90.08</v>
       </c>
       <c r="L25" t="n">
-        <v>133.09</v>
+        <v>99.81999999999999</v>
       </c>
     </row>
     <row r="26">
@@ -1144,13 +1144,13 @@
         <v>22</v>
       </c>
       <c r="J26" t="n">
-        <v>24.22</v>
+        <v>17.94</v>
       </c>
       <c r="K26" t="n">
-        <v>-143.34</v>
+        <v>-106.2</v>
       </c>
       <c r="L26" t="n">
-        <v>145.37</v>
+        <v>107.71</v>
       </c>
     </row>
     <row r="27">
@@ -1186,13 +1186,13 @@
         <v>25</v>
       </c>
       <c r="J27" t="n">
-        <v>147.13</v>
+        <v>108.49</v>
       </c>
       <c r="K27" t="n">
-        <v>-81.18000000000001</v>
+        <v>-59.85</v>
       </c>
       <c r="L27" t="n">
-        <v>168.04</v>
+        <v>123.9</v>
       </c>
     </row>
     <row r="28">
@@ -1228,13 +1228,13 @@
         <v>21</v>
       </c>
       <c r="J28" t="n">
-        <v>-485.1</v>
+        <v>-359.41</v>
       </c>
       <c r="K28" t="n">
-        <v>-44.97</v>
+        <v>-33.32</v>
       </c>
       <c r="L28" t="n">
-        <v>487.18</v>
+        <v>360.95</v>
       </c>
     </row>
     <row r="29">
@@ -1270,13 +1270,13 @@
         <v>24</v>
       </c>
       <c r="J29" t="n">
-        <v>45.33</v>
+        <v>34</v>
       </c>
       <c r="K29" t="n">
-        <v>23.56</v>
+        <v>17.67</v>
       </c>
       <c r="L29" t="n">
-        <v>51.09</v>
+        <v>38.31</v>
       </c>
     </row>
     <row r="30">
@@ -1312,13 +1312,13 @@
         <v>23</v>
       </c>
       <c r="J30" t="n">
-        <v>-60.7</v>
+        <v>-44.18</v>
       </c>
       <c r="K30" t="n">
-        <v>52.6</v>
+        <v>38.29</v>
       </c>
       <c r="L30" t="n">
-        <v>80.31999999999999</v>
+        <v>58.47</v>
       </c>
     </row>
     <row r="31">
@@ -1354,13 +1354,13 @@
         <v>21</v>
       </c>
       <c r="J31" t="n">
-        <v>-2.88</v>
+        <v>-2.16</v>
       </c>
       <c r="K31" t="n">
-        <v>-38.44</v>
+        <v>-28.83</v>
       </c>
       <c r="L31" t="n">
-        <v>38.55</v>
+        <v>28.91</v>
       </c>
     </row>
     <row r="32">
@@ -1396,13 +1396,13 @@
         <v>27</v>
       </c>
       <c r="J32" t="n">
-        <v>53.32</v>
+        <v>36.19</v>
       </c>
       <c r="K32" t="n">
-        <v>39.4</v>
+        <v>26.74</v>
       </c>
       <c r="L32" t="n">
-        <v>66.3</v>
+        <v>45</v>
       </c>
     </row>
     <row r="33">
@@ -1438,13 +1438,13 @@
         <v>25</v>
       </c>
       <c r="J33" t="n">
-        <v>44.06</v>
+        <v>30.94</v>
       </c>
       <c r="K33" t="n">
-        <v>58.96</v>
+        <v>41.41</v>
       </c>
       <c r="L33" t="n">
-        <v>73.59999999999999</v>
+        <v>51.69</v>
       </c>
     </row>
     <row r="34">
@@ -1480,13 +1480,13 @@
         <v>26</v>
       </c>
       <c r="J34" t="n">
-        <v>-85.16</v>
+        <v>-56.27</v>
       </c>
       <c r="K34" t="n">
-        <v>97.36</v>
+        <v>64.33</v>
       </c>
       <c r="L34" t="n">
-        <v>129.35</v>
+        <v>85.47</v>
       </c>
     </row>
     <row r="35">
@@ -1522,13 +1522,13 @@
         <v>22</v>
       </c>
       <c r="J35" t="n">
-        <v>119.71</v>
+        <v>85.06</v>
       </c>
       <c r="K35" t="n">
-        <v>46.08</v>
+        <v>32.75</v>
       </c>
       <c r="L35" t="n">
-        <v>128.27</v>
+        <v>91.15000000000001</v>
       </c>
     </row>
     <row r="36">
@@ -1564,13 +1564,13 @@
         <v>25</v>
       </c>
       <c r="J36" t="n">
-        <v>132.8</v>
+        <v>99.59999999999999</v>
       </c>
       <c r="K36" t="n">
-        <v>103.22</v>
+        <v>77.42</v>
       </c>
       <c r="L36" t="n">
-        <v>168.2</v>
+        <v>126.15</v>
       </c>
     </row>
     <row r="37">
@@ -1606,13 +1606,13 @@
         <v>23</v>
       </c>
       <c r="J37" t="n">
-        <v>95.45</v>
+        <v>61.66</v>
       </c>
       <c r="K37" t="n">
-        <v>-227.61</v>
+        <v>-147.04</v>
       </c>
       <c r="L37" t="n">
-        <v>246.82</v>
+        <v>159.44</v>
       </c>
     </row>
     <row r="38">
@@ -1648,13 +1648,13 @@
         <v>23</v>
       </c>
       <c r="J38" t="n">
-        <v>125.55</v>
+        <v>94.16</v>
       </c>
       <c r="K38" t="n">
-        <v>230.12</v>
+        <v>172.59</v>
       </c>
       <c r="L38" t="n">
-        <v>262.14</v>
+        <v>196.61</v>
       </c>
     </row>
     <row r="39">
@@ -1690,13 +1690,13 @@
         <v>24</v>
       </c>
       <c r="J39" t="n">
-        <v>-127.76</v>
+        <v>-90.19</v>
       </c>
       <c r="K39" t="n">
-        <v>97.70999999999999</v>
+        <v>68.98</v>
       </c>
       <c r="L39" t="n">
-        <v>160.84</v>
+        <v>113.55</v>
       </c>
     </row>
     <row r="40">
@@ -1732,13 +1732,13 @@
         <v>25</v>
       </c>
       <c r="J40" t="n">
-        <v>-55.53</v>
+        <v>-40.12</v>
       </c>
       <c r="K40" t="n">
-        <v>142.07</v>
+        <v>102.65</v>
       </c>
       <c r="L40" t="n">
-        <v>152.54</v>
+        <v>110.21</v>
       </c>
     </row>
     <row r="41">
@@ -1774,13 +1774,13 @@
         <v>23</v>
       </c>
       <c r="J41" t="n">
-        <v>-103.13</v>
+        <v>-74.61</v>
       </c>
       <c r="K41" t="n">
-        <v>172.1</v>
+        <v>124.51</v>
       </c>
       <c r="L41" t="n">
-        <v>200.63</v>
+        <v>145.15</v>
       </c>
     </row>
     <row r="42">
@@ -1816,13 +1816,13 @@
         <v>21</v>
       </c>
       <c r="J42" t="n">
-        <v>126.04</v>
+        <v>94.53</v>
       </c>
       <c r="K42" t="n">
-        <v>98.18000000000001</v>
+        <v>73.63</v>
       </c>
       <c r="L42" t="n">
-        <v>159.76</v>
+        <v>119.82</v>
       </c>
     </row>
     <row r="43">
@@ -1858,13 +1858,13 @@
         <v>22</v>
       </c>
       <c r="J43" t="n">
-        <v>173.11</v>
+        <v>129.83</v>
       </c>
       <c r="K43" t="n">
-        <v>-205.56</v>
+        <v>-154.17</v>
       </c>
       <c r="L43" t="n">
-        <v>268.74</v>
+        <v>201.55</v>
       </c>
     </row>
     <row r="44">
@@ -1900,13 +1900,13 @@
         <v>27</v>
       </c>
       <c r="J44" t="n">
-        <v>-17.02</v>
+        <v>-12.34</v>
       </c>
       <c r="K44" t="n">
-        <v>53.59</v>
+        <v>38.87</v>
       </c>
       <c r="L44" t="n">
-        <v>56.23</v>
+        <v>40.78</v>
       </c>
     </row>
     <row r="45">
@@ -1942,13 +1942,13 @@
         <v>26</v>
       </c>
       <c r="J45" t="n">
-        <v>52.95</v>
+        <v>39.26</v>
       </c>
       <c r="K45" t="n">
-        <v>-2.97</v>
+        <v>-2.2</v>
       </c>
       <c r="L45" t="n">
-        <v>53.04</v>
+        <v>39.32</v>
       </c>
     </row>
     <row r="46">
@@ -1984,13 +1984,13 @@
         <v>23</v>
       </c>
       <c r="J46" t="n">
-        <v>39.31</v>
+        <v>29.48</v>
       </c>
       <c r="K46" t="n">
-        <v>-6.36</v>
+        <v>-4.77</v>
       </c>
       <c r="L46" t="n">
-        <v>39.82</v>
+        <v>29.86</v>
       </c>
     </row>
     <row r="47">
@@ -2026,13 +2026,13 @@
         <v>23</v>
       </c>
       <c r="J47" t="n">
-        <v>-30.63</v>
+        <v>-22.97</v>
       </c>
       <c r="K47" t="n">
-        <v>50.14</v>
+        <v>37.6</v>
       </c>
       <c r="L47" t="n">
-        <v>58.75</v>
+        <v>44.06</v>
       </c>
     </row>
     <row r="48">
@@ -2068,13 +2068,13 @@
         <v>21</v>
       </c>
       <c r="J48" t="n">
-        <v>-59.18</v>
+        <v>-38.41</v>
       </c>
       <c r="K48" t="n">
-        <v>153.28</v>
+        <v>99.48999999999999</v>
       </c>
       <c r="L48" t="n">
-        <v>164.31</v>
+        <v>106.64</v>
       </c>
     </row>
     <row r="49">
@@ -2110,13 +2110,13 @@
         <v>22</v>
       </c>
       <c r="J49" t="n">
-        <v>123.61</v>
+        <v>80.63</v>
       </c>
       <c r="K49" t="n">
-        <v>52.84</v>
+        <v>34.47</v>
       </c>
       <c r="L49" t="n">
-        <v>134.43</v>
+        <v>87.69</v>
       </c>
     </row>
     <row r="50">
@@ -2152,13 +2152,13 @@
         <v>25</v>
       </c>
       <c r="J50" t="n">
-        <v>29.09</v>
+        <v>21.19</v>
       </c>
       <c r="K50" t="n">
-        <v>-84.93000000000001</v>
+        <v>-61.86</v>
       </c>
       <c r="L50" t="n">
-        <v>89.78</v>
+        <v>65.38</v>
       </c>
     </row>
     <row r="51">
@@ -2194,13 +2194,13 @@
         <v>24</v>
       </c>
       <c r="J51" t="n">
-        <v>-77.22</v>
+        <v>-49.45</v>
       </c>
       <c r="K51" t="n">
-        <v>154.39</v>
+        <v>98.87</v>
       </c>
       <c r="L51" t="n">
-        <v>172.63</v>
+        <v>110.55</v>
       </c>
     </row>
     <row r="52">
@@ -2236,13 +2236,13 @@
         <v>21</v>
       </c>
       <c r="J52" t="n">
-        <v>78.44</v>
+        <v>58.83</v>
       </c>
       <c r="K52" t="n">
-        <v>-11.83</v>
+        <v>-8.869999999999999</v>
       </c>
       <c r="L52" t="n">
-        <v>79.33</v>
+        <v>59.5</v>
       </c>
     </row>
     <row r="53">
@@ -2278,13 +2278,13 @@
         <v>23</v>
       </c>
       <c r="J53" t="n">
-        <v>-16.01</v>
+        <v>-10.89</v>
       </c>
       <c r="K53" t="n">
-        <v>185.22</v>
+        <v>126.04</v>
       </c>
       <c r="L53" t="n">
-        <v>185.91</v>
+        <v>126.51</v>
       </c>
     </row>
     <row r="54">
@@ -2320,13 +2320,13 @@
         <v>23</v>
       </c>
       <c r="J54" t="n">
-        <v>203.68</v>
+        <v>147.16</v>
       </c>
       <c r="K54" t="n">
-        <v>85.31</v>
+        <v>61.64</v>
       </c>
       <c r="L54" t="n">
-        <v>220.82</v>
+        <v>159.55</v>
       </c>
     </row>
     <row r="55">
@@ -2362,13 +2362,13 @@
         <v>21</v>
       </c>
       <c r="J55" t="n">
-        <v>281.43</v>
+        <v>192.31</v>
       </c>
       <c r="K55" t="n">
-        <v>-22.42</v>
+        <v>-15.32</v>
       </c>
       <c r="L55" t="n">
-        <v>282.32</v>
+        <v>192.92</v>
       </c>
     </row>
     <row r="56">
@@ -2404,13 +2404,13 @@
         <v>24</v>
       </c>
       <c r="J56" t="n">
-        <v>8.949999999999999</v>
+        <v>6.71</v>
       </c>
       <c r="K56" t="n">
-        <v>195.43</v>
+        <v>146.57</v>
       </c>
       <c r="L56" t="n">
-        <v>195.64</v>
+        <v>146.73</v>
       </c>
     </row>
     <row r="57">
@@ -2446,13 +2446,13 @@
         <v>24</v>
       </c>
       <c r="J57" t="n">
-        <v>210.4</v>
+        <v>152.22</v>
       </c>
       <c r="K57" t="n">
-        <v>9.289999999999999</v>
+        <v>6.72</v>
       </c>
       <c r="L57" t="n">
-        <v>210.61</v>
+        <v>152.37</v>
       </c>
     </row>
     <row r="58">
@@ -2488,13 +2488,13 @@
         <v>23</v>
       </c>
       <c r="J58" t="n">
-        <v>94.59</v>
+        <v>35.97</v>
       </c>
       <c r="K58" t="n">
-        <v>-89.37</v>
+        <v>-33.99</v>
       </c>
       <c r="L58" t="n">
-        <v>130.13</v>
+        <v>49.49</v>
       </c>
     </row>
     <row r="59">
@@ -2530,13 +2530,13 @@
         <v>24</v>
       </c>
       <c r="J59" t="n">
-        <v>6.11</v>
+        <v>4.13</v>
       </c>
       <c r="K59" t="n">
-        <v>87.65000000000001</v>
+        <v>59.24</v>
       </c>
       <c r="L59" t="n">
-        <v>87.86</v>
+        <v>59.38</v>
       </c>
     </row>
     <row r="60">
@@ -2572,13 +2572,13 @@
         <v>22</v>
       </c>
       <c r="J60" t="n">
-        <v>-52.49</v>
+        <v>-35.79</v>
       </c>
       <c r="K60" t="n">
-        <v>35.06</v>
+        <v>23.91</v>
       </c>
       <c r="L60" t="n">
-        <v>63.12</v>
+        <v>43.04</v>
       </c>
     </row>
     <row r="61">
@@ -2614,13 +2614,13 @@
         <v>21</v>
       </c>
       <c r="J61" t="n">
-        <v>-63.31</v>
+        <v>-46.08</v>
       </c>
       <c r="K61" t="n">
-        <v>54.66</v>
+        <v>39.79</v>
       </c>
       <c r="L61" t="n">
-        <v>83.64</v>
+        <v>60.88</v>
       </c>
     </row>
     <row r="62">
@@ -2656,13 +2656,13 @@
         <v>21</v>
       </c>
       <c r="J62" t="n">
-        <v>44.34</v>
+        <v>33.26</v>
       </c>
       <c r="K62" t="n">
-        <v>89</v>
+        <v>66.75</v>
       </c>
       <c r="L62" t="n">
-        <v>99.43000000000001</v>
+        <v>74.58</v>
       </c>
     </row>
     <row r="63">
@@ -2698,13 +2698,13 @@
         <v>26</v>
       </c>
       <c r="J63" t="n">
-        <v>84.33</v>
+        <v>63.25</v>
       </c>
       <c r="K63" t="n">
-        <v>33.88</v>
+        <v>25.41</v>
       </c>
       <c r="L63" t="n">
-        <v>90.88</v>
+        <v>68.16</v>
       </c>
     </row>
     <row r="64">
@@ -2740,13 +2740,13 @@
         <v>22</v>
       </c>
       <c r="J64" t="n">
-        <v>132.37</v>
+        <v>81.53</v>
       </c>
       <c r="K64" t="n">
-        <v>-99.54000000000001</v>
+        <v>-61.31</v>
       </c>
       <c r="L64" t="n">
-        <v>165.62</v>
+        <v>102.01</v>
       </c>
     </row>
     <row r="65">
@@ -2782,13 +2782,13 @@
         <v>23</v>
       </c>
       <c r="J65" t="n">
-        <v>214.11</v>
+        <v>127.12</v>
       </c>
       <c r="K65" t="n">
-        <v>-181.77</v>
+        <v>-107.93</v>
       </c>
       <c r="L65" t="n">
-        <v>280.86</v>
+        <v>166.76</v>
       </c>
     </row>
     <row r="66">
@@ -2824,13 +2824,13 @@
         <v>26</v>
       </c>
       <c r="J66" t="n">
-        <v>-13.21</v>
+        <v>-9.9</v>
       </c>
       <c r="K66" t="n">
-        <v>73.95999999999999</v>
+        <v>55.47</v>
       </c>
       <c r="L66" t="n">
-        <v>75.13</v>
+        <v>56.35</v>
       </c>
     </row>
     <row r="67">
@@ -2866,13 +2866,13 @@
         <v>23</v>
       </c>
       <c r="J67" t="n">
-        <v>-62.42</v>
+        <v>-29.46</v>
       </c>
       <c r="K67" t="n">
-        <v>64.23999999999999</v>
+        <v>30.32</v>
       </c>
       <c r="L67" t="n">
-        <v>89.56999999999999</v>
+        <v>42.28</v>
       </c>
     </row>
     <row r="68">
@@ -2908,13 +2908,13 @@
         <v>21</v>
       </c>
       <c r="J68" t="n">
-        <v>96.86</v>
+        <v>67.77</v>
       </c>
       <c r="K68" t="n">
-        <v>163.93</v>
+        <v>114.7</v>
       </c>
       <c r="L68" t="n">
-        <v>190.41</v>
+        <v>133.22</v>
       </c>
     </row>
     <row r="69">
@@ -2950,13 +2950,13 @@
         <v>27</v>
       </c>
       <c r="J69" t="n">
-        <v>92.02</v>
+        <v>62.75</v>
       </c>
       <c r="K69" t="n">
-        <v>231.21</v>
+        <v>157.66</v>
       </c>
       <c r="L69" t="n">
-        <v>248.85</v>
+        <v>169.69</v>
       </c>
     </row>
     <row r="70">
@@ -2992,13 +2992,13 @@
         <v>26</v>
       </c>
       <c r="J70" t="n">
-        <v>166.61</v>
+        <v>109.42</v>
       </c>
       <c r="K70" t="n">
-        <v>173.57</v>
+        <v>113.99</v>
       </c>
       <c r="L70" t="n">
-        <v>240.59</v>
+        <v>158.01</v>
       </c>
     </row>
     <row r="71">
@@ -3034,13 +3034,13 @@
         <v>25</v>
       </c>
       <c r="J71" t="n">
-        <v>-8.960000000000001</v>
+        <v>-4.88</v>
       </c>
       <c r="K71" t="n">
-        <v>-524.9</v>
+        <v>-286.2</v>
       </c>
       <c r="L71" t="n">
-        <v>524.97</v>
+        <v>286.24</v>
       </c>
     </row>
     <row r="72">
@@ -3076,13 +3076,13 @@
         <v>21</v>
       </c>
       <c r="J72" t="n">
-        <v>-9.1</v>
+        <v>-6.37</v>
       </c>
       <c r="K72" t="n">
-        <v>386.12</v>
+        <v>270.54</v>
       </c>
       <c r="L72" t="n">
-        <v>386.23</v>
+        <v>270.61</v>
       </c>
     </row>
     <row r="73">
@@ -3118,13 +3118,13 @@
         <v>27</v>
       </c>
       <c r="J73" t="n">
-        <v>106.09</v>
+        <v>75</v>
       </c>
       <c r="K73" t="n">
-        <v>-182.94</v>
+        <v>-129.34</v>
       </c>
       <c r="L73" t="n">
-        <v>211.47</v>
+        <v>149.51</v>
       </c>
     </row>
     <row r="74">
@@ -3160,13 +3160,13 @@
         <v>27</v>
       </c>
       <c r="J74" t="n">
-        <v>-76.34</v>
+        <v>-57.25</v>
       </c>
       <c r="K74" t="n">
-        <v>-35.94</v>
+        <v>-26.96</v>
       </c>
       <c r="L74" t="n">
-        <v>84.38</v>
+        <v>63.28</v>
       </c>
     </row>
     <row r="75">
@@ -3202,13 +3202,13 @@
         <v>23</v>
       </c>
       <c r="J75" t="n">
-        <v>23.27</v>
+        <v>15.64</v>
       </c>
       <c r="K75" t="n">
-        <v>-40.17</v>
+        <v>-27</v>
       </c>
       <c r="L75" t="n">
-        <v>46.43</v>
+        <v>31.2</v>
       </c>
     </row>
     <row r="76">
@@ -3244,13 +3244,13 @@
         <v>22</v>
       </c>
       <c r="J76" t="n">
-        <v>-61.55</v>
+        <v>-46.16</v>
       </c>
       <c r="K76" t="n">
-        <v>47.52</v>
+        <v>35.64</v>
       </c>
       <c r="L76" t="n">
-        <v>77.76000000000001</v>
+        <v>58.32</v>
       </c>
     </row>
     <row r="77">
@@ -3286,13 +3286,13 @@
         <v>22</v>
       </c>
       <c r="J77" t="n">
-        <v>-58.91</v>
+        <v>-38.33</v>
       </c>
       <c r="K77" t="n">
-        <v>100.15</v>
+        <v>65.16</v>
       </c>
       <c r="L77" t="n">
-        <v>116.19</v>
+        <v>75.59999999999999</v>
       </c>
     </row>
     <row r="78">
@@ -3328,13 +3328,13 @@
         <v>25</v>
       </c>
       <c r="J78" t="n">
-        <v>43.31</v>
+        <v>31.96</v>
       </c>
       <c r="K78" t="n">
-        <v>-38.34</v>
+        <v>-28.29</v>
       </c>
       <c r="L78" t="n">
-        <v>57.85</v>
+        <v>42.68</v>
       </c>
     </row>
     <row r="79">
@@ -3370,13 +3370,13 @@
         <v>25</v>
       </c>
       <c r="J79" t="n">
-        <v>107.78</v>
+        <v>68.92</v>
       </c>
       <c r="K79" t="n">
-        <v>73.38</v>
+        <v>46.92</v>
       </c>
       <c r="L79" t="n">
-        <v>130.39</v>
+        <v>83.38</v>
       </c>
     </row>
     <row r="80">
@@ -3412,13 +3412,13 @@
         <v>27</v>
       </c>
       <c r="J80" t="n">
-        <v>-72.12</v>
+        <v>-50.22</v>
       </c>
       <c r="K80" t="n">
-        <v>-46.52</v>
+        <v>-32.39</v>
       </c>
       <c r="L80" t="n">
-        <v>85.81999999999999</v>
+        <v>59.76</v>
       </c>
     </row>
     <row r="81">
@@ -3454,13 +3454,13 @@
         <v>21</v>
       </c>
       <c r="J81" t="n">
-        <v>-106.4</v>
+        <v>-74.84</v>
       </c>
       <c r="K81" t="n">
-        <v>36.32</v>
+        <v>25.54</v>
       </c>
       <c r="L81" t="n">
-        <v>112.43</v>
+        <v>79.06999999999999</v>
       </c>
     </row>
     <row r="82">
@@ -3496,13 +3496,13 @@
         <v>22</v>
       </c>
       <c r="J82" t="n">
-        <v>-4.61</v>
+        <v>-3.22</v>
       </c>
       <c r="K82" t="n">
-        <v>78.63</v>
+        <v>54.93</v>
       </c>
       <c r="L82" t="n">
-        <v>78.76000000000001</v>
+        <v>55.03</v>
       </c>
     </row>
     <row r="83">
@@ -3538,13 +3538,13 @@
         <v>25</v>
       </c>
       <c r="J83" t="n">
-        <v>245.04</v>
+        <v>172.6</v>
       </c>
       <c r="K83" t="n">
-        <v>22.22</v>
+        <v>15.65</v>
       </c>
       <c r="L83" t="n">
-        <v>246.05</v>
+        <v>173.31</v>
       </c>
     </row>
     <row r="84">
@@ -3580,13 +3580,13 @@
         <v>21</v>
       </c>
       <c r="J84" t="n">
-        <v>-19.22</v>
+        <v>-13.03</v>
       </c>
       <c r="K84" t="n">
-        <v>166.94</v>
+        <v>113.14</v>
       </c>
       <c r="L84" t="n">
-        <v>168.05</v>
+        <v>113.89</v>
       </c>
     </row>
     <row r="85">
@@ -3622,13 +3622,13 @@
         <v>22</v>
       </c>
       <c r="J85" t="n">
-        <v>-65.38</v>
+        <v>-46.69</v>
       </c>
       <c r="K85" t="n">
-        <v>-281.11</v>
+        <v>-200.74</v>
       </c>
       <c r="L85" t="n">
-        <v>288.62</v>
+        <v>206.09</v>
       </c>
     </row>
     <row r="86">
@@ -3664,13 +3664,13 @@
         <v>23</v>
       </c>
       <c r="J86" t="n">
-        <v>-425.12</v>
+        <v>-280.53</v>
       </c>
       <c r="K86" t="n">
-        <v>118.97</v>
+        <v>78.51000000000001</v>
       </c>
       <c r="L86" t="n">
-        <v>441.45</v>
+        <v>291.31</v>
       </c>
     </row>
     <row r="87">
@@ -3706,13 +3706,13 @@
         <v>26</v>
       </c>
       <c r="J87" t="n">
-        <v>-284.24</v>
+        <v>-204.68</v>
       </c>
       <c r="K87" t="n">
-        <v>-90.68000000000001</v>
+        <v>-65.3</v>
       </c>
       <c r="L87" t="n">
-        <v>298.35</v>
+        <v>214.84</v>
       </c>
     </row>
     <row r="88">
@@ -3748,13 +3748,13 @@
         <v>21</v>
       </c>
       <c r="J88" t="n">
-        <v>-198.61</v>
+        <v>-148.96</v>
       </c>
       <c r="K88" t="n">
-        <v>-65.94</v>
+        <v>-49.45</v>
       </c>
       <c r="L88" t="n">
-        <v>209.27</v>
+        <v>156.95</v>
       </c>
     </row>
   </sheetData>

--- a/output/2024-07-26.xlsx
+++ b/output/2024-07-26.xlsx
@@ -640,13 +640,13 @@
         <v>27</v>
       </c>
       <c r="J14" t="n">
-        <v>26.33</v>
+        <v>27.26</v>
       </c>
       <c r="K14" t="n">
-        <v>26.89</v>
+        <v>27.83</v>
       </c>
       <c r="L14" t="n">
-        <v>37.64</v>
+        <v>38.96</v>
       </c>
     </row>
     <row r="15">
@@ -682,13 +682,13 @@
         <v>25</v>
       </c>
       <c r="J15" t="n">
-        <v>20.11</v>
+        <v>21.78</v>
       </c>
       <c r="K15" t="n">
-        <v>-16.14</v>
+        <v>-17.49</v>
       </c>
       <c r="L15" t="n">
-        <v>25.79</v>
+        <v>27.94</v>
       </c>
     </row>
     <row r="16">
@@ -724,13 +724,13 @@
         <v>23</v>
       </c>
       <c r="J16" t="n">
-        <v>-12.48</v>
+        <v>-13.1</v>
       </c>
       <c r="K16" t="n">
-        <v>29.83</v>
+        <v>31.3</v>
       </c>
       <c r="L16" t="n">
-        <v>32.34</v>
+        <v>33.93</v>
       </c>
     </row>
     <row r="17">
@@ -766,13 +766,13 @@
         <v>22</v>
       </c>
       <c r="J17" t="n">
-        <v>-42.41</v>
+        <v>-43.11</v>
       </c>
       <c r="K17" t="n">
-        <v>36.98</v>
+        <v>37.59</v>
       </c>
       <c r="L17" t="n">
-        <v>56.26</v>
+        <v>57.2</v>
       </c>
     </row>
     <row r="18">
@@ -808,13 +808,13 @@
         <v>22</v>
       </c>
       <c r="J18" t="n">
-        <v>38.44</v>
+        <v>41.28</v>
       </c>
       <c r="K18" t="n">
-        <v>7.24</v>
+        <v>7.78</v>
       </c>
       <c r="L18" t="n">
-        <v>39.12</v>
+        <v>42</v>
       </c>
     </row>
     <row r="19">
@@ -850,13 +850,13 @@
         <v>25</v>
       </c>
       <c r="J19" t="n">
-        <v>72.97</v>
+        <v>71.25</v>
       </c>
       <c r="K19" t="n">
-        <v>-6.27</v>
+        <v>-6.12</v>
       </c>
       <c r="L19" t="n">
-        <v>73.23</v>
+        <v>71.51000000000001</v>
       </c>
     </row>
     <row r="20">
@@ -892,13 +892,13 @@
         <v>22</v>
       </c>
       <c r="J20" t="n">
-        <v>-17.99</v>
+        <v>-18.35</v>
       </c>
       <c r="K20" t="n">
-        <v>76.14</v>
+        <v>77.68000000000001</v>
       </c>
       <c r="L20" t="n">
-        <v>78.23</v>
+        <v>79.81999999999999</v>
       </c>
     </row>
     <row r="21">
@@ -934,13 +934,13 @@
         <v>24</v>
       </c>
       <c r="J21" t="n">
-        <v>-121.7</v>
+        <v>-118.34</v>
       </c>
       <c r="K21" t="n">
-        <v>-8.140000000000001</v>
+        <v>-7.91</v>
       </c>
       <c r="L21" t="n">
-        <v>121.97</v>
+        <v>118.61</v>
       </c>
     </row>
     <row r="22">
@@ -976,13 +976,13 @@
         <v>21</v>
       </c>
       <c r="J22" t="n">
-        <v>112.42</v>
+        <v>110.12</v>
       </c>
       <c r="K22" t="n">
-        <v>36.97</v>
+        <v>36.21</v>
       </c>
       <c r="L22" t="n">
-        <v>118.34</v>
+        <v>115.92</v>
       </c>
     </row>
     <row r="23">
@@ -1018,13 +1018,13 @@
         <v>23</v>
       </c>
       <c r="J23" t="n">
-        <v>-148.77</v>
+        <v>-142.9</v>
       </c>
       <c r="K23" t="n">
-        <v>-94.75</v>
+        <v>-91.01000000000001</v>
       </c>
       <c r="L23" t="n">
-        <v>176.38</v>
+        <v>169.42</v>
       </c>
     </row>
     <row r="24">
@@ -1060,13 +1060,13 @@
         <v>23</v>
       </c>
       <c r="J24" t="n">
-        <v>-74.22</v>
+        <v>-78.83</v>
       </c>
       <c r="K24" t="n">
-        <v>-28.72</v>
+        <v>-30.5</v>
       </c>
       <c r="L24" t="n">
-        <v>79.58</v>
+        <v>84.53</v>
       </c>
     </row>
     <row r="25">
@@ -1102,13 +1102,13 @@
         <v>27</v>
       </c>
       <c r="J25" t="n">
-        <v>42.99</v>
+        <v>43.61</v>
       </c>
       <c r="K25" t="n">
-        <v>-90.08</v>
+        <v>-91.38</v>
       </c>
       <c r="L25" t="n">
-        <v>99.81999999999999</v>
+        <v>101.25</v>
       </c>
     </row>
     <row r="26">
@@ -1144,13 +1144,13 @@
         <v>22</v>
       </c>
       <c r="J26" t="n">
-        <v>17.94</v>
+        <v>19.62</v>
       </c>
       <c r="K26" t="n">
-        <v>-106.2</v>
+        <v>-116.12</v>
       </c>
       <c r="L26" t="n">
-        <v>107.71</v>
+        <v>117.76</v>
       </c>
     </row>
     <row r="27">
@@ -1186,13 +1186,13 @@
         <v>25</v>
       </c>
       <c r="J27" t="n">
-        <v>108.49</v>
+        <v>114.11</v>
       </c>
       <c r="K27" t="n">
-        <v>-59.85</v>
+        <v>-62.96</v>
       </c>
       <c r="L27" t="n">
-        <v>123.9</v>
+        <v>130.32</v>
       </c>
     </row>
     <row r="28">
@@ -1228,13 +1228,13 @@
         <v>21</v>
       </c>
       <c r="J28" t="n">
-        <v>-359.41</v>
+        <v>-338.72</v>
       </c>
       <c r="K28" t="n">
-        <v>-33.32</v>
+        <v>-31.4</v>
       </c>
       <c r="L28" t="n">
-        <v>360.95</v>
+        <v>340.17</v>
       </c>
     </row>
     <row r="29">
@@ -1270,13 +1270,13 @@
         <v>24</v>
       </c>
       <c r="J29" t="n">
-        <v>34</v>
+        <v>34.55</v>
       </c>
       <c r="K29" t="n">
-        <v>17.67</v>
+        <v>17.96</v>
       </c>
       <c r="L29" t="n">
-        <v>38.31</v>
+        <v>38.94</v>
       </c>
     </row>
     <row r="30">
@@ -1312,13 +1312,13 @@
         <v>23</v>
       </c>
       <c r="J30" t="n">
-        <v>-44.18</v>
+        <v>-43.02</v>
       </c>
       <c r="K30" t="n">
-        <v>38.29</v>
+        <v>37.28</v>
       </c>
       <c r="L30" t="n">
-        <v>58.47</v>
+        <v>56.93</v>
       </c>
     </row>
     <row r="31">
@@ -1354,13 +1354,13 @@
         <v>21</v>
       </c>
       <c r="J31" t="n">
-        <v>-2.16</v>
+        <v>-2.32</v>
       </c>
       <c r="K31" t="n">
-        <v>-28.83</v>
+        <v>-30.99</v>
       </c>
       <c r="L31" t="n">
-        <v>28.91</v>
+        <v>31.08</v>
       </c>
     </row>
     <row r="32">
@@ -1396,13 +1396,13 @@
         <v>27</v>
       </c>
       <c r="J32" t="n">
-        <v>36.19</v>
+        <v>37.89</v>
       </c>
       <c r="K32" t="n">
-        <v>26.74</v>
+        <v>28</v>
       </c>
       <c r="L32" t="n">
-        <v>45</v>
+        <v>47.11</v>
       </c>
     </row>
     <row r="33">
@@ -1438,13 +1438,13 @@
         <v>25</v>
       </c>
       <c r="J33" t="n">
-        <v>30.94</v>
+        <v>31.78</v>
       </c>
       <c r="K33" t="n">
-        <v>41.41</v>
+        <v>42.53</v>
       </c>
       <c r="L33" t="n">
-        <v>51.69</v>
+        <v>53.09</v>
       </c>
     </row>
     <row r="34">
@@ -1480,13 +1480,13 @@
         <v>26</v>
       </c>
       <c r="J34" t="n">
-        <v>-56.27</v>
+        <v>-54.54</v>
       </c>
       <c r="K34" t="n">
-        <v>64.33</v>
+        <v>62.35</v>
       </c>
       <c r="L34" t="n">
-        <v>85.47</v>
+        <v>82.84</v>
       </c>
     </row>
     <row r="35">
@@ -1522,13 +1522,13 @@
         <v>22</v>
       </c>
       <c r="J35" t="n">
-        <v>85.06</v>
+        <v>85.64</v>
       </c>
       <c r="K35" t="n">
-        <v>32.75</v>
+        <v>32.97</v>
       </c>
       <c r="L35" t="n">
-        <v>91.15000000000001</v>
+        <v>91.76000000000001</v>
       </c>
     </row>
     <row r="36">
@@ -1564,13 +1564,13 @@
         <v>25</v>
       </c>
       <c r="J36" t="n">
-        <v>99.59999999999999</v>
+        <v>95.75</v>
       </c>
       <c r="K36" t="n">
-        <v>77.42</v>
+        <v>74.42</v>
       </c>
       <c r="L36" t="n">
-        <v>126.15</v>
+        <v>121.27</v>
       </c>
     </row>
     <row r="37">
@@ -1606,13 +1606,13 @@
         <v>23</v>
       </c>
       <c r="J37" t="n">
-        <v>61.66</v>
+        <v>58.75</v>
       </c>
       <c r="K37" t="n">
-        <v>-147.04</v>
+        <v>-140.1</v>
       </c>
       <c r="L37" t="n">
-        <v>159.44</v>
+        <v>151.92</v>
       </c>
     </row>
     <row r="38">
@@ -1648,13 +1648,13 @@
         <v>23</v>
       </c>
       <c r="J38" t="n">
-        <v>94.16</v>
+        <v>89.59</v>
       </c>
       <c r="K38" t="n">
-        <v>172.59</v>
+        <v>164.21</v>
       </c>
       <c r="L38" t="n">
-        <v>196.61</v>
+        <v>187.05</v>
       </c>
     </row>
     <row r="39">
@@ -1690,13 +1690,13 @@
         <v>24</v>
       </c>
       <c r="J39" t="n">
-        <v>-90.19</v>
+        <v>-91.14</v>
       </c>
       <c r="K39" t="n">
-        <v>68.98</v>
+        <v>69.7</v>
       </c>
       <c r="L39" t="n">
-        <v>113.55</v>
+        <v>114.74</v>
       </c>
     </row>
     <row r="40">
@@ -1732,13 +1732,13 @@
         <v>25</v>
       </c>
       <c r="J40" t="n">
-        <v>-40.12</v>
+        <v>-40.47</v>
       </c>
       <c r="K40" t="n">
-        <v>102.65</v>
+        <v>103.52</v>
       </c>
       <c r="L40" t="n">
-        <v>110.21</v>
+        <v>111.15</v>
       </c>
     </row>
     <row r="41">
@@ -1774,13 +1774,13 @@
         <v>23</v>
       </c>
       <c r="J41" t="n">
-        <v>-74.61</v>
+        <v>-76.94</v>
       </c>
       <c r="K41" t="n">
-        <v>124.51</v>
+        <v>128.4</v>
       </c>
       <c r="L41" t="n">
-        <v>145.15</v>
+        <v>149.69</v>
       </c>
     </row>
     <row r="42">
@@ -1816,13 +1816,13 @@
         <v>21</v>
       </c>
       <c r="J42" t="n">
-        <v>94.53</v>
+        <v>100.81</v>
       </c>
       <c r="K42" t="n">
-        <v>73.63</v>
+        <v>78.52</v>
       </c>
       <c r="L42" t="n">
-        <v>119.82</v>
+        <v>127.78</v>
       </c>
     </row>
     <row r="43">
@@ -1858,13 +1858,13 @@
         <v>22</v>
       </c>
       <c r="J43" t="n">
-        <v>129.83</v>
+        <v>128.25</v>
       </c>
       <c r="K43" t="n">
-        <v>-154.17</v>
+        <v>-152.29</v>
       </c>
       <c r="L43" t="n">
-        <v>201.55</v>
+        <v>199.1</v>
       </c>
     </row>
     <row r="44">
@@ -1900,13 +1900,13 @@
         <v>27</v>
       </c>
       <c r="J44" t="n">
-        <v>-12.34</v>
+        <v>-12.46</v>
       </c>
       <c r="K44" t="n">
-        <v>38.87</v>
+        <v>39.26</v>
       </c>
       <c r="L44" t="n">
-        <v>40.78</v>
+        <v>41.19</v>
       </c>
     </row>
     <row r="45">
@@ -1942,13 +1942,13 @@
         <v>26</v>
       </c>
       <c r="J45" t="n">
-        <v>39.26</v>
+        <v>39.91</v>
       </c>
       <c r="K45" t="n">
-        <v>-2.2</v>
+        <v>-2.24</v>
       </c>
       <c r="L45" t="n">
-        <v>39.32</v>
+        <v>39.97</v>
       </c>
     </row>
     <row r="46">
@@ -1984,13 +1984,13 @@
         <v>23</v>
       </c>
       <c r="J46" t="n">
-        <v>29.48</v>
+        <v>31.27</v>
       </c>
       <c r="K46" t="n">
-        <v>-4.77</v>
+        <v>-5.06</v>
       </c>
       <c r="L46" t="n">
-        <v>29.86</v>
+        <v>31.67</v>
       </c>
     </row>
     <row r="47">
@@ -2026,13 +2026,13 @@
         <v>23</v>
       </c>
       <c r="J47" t="n">
-        <v>-22.97</v>
+        <v>-24.22</v>
       </c>
       <c r="K47" t="n">
-        <v>37.6</v>
+        <v>39.64</v>
       </c>
       <c r="L47" t="n">
-        <v>44.06</v>
+        <v>46.45</v>
       </c>
     </row>
     <row r="48">
@@ -2068,13 +2068,13 @@
         <v>21</v>
       </c>
       <c r="J48" t="n">
-        <v>-38.41</v>
+        <v>-36.98</v>
       </c>
       <c r="K48" t="n">
-        <v>99.48999999999999</v>
+        <v>95.79000000000001</v>
       </c>
       <c r="L48" t="n">
-        <v>106.64</v>
+        <v>102.68</v>
       </c>
     </row>
     <row r="49">
@@ -2110,13 +2110,13 @@
         <v>22</v>
       </c>
       <c r="J49" t="n">
-        <v>80.63</v>
+        <v>78.81</v>
       </c>
       <c r="K49" t="n">
-        <v>34.47</v>
+        <v>33.69</v>
       </c>
       <c r="L49" t="n">
-        <v>87.69</v>
+        <v>85.70999999999999</v>
       </c>
     </row>
     <row r="50">
@@ -2152,13 +2152,13 @@
         <v>25</v>
       </c>
       <c r="J50" t="n">
-        <v>21.19</v>
+        <v>22.26</v>
       </c>
       <c r="K50" t="n">
-        <v>-61.86</v>
+        <v>-64.98</v>
       </c>
       <c r="L50" t="n">
-        <v>65.38</v>
+        <v>68.69</v>
       </c>
     </row>
     <row r="51">
@@ -2194,13 +2194,13 @@
         <v>24</v>
       </c>
       <c r="J51" t="n">
-        <v>-49.45</v>
+        <v>-46.55</v>
       </c>
       <c r="K51" t="n">
-        <v>98.87</v>
+        <v>93.06999999999999</v>
       </c>
       <c r="L51" t="n">
-        <v>110.55</v>
+        <v>104.06</v>
       </c>
     </row>
     <row r="52">
@@ -2236,13 +2236,13 @@
         <v>21</v>
       </c>
       <c r="J52" t="n">
-        <v>58.83</v>
+        <v>63.14</v>
       </c>
       <c r="K52" t="n">
-        <v>-8.869999999999999</v>
+        <v>-9.52</v>
       </c>
       <c r="L52" t="n">
-        <v>59.5</v>
+        <v>63.85</v>
       </c>
     </row>
     <row r="53">
@@ -2278,13 +2278,13 @@
         <v>23</v>
       </c>
       <c r="J53" t="n">
-        <v>-10.89</v>
+        <v>-10.96</v>
       </c>
       <c r="K53" t="n">
-        <v>126.04</v>
+        <v>126.76</v>
       </c>
       <c r="L53" t="n">
-        <v>126.51</v>
+        <v>127.23</v>
       </c>
     </row>
     <row r="54">
@@ -2320,13 +2320,13 @@
         <v>23</v>
       </c>
       <c r="J54" t="n">
-        <v>147.16</v>
+        <v>143.25</v>
       </c>
       <c r="K54" t="n">
-        <v>61.64</v>
+        <v>60</v>
       </c>
       <c r="L54" t="n">
-        <v>159.55</v>
+        <v>155.3</v>
       </c>
     </row>
     <row r="55">
@@ -2362,13 +2362,13 @@
         <v>21</v>
       </c>
       <c r="J55" t="n">
-        <v>192.31</v>
+        <v>185.43</v>
       </c>
       <c r="K55" t="n">
-        <v>-15.32</v>
+        <v>-14.77</v>
       </c>
       <c r="L55" t="n">
-        <v>192.92</v>
+        <v>186.01</v>
       </c>
     </row>
     <row r="56">
@@ -2404,13 +2404,13 @@
         <v>24</v>
       </c>
       <c r="J56" t="n">
-        <v>6.71</v>
+        <v>6.88</v>
       </c>
       <c r="K56" t="n">
-        <v>146.57</v>
+        <v>150.25</v>
       </c>
       <c r="L56" t="n">
-        <v>146.73</v>
+        <v>150.41</v>
       </c>
     </row>
     <row r="57">
@@ -2446,13 +2446,13 @@
         <v>24</v>
       </c>
       <c r="J57" t="n">
-        <v>152.22</v>
+        <v>156.27</v>
       </c>
       <c r="K57" t="n">
-        <v>6.72</v>
+        <v>6.9</v>
       </c>
       <c r="L57" t="n">
-        <v>152.37</v>
+        <v>156.42</v>
       </c>
     </row>
     <row r="58">
@@ -2488,13 +2488,13 @@
         <v>23</v>
       </c>
       <c r="J58" t="n">
-        <v>35.97</v>
+        <v>35.22</v>
       </c>
       <c r="K58" t="n">
-        <v>-33.99</v>
+        <v>-33.28</v>
       </c>
       <c r="L58" t="n">
-        <v>49.49</v>
+        <v>48.46</v>
       </c>
     </row>
     <row r="59">
@@ -2530,13 +2530,13 @@
         <v>24</v>
       </c>
       <c r="J59" t="n">
-        <v>4.13</v>
+        <v>4.06</v>
       </c>
       <c r="K59" t="n">
-        <v>59.24</v>
+        <v>58.3</v>
       </c>
       <c r="L59" t="n">
-        <v>59.38</v>
+        <v>58.44</v>
       </c>
     </row>
     <row r="60">
@@ -2572,13 +2572,13 @@
         <v>22</v>
       </c>
       <c r="J60" t="n">
-        <v>-35.79</v>
+        <v>-36.84</v>
       </c>
       <c r="K60" t="n">
-        <v>23.91</v>
+        <v>24.61</v>
       </c>
       <c r="L60" t="n">
-        <v>43.04</v>
+        <v>44.3</v>
       </c>
     </row>
     <row r="61">
@@ -2614,13 +2614,13 @@
         <v>21</v>
       </c>
       <c r="J61" t="n">
-        <v>-46.08</v>
+        <v>-45.15</v>
       </c>
       <c r="K61" t="n">
-        <v>39.79</v>
+        <v>38.98</v>
       </c>
       <c r="L61" t="n">
-        <v>60.88</v>
+        <v>59.65</v>
       </c>
     </row>
     <row r="62">
@@ -2656,13 +2656,13 @@
         <v>21</v>
       </c>
       <c r="J62" t="n">
-        <v>33.26</v>
+        <v>32.98</v>
       </c>
       <c r="K62" t="n">
-        <v>66.75</v>
+        <v>66.19</v>
       </c>
       <c r="L62" t="n">
-        <v>74.58</v>
+        <v>73.95</v>
       </c>
     </row>
     <row r="63">
@@ -2698,13 +2698,13 @@
         <v>26</v>
       </c>
       <c r="J63" t="n">
-        <v>63.25</v>
+        <v>62.72</v>
       </c>
       <c r="K63" t="n">
-        <v>25.41</v>
+        <v>25.2</v>
       </c>
       <c r="L63" t="n">
-        <v>68.16</v>
+        <v>67.59</v>
       </c>
     </row>
     <row r="64">
@@ -2740,13 +2740,13 @@
         <v>22</v>
       </c>
       <c r="J64" t="n">
-        <v>81.53</v>
+        <v>75.09</v>
       </c>
       <c r="K64" t="n">
-        <v>-61.31</v>
+        <v>-56.47</v>
       </c>
       <c r="L64" t="n">
-        <v>102.01</v>
+        <v>93.95999999999999</v>
       </c>
     </row>
     <row r="65">
@@ -2782,13 +2782,13 @@
         <v>23</v>
       </c>
       <c r="J65" t="n">
-        <v>127.12</v>
+        <v>121.49</v>
       </c>
       <c r="K65" t="n">
-        <v>-107.93</v>
+        <v>-103.14</v>
       </c>
       <c r="L65" t="n">
-        <v>166.76</v>
+        <v>159.37</v>
       </c>
     </row>
     <row r="66">
@@ -2824,13 +2824,13 @@
         <v>26</v>
       </c>
       <c r="J66" t="n">
-        <v>-9.9</v>
+        <v>-10.62</v>
       </c>
       <c r="K66" t="n">
-        <v>55.47</v>
+        <v>59.46</v>
       </c>
       <c r="L66" t="n">
-        <v>56.35</v>
+        <v>60.4</v>
       </c>
     </row>
     <row r="67">
@@ -2866,13 +2866,13 @@
         <v>23</v>
       </c>
       <c r="J67" t="n">
-        <v>-29.46</v>
+        <v>-28.78</v>
       </c>
       <c r="K67" t="n">
-        <v>30.32</v>
+        <v>29.62</v>
       </c>
       <c r="L67" t="n">
-        <v>42.28</v>
+        <v>41.3</v>
       </c>
     </row>
     <row r="68">
@@ -2908,13 +2908,13 @@
         <v>21</v>
       </c>
       <c r="J68" t="n">
-        <v>67.77</v>
+        <v>68.02</v>
       </c>
       <c r="K68" t="n">
-        <v>114.7</v>
+        <v>115.11</v>
       </c>
       <c r="L68" t="n">
-        <v>133.22</v>
+        <v>133.71</v>
       </c>
     </row>
     <row r="69">
@@ -2950,13 +2950,13 @@
         <v>27</v>
       </c>
       <c r="J69" t="n">
-        <v>62.75</v>
+        <v>60.61</v>
       </c>
       <c r="K69" t="n">
-        <v>157.66</v>
+        <v>152.3</v>
       </c>
       <c r="L69" t="n">
-        <v>169.69</v>
+        <v>163.92</v>
       </c>
     </row>
     <row r="70">
@@ -2992,13 +2992,13 @@
         <v>26</v>
       </c>
       <c r="J70" t="n">
-        <v>109.42</v>
+        <v>107.09</v>
       </c>
       <c r="K70" t="n">
-        <v>113.99</v>
+        <v>111.56</v>
       </c>
       <c r="L70" t="n">
-        <v>158.01</v>
+        <v>154.65</v>
       </c>
     </row>
     <row r="71">
@@ -3034,13 +3034,13 @@
         <v>25</v>
       </c>
       <c r="J71" t="n">
-        <v>-4.88</v>
+        <v>-4.95</v>
       </c>
       <c r="K71" t="n">
-        <v>-286.2</v>
+        <v>-289.92</v>
       </c>
       <c r="L71" t="n">
-        <v>286.24</v>
+        <v>289.97</v>
       </c>
     </row>
     <row r="72">
@@ -3076,13 +3076,13 @@
         <v>21</v>
       </c>
       <c r="J72" t="n">
-        <v>-6.37</v>
+        <v>-6.17</v>
       </c>
       <c r="K72" t="n">
-        <v>270.54</v>
+        <v>262</v>
       </c>
       <c r="L72" t="n">
-        <v>270.61</v>
+        <v>262.08</v>
       </c>
     </row>
     <row r="73">
@@ -3118,13 +3118,13 @@
         <v>27</v>
       </c>
       <c r="J73" t="n">
-        <v>75</v>
+        <v>76.72</v>
       </c>
       <c r="K73" t="n">
-        <v>-129.34</v>
+        <v>-132.3</v>
       </c>
       <c r="L73" t="n">
-        <v>149.51</v>
+        <v>152.93</v>
       </c>
     </row>
     <row r="74">
@@ -3160,13 +3160,13 @@
         <v>27</v>
       </c>
       <c r="J74" t="n">
-        <v>-57.25</v>
+        <v>-54.59</v>
       </c>
       <c r="K74" t="n">
-        <v>-26.96</v>
+        <v>-25.7</v>
       </c>
       <c r="L74" t="n">
-        <v>63.28</v>
+        <v>60.34</v>
       </c>
     </row>
     <row r="75">
@@ -3202,13 +3202,13 @@
         <v>23</v>
       </c>
       <c r="J75" t="n">
-        <v>15.64</v>
+        <v>16.81</v>
       </c>
       <c r="K75" t="n">
-        <v>-27</v>
+        <v>-29.02</v>
       </c>
       <c r="L75" t="n">
-        <v>31.2</v>
+        <v>33.53</v>
       </c>
     </row>
     <row r="76">
@@ -3244,13 +3244,13 @@
         <v>22</v>
       </c>
       <c r="J76" t="n">
-        <v>-46.16</v>
+        <v>-45.03</v>
       </c>
       <c r="K76" t="n">
-        <v>35.64</v>
+        <v>34.77</v>
       </c>
       <c r="L76" t="n">
-        <v>58.32</v>
+        <v>56.89</v>
       </c>
     </row>
     <row r="77">
@@ -3286,13 +3286,13 @@
         <v>22</v>
       </c>
       <c r="J77" t="n">
-        <v>-38.33</v>
+        <v>-37.95</v>
       </c>
       <c r="K77" t="n">
-        <v>65.16</v>
+        <v>64.51000000000001</v>
       </c>
       <c r="L77" t="n">
-        <v>75.59999999999999</v>
+        <v>74.84</v>
       </c>
     </row>
     <row r="78">
@@ -3328,13 +3328,13 @@
         <v>25</v>
       </c>
       <c r="J78" t="n">
-        <v>31.96</v>
+        <v>33.74</v>
       </c>
       <c r="K78" t="n">
-        <v>-28.29</v>
+        <v>-29.86</v>
       </c>
       <c r="L78" t="n">
-        <v>42.68</v>
+        <v>45.06</v>
       </c>
     </row>
     <row r="79">
@@ -3370,13 +3370,13 @@
         <v>25</v>
       </c>
       <c r="J79" t="n">
-        <v>68.92</v>
+        <v>67.22</v>
       </c>
       <c r="K79" t="n">
-        <v>46.92</v>
+        <v>45.77</v>
       </c>
       <c r="L79" t="n">
-        <v>83.38</v>
+        <v>81.31999999999999</v>
       </c>
     </row>
     <row r="80">
@@ -3412,13 +3412,13 @@
         <v>27</v>
       </c>
       <c r="J80" t="n">
-        <v>-50.22</v>
+        <v>-53.11</v>
       </c>
       <c r="K80" t="n">
-        <v>-32.39</v>
+        <v>-34.25</v>
       </c>
       <c r="L80" t="n">
-        <v>59.76</v>
+        <v>63.2</v>
       </c>
     </row>
     <row r="81">
@@ -3454,13 +3454,13 @@
         <v>21</v>
       </c>
       <c r="J81" t="n">
-        <v>-74.84</v>
+        <v>-76.95999999999999</v>
       </c>
       <c r="K81" t="n">
-        <v>25.54</v>
+        <v>26.27</v>
       </c>
       <c r="L81" t="n">
-        <v>79.06999999999999</v>
+        <v>81.31999999999999</v>
       </c>
     </row>
     <row r="82">
@@ -3496,13 +3496,13 @@
         <v>22</v>
       </c>
       <c r="J82" t="n">
-        <v>-3.22</v>
+        <v>-3.53</v>
       </c>
       <c r="K82" t="n">
-        <v>54.93</v>
+        <v>60.13</v>
       </c>
       <c r="L82" t="n">
-        <v>55.03</v>
+        <v>60.24</v>
       </c>
     </row>
     <row r="83">
@@ -3538,13 +3538,13 @@
         <v>25</v>
       </c>
       <c r="J83" t="n">
-        <v>172.6</v>
+        <v>166.03</v>
       </c>
       <c r="K83" t="n">
-        <v>15.65</v>
+        <v>15.06</v>
       </c>
       <c r="L83" t="n">
-        <v>173.31</v>
+        <v>166.71</v>
       </c>
     </row>
     <row r="84">
@@ -3580,13 +3580,13 @@
         <v>21</v>
       </c>
       <c r="J84" t="n">
-        <v>-13.03</v>
+        <v>-13.29</v>
       </c>
       <c r="K84" t="n">
-        <v>113.14</v>
+        <v>115.46</v>
       </c>
       <c r="L84" t="n">
-        <v>113.89</v>
+        <v>116.22</v>
       </c>
     </row>
     <row r="85">
@@ -3622,13 +3622,13 @@
         <v>22</v>
       </c>
       <c r="J85" t="n">
-        <v>-46.69</v>
+        <v>-44.48</v>
       </c>
       <c r="K85" t="n">
-        <v>-200.74</v>
+        <v>-191.25</v>
       </c>
       <c r="L85" t="n">
-        <v>206.09</v>
+        <v>196.35</v>
       </c>
     </row>
     <row r="86">
@@ -3664,13 +3664,13 @@
         <v>23</v>
       </c>
       <c r="J86" t="n">
-        <v>-280.53</v>
+        <v>-268.43</v>
       </c>
       <c r="K86" t="n">
-        <v>78.51000000000001</v>
+        <v>75.12</v>
       </c>
       <c r="L86" t="n">
-        <v>291.31</v>
+        <v>278.74</v>
       </c>
     </row>
     <row r="87">
@@ -3706,13 +3706,13 @@
         <v>26</v>
       </c>
       <c r="J87" t="n">
-        <v>-204.68</v>
+        <v>-199.71</v>
       </c>
       <c r="K87" t="n">
-        <v>-65.3</v>
+        <v>-63.71</v>
       </c>
       <c r="L87" t="n">
-        <v>214.84</v>
+        <v>209.62</v>
       </c>
     </row>
     <row r="88">
@@ -3748,13 +3748,13 @@
         <v>21</v>
       </c>
       <c r="J88" t="n">
-        <v>-148.96</v>
+        <v>-152.28</v>
       </c>
       <c r="K88" t="n">
-        <v>-49.45</v>
+        <v>-50.55</v>
       </c>
       <c r="L88" t="n">
-        <v>156.95</v>
+        <v>160.45</v>
       </c>
     </row>
   </sheetData>

--- a/output/2024-07-26.xlsx
+++ b/output/2024-07-26.xlsx
@@ -640,13 +640,13 @@
         <v>27</v>
       </c>
       <c r="J14" t="n">
-        <v>27.26</v>
+        <v>28.31</v>
       </c>
       <c r="K14" t="n">
-        <v>27.83</v>
+        <v>28.91</v>
       </c>
       <c r="L14" t="n">
-        <v>38.96</v>
+        <v>40.46</v>
       </c>
     </row>
     <row r="15">
@@ -682,13 +682,13 @@
         <v>25</v>
       </c>
       <c r="J15" t="n">
-        <v>21.78</v>
+        <v>23.7</v>
       </c>
       <c r="K15" t="n">
-        <v>-17.49</v>
+        <v>-19.03</v>
       </c>
       <c r="L15" t="n">
-        <v>27.94</v>
+        <v>30.4</v>
       </c>
     </row>
     <row r="16">
@@ -724,13 +724,13 @@
         <v>23</v>
       </c>
       <c r="J16" t="n">
-        <v>-13.1</v>
+        <v>-13.81</v>
       </c>
       <c r="K16" t="n">
-        <v>31.3</v>
+        <v>32.99</v>
       </c>
       <c r="L16" t="n">
-        <v>33.93</v>
+        <v>35.76</v>
       </c>
     </row>
     <row r="17">
@@ -766,13 +766,13 @@
         <v>22</v>
       </c>
       <c r="J17" t="n">
-        <v>-43.11</v>
+        <v>-43.92</v>
       </c>
       <c r="K17" t="n">
-        <v>37.59</v>
+        <v>38.29</v>
       </c>
       <c r="L17" t="n">
-        <v>57.2</v>
+        <v>58.27</v>
       </c>
     </row>
     <row r="18">
@@ -808,13 +808,13 @@
         <v>22</v>
       </c>
       <c r="J18" t="n">
-        <v>41.28</v>
+        <v>44.52</v>
       </c>
       <c r="K18" t="n">
-        <v>7.78</v>
+        <v>8.390000000000001</v>
       </c>
       <c r="L18" t="n">
-        <v>42</v>
+        <v>45.31</v>
       </c>
     </row>
     <row r="19">
@@ -850,13 +850,13 @@
         <v>25</v>
       </c>
       <c r="J19" t="n">
-        <v>71.25</v>
+        <v>69.28</v>
       </c>
       <c r="K19" t="n">
-        <v>-6.12</v>
+        <v>-5.95</v>
       </c>
       <c r="L19" t="n">
-        <v>71.51000000000001</v>
+        <v>69.53</v>
       </c>
     </row>
     <row r="20">
@@ -892,13 +892,13 @@
         <v>22</v>
       </c>
       <c r="J20" t="n">
-        <v>-18.35</v>
+        <v>-18.77</v>
       </c>
       <c r="K20" t="n">
-        <v>77.68000000000001</v>
+        <v>79.45</v>
       </c>
       <c r="L20" t="n">
-        <v>79.81999999999999</v>
+        <v>81.63</v>
       </c>
     </row>
     <row r="21">
@@ -934,13 +934,13 @@
         <v>24</v>
       </c>
       <c r="J21" t="n">
-        <v>-118.34</v>
+        <v>-114.51</v>
       </c>
       <c r="K21" t="n">
-        <v>-7.91</v>
+        <v>-7.65</v>
       </c>
       <c r="L21" t="n">
-        <v>118.61</v>
+        <v>114.76</v>
       </c>
     </row>
     <row r="22">
@@ -976,13 +976,13 @@
         <v>21</v>
       </c>
       <c r="J22" t="n">
-        <v>110.12</v>
+        <v>107.49</v>
       </c>
       <c r="K22" t="n">
-        <v>36.21</v>
+        <v>35.35</v>
       </c>
       <c r="L22" t="n">
-        <v>115.92</v>
+        <v>113.15</v>
       </c>
     </row>
     <row r="23">
@@ -1018,13 +1018,13 @@
         <v>23</v>
       </c>
       <c r="J23" t="n">
-        <v>-142.9</v>
+        <v>-136.2</v>
       </c>
       <c r="K23" t="n">
-        <v>-91.01000000000001</v>
+        <v>-86.73999999999999</v>
       </c>
       <c r="L23" t="n">
-        <v>169.42</v>
+        <v>161.47</v>
       </c>
     </row>
     <row r="24">
@@ -1060,13 +1060,13 @@
         <v>23</v>
       </c>
       <c r="J24" t="n">
-        <v>-78.83</v>
+        <v>-84.09999999999999</v>
       </c>
       <c r="K24" t="n">
-        <v>-30.5</v>
+        <v>-32.54</v>
       </c>
       <c r="L24" t="n">
-        <v>84.53</v>
+        <v>90.18000000000001</v>
       </c>
     </row>
     <row r="25">
@@ -1102,13 +1102,13 @@
         <v>27</v>
       </c>
       <c r="J25" t="n">
-        <v>43.61</v>
+        <v>44.32</v>
       </c>
       <c r="K25" t="n">
-        <v>-91.38</v>
+        <v>-92.84999999999999</v>
       </c>
       <c r="L25" t="n">
-        <v>101.25</v>
+        <v>102.89</v>
       </c>
     </row>
     <row r="26">
@@ -1144,13 +1144,13 @@
         <v>22</v>
       </c>
       <c r="J26" t="n">
-        <v>19.62</v>
+        <v>21.53</v>
       </c>
       <c r="K26" t="n">
-        <v>-116.12</v>
+        <v>-127.45</v>
       </c>
       <c r="L26" t="n">
-        <v>117.76</v>
+        <v>129.26</v>
       </c>
     </row>
     <row r="27">
@@ -1186,13 +1186,13 @@
         <v>25</v>
       </c>
       <c r="J27" t="n">
-        <v>114.11</v>
+        <v>120.54</v>
       </c>
       <c r="K27" t="n">
-        <v>-62.96</v>
+        <v>-66.5</v>
       </c>
       <c r="L27" t="n">
-        <v>130.32</v>
+        <v>137.66</v>
       </c>
     </row>
     <row r="28">
@@ -1228,13 +1228,13 @@
         <v>21</v>
       </c>
       <c r="J28" t="n">
-        <v>-338.72</v>
+        <v>-315.08</v>
       </c>
       <c r="K28" t="n">
-        <v>-31.4</v>
+        <v>-29.21</v>
       </c>
       <c r="L28" t="n">
-        <v>340.17</v>
+        <v>316.43</v>
       </c>
     </row>
     <row r="29">
@@ -1270,13 +1270,13 @@
         <v>24</v>
       </c>
       <c r="J29" t="n">
-        <v>34.55</v>
+        <v>35.19</v>
       </c>
       <c r="K29" t="n">
-        <v>17.96</v>
+        <v>18.29</v>
       </c>
       <c r="L29" t="n">
-        <v>38.94</v>
+        <v>39.66</v>
       </c>
     </row>
     <row r="30">
@@ -1312,13 +1312,13 @@
         <v>23</v>
       </c>
       <c r="J30" t="n">
-        <v>-43.02</v>
+        <v>-41.7</v>
       </c>
       <c r="K30" t="n">
-        <v>37.28</v>
+        <v>36.14</v>
       </c>
       <c r="L30" t="n">
-        <v>56.93</v>
+        <v>55.18</v>
       </c>
     </row>
     <row r="31">
@@ -1354,13 +1354,13 @@
         <v>21</v>
       </c>
       <c r="J31" t="n">
-        <v>-2.32</v>
+        <v>-2.51</v>
       </c>
       <c r="K31" t="n">
-        <v>-30.99</v>
+        <v>-33.47</v>
       </c>
       <c r="L31" t="n">
-        <v>31.08</v>
+        <v>33.56</v>
       </c>
     </row>
     <row r="32">
@@ -1396,13 +1396,13 @@
         <v>27</v>
       </c>
       <c r="J32" t="n">
-        <v>37.89</v>
+        <v>39.84</v>
       </c>
       <c r="K32" t="n">
-        <v>28</v>
+        <v>29.43</v>
       </c>
       <c r="L32" t="n">
-        <v>47.11</v>
+        <v>49.53</v>
       </c>
     </row>
     <row r="33">
@@ -1438,13 +1438,13 @@
         <v>25</v>
       </c>
       <c r="J33" t="n">
-        <v>31.78</v>
+        <v>32.74</v>
       </c>
       <c r="K33" t="n">
-        <v>42.53</v>
+        <v>43.81</v>
       </c>
       <c r="L33" t="n">
-        <v>53.09</v>
+        <v>54.69</v>
       </c>
     </row>
     <row r="34">
@@ -1480,13 +1480,13 @@
         <v>26</v>
       </c>
       <c r="J34" t="n">
-        <v>-54.54</v>
+        <v>-52.56</v>
       </c>
       <c r="K34" t="n">
-        <v>62.35</v>
+        <v>60.09</v>
       </c>
       <c r="L34" t="n">
-        <v>82.84</v>
+        <v>79.83</v>
       </c>
     </row>
     <row r="35">
@@ -1522,13 +1522,13 @@
         <v>22</v>
       </c>
       <c r="J35" t="n">
-        <v>85.64</v>
+        <v>86.29000000000001</v>
       </c>
       <c r="K35" t="n">
-        <v>32.97</v>
+        <v>33.22</v>
       </c>
       <c r="L35" t="n">
-        <v>91.76000000000001</v>
+        <v>92.45999999999999</v>
       </c>
     </row>
     <row r="36">
@@ -1564,13 +1564,13 @@
         <v>25</v>
       </c>
       <c r="J36" t="n">
-        <v>95.75</v>
+        <v>91.34</v>
       </c>
       <c r="K36" t="n">
-        <v>74.42</v>
+        <v>71</v>
       </c>
       <c r="L36" t="n">
-        <v>121.27</v>
+        <v>115.69</v>
       </c>
     </row>
     <row r="37">
@@ -1606,13 +1606,13 @@
         <v>23</v>
       </c>
       <c r="J37" t="n">
-        <v>58.75</v>
+        <v>55.42</v>
       </c>
       <c r="K37" t="n">
-        <v>-140.1</v>
+        <v>-132.16</v>
       </c>
       <c r="L37" t="n">
-        <v>151.92</v>
+        <v>143.31</v>
       </c>
     </row>
     <row r="38">
@@ -1648,13 +1648,13 @@
         <v>23</v>
       </c>
       <c r="J38" t="n">
-        <v>89.59</v>
+        <v>84.36</v>
       </c>
       <c r="K38" t="n">
-        <v>164.21</v>
+        <v>154.62</v>
       </c>
       <c r="L38" t="n">
-        <v>187.05</v>
+        <v>176.14</v>
       </c>
     </row>
     <row r="39">
@@ -1690,13 +1690,13 @@
         <v>24</v>
       </c>
       <c r="J39" t="n">
-        <v>-91.14</v>
+        <v>-92.23</v>
       </c>
       <c r="K39" t="n">
-        <v>69.7</v>
+        <v>70.53</v>
       </c>
       <c r="L39" t="n">
-        <v>114.74</v>
+        <v>116.11</v>
       </c>
     </row>
     <row r="40">
@@ -1732,13 +1732,13 @@
         <v>25</v>
       </c>
       <c r="J40" t="n">
-        <v>-40.47</v>
+        <v>-40.86</v>
       </c>
       <c r="K40" t="n">
-        <v>103.52</v>
+        <v>104.52</v>
       </c>
       <c r="L40" t="n">
-        <v>111.15</v>
+        <v>112.22</v>
       </c>
     </row>
     <row r="41">
@@ -1774,13 +1774,13 @@
         <v>23</v>
       </c>
       <c r="J41" t="n">
-        <v>-76.94</v>
+        <v>-79.61</v>
       </c>
       <c r="K41" t="n">
-        <v>128.4</v>
+        <v>132.85</v>
       </c>
       <c r="L41" t="n">
-        <v>149.69</v>
+        <v>154.88</v>
       </c>
     </row>
     <row r="42">
@@ -1816,13 +1816,13 @@
         <v>21</v>
       </c>
       <c r="J42" t="n">
-        <v>100.81</v>
+        <v>107.98</v>
       </c>
       <c r="K42" t="n">
-        <v>78.52</v>
+        <v>84.11</v>
       </c>
       <c r="L42" t="n">
-        <v>127.78</v>
+        <v>136.87</v>
       </c>
     </row>
     <row r="43">
@@ -1858,13 +1858,13 @@
         <v>22</v>
       </c>
       <c r="J43" t="n">
-        <v>128.25</v>
+        <v>126.45</v>
       </c>
       <c r="K43" t="n">
-        <v>-152.29</v>
+        <v>-150.15</v>
       </c>
       <c r="L43" t="n">
-        <v>199.1</v>
+        <v>196.3</v>
       </c>
     </row>
     <row r="44">
@@ -1900,13 +1900,13 @@
         <v>27</v>
       </c>
       <c r="J44" t="n">
-        <v>-12.46</v>
+        <v>-12.61</v>
       </c>
       <c r="K44" t="n">
-        <v>39.26</v>
+        <v>39.7</v>
       </c>
       <c r="L44" t="n">
-        <v>41.19</v>
+        <v>41.66</v>
       </c>
     </row>
     <row r="45">
@@ -1942,13 +1942,13 @@
         <v>26</v>
       </c>
       <c r="J45" t="n">
-        <v>39.91</v>
+        <v>40.66</v>
       </c>
       <c r="K45" t="n">
-        <v>-2.24</v>
+        <v>-2.28</v>
       </c>
       <c r="L45" t="n">
-        <v>39.97</v>
+        <v>40.72</v>
       </c>
     </row>
     <row r="46">
@@ -1984,13 +1984,13 @@
         <v>23</v>
       </c>
       <c r="J46" t="n">
-        <v>31.27</v>
+        <v>33.31</v>
       </c>
       <c r="K46" t="n">
-        <v>-5.06</v>
+        <v>-5.39</v>
       </c>
       <c r="L46" t="n">
-        <v>31.67</v>
+        <v>33.74</v>
       </c>
     </row>
     <row r="47">
@@ -2026,13 +2026,13 @@
         <v>23</v>
       </c>
       <c r="J47" t="n">
-        <v>-24.22</v>
+        <v>-25.64</v>
       </c>
       <c r="K47" t="n">
-        <v>39.64</v>
+        <v>41.97</v>
       </c>
       <c r="L47" t="n">
-        <v>46.45</v>
+        <v>49.18</v>
       </c>
     </row>
     <row r="48">
@@ -2068,13 +2068,13 @@
         <v>21</v>
       </c>
       <c r="J48" t="n">
-        <v>-36.98</v>
+        <v>-35.35</v>
       </c>
       <c r="K48" t="n">
-        <v>95.79000000000001</v>
+        <v>91.56</v>
       </c>
       <c r="L48" t="n">
-        <v>102.68</v>
+        <v>98.14</v>
       </c>
     </row>
     <row r="49">
@@ -2110,13 +2110,13 @@
         <v>22</v>
       </c>
       <c r="J49" t="n">
-        <v>78.81</v>
+        <v>76.73</v>
       </c>
       <c r="K49" t="n">
-        <v>33.69</v>
+        <v>32.8</v>
       </c>
       <c r="L49" t="n">
-        <v>85.70999999999999</v>
+        <v>83.45</v>
       </c>
     </row>
     <row r="50">
@@ -2152,13 +2152,13 @@
         <v>25</v>
       </c>
       <c r="J50" t="n">
-        <v>22.26</v>
+        <v>23.48</v>
       </c>
       <c r="K50" t="n">
-        <v>-64.98</v>
+        <v>-68.56</v>
       </c>
       <c r="L50" t="n">
-        <v>68.69</v>
+        <v>72.47</v>
       </c>
     </row>
     <row r="51">
@@ -2194,13 +2194,13 @@
         <v>24</v>
       </c>
       <c r="J51" t="n">
-        <v>-46.55</v>
+        <v>-47</v>
       </c>
       <c r="K51" t="n">
-        <v>93.06999999999999</v>
+        <v>93.97</v>
       </c>
       <c r="L51" t="n">
-        <v>104.06</v>
+        <v>105.07</v>
       </c>
     </row>
     <row r="52">
@@ -2236,13 +2236,13 @@
         <v>21</v>
       </c>
       <c r="J52" t="n">
-        <v>63.14</v>
+        <v>68.06999999999999</v>
       </c>
       <c r="K52" t="n">
-        <v>-9.52</v>
+        <v>-10.26</v>
       </c>
       <c r="L52" t="n">
-        <v>63.85</v>
+        <v>68.83</v>
       </c>
     </row>
     <row r="53">
@@ -2278,13 +2278,13 @@
         <v>23</v>
       </c>
       <c r="J53" t="n">
-        <v>-10.96</v>
+        <v>-11.03</v>
       </c>
       <c r="K53" t="n">
-        <v>126.76</v>
+        <v>127.59</v>
       </c>
       <c r="L53" t="n">
-        <v>127.23</v>
+        <v>128.06</v>
       </c>
     </row>
     <row r="54">
@@ -2320,13 +2320,13 @@
         <v>23</v>
       </c>
       <c r="J54" t="n">
-        <v>143.25</v>
+        <v>138.77</v>
       </c>
       <c r="K54" t="n">
-        <v>60</v>
+        <v>58.12</v>
       </c>
       <c r="L54" t="n">
-        <v>155.3</v>
+        <v>150.45</v>
       </c>
     </row>
     <row r="55">
@@ -2362,13 +2362,13 @@
         <v>21</v>
       </c>
       <c r="J55" t="n">
-        <v>185.43</v>
+        <v>177.56</v>
       </c>
       <c r="K55" t="n">
-        <v>-14.77</v>
+        <v>-14.14</v>
       </c>
       <c r="L55" t="n">
-        <v>186.01</v>
+        <v>178.12</v>
       </c>
     </row>
     <row r="56">
@@ -2404,13 +2404,13 @@
         <v>24</v>
       </c>
       <c r="J56" t="n">
-        <v>6.88</v>
+        <v>7.07</v>
       </c>
       <c r="K56" t="n">
-        <v>150.25</v>
+        <v>154.45</v>
       </c>
       <c r="L56" t="n">
-        <v>150.41</v>
+        <v>154.61</v>
       </c>
     </row>
     <row r="57">
@@ -2446,13 +2446,13 @@
         <v>24</v>
       </c>
       <c r="J57" t="n">
-        <v>156.27</v>
+        <v>160.9</v>
       </c>
       <c r="K57" t="n">
-        <v>6.9</v>
+        <v>7.11</v>
       </c>
       <c r="L57" t="n">
-        <v>156.42</v>
+        <v>161.06</v>
       </c>
     </row>
     <row r="58">
@@ -2488,13 +2488,13 @@
         <v>23</v>
       </c>
       <c r="J58" t="n">
-        <v>35.22</v>
+        <v>38.18</v>
       </c>
       <c r="K58" t="n">
-        <v>-33.28</v>
+        <v>-36.07</v>
       </c>
       <c r="L58" t="n">
-        <v>48.46</v>
+        <v>52.53</v>
       </c>
     </row>
     <row r="59">
@@ -2530,13 +2530,13 @@
         <v>24</v>
       </c>
       <c r="J59" t="n">
-        <v>4.06</v>
+        <v>3.99</v>
       </c>
       <c r="K59" t="n">
-        <v>58.3</v>
+        <v>57.23</v>
       </c>
       <c r="L59" t="n">
-        <v>58.44</v>
+        <v>57.36</v>
       </c>
     </row>
     <row r="60">
@@ -2572,13 +2572,13 @@
         <v>22</v>
       </c>
       <c r="J60" t="n">
-        <v>-36.84</v>
+        <v>-38.04</v>
       </c>
       <c r="K60" t="n">
-        <v>24.61</v>
+        <v>25.41</v>
       </c>
       <c r="L60" t="n">
-        <v>44.3</v>
+        <v>45.75</v>
       </c>
     </row>
     <row r="61">
@@ -2614,13 +2614,13 @@
         <v>21</v>
       </c>
       <c r="J61" t="n">
-        <v>-45.15</v>
+        <v>-44.09</v>
       </c>
       <c r="K61" t="n">
-        <v>38.98</v>
+        <v>38.07</v>
       </c>
       <c r="L61" t="n">
-        <v>59.65</v>
+        <v>58.25</v>
       </c>
     </row>
     <row r="62">
@@ -2656,13 +2656,13 @@
         <v>21</v>
       </c>
       <c r="J62" t="n">
-        <v>32.98</v>
+        <v>32.66</v>
       </c>
       <c r="K62" t="n">
-        <v>66.19</v>
+        <v>65.54000000000001</v>
       </c>
       <c r="L62" t="n">
-        <v>73.95</v>
+        <v>73.23</v>
       </c>
     </row>
     <row r="63">
@@ -2698,13 +2698,13 @@
         <v>26</v>
       </c>
       <c r="J63" t="n">
-        <v>62.72</v>
+        <v>62.12</v>
       </c>
       <c r="K63" t="n">
-        <v>25.2</v>
+        <v>24.95</v>
       </c>
       <c r="L63" t="n">
-        <v>67.59</v>
+        <v>66.94</v>
       </c>
     </row>
     <row r="64">
@@ -2740,13 +2740,13 @@
         <v>22</v>
       </c>
       <c r="J64" t="n">
-        <v>75.09</v>
+        <v>73.94</v>
       </c>
       <c r="K64" t="n">
-        <v>-56.47</v>
+        <v>-55.61</v>
       </c>
       <c r="L64" t="n">
-        <v>93.95999999999999</v>
+        <v>92.52</v>
       </c>
     </row>
     <row r="65">
@@ -2782,13 +2782,13 @@
         <v>23</v>
       </c>
       <c r="J65" t="n">
-        <v>121.49</v>
+        <v>115.05</v>
       </c>
       <c r="K65" t="n">
-        <v>-103.14</v>
+        <v>-97.68000000000001</v>
       </c>
       <c r="L65" t="n">
-        <v>159.37</v>
+        <v>150.92</v>
       </c>
     </row>
     <row r="66">
@@ -2824,13 +2824,13 @@
         <v>26</v>
       </c>
       <c r="J66" t="n">
-        <v>-10.62</v>
+        <v>-11.43</v>
       </c>
       <c r="K66" t="n">
-        <v>59.46</v>
+        <v>64.02</v>
       </c>
       <c r="L66" t="n">
-        <v>60.4</v>
+        <v>65.04000000000001</v>
       </c>
     </row>
     <row r="67">
@@ -2866,13 +2866,13 @@
         <v>23</v>
       </c>
       <c r="J67" t="n">
-        <v>-28.78</v>
+        <v>-31.48</v>
       </c>
       <c r="K67" t="n">
-        <v>29.62</v>
+        <v>32.39</v>
       </c>
       <c r="L67" t="n">
-        <v>41.3</v>
+        <v>45.17</v>
       </c>
     </row>
     <row r="68">
@@ -2908,13 +2908,13 @@
         <v>21</v>
       </c>
       <c r="J68" t="n">
-        <v>68.02</v>
+        <v>68.3</v>
       </c>
       <c r="K68" t="n">
-        <v>115.11</v>
+        <v>115.59</v>
       </c>
       <c r="L68" t="n">
-        <v>133.71</v>
+        <v>134.26</v>
       </c>
     </row>
     <row r="69">
@@ -2950,13 +2950,13 @@
         <v>27</v>
       </c>
       <c r="J69" t="n">
-        <v>60.61</v>
+        <v>58.17</v>
       </c>
       <c r="K69" t="n">
-        <v>152.3</v>
+        <v>146.16</v>
       </c>
       <c r="L69" t="n">
-        <v>163.92</v>
+        <v>157.32</v>
       </c>
     </row>
     <row r="70">
@@ -2992,13 +2992,13 @@
         <v>26</v>
       </c>
       <c r="J70" t="n">
-        <v>107.09</v>
+        <v>104.44</v>
       </c>
       <c r="K70" t="n">
-        <v>111.56</v>
+        <v>108.8</v>
       </c>
       <c r="L70" t="n">
-        <v>154.65</v>
+        <v>150.81</v>
       </c>
     </row>
     <row r="71">
@@ -3034,13 +3034,13 @@
         <v>25</v>
       </c>
       <c r="J71" t="n">
-        <v>-4.95</v>
+        <v>-4.82</v>
       </c>
       <c r="K71" t="n">
-        <v>-289.92</v>
+        <v>-282.29</v>
       </c>
       <c r="L71" t="n">
-        <v>289.97</v>
+        <v>282.33</v>
       </c>
     </row>
     <row r="72">
@@ -3076,13 +3076,13 @@
         <v>21</v>
       </c>
       <c r="J72" t="n">
-        <v>-6.17</v>
+        <v>-5.94</v>
       </c>
       <c r="K72" t="n">
-        <v>262</v>
+        <v>252.25</v>
       </c>
       <c r="L72" t="n">
-        <v>262.08</v>
+        <v>252.32</v>
       </c>
     </row>
     <row r="73">
@@ -3118,13 +3118,13 @@
         <v>27</v>
       </c>
       <c r="J73" t="n">
-        <v>76.72</v>
+        <v>78.68000000000001</v>
       </c>
       <c r="K73" t="n">
-        <v>-132.3</v>
+        <v>-135.68</v>
       </c>
       <c r="L73" t="n">
-        <v>152.93</v>
+        <v>156.84</v>
       </c>
     </row>
     <row r="74">
@@ -3160,13 +3160,13 @@
         <v>27</v>
       </c>
       <c r="J74" t="n">
-        <v>-54.59</v>
+        <v>-51.54</v>
       </c>
       <c r="K74" t="n">
-        <v>-25.7</v>
+        <v>-24.27</v>
       </c>
       <c r="L74" t="n">
-        <v>60.34</v>
+        <v>56.97</v>
       </c>
     </row>
     <row r="75">
@@ -3202,13 +3202,13 @@
         <v>23</v>
       </c>
       <c r="J75" t="n">
-        <v>16.81</v>
+        <v>18.15</v>
       </c>
       <c r="K75" t="n">
-        <v>-29.02</v>
+        <v>-31.33</v>
       </c>
       <c r="L75" t="n">
-        <v>33.53</v>
+        <v>36.2</v>
       </c>
     </row>
     <row r="76">
@@ -3244,13 +3244,13 @@
         <v>22</v>
       </c>
       <c r="J76" t="n">
-        <v>-45.03</v>
+        <v>-43.74</v>
       </c>
       <c r="K76" t="n">
-        <v>34.77</v>
+        <v>33.77</v>
       </c>
       <c r="L76" t="n">
-        <v>56.89</v>
+        <v>55.26</v>
       </c>
     </row>
     <row r="77">
@@ -3286,13 +3286,13 @@
         <v>22</v>
       </c>
       <c r="J77" t="n">
-        <v>-37.95</v>
+        <v>-37.5</v>
       </c>
       <c r="K77" t="n">
-        <v>64.51000000000001</v>
+        <v>63.76</v>
       </c>
       <c r="L77" t="n">
-        <v>74.84</v>
+        <v>73.97</v>
       </c>
     </row>
     <row r="78">
@@ -3328,13 +3328,13 @@
         <v>25</v>
       </c>
       <c r="J78" t="n">
-        <v>33.74</v>
+        <v>35.77</v>
       </c>
       <c r="K78" t="n">
-        <v>-29.86</v>
+        <v>-31.67</v>
       </c>
       <c r="L78" t="n">
-        <v>45.06</v>
+        <v>47.77</v>
       </c>
     </row>
     <row r="79">
@@ -3370,13 +3370,13 @@
         <v>25</v>
       </c>
       <c r="J79" t="n">
-        <v>67.22</v>
+        <v>65.28</v>
       </c>
       <c r="K79" t="n">
-        <v>45.77</v>
+        <v>44.44</v>
       </c>
       <c r="L79" t="n">
-        <v>81.31999999999999</v>
+        <v>78.97</v>
       </c>
     </row>
     <row r="80">
@@ -3412,13 +3412,13 @@
         <v>27</v>
       </c>
       <c r="J80" t="n">
-        <v>-53.11</v>
+        <v>-56.41</v>
       </c>
       <c r="K80" t="n">
-        <v>-34.25</v>
+        <v>-36.39</v>
       </c>
       <c r="L80" t="n">
-        <v>63.2</v>
+        <v>67.13</v>
       </c>
     </row>
     <row r="81">
@@ -3454,13 +3454,13 @@
         <v>21</v>
       </c>
       <c r="J81" t="n">
-        <v>-76.95999999999999</v>
+        <v>-79.39</v>
       </c>
       <c r="K81" t="n">
-        <v>26.27</v>
+        <v>27.1</v>
       </c>
       <c r="L81" t="n">
-        <v>81.31999999999999</v>
+        <v>83.89</v>
       </c>
     </row>
     <row r="82">
@@ -3496,13 +3496,13 @@
         <v>22</v>
       </c>
       <c r="J82" t="n">
-        <v>-3.53</v>
+        <v>-3.88</v>
       </c>
       <c r="K82" t="n">
-        <v>60.13</v>
+        <v>66.08</v>
       </c>
       <c r="L82" t="n">
-        <v>60.24</v>
+        <v>66.19</v>
       </c>
     </row>
     <row r="83">
@@ -3538,13 +3538,13 @@
         <v>25</v>
       </c>
       <c r="J83" t="n">
-        <v>166.03</v>
+        <v>158.52</v>
       </c>
       <c r="K83" t="n">
-        <v>15.06</v>
+        <v>14.38</v>
       </c>
       <c r="L83" t="n">
-        <v>166.71</v>
+        <v>159.17</v>
       </c>
     </row>
     <row r="84">
@@ -3580,13 +3580,13 @@
         <v>21</v>
       </c>
       <c r="J84" t="n">
-        <v>-13.29</v>
+        <v>-13.6</v>
       </c>
       <c r="K84" t="n">
-        <v>115.46</v>
+        <v>118.1</v>
       </c>
       <c r="L84" t="n">
-        <v>116.22</v>
+        <v>118.88</v>
       </c>
     </row>
     <row r="85">
@@ -3622,13 +3622,13 @@
         <v>22</v>
       </c>
       <c r="J85" t="n">
-        <v>-44.48</v>
+        <v>-41.96</v>
       </c>
       <c r="K85" t="n">
-        <v>-191.25</v>
+        <v>-180.4</v>
       </c>
       <c r="L85" t="n">
-        <v>196.35</v>
+        <v>185.22</v>
       </c>
     </row>
     <row r="86">
@@ -3664,13 +3664,13 @@
         <v>23</v>
       </c>
       <c r="J86" t="n">
-        <v>-268.43</v>
+        <v>-254.59</v>
       </c>
       <c r="K86" t="n">
-        <v>75.12</v>
+        <v>71.25</v>
       </c>
       <c r="L86" t="n">
-        <v>278.74</v>
+        <v>264.37</v>
       </c>
     </row>
     <row r="87">
@@ -3706,13 +3706,13 @@
         <v>26</v>
       </c>
       <c r="J87" t="n">
-        <v>-199.71</v>
+        <v>-194.02</v>
       </c>
       <c r="K87" t="n">
-        <v>-63.71</v>
+        <v>-61.89</v>
       </c>
       <c r="L87" t="n">
-        <v>209.62</v>
+        <v>203.65</v>
       </c>
     </row>
     <row r="88">
@@ -3748,13 +3748,13 @@
         <v>21</v>
       </c>
       <c r="J88" t="n">
-        <v>-152.28</v>
+        <v>-156.08</v>
       </c>
       <c r="K88" t="n">
-        <v>-50.55</v>
+        <v>-51.82</v>
       </c>
       <c r="L88" t="n">
-        <v>160.45</v>
+        <v>164.45</v>
       </c>
     </row>
   </sheetData>

--- a/output/2024-07-26.xlsx
+++ b/output/2024-07-26.xlsx
@@ -625,34 +625,34 @@
         <v>1</v>
       </c>
       <c r="E14" t="n">
-        <v>2.26</v>
+        <v>1.7</v>
       </c>
       <c r="F14" t="n">
-        <v>9.16</v>
+        <v>6.46</v>
       </c>
       <c r="G14" t="n">
-        <v>68.8</v>
+        <v>61.7</v>
       </c>
       <c r="H14" t="n">
-        <v>30.4</v>
+        <v>31.2</v>
       </c>
       <c r="I14" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="J14" t="n">
-        <v>28.31</v>
+        <v>-15.82</v>
       </c>
       <c r="K14" t="n">
-        <v>28.91</v>
+        <v>39.43</v>
       </c>
       <c r="L14" t="n">
-        <v>40.46</v>
+        <v>42.49</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>05:09:53</t>
+          <t>05:10:21</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -667,34 +667,34 @@
         <v>2</v>
       </c>
       <c r="E15" t="n">
-        <v>1.64</v>
+        <v>1.57</v>
       </c>
       <c r="F15" t="n">
-        <v>8</v>
+        <v>8.609999999999999</v>
       </c>
       <c r="G15" t="n">
-        <v>88.7</v>
+        <v>59.6</v>
       </c>
       <c r="H15" t="n">
-        <v>30.7</v>
+        <v>26.2</v>
       </c>
       <c r="I15" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="J15" t="n">
-        <v>23.7</v>
+        <v>-44.31</v>
       </c>
       <c r="K15" t="n">
-        <v>-19.03</v>
+        <v>38.68</v>
       </c>
       <c r="L15" t="n">
-        <v>30.4</v>
+        <v>58.82</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>05:11:09</t>
+          <t>05:12:02</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -709,34 +709,34 @@
         <v>3</v>
       </c>
       <c r="E16" t="n">
-        <v>1.7</v>
+        <v>1.49</v>
       </c>
       <c r="F16" t="n">
-        <v>8.800000000000001</v>
+        <v>4.41</v>
       </c>
       <c r="G16" t="n">
-        <v>67.40000000000001</v>
+        <v>59.9</v>
       </c>
       <c r="H16" t="n">
-        <v>29.3</v>
+        <v>26.4</v>
       </c>
       <c r="I16" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="J16" t="n">
-        <v>-13.81</v>
+        <v>38.45</v>
       </c>
       <c r="K16" t="n">
-        <v>32.99</v>
+        <v>7.21</v>
       </c>
       <c r="L16" t="n">
-        <v>35.76</v>
+        <v>39.12</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>05:17:56</t>
+          <t>05:16:21</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -751,34 +751,34 @@
         <v>1</v>
       </c>
       <c r="E17" t="n">
-        <v>1.58</v>
+        <v>1.46</v>
       </c>
       <c r="F17" t="n">
-        <v>8.699999999999999</v>
+        <v>3.05</v>
       </c>
       <c r="G17" t="n">
-        <v>57.4</v>
+        <v>65.40000000000001</v>
       </c>
       <c r="H17" t="n">
-        <v>32</v>
+        <v>33.6</v>
       </c>
       <c r="I17" t="n">
         <v>22</v>
       </c>
       <c r="J17" t="n">
-        <v>-43.92</v>
+        <v>74.52</v>
       </c>
       <c r="K17" t="n">
-        <v>38.29</v>
+        <v>-5.94</v>
       </c>
       <c r="L17" t="n">
-        <v>58.27</v>
+        <v>74.75</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>05:18:46</t>
+          <t>05:18:25</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -796,31 +796,31 @@
         <v>1.5</v>
       </c>
       <c r="F18" t="n">
-        <v>8.720000000000001</v>
+        <v>3.26</v>
       </c>
       <c r="G18" t="n">
-        <v>57.9</v>
+        <v>60.8</v>
       </c>
       <c r="H18" t="n">
-        <v>27.6</v>
+        <v>29.5</v>
       </c>
       <c r="I18" t="n">
         <v>22</v>
       </c>
       <c r="J18" t="n">
-        <v>44.52</v>
+        <v>-13.62</v>
       </c>
       <c r="K18" t="n">
-        <v>8.390000000000001</v>
+        <v>57.54</v>
       </c>
       <c r="L18" t="n">
-        <v>45.31</v>
+        <v>59.13</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>05:21:11</t>
+          <t>05:19:59</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -835,34 +835,34 @@
         <v>3</v>
       </c>
       <c r="E19" t="n">
-        <v>1.47</v>
+        <v>2.1</v>
       </c>
       <c r="F19" t="n">
-        <v>8.99</v>
+        <v>9.82</v>
       </c>
       <c r="G19" t="n">
-        <v>72.2</v>
+        <v>68.5</v>
       </c>
       <c r="H19" t="n">
-        <v>32.9</v>
+        <v>20.9</v>
       </c>
       <c r="I19" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="J19" t="n">
-        <v>69.28</v>
+        <v>-98.87</v>
       </c>
       <c r="K19" t="n">
-        <v>-5.95</v>
+        <v>-7.51</v>
       </c>
       <c r="L19" t="n">
-        <v>69.53</v>
+        <v>99.15000000000001</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>05:25:27</t>
+          <t>05:25:06</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -877,34 +877,34 @@
         <v>1</v>
       </c>
       <c r="E20" t="n">
-        <v>1.52</v>
+        <v>1.87</v>
       </c>
       <c r="F20" t="n">
-        <v>8.76</v>
+        <v>10.35</v>
       </c>
       <c r="G20" t="n">
-        <v>63.9</v>
+        <v>63.6</v>
       </c>
       <c r="H20" t="n">
-        <v>25.8</v>
+        <v>32.1</v>
       </c>
       <c r="I20" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="J20" t="n">
-        <v>-18.77</v>
+        <v>137.26</v>
       </c>
       <c r="K20" t="n">
-        <v>79.45</v>
+        <v>46.38</v>
       </c>
       <c r="L20" t="n">
-        <v>81.63</v>
+        <v>144.88</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>05:27:43</t>
+          <t>05:26:36</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -919,34 +919,34 @@
         <v>2</v>
       </c>
       <c r="E21" t="n">
-        <v>2.11</v>
+        <v>1.57</v>
       </c>
       <c r="F21" t="n">
-        <v>9.15</v>
+        <v>2.74</v>
       </c>
       <c r="G21" t="n">
-        <v>46.7</v>
+        <v>63</v>
       </c>
       <c r="H21" t="n">
-        <v>29.3</v>
+        <v>26.1</v>
       </c>
       <c r="I21" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="J21" t="n">
-        <v>-114.51</v>
+        <v>-99.54000000000001</v>
       </c>
       <c r="K21" t="n">
-        <v>-7.65</v>
+        <v>-63.99</v>
       </c>
       <c r="L21" t="n">
-        <v>114.76</v>
+        <v>118.33</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>05:28:12</t>
+          <t>05:28:16</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -961,34 +961,34 @@
         <v>3</v>
       </c>
       <c r="E22" t="n">
-        <v>1.87</v>
+        <v>1.65</v>
       </c>
       <c r="F22" t="n">
-        <v>8.9</v>
+        <v>5.69</v>
       </c>
       <c r="G22" t="n">
-        <v>69.3</v>
+        <v>60</v>
       </c>
       <c r="H22" t="n">
-        <v>36.4</v>
+        <v>29.2</v>
       </c>
       <c r="I22" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="J22" t="n">
-        <v>107.49</v>
+        <v>-75.23999999999999</v>
       </c>
       <c r="K22" t="n">
-        <v>35.35</v>
+        <v>-27.35</v>
       </c>
       <c r="L22" t="n">
-        <v>113.15</v>
+        <v>80.05</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>05:33:07</t>
+          <t>05:32:23</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1003,34 +1003,34 @@
         <v>1</v>
       </c>
       <c r="E23" t="n">
-        <v>1.58</v>
+        <v>1.71</v>
       </c>
       <c r="F23" t="n">
-        <v>8.869999999999999</v>
+        <v>8.449999999999999</v>
       </c>
       <c r="G23" t="n">
-        <v>57.2</v>
+        <v>53</v>
       </c>
       <c r="H23" t="n">
-        <v>30.1</v>
+        <v>27.8</v>
       </c>
       <c r="I23" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="J23" t="n">
-        <v>-136.2</v>
+        <v>75.06999999999999</v>
       </c>
       <c r="K23" t="n">
-        <v>-86.73999999999999</v>
+        <v>-120.53</v>
       </c>
       <c r="L23" t="n">
-        <v>161.47</v>
+        <v>142</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>05:34:12</t>
+          <t>05:33:32</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1045,34 +1045,34 @@
         <v>2</v>
       </c>
       <c r="E24" t="n">
-        <v>1.66</v>
+        <v>1.88</v>
       </c>
       <c r="F24" t="n">
-        <v>8.720000000000001</v>
+        <v>10.35</v>
       </c>
       <c r="G24" t="n">
-        <v>63.4</v>
+        <v>74.09999999999999</v>
       </c>
       <c r="H24" t="n">
-        <v>28.3</v>
+        <v>31.3</v>
       </c>
       <c r="I24" t="n">
         <v>23</v>
       </c>
       <c r="J24" t="n">
-        <v>-84.09999999999999</v>
+        <v>57.32</v>
       </c>
       <c r="K24" t="n">
-        <v>-32.54</v>
+        <v>-105.69</v>
       </c>
       <c r="L24" t="n">
-        <v>90.18000000000001</v>
+        <v>120.23</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>05:35:23</t>
+          <t>05:34:58</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1087,34 +1087,34 @@
         <v>3</v>
       </c>
       <c r="E25" t="n">
-        <v>1.72</v>
+        <v>1.91</v>
       </c>
       <c r="F25" t="n">
-        <v>8.369999999999999</v>
+        <v>8.859999999999999</v>
       </c>
       <c r="G25" t="n">
-        <v>60.5</v>
+        <v>78.8</v>
       </c>
       <c r="H25" t="n">
-        <v>33</v>
+        <v>25.2</v>
       </c>
       <c r="I25" t="n">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="J25" t="n">
-        <v>44.32</v>
+        <v>122.43</v>
       </c>
       <c r="K25" t="n">
-        <v>-92.84999999999999</v>
+        <v>-58.05</v>
       </c>
       <c r="L25" t="n">
-        <v>102.89</v>
+        <v>135.49</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>05:39:59</t>
+          <t>05:40:04</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1129,34 +1129,34 @@
         <v>1</v>
       </c>
       <c r="E26" t="n">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="F26" t="n">
-        <v>9.42</v>
+        <v>9.17</v>
       </c>
       <c r="G26" t="n">
-        <v>67.59999999999999</v>
+        <v>62.7</v>
       </c>
       <c r="H26" t="n">
-        <v>37.2</v>
+        <v>25.6</v>
       </c>
       <c r="I26" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="J26" t="n">
-        <v>21.53</v>
+        <v>-380</v>
       </c>
       <c r="K26" t="n">
-        <v>-127.45</v>
+        <v>-27.26</v>
       </c>
       <c r="L26" t="n">
-        <v>129.26</v>
+        <v>380.98</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>05:41:58</t>
+          <t>05:42:25</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1171,34 +1171,34 @@
         <v>2</v>
       </c>
       <c r="E27" t="n">
-        <v>1.92</v>
+        <v>1.56</v>
       </c>
       <c r="F27" t="n">
-        <v>9.66</v>
+        <v>6.72</v>
       </c>
       <c r="G27" t="n">
-        <v>55.5</v>
+        <v>68.3</v>
       </c>
       <c r="H27" t="n">
-        <v>26.5</v>
+        <v>31.5</v>
       </c>
       <c r="I27" t="n">
         <v>25</v>
       </c>
       <c r="J27" t="n">
-        <v>120.54</v>
+        <v>190.63</v>
       </c>
       <c r="K27" t="n">
-        <v>-66.5</v>
+        <v>94.61</v>
       </c>
       <c r="L27" t="n">
-        <v>137.66</v>
+        <v>212.82</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>05:43:40</t>
+          <t>05:44:14</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1213,34 +1213,34 @@
         <v>3</v>
       </c>
       <c r="E28" t="n">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="F28" t="n">
-        <v>8.859999999999999</v>
+        <v>2.21</v>
       </c>
       <c r="G28" t="n">
-        <v>56.2</v>
+        <v>78.3</v>
       </c>
       <c r="H28" t="n">
-        <v>31.8</v>
+        <v>38.7</v>
       </c>
       <c r="I28" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J28" t="n">
-        <v>-315.08</v>
+        <v>-138.89</v>
       </c>
       <c r="K28" t="n">
-        <v>-29.21</v>
+        <v>156.03</v>
       </c>
       <c r="L28" t="n">
-        <v>316.43</v>
+        <v>208.89</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>05:53:38</t>
+          <t>05:53:58</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1255,34 +1255,34 @@
         <v>1</v>
       </c>
       <c r="E29" t="n">
-        <v>1.58</v>
+        <v>1.64</v>
       </c>
       <c r="F29" t="n">
-        <v>9.130000000000001</v>
+        <v>3.61</v>
       </c>
       <c r="G29" t="n">
-        <v>68</v>
+        <v>66.2</v>
       </c>
       <c r="H29" t="n">
-        <v>37.4</v>
+        <v>24.5</v>
       </c>
       <c r="I29" t="n">
         <v>24</v>
       </c>
       <c r="J29" t="n">
-        <v>35.19</v>
+        <v>-1.61</v>
       </c>
       <c r="K29" t="n">
-        <v>18.29</v>
+        <v>-30.61</v>
       </c>
       <c r="L29" t="n">
-        <v>39.66</v>
+        <v>30.65</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>05:54:58</t>
+          <t>05:55:37</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1297,34 +1297,34 @@
         <v>2</v>
       </c>
       <c r="E30" t="n">
-        <v>1.93</v>
+        <v>2.17</v>
       </c>
       <c r="F30" t="n">
-        <v>9.640000000000001</v>
+        <v>10.35</v>
       </c>
       <c r="G30" t="n">
-        <v>82.3</v>
+        <v>63.3</v>
       </c>
       <c r="H30" t="n">
-        <v>20.6</v>
+        <v>26.2</v>
       </c>
       <c r="I30" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="J30" t="n">
-        <v>-41.7</v>
+        <v>37.24</v>
       </c>
       <c r="K30" t="n">
-        <v>36.14</v>
+        <v>27.26</v>
       </c>
       <c r="L30" t="n">
-        <v>55.18</v>
+        <v>46.15</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>05:56:07</t>
+          <t>05:58:18</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1339,34 +1339,34 @@
         <v>3</v>
       </c>
       <c r="E31" t="n">
-        <v>1.65</v>
+        <v>2.06</v>
       </c>
       <c r="F31" t="n">
-        <v>9.029999999999999</v>
+        <v>10.35</v>
       </c>
       <c r="G31" t="n">
-        <v>54.1</v>
+        <v>78.5</v>
       </c>
       <c r="H31" t="n">
-        <v>39.2</v>
+        <v>31.9</v>
       </c>
       <c r="I31" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="J31" t="n">
-        <v>-2.51</v>
+        <v>30.95</v>
       </c>
       <c r="K31" t="n">
-        <v>-33.47</v>
+        <v>40.99</v>
       </c>
       <c r="L31" t="n">
-        <v>33.56</v>
+        <v>51.37</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>05:59:58</t>
+          <t>06:02:35</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1381,34 +1381,34 @@
         <v>1</v>
       </c>
       <c r="E32" t="n">
-        <v>2.18</v>
+        <v>2.28</v>
       </c>
       <c r="F32" t="n">
-        <v>8.890000000000001</v>
+        <v>10.21</v>
       </c>
       <c r="G32" t="n">
-        <v>57.4</v>
+        <v>59.7</v>
       </c>
       <c r="H32" t="n">
-        <v>34.9</v>
+        <v>32</v>
       </c>
       <c r="I32" t="n">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="J32" t="n">
-        <v>39.84</v>
+        <v>-64.06999999999999</v>
       </c>
       <c r="K32" t="n">
-        <v>29.43</v>
+        <v>75.48999999999999</v>
       </c>
       <c r="L32" t="n">
-        <v>49.53</v>
+        <v>99.01000000000001</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>06:01:32</t>
+          <t>06:04:20</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1423,34 +1423,34 @@
         <v>2</v>
       </c>
       <c r="E33" t="n">
-        <v>2.06</v>
+        <v>1.99</v>
       </c>
       <c r="F33" t="n">
-        <v>9.640000000000001</v>
+        <v>9.42</v>
       </c>
       <c r="G33" t="n">
-        <v>68.7</v>
+        <v>58.2</v>
       </c>
       <c r="H33" t="n">
-        <v>26.7</v>
+        <v>34.3</v>
       </c>
       <c r="I33" t="n">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="J33" t="n">
-        <v>32.74</v>
+        <v>74.52</v>
       </c>
       <c r="K33" t="n">
-        <v>43.81</v>
+        <v>29.68</v>
       </c>
       <c r="L33" t="n">
-        <v>54.69</v>
+        <v>80.20999999999999</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>06:03:53</t>
+          <t>06:06:46</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1465,34 +1465,34 @@
         <v>3</v>
       </c>
       <c r="E34" t="n">
-        <v>2.28</v>
+        <v>1.61</v>
       </c>
       <c r="F34" t="n">
-        <v>8.710000000000001</v>
+        <v>9.630000000000001</v>
       </c>
       <c r="G34" t="n">
-        <v>69</v>
+        <v>79.59999999999999</v>
       </c>
       <c r="H34" t="n">
-        <v>30.7</v>
+        <v>34.8</v>
       </c>
       <c r="I34" t="n">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="J34" t="n">
-        <v>-52.56</v>
+        <v>86.36</v>
       </c>
       <c r="K34" t="n">
-        <v>60.09</v>
+        <v>66.92</v>
       </c>
       <c r="L34" t="n">
-        <v>79.83</v>
+        <v>109.25</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>06:09:24</t>
+          <t>06:11:10</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1507,34 +1507,34 @@
         <v>1</v>
       </c>
       <c r="E35" t="n">
-        <v>2</v>
+        <v>2.3</v>
       </c>
       <c r="F35" t="n">
-        <v>8.630000000000001</v>
+        <v>6.56</v>
       </c>
       <c r="G35" t="n">
-        <v>73.5</v>
+        <v>75.40000000000001</v>
       </c>
       <c r="H35" t="n">
-        <v>34.9</v>
+        <v>30.6</v>
       </c>
       <c r="I35" t="n">
         <v>22</v>
       </c>
       <c r="J35" t="n">
-        <v>86.29000000000001</v>
+        <v>58.19</v>
       </c>
       <c r="K35" t="n">
-        <v>33.22</v>
+        <v>-127.36</v>
       </c>
       <c r="L35" t="n">
-        <v>92.45999999999999</v>
+        <v>140.02</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>06:11:27</t>
+          <t>06:13:45</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1549,34 +1549,34 @@
         <v>2</v>
       </c>
       <c r="E36" t="n">
-        <v>1.62</v>
+        <v>1.76</v>
       </c>
       <c r="F36" t="n">
-        <v>9.699999999999999</v>
+        <v>8.99</v>
       </c>
       <c r="G36" t="n">
-        <v>74.5</v>
+        <v>56.8</v>
       </c>
       <c r="H36" t="n">
-        <v>34.1</v>
+        <v>34.6</v>
       </c>
       <c r="I36" t="n">
         <v>25</v>
       </c>
       <c r="J36" t="n">
-        <v>91.34</v>
+        <v>73.3</v>
       </c>
       <c r="K36" t="n">
-        <v>71</v>
+        <v>133.84</v>
       </c>
       <c r="L36" t="n">
-        <v>115.69</v>
+        <v>152.6</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>06:14:02</t>
+          <t>06:15:13</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1591,34 +1591,34 @@
         <v>3</v>
       </c>
       <c r="E37" t="n">
-        <v>2.3</v>
+        <v>2.08</v>
       </c>
       <c r="F37" t="n">
-        <v>9.49</v>
+        <v>5.67</v>
       </c>
       <c r="G37" t="n">
-        <v>66.09999999999999</v>
+        <v>65.40000000000001</v>
       </c>
       <c r="H37" t="n">
-        <v>40.2</v>
+        <v>33.2</v>
       </c>
       <c r="I37" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="J37" t="n">
-        <v>55.42</v>
+        <v>-69.47</v>
       </c>
       <c r="K37" t="n">
-        <v>-132.16</v>
+        <v>58.37</v>
       </c>
       <c r="L37" t="n">
-        <v>143.31</v>
+        <v>90.73999999999999</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>06:19:23</t>
+          <t>06:19:35</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1633,34 +1633,34 @@
         <v>1</v>
       </c>
       <c r="E38" t="n">
-        <v>1.77</v>
+        <v>1.99</v>
       </c>
       <c r="F38" t="n">
-        <v>8.56</v>
+        <v>10.35</v>
       </c>
       <c r="G38" t="n">
-        <v>74.2</v>
+        <v>76.40000000000001</v>
       </c>
       <c r="H38" t="n">
-        <v>32.2</v>
+        <v>24</v>
       </c>
       <c r="I38" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="J38" t="n">
-        <v>84.36</v>
+        <v>-33.23</v>
       </c>
       <c r="K38" t="n">
-        <v>154.62</v>
+        <v>131.87</v>
       </c>
       <c r="L38" t="n">
-        <v>176.14</v>
+        <v>135.99</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>06:21:24</t>
+          <t>06:20:42</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1675,34 +1675,34 @@
         <v>2</v>
       </c>
       <c r="E39" t="n">
-        <v>2.1</v>
+        <v>1.99</v>
       </c>
       <c r="F39" t="n">
         <v>8.99</v>
       </c>
       <c r="G39" t="n">
-        <v>71.5</v>
+        <v>67.7</v>
       </c>
       <c r="H39" t="n">
-        <v>37.6</v>
+        <v>29.2</v>
       </c>
       <c r="I39" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="J39" t="n">
-        <v>-92.23</v>
+        <v>-49.51</v>
       </c>
       <c r="K39" t="n">
-        <v>70.53</v>
+        <v>115.75</v>
       </c>
       <c r="L39" t="n">
-        <v>116.11</v>
+        <v>125.89</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>06:23:30</t>
+          <t>06:22:09</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1717,34 +1717,34 @@
         <v>3</v>
       </c>
       <c r="E40" t="n">
-        <v>2</v>
+        <v>1.64</v>
       </c>
       <c r="F40" t="n">
-        <v>9.539999999999999</v>
+        <v>7.8</v>
       </c>
       <c r="G40" t="n">
-        <v>53.1</v>
+        <v>64.7</v>
       </c>
       <c r="H40" t="n">
-        <v>32.8</v>
+        <v>31.8</v>
       </c>
       <c r="I40" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="J40" t="n">
-        <v>-40.86</v>
+        <v>88.92</v>
       </c>
       <c r="K40" t="n">
-        <v>104.52</v>
+        <v>65.76000000000001</v>
       </c>
       <c r="L40" t="n">
-        <v>112.22</v>
+        <v>110.6</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>06:27:51</t>
+          <t>06:26:28</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1759,34 +1759,34 @@
         <v>1</v>
       </c>
       <c r="E41" t="n">
-        <v>2</v>
+        <v>1.64</v>
       </c>
       <c r="F41" t="n">
-        <v>9.109999999999999</v>
+        <v>6.57</v>
       </c>
       <c r="G41" t="n">
-        <v>63.3</v>
+        <v>58.6</v>
       </c>
       <c r="H41" t="n">
-        <v>30.9</v>
+        <v>32</v>
       </c>
       <c r="I41" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="J41" t="n">
-        <v>-79.61</v>
+        <v>159.76</v>
       </c>
       <c r="K41" t="n">
-        <v>132.85</v>
+        <v>-151.61</v>
       </c>
       <c r="L41" t="n">
-        <v>154.88</v>
+        <v>220.25</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>06:29:10</t>
+          <t>06:27:26</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -1801,34 +1801,34 @@
         <v>2</v>
       </c>
       <c r="E42" t="n">
-        <v>1.65</v>
+        <v>1.92</v>
       </c>
       <c r="F42" t="n">
-        <v>8.960000000000001</v>
+        <v>5.02</v>
       </c>
       <c r="G42" t="n">
-        <v>68.59999999999999</v>
+        <v>78.59999999999999</v>
       </c>
       <c r="H42" t="n">
-        <v>31.1</v>
+        <v>34.9</v>
       </c>
       <c r="I42" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="J42" t="n">
-        <v>107.98</v>
+        <v>-9.74</v>
       </c>
       <c r="K42" t="n">
-        <v>84.11</v>
+        <v>183.72</v>
       </c>
       <c r="L42" t="n">
-        <v>136.87</v>
+        <v>183.98</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>06:30:17</t>
+          <t>06:29:15</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -1843,34 +1843,34 @@
         <v>3</v>
       </c>
       <c r="E43" t="n">
-        <v>1.65</v>
+        <v>1.85</v>
       </c>
       <c r="F43" t="n">
-        <v>8.65</v>
+        <v>7.93</v>
       </c>
       <c r="G43" t="n">
-        <v>68.90000000000001</v>
+        <v>58.6</v>
       </c>
       <c r="H43" t="n">
-        <v>32.9</v>
+        <v>33.3</v>
       </c>
       <c r="I43" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="J43" t="n">
-        <v>126.45</v>
+        <v>209.92</v>
       </c>
       <c r="K43" t="n">
-        <v>-150.15</v>
+        <v>14.85</v>
       </c>
       <c r="L43" t="n">
-        <v>196.3</v>
+        <v>210.45</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>06:41:01</t>
+          <t>06:39:21</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -1885,34 +1885,34 @@
         <v>1</v>
       </c>
       <c r="E44" t="n">
-        <v>1.94</v>
+        <v>1.48</v>
       </c>
       <c r="F44" t="n">
-        <v>9.65</v>
+        <v>6.01</v>
       </c>
       <c r="G44" t="n">
-        <v>74.8</v>
+        <v>54.4</v>
       </c>
       <c r="H44" t="n">
-        <v>25.2</v>
+        <v>34.7</v>
       </c>
       <c r="I44" t="n">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="J44" t="n">
-        <v>-12.61</v>
+        <v>41.49</v>
       </c>
       <c r="K44" t="n">
-        <v>39.7</v>
+        <v>-6.01</v>
       </c>
       <c r="L44" t="n">
-        <v>41.66</v>
+        <v>41.93</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>06:42:40</t>
+          <t>06:40:34</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -1927,34 +1927,34 @@
         <v>2</v>
       </c>
       <c r="E45" t="n">
-        <v>1.88</v>
+        <v>1.58</v>
       </c>
       <c r="F45" t="n">
-        <v>8.65</v>
+        <v>10.35</v>
       </c>
       <c r="G45" t="n">
-        <v>71.5</v>
+        <v>73</v>
       </c>
       <c r="H45" t="n">
-        <v>32.2</v>
+        <v>35</v>
       </c>
       <c r="I45" t="n">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="J45" t="n">
-        <v>40.66</v>
+        <v>-28.01</v>
       </c>
       <c r="K45" t="n">
-        <v>-2.28</v>
+        <v>45.99</v>
       </c>
       <c r="L45" t="n">
-        <v>40.72</v>
+        <v>53.85</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>06:43:46</t>
+          <t>06:42:34</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -1969,34 +1969,34 @@
         <v>3</v>
       </c>
       <c r="E46" t="n">
-        <v>1.49</v>
+        <v>2.34</v>
       </c>
       <c r="F46" t="n">
-        <v>8.44</v>
+        <v>10.35</v>
       </c>
       <c r="G46" t="n">
-        <v>74.3</v>
+        <v>52.7</v>
       </c>
       <c r="H46" t="n">
-        <v>29.4</v>
+        <v>24.3</v>
       </c>
       <c r="I46" t="n">
         <v>23</v>
       </c>
       <c r="J46" t="n">
-        <v>33.31</v>
+        <v>-29.19</v>
       </c>
       <c r="K46" t="n">
-        <v>-5.39</v>
+        <v>75.73</v>
       </c>
       <c r="L46" t="n">
-        <v>33.74</v>
+        <v>81.16</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>06:48:37</t>
+          <t>06:48:48</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -2011,34 +2011,34 @@
         <v>1</v>
       </c>
       <c r="E47" t="n">
-        <v>1.6</v>
+        <v>2.32</v>
       </c>
       <c r="F47" t="n">
-        <v>9.369999999999999</v>
+        <v>10.35</v>
       </c>
       <c r="G47" t="n">
-        <v>74.90000000000001</v>
+        <v>77.59999999999999</v>
       </c>
       <c r="H47" t="n">
-        <v>31.3</v>
+        <v>23.7</v>
       </c>
       <c r="I47" t="n">
         <v>23</v>
       </c>
       <c r="J47" t="n">
-        <v>-25.64</v>
+        <v>87.8</v>
       </c>
       <c r="K47" t="n">
-        <v>41.97</v>
+        <v>36.48</v>
       </c>
       <c r="L47" t="n">
-        <v>49.18</v>
+        <v>95.08</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>06:49:27</t>
+          <t>06:49:23</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2053,34 +2053,34 @@
         <v>2</v>
       </c>
       <c r="E48" t="n">
-        <v>2.35</v>
+        <v>1.92</v>
       </c>
       <c r="F48" t="n">
-        <v>8.359999999999999</v>
+        <v>9.880000000000001</v>
       </c>
       <c r="G48" t="n">
-        <v>53.6</v>
+        <v>77</v>
       </c>
       <c r="H48" t="n">
-        <v>37.9</v>
+        <v>29.5</v>
       </c>
       <c r="I48" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="J48" t="n">
-        <v>-35.35</v>
+        <v>21.88</v>
       </c>
       <c r="K48" t="n">
-        <v>91.56</v>
+        <v>-63.69</v>
       </c>
       <c r="L48" t="n">
-        <v>98.14</v>
+        <v>67.34</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>06:50:25</t>
+          <t>06:51:52</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2095,34 +2095,34 @@
         <v>3</v>
       </c>
       <c r="E49" t="n">
-        <v>2.33</v>
+        <v>2.32</v>
       </c>
       <c r="F49" t="n">
-        <v>9.6</v>
+        <v>10.35</v>
       </c>
       <c r="G49" t="n">
-        <v>52.3</v>
+        <v>73.40000000000001</v>
       </c>
       <c r="H49" t="n">
-        <v>26.6</v>
+        <v>27</v>
       </c>
       <c r="I49" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="J49" t="n">
-        <v>76.73</v>
+        <v>-41.85</v>
       </c>
       <c r="K49" t="n">
-        <v>32.8</v>
+        <v>83.66</v>
       </c>
       <c r="L49" t="n">
-        <v>83.45</v>
+        <v>93.54000000000001</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>06:55:40</t>
+          <t>06:56:17</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -2137,34 +2137,34 @@
         <v>1</v>
       </c>
       <c r="E50" t="n">
-        <v>1.93</v>
+        <v>1.64</v>
       </c>
       <c r="F50" t="n">
-        <v>9.57</v>
+        <v>1.98</v>
       </c>
       <c r="G50" t="n">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="H50" t="n">
-        <v>32.2</v>
+        <v>31.4</v>
       </c>
       <c r="I50" t="n">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="J50" t="n">
-        <v>23.48</v>
+        <v>69.98999999999999</v>
       </c>
       <c r="K50" t="n">
-        <v>-68.56</v>
+        <v>-5.6</v>
       </c>
       <c r="L50" t="n">
-        <v>72.47</v>
+        <v>70.20999999999999</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>06:56:38</t>
+          <t>06:58:38</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -2179,34 +2179,34 @@
         <v>2</v>
       </c>
       <c r="E51" t="n">
-        <v>2.33</v>
+        <v>2.26</v>
       </c>
       <c r="F51" t="n">
-        <v>9.390000000000001</v>
+        <v>10.35</v>
       </c>
       <c r="G51" t="n">
-        <v>59</v>
+        <v>63.2</v>
       </c>
       <c r="H51" t="n">
-        <v>33.3</v>
+        <v>28.4</v>
       </c>
       <c r="I51" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="J51" t="n">
-        <v>-47</v>
+        <v>-5.11</v>
       </c>
       <c r="K51" t="n">
-        <v>93.97</v>
+        <v>121.85</v>
       </c>
       <c r="L51" t="n">
-        <v>105.07</v>
+        <v>121.96</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>06:58:40</t>
+          <t>07:00:21</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -2221,34 +2221,34 @@
         <v>3</v>
       </c>
       <c r="E52" t="n">
-        <v>1.64</v>
+        <v>1.99</v>
       </c>
       <c r="F52" t="n">
-        <v>9.02</v>
+        <v>5.16</v>
       </c>
       <c r="G52" t="n">
-        <v>67.90000000000001</v>
+        <v>61</v>
       </c>
       <c r="H52" t="n">
-        <v>22.4</v>
+        <v>34.1</v>
       </c>
       <c r="I52" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="J52" t="n">
-        <v>68.06999999999999</v>
+        <v>113.59</v>
       </c>
       <c r="K52" t="n">
-        <v>-10.26</v>
+        <v>49.04</v>
       </c>
       <c r="L52" t="n">
-        <v>68.83</v>
+        <v>123.72</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>07:03:15</t>
+          <t>07:05:58</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -2263,34 +2263,34 @@
         <v>1</v>
       </c>
       <c r="E53" t="n">
-        <v>2.27</v>
+        <v>2.25</v>
       </c>
       <c r="F53" t="n">
-        <v>8.880000000000001</v>
+        <v>9.93</v>
       </c>
       <c r="G53" t="n">
-        <v>61.8</v>
+        <v>74.7</v>
       </c>
       <c r="H53" t="n">
-        <v>31.5</v>
+        <v>33.4</v>
       </c>
       <c r="I53" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="J53" t="n">
-        <v>-11.03</v>
+        <v>211.26</v>
       </c>
       <c r="K53" t="n">
-        <v>127.59</v>
+        <v>-12.45</v>
       </c>
       <c r="L53" t="n">
-        <v>128.06</v>
+        <v>211.62</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>07:05:50</t>
+          <t>07:07:55</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -2305,34 +2305,34 @@
         <v>2</v>
       </c>
       <c r="E54" t="n">
-        <v>2</v>
+        <v>1.57</v>
       </c>
       <c r="F54" t="n">
-        <v>8.77</v>
+        <v>2.51</v>
       </c>
       <c r="G54" t="n">
-        <v>73.09999999999999</v>
+        <v>63.7</v>
       </c>
       <c r="H54" t="n">
-        <v>24.7</v>
+        <v>28.6</v>
       </c>
       <c r="I54" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="J54" t="n">
-        <v>138.77</v>
+        <v>12.31</v>
       </c>
       <c r="K54" t="n">
-        <v>58.12</v>
+        <v>95.47</v>
       </c>
       <c r="L54" t="n">
-        <v>150.45</v>
+        <v>96.26000000000001</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>07:07:48</t>
+          <t>07:09:32</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -2347,34 +2347,34 @@
         <v>3</v>
       </c>
       <c r="E55" t="n">
-        <v>2.25</v>
+        <v>1.99</v>
       </c>
       <c r="F55" t="n">
-        <v>9.449999999999999</v>
+        <v>7.45</v>
       </c>
       <c r="G55" t="n">
-        <v>71.8</v>
+        <v>68</v>
       </c>
       <c r="H55" t="n">
-        <v>29.2</v>
+        <v>24.2</v>
       </c>
       <c r="I55" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J55" t="n">
-        <v>177.56</v>
+        <v>129.8</v>
       </c>
       <c r="K55" t="n">
-        <v>-14.14</v>
+        <v>7.58</v>
       </c>
       <c r="L55" t="n">
-        <v>178.12</v>
+        <v>130.02</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>07:12:45</t>
+          <t>07:12:49</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -2389,34 +2389,34 @@
         <v>1</v>
       </c>
       <c r="E56" t="n">
-        <v>1.58</v>
+        <v>1.98</v>
       </c>
       <c r="F56" t="n">
-        <v>8.91</v>
+        <v>10.35</v>
       </c>
       <c r="G56" t="n">
-        <v>62.3</v>
+        <v>81.40000000000001</v>
       </c>
       <c r="H56" t="n">
-        <v>23.5</v>
+        <v>30.3</v>
       </c>
       <c r="I56" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="J56" t="n">
-        <v>7.07</v>
+        <v>172.13</v>
       </c>
       <c r="K56" t="n">
-        <v>154.45</v>
+        <v>-54.31</v>
       </c>
       <c r="L56" t="n">
-        <v>154.61</v>
+        <v>180.49</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>07:14:17</t>
+          <t>07:14:05</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -2431,34 +2431,34 @@
         <v>2</v>
       </c>
       <c r="E57" t="n">
-        <v>2</v>
+        <v>2.14</v>
       </c>
       <c r="F57" t="n">
-        <v>9.119999999999999</v>
+        <v>10.13</v>
       </c>
       <c r="G57" t="n">
-        <v>53.3</v>
+        <v>68.40000000000001</v>
       </c>
       <c r="H57" t="n">
-        <v>36</v>
+        <v>31.6</v>
       </c>
       <c r="I57" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="J57" t="n">
-        <v>160.9</v>
+        <v>57.32</v>
       </c>
       <c r="K57" t="n">
-        <v>7.11</v>
+        <v>244.14</v>
       </c>
       <c r="L57" t="n">
-        <v>161.06</v>
+        <v>250.78</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>07:15:15</t>
+          <t>07:15:25</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -2473,34 +2473,34 @@
         <v>3</v>
       </c>
       <c r="E58" t="n">
-        <v>1.99</v>
+        <v>2.11</v>
       </c>
       <c r="F58" t="n">
-        <v>9.789999999999999</v>
+        <v>9.74</v>
       </c>
       <c r="G58" t="n">
-        <v>65.59999999999999</v>
+        <v>59.8</v>
       </c>
       <c r="H58" t="n">
-        <v>35.9</v>
+        <v>34.1</v>
       </c>
       <c r="I58" t="n">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="J58" t="n">
-        <v>38.18</v>
+        <v>-118.78</v>
       </c>
       <c r="K58" t="n">
-        <v>-36.07</v>
+        <v>171.17</v>
       </c>
       <c r="L58" t="n">
-        <v>52.53</v>
+        <v>208.35</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>07:26:40</t>
+          <t>07:26:39</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -2515,34 +2515,34 @@
         <v>1</v>
       </c>
       <c r="E59" t="n">
-        <v>2.16</v>
+        <v>1.93</v>
       </c>
       <c r="F59" t="n">
-        <v>9.140000000000001</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="G59" t="n">
-        <v>68.2</v>
+        <v>77.90000000000001</v>
       </c>
       <c r="H59" t="n">
-        <v>30.3</v>
+        <v>29.2</v>
       </c>
       <c r="I59" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="J59" t="n">
-        <v>3.99</v>
+        <v>-45.41</v>
       </c>
       <c r="K59" t="n">
-        <v>57.23</v>
+        <v>39.53</v>
       </c>
       <c r="L59" t="n">
-        <v>57.36</v>
+        <v>60.21</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>07:28:12</t>
+          <t>07:28:08</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -2557,34 +2557,34 @@
         <v>2</v>
       </c>
       <c r="E60" t="n">
-        <v>2.13</v>
+        <v>1.75</v>
       </c>
       <c r="F60" t="n">
-        <v>8.710000000000001</v>
+        <v>9.529999999999999</v>
       </c>
       <c r="G60" t="n">
-        <v>73.3</v>
+        <v>80.40000000000001</v>
       </c>
       <c r="H60" t="n">
-        <v>30.5</v>
+        <v>32.8</v>
       </c>
       <c r="I60" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J60" t="n">
-        <v>-38.04</v>
+        <v>27.64</v>
       </c>
       <c r="K60" t="n">
-        <v>25.41</v>
+        <v>55.17</v>
       </c>
       <c r="L60" t="n">
-        <v>45.75</v>
+        <v>61.7</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>07:30:09</t>
+          <t>07:29:11</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -2599,34 +2599,34 @@
         <v>3</v>
       </c>
       <c r="E61" t="n">
-        <v>1.93</v>
+        <v>1.82</v>
       </c>
       <c r="F61" t="n">
-        <v>9.619999999999999</v>
+        <v>7.56</v>
       </c>
       <c r="G61" t="n">
-        <v>63.4</v>
+        <v>70</v>
       </c>
       <c r="H61" t="n">
-        <v>27.1</v>
+        <v>24.7</v>
       </c>
       <c r="I61" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="J61" t="n">
-        <v>-44.09</v>
+        <v>56.02</v>
       </c>
       <c r="K61" t="n">
-        <v>38.07</v>
+        <v>22.22</v>
       </c>
       <c r="L61" t="n">
-        <v>58.25</v>
+        <v>60.26</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>07:34:48</t>
+          <t>07:35:20</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -2641,34 +2641,34 @@
         <v>1</v>
       </c>
       <c r="E62" t="n">
-        <v>1.76</v>
+        <v>2.57</v>
       </c>
       <c r="F62" t="n">
-        <v>9.74</v>
+        <v>10.35</v>
       </c>
       <c r="G62" t="n">
-        <v>70.5</v>
+        <v>67.5</v>
       </c>
       <c r="H62" t="n">
-        <v>32.5</v>
+        <v>27.1</v>
       </c>
       <c r="I62" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="J62" t="n">
-        <v>32.66</v>
+        <v>87.67</v>
       </c>
       <c r="K62" t="n">
-        <v>65.54000000000001</v>
+        <v>-63.64</v>
       </c>
       <c r="L62" t="n">
-        <v>73.23</v>
+        <v>108.33</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>07:35:54</t>
+          <t>07:37:27</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -2683,34 +2683,34 @@
         <v>2</v>
       </c>
       <c r="E63" t="n">
-        <v>1.83</v>
+        <v>2.6</v>
       </c>
       <c r="F63" t="n">
-        <v>9.220000000000001</v>
+        <v>10.35</v>
       </c>
       <c r="G63" t="n">
-        <v>54.3</v>
+        <v>67.2</v>
       </c>
       <c r="H63" t="n">
-        <v>31.6</v>
+        <v>27.2</v>
       </c>
       <c r="I63" t="n">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="J63" t="n">
-        <v>62.12</v>
+        <v>93.04000000000001</v>
       </c>
       <c r="K63" t="n">
-        <v>24.95</v>
+        <v>-79.16</v>
       </c>
       <c r="L63" t="n">
-        <v>66.94</v>
+        <v>122.16</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>07:37:10</t>
+          <t>07:38:18</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -2725,34 +2725,34 @@
         <v>3</v>
       </c>
       <c r="E64" t="n">
-        <v>2.57</v>
+        <v>1.61</v>
       </c>
       <c r="F64" t="n">
-        <v>9.1</v>
+        <v>10.35</v>
       </c>
       <c r="G64" t="n">
-        <v>59.2</v>
+        <v>66.59999999999999</v>
       </c>
       <c r="H64" t="n">
-        <v>29.1</v>
+        <v>34.1</v>
       </c>
       <c r="I64" t="n">
         <v>22</v>
       </c>
       <c r="J64" t="n">
-        <v>73.94</v>
+        <v>-11.88</v>
       </c>
       <c r="K64" t="n">
-        <v>-55.61</v>
+        <v>66.37</v>
       </c>
       <c r="L64" t="n">
-        <v>92.52</v>
+        <v>67.42</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>07:42:00</t>
+          <t>07:43:52</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -2767,34 +2767,34 @@
         <v>1</v>
       </c>
       <c r="E65" t="n">
-        <v>2.61</v>
+        <v>2.5</v>
       </c>
       <c r="F65" t="n">
-        <v>9.08</v>
+        <v>9.460000000000001</v>
       </c>
       <c r="G65" t="n">
-        <v>59.3</v>
+        <v>66.5</v>
       </c>
       <c r="H65" t="n">
-        <v>37.5</v>
+        <v>33.3</v>
       </c>
       <c r="I65" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="J65" t="n">
-        <v>115.05</v>
+        <v>-14.73</v>
       </c>
       <c r="K65" t="n">
-        <v>-97.68000000000001</v>
+        <v>46.24</v>
       </c>
       <c r="L65" t="n">
-        <v>150.92</v>
+        <v>48.53</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>07:42:55</t>
+          <t>07:45:07</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -2809,34 +2809,34 @@
         <v>2</v>
       </c>
       <c r="E66" t="n">
-        <v>1.61</v>
+        <v>2.14</v>
       </c>
       <c r="F66" t="n">
-        <v>9.050000000000001</v>
+        <v>9.109999999999999</v>
       </c>
       <c r="G66" t="n">
-        <v>73.2</v>
+        <v>68.59999999999999</v>
       </c>
       <c r="H66" t="n">
-        <v>35.6</v>
+        <v>36.8</v>
       </c>
       <c r="I66" t="n">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="J66" t="n">
-        <v>-11.43</v>
+        <v>61.23</v>
       </c>
       <c r="K66" t="n">
-        <v>64.02</v>
+        <v>99.47</v>
       </c>
       <c r="L66" t="n">
-        <v>65.04000000000001</v>
+        <v>116.8</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>07:43:47</t>
+          <t>07:47:26</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -2851,34 +2851,34 @@
         <v>3</v>
       </c>
       <c r="E67" t="n">
-        <v>2.5</v>
+        <v>2.26</v>
       </c>
       <c r="F67" t="n">
-        <v>9.039999999999999</v>
+        <v>6.38</v>
       </c>
       <c r="G67" t="n">
-        <v>71.5</v>
+        <v>69.09999999999999</v>
       </c>
       <c r="H67" t="n">
-        <v>32.2</v>
+        <v>35.4</v>
       </c>
       <c r="I67" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="J67" t="n">
-        <v>-31.48</v>
+        <v>51.1</v>
       </c>
       <c r="K67" t="n">
-        <v>32.39</v>
+        <v>122.57</v>
       </c>
       <c r="L67" t="n">
-        <v>45.17</v>
+        <v>132.8</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>07:47:30</t>
+          <t>07:52:22</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -2893,34 +2893,34 @@
         <v>1</v>
       </c>
       <c r="E68" t="n">
-        <v>2.14</v>
+        <v>2.45</v>
       </c>
       <c r="F68" t="n">
-        <v>9.15</v>
+        <v>8.949999999999999</v>
       </c>
       <c r="G68" t="n">
-        <v>78.5</v>
+        <v>46.5</v>
       </c>
       <c r="H68" t="n">
-        <v>29.1</v>
+        <v>27.3</v>
       </c>
       <c r="I68" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J68" t="n">
-        <v>68.3</v>
+        <v>124.89</v>
       </c>
       <c r="K68" t="n">
-        <v>115.59</v>
+        <v>131.85</v>
       </c>
       <c r="L68" t="n">
-        <v>134.26</v>
+        <v>181.6</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>07:49:58</t>
+          <t>07:54:08</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -2935,34 +2935,34 @@
         <v>2</v>
       </c>
       <c r="E69" t="n">
-        <v>2.26</v>
+        <v>3.98</v>
       </c>
       <c r="F69" t="n">
-        <v>9.18</v>
+        <v>10.35</v>
       </c>
       <c r="G69" t="n">
-        <v>75.8</v>
+        <v>79.59999999999999</v>
       </c>
       <c r="H69" t="n">
-        <v>20.3</v>
+        <v>26.4</v>
       </c>
       <c r="I69" t="n">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="J69" t="n">
-        <v>58.17</v>
+        <v>20.88</v>
       </c>
       <c r="K69" t="n">
-        <v>146.16</v>
+        <v>-198.24</v>
       </c>
       <c r="L69" t="n">
-        <v>157.32</v>
+        <v>199.33</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>07:52:32</t>
+          <t>07:56:03</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -2977,34 +2977,34 @@
         <v>3</v>
       </c>
       <c r="E70" t="n">
-        <v>2.45</v>
+        <v>2.13</v>
       </c>
       <c r="F70" t="n">
-        <v>8.050000000000001</v>
+        <v>8.93</v>
       </c>
       <c r="G70" t="n">
-        <v>59.5</v>
+        <v>65.59999999999999</v>
       </c>
       <c r="H70" t="n">
-        <v>26.8</v>
+        <v>26.6</v>
       </c>
       <c r="I70" t="n">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="J70" t="n">
-        <v>104.44</v>
+        <v>6.18</v>
       </c>
       <c r="K70" t="n">
-        <v>108.8</v>
+        <v>193.84</v>
       </c>
       <c r="L70" t="n">
-        <v>150.81</v>
+        <v>193.94</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>07:55:54</t>
+          <t>07:59:24</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -3019,34 +3019,34 @@
         <v>1</v>
       </c>
       <c r="E71" t="n">
-        <v>3.98</v>
+        <v>2.1</v>
       </c>
       <c r="F71" t="n">
-        <v>9.699999999999999</v>
+        <v>8.51</v>
       </c>
       <c r="G71" t="n">
-        <v>57.8</v>
+        <v>85.59999999999999</v>
       </c>
       <c r="H71" t="n">
-        <v>29.6</v>
+        <v>30.2</v>
       </c>
       <c r="I71" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="J71" t="n">
-        <v>-4.82</v>
+        <v>133.58</v>
       </c>
       <c r="K71" t="n">
-        <v>-282.29</v>
+        <v>-158.24</v>
       </c>
       <c r="L71" t="n">
-        <v>282.33</v>
+        <v>207.08</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>07:58:02</t>
+          <t>08:00:30</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -3061,34 +3061,34 @@
         <v>2</v>
       </c>
       <c r="E72" t="n">
-        <v>2.14</v>
+        <v>1.26</v>
       </c>
       <c r="F72" t="n">
-        <v>9</v>
+        <v>10.35</v>
       </c>
       <c r="G72" t="n">
-        <v>58.1</v>
+        <v>78.7</v>
       </c>
       <c r="H72" t="n">
-        <v>28.9</v>
+        <v>32.7</v>
       </c>
       <c r="I72" t="n">
         <v>21</v>
       </c>
       <c r="J72" t="n">
-        <v>-5.94</v>
+        <v>-340.18</v>
       </c>
       <c r="K72" t="n">
-        <v>252.25</v>
+        <v>-167.97</v>
       </c>
       <c r="L72" t="n">
-        <v>252.32</v>
+        <v>379.39</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>07:58:59</t>
+          <t>08:02:49</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -3103,34 +3103,34 @@
         <v>3</v>
       </c>
       <c r="E73" t="n">
-        <v>2.1</v>
+        <v>2.17</v>
       </c>
       <c r="F73" t="n">
-        <v>10</v>
+        <v>10.09</v>
       </c>
       <c r="G73" t="n">
-        <v>65.40000000000001</v>
+        <v>61.6</v>
       </c>
       <c r="H73" t="n">
-        <v>27.2</v>
+        <v>34.1</v>
       </c>
       <c r="I73" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="J73" t="n">
-        <v>78.68000000000001</v>
+        <v>158.17</v>
       </c>
       <c r="K73" t="n">
-        <v>-135.68</v>
+        <v>-69.23999999999999</v>
       </c>
       <c r="L73" t="n">
-        <v>156.84</v>
+        <v>172.66</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>08:10:03</t>
+          <t>08:16:22</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -3145,34 +3145,34 @@
         <v>1</v>
       </c>
       <c r="E74" t="n">
-        <v>1.27</v>
+        <v>1.82</v>
       </c>
       <c r="F74" t="n">
-        <v>9.66</v>
+        <v>10.35</v>
       </c>
       <c r="G74" t="n">
-        <v>70.40000000000001</v>
+        <v>73.8</v>
       </c>
       <c r="H74" t="n">
-        <v>39.8</v>
+        <v>34.7</v>
       </c>
       <c r="I74" t="n">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="J74" t="n">
-        <v>-51.54</v>
+        <v>-55.99</v>
       </c>
       <c r="K74" t="n">
-        <v>-24.27</v>
+        <v>43.64</v>
       </c>
       <c r="L74" t="n">
-        <v>56.97</v>
+        <v>70.98999999999999</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>08:11:28</t>
+          <t>08:17:14</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -3187,34 +3187,34 @@
         <v>2</v>
       </c>
       <c r="E75" t="n">
-        <v>2.18</v>
+        <v>2.34</v>
       </c>
       <c r="F75" t="n">
-        <v>8.800000000000001</v>
+        <v>9.98</v>
       </c>
       <c r="G75" t="n">
-        <v>73.09999999999999</v>
+        <v>75.09999999999999</v>
       </c>
       <c r="H75" t="n">
-        <v>28.2</v>
+        <v>33.8</v>
       </c>
       <c r="I75" t="n">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="J75" t="n">
-        <v>18.15</v>
+        <v>-36.26</v>
       </c>
       <c r="K75" t="n">
-        <v>-31.33</v>
+        <v>61.73</v>
       </c>
       <c r="L75" t="n">
-        <v>36.2</v>
+        <v>71.59</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>08:13:14</t>
+          <t>08:18:42</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -3229,34 +3229,34 @@
         <v>3</v>
       </c>
       <c r="E76" t="n">
-        <v>1.82</v>
+        <v>1.9</v>
       </c>
       <c r="F76" t="n">
-        <v>9.41</v>
+        <v>8.630000000000001</v>
       </c>
       <c r="G76" t="n">
-        <v>74.5</v>
+        <v>66</v>
       </c>
       <c r="H76" t="n">
-        <v>37.8</v>
+        <v>28.8</v>
       </c>
       <c r="I76" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="J76" t="n">
-        <v>-43.74</v>
+        <v>35.34</v>
       </c>
       <c r="K76" t="n">
-        <v>33.77</v>
+        <v>-31.24</v>
       </c>
       <c r="L76" t="n">
-        <v>55.26</v>
+        <v>47.17</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>08:17:57</t>
+          <t>08:22:12</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -3271,34 +3271,34 @@
         <v>1</v>
       </c>
       <c r="E77" t="n">
-        <v>2.34</v>
+        <v>2.41</v>
       </c>
       <c r="F77" t="n">
-        <v>9.470000000000001</v>
+        <v>10.35</v>
       </c>
       <c r="G77" t="n">
-        <v>72.5</v>
+        <v>65.5</v>
       </c>
       <c r="H77" t="n">
-        <v>24.4</v>
+        <v>28.5</v>
       </c>
       <c r="I77" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J77" t="n">
-        <v>-37.5</v>
+        <v>79.68000000000001</v>
       </c>
       <c r="K77" t="n">
-        <v>63.76</v>
+        <v>53.8</v>
       </c>
       <c r="L77" t="n">
-        <v>73.97</v>
+        <v>96.15000000000001</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>08:18:53</t>
+          <t>08:24:05</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -3313,34 +3313,34 @@
         <v>2</v>
       </c>
       <c r="E78" t="n">
-        <v>1.9</v>
+        <v>2.06</v>
       </c>
       <c r="F78" t="n">
-        <v>9.02</v>
+        <v>10.35</v>
       </c>
       <c r="G78" t="n">
-        <v>62.5</v>
+        <v>64.59999999999999</v>
       </c>
       <c r="H78" t="n">
-        <v>29.9</v>
+        <v>30.8</v>
       </c>
       <c r="I78" t="n">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="J78" t="n">
-        <v>35.77</v>
+        <v>-57.54</v>
       </c>
       <c r="K78" t="n">
-        <v>-31.67</v>
+        <v>-36.86</v>
       </c>
       <c r="L78" t="n">
-        <v>47.77</v>
+        <v>68.34</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>08:19:59</t>
+          <t>08:26:13</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -3355,34 +3355,34 @@
         <v>3</v>
       </c>
       <c r="E79" t="n">
-        <v>2.41</v>
+        <v>2.02</v>
       </c>
       <c r="F79" t="n">
-        <v>9</v>
+        <v>10.35</v>
       </c>
       <c r="G79" t="n">
-        <v>61.9</v>
+        <v>60</v>
       </c>
       <c r="H79" t="n">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="I79" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="J79" t="n">
-        <v>65.28</v>
+        <v>-67.43000000000001</v>
       </c>
       <c r="K79" t="n">
-        <v>44.44</v>
+        <v>23.1</v>
       </c>
       <c r="L79" t="n">
-        <v>78.97</v>
+        <v>71.28</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>08:25:53</t>
+          <t>08:30:47</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -3397,34 +3397,34 @@
         <v>1</v>
       </c>
       <c r="E80" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="F80" t="n">
-        <v>8.949999999999999</v>
+        <v>10.35</v>
       </c>
       <c r="G80" t="n">
-        <v>66.7</v>
+        <v>70.40000000000001</v>
       </c>
       <c r="H80" t="n">
-        <v>36.5</v>
+        <v>29.7</v>
       </c>
       <c r="I80" t="n">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="J80" t="n">
-        <v>-56.41</v>
+        <v>15.56</v>
       </c>
       <c r="K80" t="n">
-        <v>-36.39</v>
+        <v>87.84999999999999</v>
       </c>
       <c r="L80" t="n">
-        <v>67.13</v>
+        <v>89.22</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>08:28:03</t>
+          <t>08:32:17</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -3439,34 +3439,34 @@
         <v>2</v>
       </c>
       <c r="E81" t="n">
-        <v>2.03</v>
+        <v>2.11</v>
       </c>
       <c r="F81" t="n">
-        <v>8.720000000000001</v>
+        <v>8.380000000000001</v>
       </c>
       <c r="G81" t="n">
-        <v>61</v>
+        <v>49.8</v>
       </c>
       <c r="H81" t="n">
-        <v>27.3</v>
+        <v>30.4</v>
       </c>
       <c r="I81" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="J81" t="n">
-        <v>-79.39</v>
+        <v>142.08</v>
       </c>
       <c r="K81" t="n">
-        <v>27.1</v>
+        <v>15.98</v>
       </c>
       <c r="L81" t="n">
-        <v>83.89</v>
+        <v>142.98</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>08:30:08</t>
+          <t>08:35:06</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -3481,34 +3481,34 @@
         <v>3</v>
       </c>
       <c r="E82" t="n">
-        <v>2.05</v>
+        <v>2.29</v>
       </c>
       <c r="F82" t="n">
-        <v>9.24</v>
+        <v>7.23</v>
       </c>
       <c r="G82" t="n">
-        <v>64.40000000000001</v>
+        <v>62.2</v>
       </c>
       <c r="H82" t="n">
-        <v>39.7</v>
+        <v>34</v>
       </c>
       <c r="I82" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="J82" t="n">
-        <v>-3.88</v>
+        <v>-6.17</v>
       </c>
       <c r="K82" t="n">
-        <v>66.08</v>
+        <v>94.54000000000001</v>
       </c>
       <c r="L82" t="n">
-        <v>66.19</v>
+        <v>94.73999999999999</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>08:33:49</t>
+          <t>08:40:54</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -3523,34 +3523,34 @@
         <v>1</v>
       </c>
       <c r="E83" t="n">
-        <v>2.11</v>
+        <v>2.06</v>
       </c>
       <c r="F83" t="n">
-        <v>8.210000000000001</v>
+        <v>8.380000000000001</v>
       </c>
       <c r="G83" t="n">
-        <v>65.7</v>
+        <v>68.8</v>
       </c>
       <c r="H83" t="n">
-        <v>28.3</v>
+        <v>32.8</v>
       </c>
       <c r="I83" t="n">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="J83" t="n">
-        <v>158.52</v>
+        <v>-39.51</v>
       </c>
       <c r="K83" t="n">
-        <v>14.38</v>
+        <v>-212.34</v>
       </c>
       <c r="L83" t="n">
-        <v>159.17</v>
+        <v>215.98</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>08:34:33</t>
+          <t>08:42:00</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -3565,34 +3565,34 @@
         <v>2</v>
       </c>
       <c r="E84" t="n">
-        <v>2.29</v>
+        <v>2.42</v>
       </c>
       <c r="F84" t="n">
-        <v>8.83</v>
+        <v>10.35</v>
       </c>
       <c r="G84" t="n">
-        <v>73</v>
+        <v>75.2</v>
       </c>
       <c r="H84" t="n">
-        <v>25</v>
+        <v>31.7</v>
       </c>
       <c r="I84" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="J84" t="n">
-        <v>-13.6</v>
+        <v>-208.49</v>
       </c>
       <c r="K84" t="n">
-        <v>118.1</v>
+        <v>63.78</v>
       </c>
       <c r="L84" t="n">
-        <v>118.88</v>
+        <v>218.03</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>08:36:24</t>
+          <t>08:44:37</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -3607,34 +3607,34 @@
         <v>3</v>
       </c>
       <c r="E85" t="n">
-        <v>2.05</v>
+        <v>2.02</v>
       </c>
       <c r="F85" t="n">
-        <v>9.16</v>
+        <v>10.35</v>
       </c>
       <c r="G85" t="n">
-        <v>70.59999999999999</v>
+        <v>58.3</v>
       </c>
       <c r="H85" t="n">
-        <v>35</v>
+        <v>29.2</v>
       </c>
       <c r="I85" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="J85" t="n">
-        <v>-41.96</v>
+        <v>-164.53</v>
       </c>
       <c r="K85" t="n">
-        <v>-180.4</v>
+        <v>-48.7</v>
       </c>
       <c r="L85" t="n">
-        <v>185.22</v>
+        <v>171.59</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>08:41:47</t>
+          <t>08:50:41</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -3649,34 +3649,34 @@
         <v>1</v>
       </c>
       <c r="E86" t="n">
-        <v>2.42</v>
+        <v>1.7</v>
       </c>
       <c r="F86" t="n">
-        <v>9.48</v>
+        <v>8.42</v>
       </c>
       <c r="G86" t="n">
-        <v>68.40000000000001</v>
+        <v>65.3</v>
       </c>
       <c r="H86" t="n">
-        <v>35</v>
+        <v>32.4</v>
       </c>
       <c r="I86" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="J86" t="n">
-        <v>-254.59</v>
+        <v>-174.84</v>
       </c>
       <c r="K86" t="n">
-        <v>71.25</v>
+        <v>-51.36</v>
       </c>
       <c r="L86" t="n">
-        <v>264.37</v>
+        <v>182.22</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>08:43:47</t>
+          <t>08:51:31</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -3691,34 +3691,34 @@
         <v>2</v>
       </c>
       <c r="E87" t="n">
-        <v>2.02</v>
+        <v>1.89</v>
       </c>
       <c r="F87" t="n">
-        <v>8.630000000000001</v>
+        <v>4.86</v>
       </c>
       <c r="G87" t="n">
-        <v>63.4</v>
+        <v>68.59999999999999</v>
       </c>
       <c r="H87" t="n">
-        <v>32.7</v>
+        <v>28</v>
       </c>
       <c r="I87" t="n">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="J87" t="n">
-        <v>-194.02</v>
+        <v>100.36</v>
       </c>
       <c r="K87" t="n">
-        <v>-61.89</v>
+        <v>152.55</v>
       </c>
       <c r="L87" t="n">
-        <v>203.65</v>
+        <v>182.6</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>08:46:18</t>
+          <t>08:53:27</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -3733,28 +3733,28 @@
         <v>3</v>
       </c>
       <c r="E88" t="n">
-        <v>1.7</v>
+        <v>1.53</v>
       </c>
       <c r="F88" t="n">
-        <v>8.99</v>
+        <v>10.31</v>
       </c>
       <c r="G88" t="n">
-        <v>69.90000000000001</v>
+        <v>80.40000000000001</v>
       </c>
       <c r="H88" t="n">
-        <v>30.8</v>
+        <v>32.3</v>
       </c>
       <c r="I88" t="n">
         <v>21</v>
       </c>
       <c r="J88" t="n">
-        <v>-156.08</v>
+        <v>192.1</v>
       </c>
       <c r="K88" t="n">
-        <v>-51.82</v>
+        <v>-77.58</v>
       </c>
       <c r="L88" t="n">
-        <v>164.45</v>
+        <v>207.17</v>
       </c>
     </row>
   </sheetData>

--- a/output/2024-07-26.xlsx
+++ b/output/2024-07-26.xlsx
@@ -640,13 +640,13 @@
         <v>25</v>
       </c>
       <c r="J14" t="n">
-        <v>-15.82</v>
+        <v>-15.5</v>
       </c>
       <c r="K14" t="n">
-        <v>39.43</v>
+        <v>38.63</v>
       </c>
       <c r="L14" t="n">
-        <v>42.49</v>
+        <v>41.62</v>
       </c>
     </row>
     <row r="15">
@@ -682,13 +682,13 @@
         <v>20</v>
       </c>
       <c r="J15" t="n">
-        <v>-44.31</v>
+        <v>-47.6</v>
       </c>
       <c r="K15" t="n">
-        <v>38.68</v>
+        <v>41.54</v>
       </c>
       <c r="L15" t="n">
-        <v>58.82</v>
+        <v>63.18</v>
       </c>
     </row>
     <row r="16">
@@ -724,13 +724,13 @@
         <v>20</v>
       </c>
       <c r="J16" t="n">
-        <v>38.45</v>
+        <v>41.3</v>
       </c>
       <c r="K16" t="n">
-        <v>7.21</v>
+        <v>7.74</v>
       </c>
       <c r="L16" t="n">
-        <v>39.12</v>
+        <v>42.02</v>
       </c>
     </row>
     <row r="17">
@@ -766,13 +766,13 @@
         <v>22</v>
       </c>
       <c r="J17" t="n">
-        <v>74.52</v>
+        <v>77.38</v>
       </c>
       <c r="K17" t="n">
-        <v>-5.94</v>
+        <v>-6.17</v>
       </c>
       <c r="L17" t="n">
-        <v>74.75</v>
+        <v>77.63</v>
       </c>
     </row>
     <row r="18">
@@ -808,13 +808,13 @@
         <v>22</v>
       </c>
       <c r="J18" t="n">
-        <v>-13.62</v>
+        <v>-14.15</v>
       </c>
       <c r="K18" t="n">
-        <v>57.54</v>
+        <v>59.75</v>
       </c>
       <c r="L18" t="n">
-        <v>59.13</v>
+        <v>61.41</v>
       </c>
     </row>
     <row r="19">
@@ -934,13 +934,13 @@
         <v>22</v>
       </c>
       <c r="J21" t="n">
-        <v>-99.54000000000001</v>
+        <v>-103.37</v>
       </c>
       <c r="K21" t="n">
-        <v>-63.99</v>
+        <v>-66.45</v>
       </c>
       <c r="L21" t="n">
-        <v>118.33</v>
+        <v>122.88</v>
       </c>
     </row>
     <row r="22">
@@ -1060,13 +1060,13 @@
         <v>23</v>
       </c>
       <c r="J24" t="n">
-        <v>57.32</v>
+        <v>58.45</v>
       </c>
       <c r="K24" t="n">
-        <v>-105.69</v>
+        <v>-107.76</v>
       </c>
       <c r="L24" t="n">
-        <v>120.23</v>
+        <v>122.59</v>
       </c>
     </row>
     <row r="25">
@@ -1102,13 +1102,13 @@
         <v>21</v>
       </c>
       <c r="J25" t="n">
-        <v>122.43</v>
+        <v>129.36</v>
       </c>
       <c r="K25" t="n">
-        <v>-58.05</v>
+        <v>-61.33</v>
       </c>
       <c r="L25" t="n">
-        <v>135.49</v>
+        <v>143.16</v>
       </c>
     </row>
     <row r="26">
@@ -1144,13 +1144,13 @@
         <v>20</v>
       </c>
       <c r="J26" t="n">
-        <v>-380</v>
+        <v>-408.15</v>
       </c>
       <c r="K26" t="n">
-        <v>-27.26</v>
+        <v>-29.28</v>
       </c>
       <c r="L26" t="n">
-        <v>380.98</v>
+        <v>409.2</v>
       </c>
     </row>
     <row r="27">
@@ -1186,13 +1186,13 @@
         <v>25</v>
       </c>
       <c r="J27" t="n">
-        <v>190.63</v>
+        <v>186.74</v>
       </c>
       <c r="K27" t="n">
-        <v>94.61</v>
+        <v>92.68000000000001</v>
       </c>
       <c r="L27" t="n">
-        <v>212.82</v>
+        <v>208.47</v>
       </c>
     </row>
     <row r="28">
@@ -1228,13 +1228,13 @@
         <v>22</v>
       </c>
       <c r="J28" t="n">
-        <v>-138.89</v>
+        <v>-144.23</v>
       </c>
       <c r="K28" t="n">
-        <v>156.03</v>
+        <v>162.03</v>
       </c>
       <c r="L28" t="n">
-        <v>208.89</v>
+        <v>216.92</v>
       </c>
     </row>
     <row r="29">
@@ -1312,13 +1312,13 @@
         <v>25</v>
       </c>
       <c r="J30" t="n">
-        <v>37.24</v>
+        <v>36.48</v>
       </c>
       <c r="K30" t="n">
-        <v>27.26</v>
+        <v>26.7</v>
       </c>
       <c r="L30" t="n">
-        <v>46.15</v>
+        <v>45.21</v>
       </c>
     </row>
     <row r="31">
@@ -1354,13 +1354,13 @@
         <v>23</v>
       </c>
       <c r="J31" t="n">
-        <v>30.95</v>
+        <v>31.56</v>
       </c>
       <c r="K31" t="n">
-        <v>40.99</v>
+        <v>41.8</v>
       </c>
       <c r="L31" t="n">
-        <v>51.37</v>
+        <v>52.37</v>
       </c>
     </row>
     <row r="32">
@@ -1396,13 +1396,13 @@
         <v>21</v>
       </c>
       <c r="J32" t="n">
-        <v>-64.06999999999999</v>
+        <v>-67.69</v>
       </c>
       <c r="K32" t="n">
-        <v>75.48999999999999</v>
+        <v>79.76000000000001</v>
       </c>
       <c r="L32" t="n">
-        <v>99.01000000000001</v>
+        <v>104.61</v>
       </c>
     </row>
     <row r="33">
@@ -1438,13 +1438,13 @@
         <v>19</v>
       </c>
       <c r="J33" t="n">
-        <v>74.52</v>
+        <v>81.29000000000001</v>
       </c>
       <c r="K33" t="n">
-        <v>29.68</v>
+        <v>32.38</v>
       </c>
       <c r="L33" t="n">
-        <v>80.20999999999999</v>
+        <v>87.5</v>
       </c>
     </row>
     <row r="34">
@@ -1480,13 +1480,13 @@
         <v>20</v>
       </c>
       <c r="J34" t="n">
-        <v>86.36</v>
+        <v>92.76000000000001</v>
       </c>
       <c r="K34" t="n">
-        <v>66.92</v>
+        <v>71.88</v>
       </c>
       <c r="L34" t="n">
-        <v>109.25</v>
+        <v>117.35</v>
       </c>
     </row>
     <row r="35">
@@ -1522,13 +1522,13 @@
         <v>22</v>
       </c>
       <c r="J35" t="n">
-        <v>58.19</v>
+        <v>60.43</v>
       </c>
       <c r="K35" t="n">
-        <v>-127.36</v>
+        <v>-132.25</v>
       </c>
       <c r="L35" t="n">
-        <v>140.02</v>
+        <v>145.41</v>
       </c>
     </row>
     <row r="36">
@@ -1564,13 +1564,13 @@
         <v>25</v>
       </c>
       <c r="J36" t="n">
-        <v>73.3</v>
+        <v>71.81</v>
       </c>
       <c r="K36" t="n">
-        <v>133.84</v>
+        <v>131.11</v>
       </c>
       <c r="L36" t="n">
-        <v>152.6</v>
+        <v>149.49</v>
       </c>
     </row>
     <row r="37">
@@ -1606,13 +1606,13 @@
         <v>22</v>
       </c>
       <c r="J37" t="n">
-        <v>-69.47</v>
+        <v>-72.14</v>
       </c>
       <c r="K37" t="n">
-        <v>58.37</v>
+        <v>60.62</v>
       </c>
       <c r="L37" t="n">
-        <v>90.73999999999999</v>
+        <v>94.23</v>
       </c>
     </row>
     <row r="38">
@@ -1690,13 +1690,13 @@
         <v>21</v>
       </c>
       <c r="J39" t="n">
-        <v>-49.51</v>
+        <v>-52.31</v>
       </c>
       <c r="K39" t="n">
-        <v>115.75</v>
+        <v>122.3</v>
       </c>
       <c r="L39" t="n">
-        <v>125.89</v>
+        <v>133.02</v>
       </c>
     </row>
     <row r="40">
@@ -1732,13 +1732,13 @@
         <v>23</v>
       </c>
       <c r="J40" t="n">
-        <v>88.92</v>
+        <v>90.66</v>
       </c>
       <c r="K40" t="n">
-        <v>65.76000000000001</v>
+        <v>67.05</v>
       </c>
       <c r="L40" t="n">
-        <v>110.6</v>
+        <v>112.77</v>
       </c>
     </row>
     <row r="41">
@@ -1774,13 +1774,13 @@
         <v>21</v>
       </c>
       <c r="J41" t="n">
-        <v>159.76</v>
+        <v>168.8</v>
       </c>
       <c r="K41" t="n">
-        <v>-151.61</v>
+        <v>-160.19</v>
       </c>
       <c r="L41" t="n">
-        <v>220.25</v>
+        <v>232.71</v>
       </c>
     </row>
     <row r="42">
@@ -1816,13 +1816,13 @@
         <v>19</v>
       </c>
       <c r="J42" t="n">
-        <v>-9.74</v>
+        <v>-10.63</v>
       </c>
       <c r="K42" t="n">
-        <v>183.72</v>
+        <v>200.42</v>
       </c>
       <c r="L42" t="n">
-        <v>183.98</v>
+        <v>200.7</v>
       </c>
     </row>
     <row r="43">
@@ -1858,13 +1858,13 @@
         <v>21</v>
       </c>
       <c r="J43" t="n">
-        <v>209.92</v>
+        <v>221.81</v>
       </c>
       <c r="K43" t="n">
-        <v>14.85</v>
+        <v>15.69</v>
       </c>
       <c r="L43" t="n">
-        <v>210.45</v>
+        <v>222.36</v>
       </c>
     </row>
     <row r="44">
@@ -1900,13 +1900,13 @@
         <v>21</v>
       </c>
       <c r="J44" t="n">
-        <v>41.49</v>
+        <v>43.84</v>
       </c>
       <c r="K44" t="n">
-        <v>-6.01</v>
+        <v>-6.35</v>
       </c>
       <c r="L44" t="n">
-        <v>41.93</v>
+        <v>44.3</v>
       </c>
     </row>
     <row r="45">
@@ -1942,13 +1942,13 @@
         <v>19</v>
       </c>
       <c r="J45" t="n">
-        <v>-28.01</v>
+        <v>-30.56</v>
       </c>
       <c r="K45" t="n">
-        <v>45.99</v>
+        <v>50.18</v>
       </c>
       <c r="L45" t="n">
-        <v>53.85</v>
+        <v>58.75</v>
       </c>
     </row>
     <row r="46">
@@ -1984,13 +1984,13 @@
         <v>23</v>
       </c>
       <c r="J46" t="n">
-        <v>-29.19</v>
+        <v>-29.77</v>
       </c>
       <c r="K46" t="n">
-        <v>75.73</v>
+        <v>77.20999999999999</v>
       </c>
       <c r="L46" t="n">
-        <v>81.16</v>
+        <v>82.75</v>
       </c>
     </row>
     <row r="47">
@@ -2026,13 +2026,13 @@
         <v>23</v>
       </c>
       <c r="J47" t="n">
-        <v>87.8</v>
+        <v>89.53</v>
       </c>
       <c r="K47" t="n">
-        <v>36.48</v>
+        <v>37.2</v>
       </c>
       <c r="L47" t="n">
-        <v>95.08</v>
+        <v>96.95</v>
       </c>
     </row>
     <row r="48">
@@ -2068,13 +2068,13 @@
         <v>23</v>
       </c>
       <c r="J48" t="n">
-        <v>21.88</v>
+        <v>22.31</v>
       </c>
       <c r="K48" t="n">
-        <v>-63.69</v>
+        <v>-64.94</v>
       </c>
       <c r="L48" t="n">
-        <v>67.34</v>
+        <v>68.66</v>
       </c>
     </row>
     <row r="49">
@@ -2110,13 +2110,13 @@
         <v>20</v>
       </c>
       <c r="J49" t="n">
-        <v>-41.85</v>
+        <v>-44.95</v>
       </c>
       <c r="K49" t="n">
-        <v>83.66</v>
+        <v>89.84999999999999</v>
       </c>
       <c r="L49" t="n">
-        <v>93.54000000000001</v>
+        <v>100.47</v>
       </c>
     </row>
     <row r="50">
@@ -2152,13 +2152,13 @@
         <v>19</v>
       </c>
       <c r="J50" t="n">
-        <v>69.98999999999999</v>
+        <v>76.34999999999999</v>
       </c>
       <c r="K50" t="n">
-        <v>-5.6</v>
+        <v>-6.1</v>
       </c>
       <c r="L50" t="n">
-        <v>70.20999999999999</v>
+        <v>76.59</v>
       </c>
     </row>
     <row r="51">
@@ -2194,13 +2194,13 @@
         <v>20</v>
       </c>
       <c r="J51" t="n">
-        <v>-5.11</v>
+        <v>-5.49</v>
       </c>
       <c r="K51" t="n">
-        <v>121.85</v>
+        <v>130.88</v>
       </c>
       <c r="L51" t="n">
-        <v>121.96</v>
+        <v>131</v>
       </c>
     </row>
     <row r="52">
@@ -2236,13 +2236,13 @@
         <v>20</v>
       </c>
       <c r="J52" t="n">
-        <v>113.59</v>
+        <v>122</v>
       </c>
       <c r="K52" t="n">
-        <v>49.04</v>
+        <v>52.68</v>
       </c>
       <c r="L52" t="n">
-        <v>123.72</v>
+        <v>132.89</v>
       </c>
     </row>
     <row r="53">
@@ -2278,13 +2278,13 @@
         <v>21</v>
       </c>
       <c r="J53" t="n">
-        <v>211.26</v>
+        <v>223.21</v>
       </c>
       <c r="K53" t="n">
-        <v>-12.45</v>
+        <v>-13.15</v>
       </c>
       <c r="L53" t="n">
-        <v>211.62</v>
+        <v>223.6</v>
       </c>
     </row>
     <row r="54">
@@ -2320,13 +2320,13 @@
         <v>25</v>
       </c>
       <c r="J54" t="n">
-        <v>12.31</v>
+        <v>12.06</v>
       </c>
       <c r="K54" t="n">
-        <v>95.47</v>
+        <v>93.52</v>
       </c>
       <c r="L54" t="n">
-        <v>96.26000000000001</v>
+        <v>94.29000000000001</v>
       </c>
     </row>
     <row r="55">
@@ -2362,13 +2362,13 @@
         <v>22</v>
       </c>
       <c r="J55" t="n">
-        <v>129.8</v>
+        <v>134.79</v>
       </c>
       <c r="K55" t="n">
-        <v>7.58</v>
+        <v>7.87</v>
       </c>
       <c r="L55" t="n">
-        <v>130.02</v>
+        <v>135.02</v>
       </c>
     </row>
     <row r="56">
@@ -2404,13 +2404,13 @@
         <v>20</v>
       </c>
       <c r="J56" t="n">
-        <v>172.13</v>
+        <v>184.88</v>
       </c>
       <c r="K56" t="n">
-        <v>-54.31</v>
+        <v>-58.33</v>
       </c>
       <c r="L56" t="n">
-        <v>180.49</v>
+        <v>193.86</v>
       </c>
     </row>
     <row r="57">
@@ -2446,13 +2446,13 @@
         <v>25</v>
       </c>
       <c r="J57" t="n">
-        <v>57.32</v>
+        <v>56.15</v>
       </c>
       <c r="K57" t="n">
-        <v>244.14</v>
+        <v>239.16</v>
       </c>
       <c r="L57" t="n">
-        <v>250.78</v>
+        <v>245.66</v>
       </c>
     </row>
     <row r="58">
@@ -2488,13 +2488,13 @@
         <v>19</v>
       </c>
       <c r="J58" t="n">
-        <v>-118.78</v>
+        <v>-129.58</v>
       </c>
       <c r="K58" t="n">
-        <v>171.17</v>
+        <v>186.73</v>
       </c>
       <c r="L58" t="n">
-        <v>208.35</v>
+        <v>227.29</v>
       </c>
     </row>
     <row r="59">
@@ -2530,13 +2530,13 @@
         <v>25</v>
       </c>
       <c r="J59" t="n">
-        <v>-45.41</v>
+        <v>-44.49</v>
       </c>
       <c r="K59" t="n">
-        <v>39.53</v>
+        <v>38.72</v>
       </c>
       <c r="L59" t="n">
-        <v>60.21</v>
+        <v>58.98</v>
       </c>
     </row>
     <row r="60">
@@ -2572,13 +2572,13 @@
         <v>23</v>
       </c>
       <c r="J60" t="n">
-        <v>27.64</v>
+        <v>28.18</v>
       </c>
       <c r="K60" t="n">
-        <v>55.17</v>
+        <v>56.25</v>
       </c>
       <c r="L60" t="n">
-        <v>61.7</v>
+        <v>62.91</v>
       </c>
     </row>
     <row r="61">
@@ -2614,13 +2614,13 @@
         <v>19</v>
       </c>
       <c r="J61" t="n">
-        <v>56.02</v>
+        <v>61.11</v>
       </c>
       <c r="K61" t="n">
-        <v>22.22</v>
+        <v>24.24</v>
       </c>
       <c r="L61" t="n">
-        <v>60.26</v>
+        <v>65.73999999999999</v>
       </c>
     </row>
     <row r="62">
@@ -2656,13 +2656,13 @@
         <v>19</v>
       </c>
       <c r="J62" t="n">
-        <v>87.67</v>
+        <v>95.64</v>
       </c>
       <c r="K62" t="n">
-        <v>-63.64</v>
+        <v>-69.42</v>
       </c>
       <c r="L62" t="n">
-        <v>108.33</v>
+        <v>118.18</v>
       </c>
     </row>
     <row r="63">
@@ -2698,13 +2698,13 @@
         <v>19</v>
       </c>
       <c r="J63" t="n">
-        <v>93.04000000000001</v>
+        <v>101.49</v>
       </c>
       <c r="K63" t="n">
-        <v>-79.16</v>
+        <v>-86.36</v>
       </c>
       <c r="L63" t="n">
-        <v>122.16</v>
+        <v>133.26</v>
       </c>
     </row>
     <row r="64">
@@ -2740,13 +2740,13 @@
         <v>22</v>
       </c>
       <c r="J64" t="n">
-        <v>-11.88</v>
+        <v>-12.34</v>
       </c>
       <c r="K64" t="n">
-        <v>66.37</v>
+        <v>68.92</v>
       </c>
       <c r="L64" t="n">
-        <v>67.42</v>
+        <v>70.02</v>
       </c>
     </row>
     <row r="65">
@@ -2824,13 +2824,13 @@
         <v>22</v>
       </c>
       <c r="J66" t="n">
-        <v>61.23</v>
+        <v>63.58</v>
       </c>
       <c r="K66" t="n">
-        <v>99.47</v>
+        <v>103.29</v>
       </c>
       <c r="L66" t="n">
-        <v>116.8</v>
+        <v>121.3</v>
       </c>
     </row>
     <row r="67">
@@ -2866,13 +2866,13 @@
         <v>22</v>
       </c>
       <c r="J67" t="n">
-        <v>51.1</v>
+        <v>53.07</v>
       </c>
       <c r="K67" t="n">
-        <v>122.57</v>
+        <v>127.29</v>
       </c>
       <c r="L67" t="n">
-        <v>132.8</v>
+        <v>137.91</v>
       </c>
     </row>
     <row r="68">
@@ -2908,13 +2908,13 @@
         <v>22</v>
       </c>
       <c r="J68" t="n">
-        <v>124.89</v>
+        <v>129.69</v>
       </c>
       <c r="K68" t="n">
-        <v>131.85</v>
+        <v>136.92</v>
       </c>
       <c r="L68" t="n">
-        <v>181.6</v>
+        <v>188.59</v>
       </c>
     </row>
     <row r="69">
@@ -2950,13 +2950,13 @@
         <v>22</v>
       </c>
       <c r="J69" t="n">
-        <v>20.88</v>
+        <v>21.71</v>
       </c>
       <c r="K69" t="n">
-        <v>-198.24</v>
+        <v>-206.04</v>
       </c>
       <c r="L69" t="n">
-        <v>199.33</v>
+        <v>207.18</v>
       </c>
     </row>
     <row r="70">
@@ -2992,13 +2992,13 @@
         <v>20</v>
       </c>
       <c r="J70" t="n">
-        <v>6.18</v>
+        <v>6.64</v>
       </c>
       <c r="K70" t="n">
-        <v>193.84</v>
+        <v>208.2</v>
       </c>
       <c r="L70" t="n">
-        <v>193.94</v>
+        <v>208.3</v>
       </c>
     </row>
     <row r="71">
@@ -3034,13 +3034,13 @@
         <v>22</v>
       </c>
       <c r="J71" t="n">
-        <v>133.58</v>
+        <v>138.72</v>
       </c>
       <c r="K71" t="n">
-        <v>-158.24</v>
+        <v>-164.32</v>
       </c>
       <c r="L71" t="n">
-        <v>207.08</v>
+        <v>215.05</v>
       </c>
     </row>
     <row r="72">
@@ -3076,13 +3076,13 @@
         <v>21</v>
       </c>
       <c r="J72" t="n">
-        <v>-340.18</v>
+        <v>-359.44</v>
       </c>
       <c r="K72" t="n">
-        <v>-167.97</v>
+        <v>-177.48</v>
       </c>
       <c r="L72" t="n">
-        <v>379.39</v>
+        <v>400.87</v>
       </c>
     </row>
     <row r="73">
@@ -3118,13 +3118,13 @@
         <v>25</v>
       </c>
       <c r="J73" t="n">
-        <v>158.17</v>
+        <v>154.95</v>
       </c>
       <c r="K73" t="n">
-        <v>-69.23999999999999</v>
+        <v>-67.83</v>
       </c>
       <c r="L73" t="n">
-        <v>172.66</v>
+        <v>169.14</v>
       </c>
     </row>
     <row r="74">
@@ -3160,13 +3160,13 @@
         <v>22</v>
       </c>
       <c r="J74" t="n">
-        <v>-55.99</v>
+        <v>-58.14</v>
       </c>
       <c r="K74" t="n">
-        <v>43.64</v>
+        <v>45.32</v>
       </c>
       <c r="L74" t="n">
-        <v>70.98999999999999</v>
+        <v>73.72</v>
       </c>
     </row>
     <row r="75">
@@ -3202,13 +3202,13 @@
         <v>19</v>
       </c>
       <c r="J75" t="n">
-        <v>-36.26</v>
+        <v>-39.56</v>
       </c>
       <c r="K75" t="n">
-        <v>61.73</v>
+        <v>67.34</v>
       </c>
       <c r="L75" t="n">
-        <v>71.59</v>
+        <v>78.09999999999999</v>
       </c>
     </row>
     <row r="76">
@@ -3244,13 +3244,13 @@
         <v>20</v>
       </c>
       <c r="J76" t="n">
-        <v>35.34</v>
+        <v>37.96</v>
       </c>
       <c r="K76" t="n">
-        <v>-31.24</v>
+        <v>-33.55</v>
       </c>
       <c r="L76" t="n">
-        <v>47.17</v>
+        <v>50.66</v>
       </c>
     </row>
     <row r="77">
@@ -3286,13 +3286,13 @@
         <v>23</v>
       </c>
       <c r="J77" t="n">
-        <v>79.68000000000001</v>
+        <v>81.25</v>
       </c>
       <c r="K77" t="n">
-        <v>53.8</v>
+        <v>54.86</v>
       </c>
       <c r="L77" t="n">
-        <v>96.15000000000001</v>
+        <v>98.03</v>
       </c>
     </row>
     <row r="78">
@@ -3328,13 +3328,13 @@
         <v>21</v>
       </c>
       <c r="J78" t="n">
-        <v>-57.54</v>
+        <v>-60.8</v>
       </c>
       <c r="K78" t="n">
-        <v>-36.86</v>
+        <v>-38.95</v>
       </c>
       <c r="L78" t="n">
-        <v>68.34</v>
+        <v>72.20999999999999</v>
       </c>
     </row>
     <row r="79">
@@ -3412,13 +3412,13 @@
         <v>21</v>
       </c>
       <c r="J80" t="n">
-        <v>15.56</v>
+        <v>16.44</v>
       </c>
       <c r="K80" t="n">
-        <v>87.84999999999999</v>
+        <v>92.81999999999999</v>
       </c>
       <c r="L80" t="n">
-        <v>89.22</v>
+        <v>94.27</v>
       </c>
     </row>
     <row r="81">
@@ -3454,13 +3454,13 @@
         <v>23</v>
       </c>
       <c r="J81" t="n">
-        <v>142.08</v>
+        <v>144.87</v>
       </c>
       <c r="K81" t="n">
-        <v>15.98</v>
+        <v>16.29</v>
       </c>
       <c r="L81" t="n">
-        <v>142.98</v>
+        <v>145.78</v>
       </c>
     </row>
     <row r="82">
@@ -3538,13 +3538,13 @@
         <v>19</v>
       </c>
       <c r="J83" t="n">
-        <v>-39.51</v>
+        <v>-43.11</v>
       </c>
       <c r="K83" t="n">
-        <v>-212.34</v>
+        <v>-231.64</v>
       </c>
       <c r="L83" t="n">
-        <v>215.98</v>
+        <v>235.62</v>
       </c>
     </row>
     <row r="84">
@@ -3580,13 +3580,13 @@
         <v>20</v>
       </c>
       <c r="J84" t="n">
-        <v>-208.49</v>
+        <v>-223.93</v>
       </c>
       <c r="K84" t="n">
-        <v>63.78</v>
+        <v>68.5</v>
       </c>
       <c r="L84" t="n">
-        <v>218.03</v>
+        <v>234.18</v>
       </c>
     </row>
     <row r="85">
@@ -3664,13 +3664,13 @@
         <v>25</v>
       </c>
       <c r="J86" t="n">
-        <v>-174.84</v>
+        <v>-171.27</v>
       </c>
       <c r="K86" t="n">
-        <v>-51.36</v>
+        <v>-50.31</v>
       </c>
       <c r="L86" t="n">
-        <v>182.22</v>
+        <v>178.51</v>
       </c>
     </row>
     <row r="87">
@@ -3706,13 +3706,13 @@
         <v>21</v>
       </c>
       <c r="J87" t="n">
-        <v>100.36</v>
+        <v>106.05</v>
       </c>
       <c r="K87" t="n">
-        <v>152.55</v>
+        <v>161.18</v>
       </c>
       <c r="L87" t="n">
-        <v>182.6</v>
+        <v>192.94</v>
       </c>
     </row>
     <row r="88">
@@ -3748,13 +3748,13 @@
         <v>21</v>
       </c>
       <c r="J88" t="n">
-        <v>192.1</v>
+        <v>202.97</v>
       </c>
       <c r="K88" t="n">
-        <v>-77.58</v>
+        <v>-81.97</v>
       </c>
       <c r="L88" t="n">
-        <v>207.17</v>
+        <v>218.9</v>
       </c>
     </row>
   </sheetData>

--- a/output/2024-07-26.xlsx
+++ b/output/2024-07-26.xlsx
@@ -628,31 +628,31 @@
         <v>1.7</v>
       </c>
       <c r="F14" t="n">
-        <v>6.46</v>
+        <v>7.78</v>
       </c>
       <c r="G14" t="n">
-        <v>61.7</v>
+        <v>63.7</v>
       </c>
       <c r="H14" t="n">
-        <v>31.2</v>
+        <v>29.4</v>
       </c>
       <c r="I14" t="n">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="J14" t="n">
-        <v>-15.5</v>
+        <v>-6.08</v>
       </c>
       <c r="K14" t="n">
-        <v>38.63</v>
+        <v>-28.79</v>
       </c>
       <c r="L14" t="n">
-        <v>41.62</v>
+        <v>29.43</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>05:10:21</t>
+          <t>05:10:54</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -667,34 +667,34 @@
         <v>2</v>
       </c>
       <c r="E15" t="n">
-        <v>1.57</v>
+        <v>2.09</v>
       </c>
       <c r="F15" t="n">
-        <v>8.609999999999999</v>
+        <v>10.35</v>
       </c>
       <c r="G15" t="n">
-        <v>59.6</v>
+        <v>73.90000000000001</v>
       </c>
       <c r="H15" t="n">
-        <v>26.2</v>
+        <v>61.4</v>
       </c>
       <c r="I15" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="J15" t="n">
-        <v>-47.6</v>
+        <v>16.24</v>
       </c>
       <c r="K15" t="n">
-        <v>41.54</v>
+        <v>28.85</v>
       </c>
       <c r="L15" t="n">
-        <v>63.18</v>
+        <v>33.11</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>05:12:02</t>
+          <t>05:11:47</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -709,34 +709,34 @@
         <v>3</v>
       </c>
       <c r="E16" t="n">
-        <v>1.49</v>
+        <v>1.59</v>
       </c>
       <c r="F16" t="n">
-        <v>4.41</v>
+        <v>9.6</v>
       </c>
       <c r="G16" t="n">
-        <v>59.9</v>
+        <v>51.4</v>
       </c>
       <c r="H16" t="n">
-        <v>26.4</v>
+        <v>14.9</v>
       </c>
       <c r="I16" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="J16" t="n">
-        <v>41.3</v>
+        <v>-28.58</v>
       </c>
       <c r="K16" t="n">
-        <v>7.74</v>
+        <v>-0.9399999999999999</v>
       </c>
       <c r="L16" t="n">
-        <v>42.02</v>
+        <v>28.6</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>05:16:21</t>
+          <t>05:17:05</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -751,34 +751,34 @@
         <v>1</v>
       </c>
       <c r="E17" t="n">
-        <v>1.46</v>
+        <v>1.78</v>
       </c>
       <c r="F17" t="n">
-        <v>3.05</v>
+        <v>5.58</v>
       </c>
       <c r="G17" t="n">
-        <v>65.40000000000001</v>
+        <v>63</v>
       </c>
       <c r="H17" t="n">
-        <v>33.6</v>
+        <v>37.9</v>
       </c>
       <c r="I17" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="J17" t="n">
-        <v>77.38</v>
+        <v>16.83</v>
       </c>
       <c r="K17" t="n">
-        <v>-6.17</v>
+        <v>-39.26</v>
       </c>
       <c r="L17" t="n">
-        <v>77.63</v>
+        <v>42.71</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>05:18:25</t>
+          <t>05:17:54</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -793,34 +793,34 @@
         <v>2</v>
       </c>
       <c r="E18" t="n">
-        <v>1.5</v>
+        <v>1.76</v>
       </c>
       <c r="F18" t="n">
-        <v>3.26</v>
+        <v>10.35</v>
       </c>
       <c r="G18" t="n">
-        <v>60.8</v>
+        <v>61.5</v>
       </c>
       <c r="H18" t="n">
-        <v>29.5</v>
+        <v>10.8</v>
       </c>
       <c r="I18" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="J18" t="n">
-        <v>-14.15</v>
+        <v>-38.41</v>
       </c>
       <c r="K18" t="n">
-        <v>59.75</v>
+        <v>31.62</v>
       </c>
       <c r="L18" t="n">
-        <v>61.41</v>
+        <v>49.75</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>05:19:59</t>
+          <t>05:18:56</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -835,34 +835,34 @@
         <v>3</v>
       </c>
       <c r="E19" t="n">
-        <v>2.1</v>
+        <v>1.87</v>
       </c>
       <c r="F19" t="n">
-        <v>9.82</v>
+        <v>6.01</v>
       </c>
       <c r="G19" t="n">
-        <v>68.5</v>
+        <v>69.59999999999999</v>
       </c>
       <c r="H19" t="n">
-        <v>20.9</v>
+        <v>16.8</v>
       </c>
       <c r="I19" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="J19" t="n">
-        <v>-98.87</v>
+        <v>43.25</v>
       </c>
       <c r="K19" t="n">
-        <v>-7.51</v>
+        <v>-29.78</v>
       </c>
       <c r="L19" t="n">
-        <v>99.15000000000001</v>
+        <v>52.51</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>05:25:06</t>
+          <t>05:22:39</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -877,34 +877,34 @@
         <v>1</v>
       </c>
       <c r="E20" t="n">
-        <v>1.87</v>
+        <v>1.21</v>
       </c>
       <c r="F20" t="n">
-        <v>10.35</v>
+        <v>4.37</v>
       </c>
       <c r="G20" t="n">
-        <v>63.6</v>
+        <v>65.8</v>
       </c>
       <c r="H20" t="n">
-        <v>32.1</v>
+        <v>14.6</v>
       </c>
       <c r="I20" t="n">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="J20" t="n">
-        <v>137.26</v>
+        <v>-62.32</v>
       </c>
       <c r="K20" t="n">
-        <v>46.38</v>
+        <v>26.62</v>
       </c>
       <c r="L20" t="n">
-        <v>144.88</v>
+        <v>67.77</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>05:26:36</t>
+          <t>05:24:07</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -919,34 +919,34 @@
         <v>2</v>
       </c>
       <c r="E21" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="F21" t="n">
-        <v>2.74</v>
+        <v>8.720000000000001</v>
       </c>
       <c r="G21" t="n">
-        <v>63</v>
+        <v>60.2</v>
       </c>
       <c r="H21" t="n">
-        <v>26.1</v>
+        <v>60.9</v>
       </c>
       <c r="I21" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="J21" t="n">
-        <v>-103.37</v>
+        <v>-56.33</v>
       </c>
       <c r="K21" t="n">
-        <v>-66.45</v>
+        <v>-10</v>
       </c>
       <c r="L21" t="n">
-        <v>122.88</v>
+        <v>57.21</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>05:28:16</t>
+          <t>05:25:48</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -961,34 +961,34 @@
         <v>3</v>
       </c>
       <c r="E22" t="n">
-        <v>1.65</v>
+        <v>1.27</v>
       </c>
       <c r="F22" t="n">
-        <v>5.69</v>
+        <v>8.58</v>
       </c>
       <c r="G22" t="n">
-        <v>60</v>
+        <v>63.7</v>
       </c>
       <c r="H22" t="n">
-        <v>29.2</v>
+        <v>49.1</v>
       </c>
       <c r="I22" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="J22" t="n">
-        <v>-75.23999999999999</v>
+        <v>7.17</v>
       </c>
       <c r="K22" t="n">
-        <v>-27.35</v>
+        <v>60.25</v>
       </c>
       <c r="L22" t="n">
-        <v>80.05</v>
+        <v>60.67</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>05:32:23</t>
+          <t>05:30:11</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1003,34 +1003,34 @@
         <v>1</v>
       </c>
       <c r="E23" t="n">
-        <v>1.71</v>
+        <v>1.82</v>
       </c>
       <c r="F23" t="n">
-        <v>8.449999999999999</v>
+        <v>7.68</v>
       </c>
       <c r="G23" t="n">
-        <v>53</v>
+        <v>66.3</v>
       </c>
       <c r="H23" t="n">
-        <v>27.8</v>
+        <v>38.9</v>
       </c>
       <c r="I23" t="n">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="J23" t="n">
-        <v>75.06999999999999</v>
+        <v>-98.08</v>
       </c>
       <c r="K23" t="n">
-        <v>-120.53</v>
+        <v>54.64</v>
       </c>
       <c r="L23" t="n">
-        <v>142</v>
+        <v>112.27</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>05:33:32</t>
+          <t>05:32:27</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1045,34 +1045,34 @@
         <v>2</v>
       </c>
       <c r="E24" t="n">
-        <v>1.88</v>
+        <v>1.75</v>
       </c>
       <c r="F24" t="n">
         <v>10.35</v>
       </c>
       <c r="G24" t="n">
-        <v>74.09999999999999</v>
+        <v>50.6</v>
       </c>
       <c r="H24" t="n">
-        <v>31.3</v>
+        <v>26.2</v>
       </c>
       <c r="I24" t="n">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="J24" t="n">
-        <v>58.45</v>
+        <v>-21.51</v>
       </c>
       <c r="K24" t="n">
-        <v>-107.76</v>
+        <v>-83.84999999999999</v>
       </c>
       <c r="L24" t="n">
-        <v>122.59</v>
+        <v>86.56999999999999</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>05:34:58</t>
+          <t>05:34:20</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1087,34 +1087,34 @@
         <v>3</v>
       </c>
       <c r="E25" t="n">
-        <v>1.91</v>
+        <v>2.36</v>
       </c>
       <c r="F25" t="n">
-        <v>8.859999999999999</v>
+        <v>9.859999999999999</v>
       </c>
       <c r="G25" t="n">
-        <v>78.8</v>
+        <v>60.5</v>
       </c>
       <c r="H25" t="n">
-        <v>25.2</v>
+        <v>50.5</v>
       </c>
       <c r="I25" t="n">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="J25" t="n">
-        <v>129.36</v>
+        <v>114.97</v>
       </c>
       <c r="K25" t="n">
-        <v>-61.33</v>
+        <v>79.39</v>
       </c>
       <c r="L25" t="n">
-        <v>143.16</v>
+        <v>139.72</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>05:40:04</t>
+          <t>05:39:10</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1129,34 +1129,34 @@
         <v>1</v>
       </c>
       <c r="E26" t="n">
-        <v>1.89</v>
+        <v>1.74</v>
       </c>
       <c r="F26" t="n">
-        <v>9.17</v>
+        <v>4.59</v>
       </c>
       <c r="G26" t="n">
-        <v>62.7</v>
+        <v>78</v>
       </c>
       <c r="H26" t="n">
-        <v>25.6</v>
+        <v>30.3</v>
       </c>
       <c r="I26" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="J26" t="n">
-        <v>-408.15</v>
+        <v>149.21</v>
       </c>
       <c r="K26" t="n">
-        <v>-29.28</v>
+        <v>-9.859999999999999</v>
       </c>
       <c r="L26" t="n">
-        <v>409.2</v>
+        <v>149.54</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>05:42:25</t>
+          <t>05:41:29</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1171,34 +1171,34 @@
         <v>2</v>
       </c>
       <c r="E27" t="n">
-        <v>1.56</v>
+        <v>1.87</v>
       </c>
       <c r="F27" t="n">
-        <v>6.72</v>
+        <v>7.94</v>
       </c>
       <c r="G27" t="n">
-        <v>68.3</v>
+        <v>72.5</v>
       </c>
       <c r="H27" t="n">
-        <v>31.5</v>
+        <v>44.9</v>
       </c>
       <c r="I27" t="n">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="J27" t="n">
-        <v>186.74</v>
+        <v>153.73</v>
       </c>
       <c r="K27" t="n">
-        <v>92.68000000000001</v>
+        <v>8.16</v>
       </c>
       <c r="L27" t="n">
-        <v>208.47</v>
+        <v>153.95</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>05:44:14</t>
+          <t>05:42:54</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1213,34 +1213,34 @@
         <v>3</v>
       </c>
       <c r="E28" t="n">
-        <v>1.91</v>
+        <v>1.63</v>
       </c>
       <c r="F28" t="n">
-        <v>2.21</v>
+        <v>6.63</v>
       </c>
       <c r="G28" t="n">
-        <v>78.3</v>
+        <v>77.3</v>
       </c>
       <c r="H28" t="n">
-        <v>38.7</v>
+        <v>40.6</v>
       </c>
       <c r="I28" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="J28" t="n">
-        <v>-144.23</v>
+        <v>93.06</v>
       </c>
       <c r="K28" t="n">
-        <v>162.03</v>
+        <v>111.45</v>
       </c>
       <c r="L28" t="n">
-        <v>216.92</v>
+        <v>145.2</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>05:53:58</t>
+          <t>05:54:13</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1255,34 +1255,34 @@
         <v>1</v>
       </c>
       <c r="E29" t="n">
-        <v>1.64</v>
+        <v>2.15</v>
       </c>
       <c r="F29" t="n">
-        <v>3.61</v>
+        <v>9.41</v>
       </c>
       <c r="G29" t="n">
-        <v>66.2</v>
+        <v>57</v>
       </c>
       <c r="H29" t="n">
-        <v>24.5</v>
+        <v>75.8</v>
       </c>
       <c r="I29" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="J29" t="n">
-        <v>-1.61</v>
+        <v>4.67</v>
       </c>
       <c r="K29" t="n">
-        <v>-30.61</v>
+        <v>43.34</v>
       </c>
       <c r="L29" t="n">
-        <v>30.65</v>
+        <v>43.59</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>05:55:37</t>
+          <t>05:55:50</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1297,34 +1297,34 @@
         <v>2</v>
       </c>
       <c r="E30" t="n">
-        <v>2.17</v>
+        <v>1.93</v>
       </c>
       <c r="F30" t="n">
-        <v>10.35</v>
+        <v>7.52</v>
       </c>
       <c r="G30" t="n">
-        <v>63.3</v>
+        <v>64.2</v>
       </c>
       <c r="H30" t="n">
-        <v>26.2</v>
+        <v>57.3</v>
       </c>
       <c r="I30" t="n">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="J30" t="n">
-        <v>36.48</v>
+        <v>30.18</v>
       </c>
       <c r="K30" t="n">
-        <v>26.7</v>
+        <v>-19.92</v>
       </c>
       <c r="L30" t="n">
-        <v>45.21</v>
+        <v>36.16</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>05:58:18</t>
+          <t>05:57:11</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1339,34 +1339,34 @@
         <v>3</v>
       </c>
       <c r="E31" t="n">
-        <v>2.06</v>
+        <v>2.23</v>
       </c>
       <c r="F31" t="n">
         <v>10.35</v>
       </c>
       <c r="G31" t="n">
-        <v>78.5</v>
+        <v>62.4</v>
       </c>
       <c r="H31" t="n">
-        <v>31.9</v>
+        <v>54.3</v>
       </c>
       <c r="I31" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="J31" t="n">
-        <v>31.56</v>
+        <v>-4.3</v>
       </c>
       <c r="K31" t="n">
-        <v>41.8</v>
+        <v>41.01</v>
       </c>
       <c r="L31" t="n">
-        <v>52.37</v>
+        <v>41.23</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>06:02:35</t>
+          <t>06:00:45</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1381,34 +1381,34 @@
         <v>1</v>
       </c>
       <c r="E32" t="n">
-        <v>2.28</v>
+        <v>1.65</v>
       </c>
       <c r="F32" t="n">
-        <v>10.21</v>
+        <v>2.85</v>
       </c>
       <c r="G32" t="n">
-        <v>59.7</v>
+        <v>64.2</v>
       </c>
       <c r="H32" t="n">
-        <v>32</v>
+        <v>38.3</v>
       </c>
       <c r="I32" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J32" t="n">
-        <v>-67.69</v>
+        <v>-36.11</v>
       </c>
       <c r="K32" t="n">
-        <v>79.76000000000001</v>
+        <v>16.31</v>
       </c>
       <c r="L32" t="n">
-        <v>104.61</v>
+        <v>39.63</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>06:04:20</t>
+          <t>06:02:00</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1423,34 +1423,34 @@
         <v>2</v>
       </c>
       <c r="E33" t="n">
-        <v>1.99</v>
+        <v>1.4</v>
       </c>
       <c r="F33" t="n">
-        <v>9.42</v>
+        <v>7.32</v>
       </c>
       <c r="G33" t="n">
-        <v>58.2</v>
+        <v>67</v>
       </c>
       <c r="H33" t="n">
-        <v>34.3</v>
+        <v>30.5</v>
       </c>
       <c r="I33" t="n">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="J33" t="n">
-        <v>81.29000000000001</v>
+        <v>-40.45</v>
       </c>
       <c r="K33" t="n">
-        <v>32.38</v>
+        <v>18.61</v>
       </c>
       <c r="L33" t="n">
-        <v>87.5</v>
+        <v>44.53</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>06:06:46</t>
+          <t>06:03:22</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1465,34 +1465,34 @@
         <v>3</v>
       </c>
       <c r="E34" t="n">
-        <v>1.61</v>
+        <v>1.75</v>
       </c>
       <c r="F34" t="n">
-        <v>9.630000000000001</v>
+        <v>5.41</v>
       </c>
       <c r="G34" t="n">
-        <v>79.59999999999999</v>
+        <v>67.59999999999999</v>
       </c>
       <c r="H34" t="n">
-        <v>34.8</v>
+        <v>47.9</v>
       </c>
       <c r="I34" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="J34" t="n">
-        <v>92.76000000000001</v>
+        <v>1.87</v>
       </c>
       <c r="K34" t="n">
-        <v>71.88</v>
+        <v>39.06</v>
       </c>
       <c r="L34" t="n">
-        <v>117.35</v>
+        <v>39.11</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>06:11:10</t>
+          <t>06:08:26</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1507,34 +1507,34 @@
         <v>1</v>
       </c>
       <c r="E35" t="n">
-        <v>2.3</v>
+        <v>2.11</v>
       </c>
       <c r="F35" t="n">
-        <v>6.56</v>
+        <v>4.25</v>
       </c>
       <c r="G35" t="n">
-        <v>75.40000000000001</v>
+        <v>84.90000000000001</v>
       </c>
       <c r="H35" t="n">
-        <v>30.6</v>
+        <v>38.9</v>
       </c>
       <c r="I35" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="J35" t="n">
-        <v>60.43</v>
+        <v>64.43000000000001</v>
       </c>
       <c r="K35" t="n">
-        <v>-132.25</v>
+        <v>59.85</v>
       </c>
       <c r="L35" t="n">
-        <v>145.41</v>
+        <v>87.94</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>06:13:45</t>
+          <t>06:10:49</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1549,34 +1549,34 @@
         <v>2</v>
       </c>
       <c r="E36" t="n">
-        <v>1.76</v>
+        <v>1.87</v>
       </c>
       <c r="F36" t="n">
-        <v>8.99</v>
+        <v>2.17</v>
       </c>
       <c r="G36" t="n">
-        <v>56.8</v>
+        <v>60.7</v>
       </c>
       <c r="H36" t="n">
-        <v>34.6</v>
+        <v>70.7</v>
       </c>
       <c r="I36" t="n">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="J36" t="n">
-        <v>71.81</v>
+        <v>-38.13</v>
       </c>
       <c r="K36" t="n">
-        <v>131.11</v>
+        <v>73.12</v>
       </c>
       <c r="L36" t="n">
-        <v>149.49</v>
+        <v>82.47</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>06:15:13</t>
+          <t>06:12:32</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1591,34 +1591,34 @@
         <v>3</v>
       </c>
       <c r="E37" t="n">
-        <v>2.08</v>
+        <v>1.62</v>
       </c>
       <c r="F37" t="n">
-        <v>5.67</v>
+        <v>9.35</v>
       </c>
       <c r="G37" t="n">
-        <v>65.40000000000001</v>
+        <v>73.09999999999999</v>
       </c>
       <c r="H37" t="n">
-        <v>33.2</v>
+        <v>47.6</v>
       </c>
       <c r="I37" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="J37" t="n">
-        <v>-72.14</v>
+        <v>72.48</v>
       </c>
       <c r="K37" t="n">
-        <v>60.62</v>
+        <v>40.78</v>
       </c>
       <c r="L37" t="n">
-        <v>94.23</v>
+        <v>83.17</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>06:19:35</t>
+          <t>06:17:08</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1633,34 +1633,34 @@
         <v>1</v>
       </c>
       <c r="E38" t="n">
-        <v>1.99</v>
+        <v>2.27</v>
       </c>
       <c r="F38" t="n">
-        <v>10.35</v>
+        <v>5.2</v>
       </c>
       <c r="G38" t="n">
-        <v>76.40000000000001</v>
+        <v>58.2</v>
       </c>
       <c r="H38" t="n">
-        <v>24</v>
+        <v>80.8</v>
       </c>
       <c r="I38" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="J38" t="n">
-        <v>-33.23</v>
+        <v>-20.74</v>
       </c>
       <c r="K38" t="n">
-        <v>131.87</v>
+        <v>139.46</v>
       </c>
       <c r="L38" t="n">
-        <v>135.99</v>
+        <v>141</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>06:20:42</t>
+          <t>06:19:13</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1675,34 +1675,34 @@
         <v>2</v>
       </c>
       <c r="E39" t="n">
-        <v>1.99</v>
+        <v>2.09</v>
       </c>
       <c r="F39" t="n">
-        <v>8.99</v>
+        <v>4.25</v>
       </c>
       <c r="G39" t="n">
-        <v>67.7</v>
+        <v>73.90000000000001</v>
       </c>
       <c r="H39" t="n">
-        <v>29.2</v>
+        <v>0</v>
       </c>
       <c r="I39" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="J39" t="n">
-        <v>-52.31</v>
+        <v>-40.25</v>
       </c>
       <c r="K39" t="n">
-        <v>122.3</v>
+        <v>-125.17</v>
       </c>
       <c r="L39" t="n">
-        <v>133.02</v>
+        <v>131.48</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>06:22:09</t>
+          <t>06:20:46</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1717,34 +1717,34 @@
         <v>3</v>
       </c>
       <c r="E40" t="n">
-        <v>1.64</v>
+        <v>2.1</v>
       </c>
       <c r="F40" t="n">
-        <v>7.8</v>
+        <v>5.6</v>
       </c>
       <c r="G40" t="n">
-        <v>64.7</v>
+        <v>62.3</v>
       </c>
       <c r="H40" t="n">
-        <v>31.8</v>
+        <v>0</v>
       </c>
       <c r="I40" t="n">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="J40" t="n">
-        <v>90.66</v>
+        <v>53.06</v>
       </c>
       <c r="K40" t="n">
-        <v>67.05</v>
+        <v>-91.02</v>
       </c>
       <c r="L40" t="n">
-        <v>112.77</v>
+        <v>105.36</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>06:26:28</t>
+          <t>06:26:05</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1759,34 +1759,34 @@
         <v>1</v>
       </c>
       <c r="E41" t="n">
-        <v>1.64</v>
+        <v>2.08</v>
       </c>
       <c r="F41" t="n">
-        <v>6.57</v>
+        <v>10.35</v>
       </c>
       <c r="G41" t="n">
-        <v>58.6</v>
+        <v>62.8</v>
       </c>
       <c r="H41" t="n">
-        <v>32</v>
+        <v>46.1</v>
       </c>
       <c r="I41" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="J41" t="n">
-        <v>168.8</v>
+        <v>184.96</v>
       </c>
       <c r="K41" t="n">
-        <v>-160.19</v>
+        <v>-18.55</v>
       </c>
       <c r="L41" t="n">
-        <v>232.71</v>
+        <v>185.88</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>06:27:26</t>
+          <t>06:28:20</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -1801,34 +1801,34 @@
         <v>2</v>
       </c>
       <c r="E42" t="n">
-        <v>1.92</v>
+        <v>2.07</v>
       </c>
       <c r="F42" t="n">
-        <v>5.02</v>
+        <v>8.42</v>
       </c>
       <c r="G42" t="n">
-        <v>78.59999999999999</v>
+        <v>70.40000000000001</v>
       </c>
       <c r="H42" t="n">
-        <v>34.9</v>
+        <v>30.5</v>
       </c>
       <c r="I42" t="n">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="J42" t="n">
-        <v>-10.63</v>
+        <v>-84.36</v>
       </c>
       <c r="K42" t="n">
-        <v>200.42</v>
+        <v>189.31</v>
       </c>
       <c r="L42" t="n">
-        <v>200.7</v>
+        <v>207.26</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>06:29:15</t>
+          <t>06:30:28</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -1843,34 +1843,34 @@
         <v>3</v>
       </c>
       <c r="E43" t="n">
-        <v>1.85</v>
+        <v>1.98</v>
       </c>
       <c r="F43" t="n">
-        <v>7.93</v>
+        <v>6.94</v>
       </c>
       <c r="G43" t="n">
-        <v>58.6</v>
+        <v>69.3</v>
       </c>
       <c r="H43" t="n">
-        <v>33.3</v>
+        <v>44.9</v>
       </c>
       <c r="I43" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="J43" t="n">
-        <v>221.81</v>
+        <v>-56.7</v>
       </c>
       <c r="K43" t="n">
-        <v>15.69</v>
+        <v>-156.37</v>
       </c>
       <c r="L43" t="n">
-        <v>222.36</v>
+        <v>166.33</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>06:39:21</t>
+          <t>06:40:23</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -1885,34 +1885,34 @@
         <v>1</v>
       </c>
       <c r="E44" t="n">
-        <v>1.48</v>
+        <v>1.57</v>
       </c>
       <c r="F44" t="n">
-        <v>6.01</v>
+        <v>6.84</v>
       </c>
       <c r="G44" t="n">
-        <v>54.4</v>
+        <v>67.5</v>
       </c>
       <c r="H44" t="n">
-        <v>34.7</v>
+        <v>55.3</v>
       </c>
       <c r="I44" t="n">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="J44" t="n">
-        <v>43.84</v>
+        <v>-2.93</v>
       </c>
       <c r="K44" t="n">
-        <v>-6.35</v>
+        <v>37.89</v>
       </c>
       <c r="L44" t="n">
-        <v>44.3</v>
+        <v>38</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>06:40:34</t>
+          <t>06:42:39</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -1927,34 +1927,34 @@
         <v>2</v>
       </c>
       <c r="E45" t="n">
-        <v>1.58</v>
+        <v>1.72</v>
       </c>
       <c r="F45" t="n">
-        <v>10.35</v>
+        <v>8.44</v>
       </c>
       <c r="G45" t="n">
-        <v>73</v>
+        <v>62.6</v>
       </c>
       <c r="H45" t="n">
-        <v>35</v>
+        <v>52.8</v>
       </c>
       <c r="I45" t="n">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="J45" t="n">
-        <v>-30.56</v>
+        <v>-26.81</v>
       </c>
       <c r="K45" t="n">
-        <v>50.18</v>
+        <v>-12.8</v>
       </c>
       <c r="L45" t="n">
-        <v>58.75</v>
+        <v>29.71</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>06:42:34</t>
+          <t>06:43:17</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -1969,34 +1969,34 @@
         <v>3</v>
       </c>
       <c r="E46" t="n">
-        <v>2.34</v>
+        <v>2.2</v>
       </c>
       <c r="F46" t="n">
         <v>10.35</v>
       </c>
       <c r="G46" t="n">
-        <v>52.7</v>
+        <v>74.5</v>
       </c>
       <c r="H46" t="n">
-        <v>24.3</v>
+        <v>44.9</v>
       </c>
       <c r="I46" t="n">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="J46" t="n">
-        <v>-29.77</v>
+        <v>25.33</v>
       </c>
       <c r="K46" t="n">
-        <v>77.20999999999999</v>
+        <v>-27.71</v>
       </c>
       <c r="L46" t="n">
-        <v>82.75</v>
+        <v>37.54</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>06:48:48</t>
+          <t>06:48:42</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -2011,34 +2011,34 @@
         <v>1</v>
       </c>
       <c r="E47" t="n">
-        <v>2.32</v>
+        <v>2.11</v>
       </c>
       <c r="F47" t="n">
-        <v>10.35</v>
+        <v>8.529999999999999</v>
       </c>
       <c r="G47" t="n">
-        <v>77.59999999999999</v>
+        <v>68.90000000000001</v>
       </c>
       <c r="H47" t="n">
-        <v>23.7</v>
+        <v>35.7</v>
       </c>
       <c r="I47" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="J47" t="n">
-        <v>89.53</v>
+        <v>-52.14</v>
       </c>
       <c r="K47" t="n">
-        <v>37.2</v>
+        <v>-18.02</v>
       </c>
       <c r="L47" t="n">
-        <v>96.95</v>
+        <v>55.16</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>06:49:23</t>
+          <t>06:50:06</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2053,34 +2053,34 @@
         <v>2</v>
       </c>
       <c r="E48" t="n">
-        <v>1.92</v>
+        <v>1.32</v>
       </c>
       <c r="F48" t="n">
-        <v>9.880000000000001</v>
+        <v>6.89</v>
       </c>
       <c r="G48" t="n">
-        <v>77</v>
+        <v>71.90000000000001</v>
       </c>
       <c r="H48" t="n">
-        <v>29.5</v>
+        <v>16.9</v>
       </c>
       <c r="I48" t="n">
         <v>23</v>
       </c>
       <c r="J48" t="n">
-        <v>22.31</v>
+        <v>25.55</v>
       </c>
       <c r="K48" t="n">
-        <v>-64.94</v>
+        <v>31.01</v>
       </c>
       <c r="L48" t="n">
-        <v>68.66</v>
+        <v>40.18</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>06:51:52</t>
+          <t>06:51:07</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2095,34 +2095,34 @@
         <v>3</v>
       </c>
       <c r="E49" t="n">
-        <v>2.32</v>
+        <v>2.46</v>
       </c>
       <c r="F49" t="n">
-        <v>10.35</v>
+        <v>8.06</v>
       </c>
       <c r="G49" t="n">
-        <v>73.40000000000001</v>
+        <v>69.40000000000001</v>
       </c>
       <c r="H49" t="n">
-        <v>27</v>
+        <v>42.5</v>
       </c>
       <c r="I49" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J49" t="n">
-        <v>-44.95</v>
+        <v>50.6</v>
       </c>
       <c r="K49" t="n">
-        <v>89.84999999999999</v>
+        <v>53.71</v>
       </c>
       <c r="L49" t="n">
-        <v>100.47</v>
+        <v>73.79000000000001</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>06:56:17</t>
+          <t>06:56:10</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -2137,34 +2137,34 @@
         <v>1</v>
       </c>
       <c r="E50" t="n">
-        <v>1.64</v>
+        <v>2.37</v>
       </c>
       <c r="F50" t="n">
-        <v>1.98</v>
+        <v>10.35</v>
       </c>
       <c r="G50" t="n">
-        <v>66</v>
+        <v>63.8</v>
       </c>
       <c r="H50" t="n">
-        <v>31.4</v>
+        <v>38.4</v>
       </c>
       <c r="I50" t="n">
-        <v>19</v>
+        <v>28</v>
       </c>
       <c r="J50" t="n">
-        <v>76.34999999999999</v>
+        <v>15.39</v>
       </c>
       <c r="K50" t="n">
-        <v>-6.1</v>
+        <v>135.07</v>
       </c>
       <c r="L50" t="n">
-        <v>76.59</v>
+        <v>135.94</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>06:58:38</t>
+          <t>06:57:36</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -2179,34 +2179,34 @@
         <v>2</v>
       </c>
       <c r="E51" t="n">
-        <v>2.26</v>
+        <v>2.17</v>
       </c>
       <c r="F51" t="n">
-        <v>10.35</v>
+        <v>8.77</v>
       </c>
       <c r="G51" t="n">
-        <v>63.2</v>
+        <v>56.6</v>
       </c>
       <c r="H51" t="n">
-        <v>28.4</v>
+        <v>49.1</v>
       </c>
       <c r="I51" t="n">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="J51" t="n">
-        <v>-5.49</v>
+        <v>58.52</v>
       </c>
       <c r="K51" t="n">
-        <v>130.88</v>
+        <v>-83.79000000000001</v>
       </c>
       <c r="L51" t="n">
-        <v>131</v>
+        <v>102.21</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>07:00:21</t>
+          <t>06:59:52</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -2221,34 +2221,34 @@
         <v>3</v>
       </c>
       <c r="E52" t="n">
-        <v>1.99</v>
+        <v>2.06</v>
       </c>
       <c r="F52" t="n">
-        <v>5.16</v>
+        <v>4.31</v>
       </c>
       <c r="G52" t="n">
-        <v>61</v>
+        <v>69.8</v>
       </c>
       <c r="H52" t="n">
-        <v>34.1</v>
+        <v>45.3</v>
       </c>
       <c r="I52" t="n">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="J52" t="n">
-        <v>122</v>
+        <v>-80.47</v>
       </c>
       <c r="K52" t="n">
-        <v>52.68</v>
+        <v>3.7</v>
       </c>
       <c r="L52" t="n">
-        <v>132.89</v>
+        <v>80.56</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>07:05:58</t>
+          <t>07:05:15</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -2263,34 +2263,34 @@
         <v>1</v>
       </c>
       <c r="E53" t="n">
-        <v>2.25</v>
+        <v>2.09</v>
       </c>
       <c r="F53" t="n">
-        <v>9.93</v>
+        <v>10.35</v>
       </c>
       <c r="G53" t="n">
-        <v>74.7</v>
+        <v>67.3</v>
       </c>
       <c r="H53" t="n">
-        <v>33.4</v>
+        <v>48.8</v>
       </c>
       <c r="I53" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J53" t="n">
-        <v>223.21</v>
+        <v>135.28</v>
       </c>
       <c r="K53" t="n">
-        <v>-13.15</v>
+        <v>-69.48999999999999</v>
       </c>
       <c r="L53" t="n">
-        <v>223.6</v>
+        <v>152.09</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>07:07:55</t>
+          <t>07:07:32</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -2305,34 +2305,34 @@
         <v>2</v>
       </c>
       <c r="E54" t="n">
-        <v>1.57</v>
+        <v>1.9</v>
       </c>
       <c r="F54" t="n">
-        <v>2.51</v>
+        <v>8.44</v>
       </c>
       <c r="G54" t="n">
-        <v>63.7</v>
+        <v>79</v>
       </c>
       <c r="H54" t="n">
-        <v>28.6</v>
+        <v>30.9</v>
       </c>
       <c r="I54" t="n">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="J54" t="n">
-        <v>12.06</v>
+        <v>-42.22</v>
       </c>
       <c r="K54" t="n">
-        <v>93.52</v>
+        <v>-72.11</v>
       </c>
       <c r="L54" t="n">
-        <v>94.29000000000001</v>
+        <v>83.56</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>07:09:32</t>
+          <t>07:08:25</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -2347,34 +2347,34 @@
         <v>3</v>
       </c>
       <c r="E55" t="n">
-        <v>1.99</v>
+        <v>2.15</v>
       </c>
       <c r="F55" t="n">
-        <v>7.45</v>
+        <v>10.35</v>
       </c>
       <c r="G55" t="n">
-        <v>68</v>
+        <v>54.4</v>
       </c>
       <c r="H55" t="n">
-        <v>24.2</v>
+        <v>12.3</v>
       </c>
       <c r="I55" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="J55" t="n">
-        <v>134.79</v>
+        <v>101.82</v>
       </c>
       <c r="K55" t="n">
-        <v>7.87</v>
+        <v>13.77</v>
       </c>
       <c r="L55" t="n">
-        <v>135.02</v>
+        <v>102.75</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>07:12:49</t>
+          <t>07:12:57</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -2389,34 +2389,34 @@
         <v>1</v>
       </c>
       <c r="E56" t="n">
-        <v>1.98</v>
+        <v>1.89</v>
       </c>
       <c r="F56" t="n">
-        <v>10.35</v>
+        <v>8.34</v>
       </c>
       <c r="G56" t="n">
-        <v>81.40000000000001</v>
+        <v>80.3</v>
       </c>
       <c r="H56" t="n">
-        <v>30.3</v>
+        <v>67.59999999999999</v>
       </c>
       <c r="I56" t="n">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="J56" t="n">
-        <v>184.88</v>
+        <v>161.78</v>
       </c>
       <c r="K56" t="n">
-        <v>-58.33</v>
+        <v>-59.19</v>
       </c>
       <c r="L56" t="n">
-        <v>193.86</v>
+        <v>172.27</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>07:14:05</t>
+          <t>07:15:04</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -2431,34 +2431,34 @@
         <v>2</v>
       </c>
       <c r="E57" t="n">
-        <v>2.14</v>
+        <v>1.74</v>
       </c>
       <c r="F57" t="n">
-        <v>10.13</v>
+        <v>4.75</v>
       </c>
       <c r="G57" t="n">
-        <v>68.40000000000001</v>
+        <v>70.5</v>
       </c>
       <c r="H57" t="n">
-        <v>31.6</v>
+        <v>42.7</v>
       </c>
       <c r="I57" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="J57" t="n">
-        <v>56.15</v>
+        <v>14.88</v>
       </c>
       <c r="K57" t="n">
-        <v>239.16</v>
+        <v>-109.92</v>
       </c>
       <c r="L57" t="n">
-        <v>245.66</v>
+        <v>110.92</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>07:15:25</t>
+          <t>07:16:57</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -2473,34 +2473,34 @@
         <v>3</v>
       </c>
       <c r="E58" t="n">
-        <v>2.11</v>
+        <v>1.94</v>
       </c>
       <c r="F58" t="n">
-        <v>9.74</v>
+        <v>9.210000000000001</v>
       </c>
       <c r="G58" t="n">
-        <v>59.8</v>
+        <v>59.4</v>
       </c>
       <c r="H58" t="n">
-        <v>34.1</v>
+        <v>43</v>
       </c>
       <c r="I58" t="n">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="J58" t="n">
-        <v>-129.58</v>
+        <v>-158.48</v>
       </c>
       <c r="K58" t="n">
-        <v>186.73</v>
+        <v>-62.24</v>
       </c>
       <c r="L58" t="n">
-        <v>227.29</v>
+        <v>170.26</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>07:26:39</t>
+          <t>07:26:43</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -2515,34 +2515,34 @@
         <v>1</v>
       </c>
       <c r="E59" t="n">
-        <v>1.93</v>
+        <v>1.82</v>
       </c>
       <c r="F59" t="n">
-        <v>8.199999999999999</v>
+        <v>9.44</v>
       </c>
       <c r="G59" t="n">
-        <v>77.90000000000001</v>
+        <v>58.7</v>
       </c>
       <c r="H59" t="n">
-        <v>29.2</v>
+        <v>33.3</v>
       </c>
       <c r="I59" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="J59" t="n">
-        <v>-44.49</v>
+        <v>-12.54</v>
       </c>
       <c r="K59" t="n">
-        <v>38.72</v>
+        <v>29.88</v>
       </c>
       <c r="L59" t="n">
-        <v>58.98</v>
+        <v>32.4</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>07:28:08</t>
+          <t>07:28:34</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -2557,34 +2557,34 @@
         <v>2</v>
       </c>
       <c r="E60" t="n">
-        <v>1.75</v>
+        <v>2.15</v>
       </c>
       <c r="F60" t="n">
-        <v>9.529999999999999</v>
+        <v>10.35</v>
       </c>
       <c r="G60" t="n">
-        <v>80.40000000000001</v>
+        <v>67.09999999999999</v>
       </c>
       <c r="H60" t="n">
-        <v>32.8</v>
+        <v>41.9</v>
       </c>
       <c r="I60" t="n">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="J60" t="n">
-        <v>28.18</v>
+        <v>5.51</v>
       </c>
       <c r="K60" t="n">
-        <v>56.25</v>
+        <v>35.76</v>
       </c>
       <c r="L60" t="n">
-        <v>62.91</v>
+        <v>36.18</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>07:29:11</t>
+          <t>07:30:03</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -2599,34 +2599,34 @@
         <v>3</v>
       </c>
       <c r="E61" t="n">
-        <v>1.82</v>
+        <v>1.8</v>
       </c>
       <c r="F61" t="n">
-        <v>7.56</v>
+        <v>6.36</v>
       </c>
       <c r="G61" t="n">
-        <v>70</v>
+        <v>59.6</v>
       </c>
       <c r="H61" t="n">
-        <v>24.7</v>
+        <v>51.8</v>
       </c>
       <c r="I61" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J61" t="n">
-        <v>61.11</v>
+        <v>26.01</v>
       </c>
       <c r="K61" t="n">
-        <v>24.24</v>
+        <v>6.89</v>
       </c>
       <c r="L61" t="n">
-        <v>65.73999999999999</v>
+        <v>26.91</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>07:35:20</t>
+          <t>07:34:36</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -2641,34 +2641,34 @@
         <v>1</v>
       </c>
       <c r="E62" t="n">
-        <v>2.57</v>
+        <v>1.44</v>
       </c>
       <c r="F62" t="n">
-        <v>10.35</v>
+        <v>1.74</v>
       </c>
       <c r="G62" t="n">
-        <v>67.5</v>
+        <v>74.3</v>
       </c>
       <c r="H62" t="n">
-        <v>27.1</v>
+        <v>34.1</v>
       </c>
       <c r="I62" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="J62" t="n">
-        <v>95.64</v>
+        <v>-35.3</v>
       </c>
       <c r="K62" t="n">
-        <v>-69.42</v>
+        <v>-15.49</v>
       </c>
       <c r="L62" t="n">
-        <v>118.18</v>
+        <v>38.55</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>07:37:27</t>
+          <t>07:36:58</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -2683,34 +2683,34 @@
         <v>2</v>
       </c>
       <c r="E63" t="n">
-        <v>2.6</v>
+        <v>2.04</v>
       </c>
       <c r="F63" t="n">
-        <v>10.35</v>
+        <v>6.87</v>
       </c>
       <c r="G63" t="n">
-        <v>67.2</v>
+        <v>64.2</v>
       </c>
       <c r="H63" t="n">
-        <v>27.2</v>
+        <v>53</v>
       </c>
       <c r="I63" t="n">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="J63" t="n">
-        <v>101.49</v>
+        <v>-39.45</v>
       </c>
       <c r="K63" t="n">
-        <v>-86.36</v>
+        <v>29.58</v>
       </c>
       <c r="L63" t="n">
-        <v>133.26</v>
+        <v>49.31</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>07:38:18</t>
+          <t>07:39:05</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -2725,34 +2725,34 @@
         <v>3</v>
       </c>
       <c r="E64" t="n">
-        <v>1.61</v>
+        <v>1.96</v>
       </c>
       <c r="F64" t="n">
         <v>10.35</v>
       </c>
       <c r="G64" t="n">
-        <v>66.59999999999999</v>
+        <v>54.5</v>
       </c>
       <c r="H64" t="n">
-        <v>34.1</v>
+        <v>53.4</v>
       </c>
       <c r="I64" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="J64" t="n">
-        <v>-12.34</v>
+        <v>37.62</v>
       </c>
       <c r="K64" t="n">
-        <v>68.92</v>
+        <v>-8.02</v>
       </c>
       <c r="L64" t="n">
-        <v>70.02</v>
+        <v>38.47</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>07:43:52</t>
+          <t>07:44:17</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -2767,34 +2767,34 @@
         <v>1</v>
       </c>
       <c r="E65" t="n">
-        <v>2.5</v>
+        <v>2.01</v>
       </c>
       <c r="F65" t="n">
-        <v>9.460000000000001</v>
+        <v>5.25</v>
       </c>
       <c r="G65" t="n">
-        <v>66.5</v>
+        <v>59.6</v>
       </c>
       <c r="H65" t="n">
-        <v>33.3</v>
+        <v>58.3</v>
       </c>
       <c r="I65" t="n">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="J65" t="n">
-        <v>-14.73</v>
+        <v>75.43000000000001</v>
       </c>
       <c r="K65" t="n">
-        <v>46.24</v>
+        <v>-22.67</v>
       </c>
       <c r="L65" t="n">
-        <v>48.53</v>
+        <v>78.76000000000001</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>07:45:07</t>
+          <t>07:46:29</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -2809,34 +2809,34 @@
         <v>2</v>
       </c>
       <c r="E66" t="n">
-        <v>2.14</v>
+        <v>1.87</v>
       </c>
       <c r="F66" t="n">
-        <v>9.109999999999999</v>
+        <v>2.62</v>
       </c>
       <c r="G66" t="n">
-        <v>68.59999999999999</v>
+        <v>62.8</v>
       </c>
       <c r="H66" t="n">
-        <v>36.8</v>
+        <v>70</v>
       </c>
       <c r="I66" t="n">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="J66" t="n">
-        <v>63.58</v>
+        <v>-47.3</v>
       </c>
       <c r="K66" t="n">
-        <v>103.29</v>
+        <v>-41.3</v>
       </c>
       <c r="L66" t="n">
-        <v>121.3</v>
+        <v>62.79</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>07:47:26</t>
+          <t>07:48:57</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -2851,34 +2851,34 @@
         <v>3</v>
       </c>
       <c r="E67" t="n">
-        <v>2.26</v>
+        <v>1.85</v>
       </c>
       <c r="F67" t="n">
-        <v>6.38</v>
+        <v>8.18</v>
       </c>
       <c r="G67" t="n">
-        <v>69.09999999999999</v>
+        <v>67.09999999999999</v>
       </c>
       <c r="H67" t="n">
-        <v>35.4</v>
+        <v>58.8</v>
       </c>
       <c r="I67" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="J67" t="n">
-        <v>53.07</v>
+        <v>-1.84</v>
       </c>
       <c r="K67" t="n">
-        <v>127.29</v>
+        <v>78.2</v>
       </c>
       <c r="L67" t="n">
-        <v>137.91</v>
+        <v>78.22</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>07:52:22</t>
+          <t>07:54:13</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -2893,34 +2893,34 @@
         <v>1</v>
       </c>
       <c r="E68" t="n">
-        <v>2.45</v>
+        <v>1.93</v>
       </c>
       <c r="F68" t="n">
-        <v>8.949999999999999</v>
+        <v>8.289999999999999</v>
       </c>
       <c r="G68" t="n">
-        <v>46.5</v>
+        <v>84.7</v>
       </c>
       <c r="H68" t="n">
-        <v>27.3</v>
+        <v>54.3</v>
       </c>
       <c r="I68" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="J68" t="n">
-        <v>129.69</v>
+        <v>-55.93</v>
       </c>
       <c r="K68" t="n">
-        <v>136.92</v>
+        <v>-84.16</v>
       </c>
       <c r="L68" t="n">
-        <v>188.59</v>
+        <v>101.05</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>07:54:08</t>
+          <t>07:56:30</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -2935,34 +2935,34 @@
         <v>2</v>
       </c>
       <c r="E69" t="n">
-        <v>3.98</v>
+        <v>2.3</v>
       </c>
       <c r="F69" t="n">
         <v>10.35</v>
       </c>
       <c r="G69" t="n">
-        <v>79.59999999999999</v>
+        <v>70.09999999999999</v>
       </c>
       <c r="H69" t="n">
-        <v>26.4</v>
+        <v>48.1</v>
       </c>
       <c r="I69" t="n">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="J69" t="n">
-        <v>21.71</v>
+        <v>96.88</v>
       </c>
       <c r="K69" t="n">
-        <v>-206.04</v>
+        <v>-34.58</v>
       </c>
       <c r="L69" t="n">
-        <v>207.18</v>
+        <v>102.87</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>07:56:03</t>
+          <t>07:57:32</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -2977,34 +2977,34 @@
         <v>3</v>
       </c>
       <c r="E70" t="n">
-        <v>2.13</v>
+        <v>2.22</v>
       </c>
       <c r="F70" t="n">
-        <v>8.93</v>
+        <v>10.31</v>
       </c>
       <c r="G70" t="n">
-        <v>65.59999999999999</v>
+        <v>63.6</v>
       </c>
       <c r="H70" t="n">
-        <v>26.6</v>
+        <v>0</v>
       </c>
       <c r="I70" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="J70" t="n">
-        <v>6.64</v>
+        <v>74.76000000000001</v>
       </c>
       <c r="K70" t="n">
-        <v>208.2</v>
+        <v>126.84</v>
       </c>
       <c r="L70" t="n">
-        <v>208.3</v>
+        <v>147.23</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>07:59:24</t>
+          <t>08:02:50</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -3019,34 +3019,34 @@
         <v>1</v>
       </c>
       <c r="E71" t="n">
-        <v>2.1</v>
+        <v>1.86</v>
       </c>
       <c r="F71" t="n">
-        <v>8.51</v>
+        <v>10.35</v>
       </c>
       <c r="G71" t="n">
-        <v>85.59999999999999</v>
+        <v>69.59999999999999</v>
       </c>
       <c r="H71" t="n">
-        <v>30.2</v>
+        <v>63.8</v>
       </c>
       <c r="I71" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="J71" t="n">
-        <v>138.72</v>
+        <v>126.25</v>
       </c>
       <c r="K71" t="n">
-        <v>-164.32</v>
+        <v>-149.89</v>
       </c>
       <c r="L71" t="n">
-        <v>215.05</v>
+        <v>195.98</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>08:00:30</t>
+          <t>08:03:26</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -3061,34 +3061,34 @@
         <v>2</v>
       </c>
       <c r="E72" t="n">
-        <v>1.26</v>
+        <v>1.94</v>
       </c>
       <c r="F72" t="n">
-        <v>10.35</v>
+        <v>9.75</v>
       </c>
       <c r="G72" t="n">
-        <v>78.7</v>
+        <v>74.40000000000001</v>
       </c>
       <c r="H72" t="n">
-        <v>32.7</v>
+        <v>83.59999999999999</v>
       </c>
       <c r="I72" t="n">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="J72" t="n">
-        <v>-359.44</v>
+        <v>-82.73</v>
       </c>
       <c r="K72" t="n">
-        <v>-177.48</v>
+        <v>-107.82</v>
       </c>
       <c r="L72" t="n">
-        <v>400.87</v>
+        <v>135.9</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>08:02:49</t>
+          <t>08:06:06</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -3103,34 +3103,34 @@
         <v>3</v>
       </c>
       <c r="E73" t="n">
-        <v>2.17</v>
+        <v>1.79</v>
       </c>
       <c r="F73" t="n">
-        <v>10.09</v>
+        <v>10.35</v>
       </c>
       <c r="G73" t="n">
-        <v>61.6</v>
+        <v>69.8</v>
       </c>
       <c r="H73" t="n">
-        <v>34.1</v>
+        <v>41.2</v>
       </c>
       <c r="I73" t="n">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="J73" t="n">
-        <v>154.95</v>
+        <v>109.46</v>
       </c>
       <c r="K73" t="n">
-        <v>-67.83</v>
+        <v>-14.91</v>
       </c>
       <c r="L73" t="n">
-        <v>169.14</v>
+        <v>110.47</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>08:16:22</t>
+          <t>08:13:25</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -3145,34 +3145,34 @@
         <v>1</v>
       </c>
       <c r="E74" t="n">
-        <v>1.82</v>
+        <v>1.84</v>
       </c>
       <c r="F74" t="n">
-        <v>10.35</v>
+        <v>10</v>
       </c>
       <c r="G74" t="n">
-        <v>73.8</v>
+        <v>73.59999999999999</v>
       </c>
       <c r="H74" t="n">
-        <v>34.7</v>
+        <v>31.3</v>
       </c>
       <c r="I74" t="n">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="J74" t="n">
-        <v>-58.14</v>
+        <v>30.94</v>
       </c>
       <c r="K74" t="n">
-        <v>45.32</v>
+        <v>19.25</v>
       </c>
       <c r="L74" t="n">
-        <v>73.72</v>
+        <v>36.44</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>08:17:14</t>
+          <t>08:15:22</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -3187,34 +3187,34 @@
         <v>2</v>
       </c>
       <c r="E75" t="n">
-        <v>2.34</v>
+        <v>1.87</v>
       </c>
       <c r="F75" t="n">
-        <v>9.98</v>
+        <v>7.33</v>
       </c>
       <c r="G75" t="n">
-        <v>75.09999999999999</v>
+        <v>68.7</v>
       </c>
       <c r="H75" t="n">
-        <v>33.8</v>
+        <v>50.7</v>
       </c>
       <c r="I75" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="J75" t="n">
-        <v>-39.56</v>
+        <v>-30.57</v>
       </c>
       <c r="K75" t="n">
-        <v>67.34</v>
+        <v>25.53</v>
       </c>
       <c r="L75" t="n">
-        <v>78.09999999999999</v>
+        <v>39.83</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>08:18:42</t>
+          <t>08:17:23</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -3229,34 +3229,34 @@
         <v>3</v>
       </c>
       <c r="E76" t="n">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="F76" t="n">
-        <v>8.630000000000001</v>
+        <v>10.35</v>
       </c>
       <c r="G76" t="n">
-        <v>66</v>
+        <v>52.7</v>
       </c>
       <c r="H76" t="n">
-        <v>28.8</v>
+        <v>56.2</v>
       </c>
       <c r="I76" t="n">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="J76" t="n">
-        <v>37.96</v>
+        <v>-33.49</v>
       </c>
       <c r="K76" t="n">
-        <v>-33.55</v>
+        <v>-2.98</v>
       </c>
       <c r="L76" t="n">
-        <v>50.66</v>
+        <v>33.62</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>08:22:12</t>
+          <t>08:21:12</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -3271,34 +3271,34 @@
         <v>1</v>
       </c>
       <c r="E77" t="n">
-        <v>2.41</v>
+        <v>1.79</v>
       </c>
       <c r="F77" t="n">
-        <v>10.35</v>
+        <v>10.09</v>
       </c>
       <c r="G77" t="n">
-        <v>65.5</v>
+        <v>62.4</v>
       </c>
       <c r="H77" t="n">
-        <v>28.5</v>
+        <v>55.1</v>
       </c>
       <c r="I77" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="J77" t="n">
-        <v>81.25</v>
+        <v>45.09</v>
       </c>
       <c r="K77" t="n">
-        <v>54.86</v>
+        <v>0.23</v>
       </c>
       <c r="L77" t="n">
-        <v>98.03</v>
+        <v>45.09</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>08:24:05</t>
+          <t>08:23:45</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -3313,34 +3313,34 @@
         <v>2</v>
       </c>
       <c r="E78" t="n">
-        <v>2.06</v>
+        <v>2.1</v>
       </c>
       <c r="F78" t="n">
-        <v>10.35</v>
+        <v>7.76</v>
       </c>
       <c r="G78" t="n">
-        <v>64.59999999999999</v>
+        <v>77.3</v>
       </c>
       <c r="H78" t="n">
-        <v>30.8</v>
+        <v>53.8</v>
       </c>
       <c r="I78" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="J78" t="n">
-        <v>-60.8</v>
+        <v>33.2</v>
       </c>
       <c r="K78" t="n">
-        <v>-38.95</v>
+        <v>35.58</v>
       </c>
       <c r="L78" t="n">
-        <v>72.20999999999999</v>
+        <v>48.66</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>08:26:13</t>
+          <t>08:25:37</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -3355,34 +3355,34 @@
         <v>3</v>
       </c>
       <c r="E79" t="n">
-        <v>2.02</v>
+        <v>2.19</v>
       </c>
       <c r="F79" t="n">
         <v>10.35</v>
       </c>
       <c r="G79" t="n">
-        <v>60</v>
+        <v>54.8</v>
       </c>
       <c r="H79" t="n">
+        <v>27.9</v>
+      </c>
+      <c r="I79" t="n">
         <v>28</v>
       </c>
-      <c r="I79" t="n">
-        <v>24</v>
-      </c>
       <c r="J79" t="n">
-        <v>-67.43000000000001</v>
+        <v>55.88</v>
       </c>
       <c r="K79" t="n">
-        <v>23.1</v>
+        <v>3.5</v>
       </c>
       <c r="L79" t="n">
-        <v>71.28</v>
+        <v>55.99</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>08:30:47</t>
+          <t>08:29:28</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -3397,34 +3397,34 @@
         <v>1</v>
       </c>
       <c r="E80" t="n">
-        <v>2.05</v>
+        <v>2.14</v>
       </c>
       <c r="F80" t="n">
-        <v>10.35</v>
+        <v>10.15</v>
       </c>
       <c r="G80" t="n">
-        <v>70.40000000000001</v>
+        <v>69.59999999999999</v>
       </c>
       <c r="H80" t="n">
-        <v>29.7</v>
+        <v>58.8</v>
       </c>
       <c r="I80" t="n">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="J80" t="n">
-        <v>16.44</v>
+        <v>-69.09999999999999</v>
       </c>
       <c r="K80" t="n">
-        <v>92.81999999999999</v>
+        <v>-28.57</v>
       </c>
       <c r="L80" t="n">
-        <v>94.27</v>
+        <v>74.77</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>08:32:17</t>
+          <t>08:31:43</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -3439,34 +3439,34 @@
         <v>2</v>
       </c>
       <c r="E81" t="n">
-        <v>2.11</v>
+        <v>1.76</v>
       </c>
       <c r="F81" t="n">
-        <v>8.380000000000001</v>
+        <v>6.98</v>
       </c>
       <c r="G81" t="n">
-        <v>49.8</v>
+        <v>57.5</v>
       </c>
       <c r="H81" t="n">
-        <v>30.4</v>
+        <v>22.4</v>
       </c>
       <c r="I81" t="n">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="J81" t="n">
-        <v>144.87</v>
+        <v>-74.73</v>
       </c>
       <c r="K81" t="n">
-        <v>16.29</v>
+        <v>-68.27</v>
       </c>
       <c r="L81" t="n">
-        <v>145.78</v>
+        <v>101.22</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>08:35:06</t>
+          <t>08:33:40</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -3481,34 +3481,34 @@
         <v>3</v>
       </c>
       <c r="E82" t="n">
-        <v>2.29</v>
+        <v>2.22</v>
       </c>
       <c r="F82" t="n">
-        <v>7.23</v>
+        <v>10.35</v>
       </c>
       <c r="G82" t="n">
-        <v>62.2</v>
+        <v>49.7</v>
       </c>
       <c r="H82" t="n">
-        <v>34</v>
+        <v>50.7</v>
       </c>
       <c r="I82" t="n">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="J82" t="n">
-        <v>-6.17</v>
+        <v>32.92</v>
       </c>
       <c r="K82" t="n">
-        <v>94.54000000000001</v>
+        <v>83.56</v>
       </c>
       <c r="L82" t="n">
-        <v>94.73999999999999</v>
+        <v>89.81</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>08:40:54</t>
+          <t>08:38:37</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -3523,34 +3523,34 @@
         <v>1</v>
       </c>
       <c r="E83" t="n">
-        <v>2.06</v>
+        <v>2.11</v>
       </c>
       <c r="F83" t="n">
-        <v>8.380000000000001</v>
+        <v>10.35</v>
       </c>
       <c r="G83" t="n">
-        <v>68.8</v>
+        <v>77.5</v>
       </c>
       <c r="H83" t="n">
-        <v>32.8</v>
+        <v>28.7</v>
       </c>
       <c r="I83" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="J83" t="n">
-        <v>-43.11</v>
+        <v>47.66</v>
       </c>
       <c r="K83" t="n">
-        <v>-231.64</v>
+        <v>-98.34999999999999</v>
       </c>
       <c r="L83" t="n">
-        <v>235.62</v>
+        <v>109.29</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>08:42:00</t>
+          <t>08:39:49</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -3565,34 +3565,34 @@
         <v>2</v>
       </c>
       <c r="E84" t="n">
-        <v>2.42</v>
+        <v>2.34</v>
       </c>
       <c r="F84" t="n">
-        <v>10.35</v>
+        <v>9.6</v>
       </c>
       <c r="G84" t="n">
-        <v>75.2</v>
+        <v>59</v>
       </c>
       <c r="H84" t="n">
-        <v>31.7</v>
+        <v>52.2</v>
       </c>
       <c r="I84" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="J84" t="n">
-        <v>-223.93</v>
+        <v>120.16</v>
       </c>
       <c r="K84" t="n">
-        <v>68.5</v>
+        <v>29.07</v>
       </c>
       <c r="L84" t="n">
-        <v>234.18</v>
+        <v>123.62</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>08:44:37</t>
+          <t>08:41:18</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -3607,34 +3607,34 @@
         <v>3</v>
       </c>
       <c r="E85" t="n">
-        <v>2.02</v>
+        <v>2.07</v>
       </c>
       <c r="F85" t="n">
-        <v>10.35</v>
+        <v>8.08</v>
       </c>
       <c r="G85" t="n">
-        <v>58.3</v>
+        <v>61.2</v>
       </c>
       <c r="H85" t="n">
-        <v>29.2</v>
+        <v>47.8</v>
       </c>
       <c r="I85" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="J85" t="n">
-        <v>-164.53</v>
+        <v>69.98999999999999</v>
       </c>
       <c r="K85" t="n">
-        <v>-48.7</v>
+        <v>91.83</v>
       </c>
       <c r="L85" t="n">
-        <v>171.59</v>
+        <v>115.47</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>08:50:41</t>
+          <t>08:46:41</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -3649,34 +3649,34 @@
         <v>1</v>
       </c>
       <c r="E86" t="n">
-        <v>1.7</v>
+        <v>2.39</v>
       </c>
       <c r="F86" t="n">
-        <v>8.42</v>
+        <v>10.35</v>
       </c>
       <c r="G86" t="n">
-        <v>65.3</v>
+        <v>57.8</v>
       </c>
       <c r="H86" t="n">
-        <v>32.4</v>
+        <v>1.3</v>
       </c>
       <c r="I86" t="n">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="J86" t="n">
-        <v>-171.27</v>
+        <v>110.34</v>
       </c>
       <c r="K86" t="n">
-        <v>-50.31</v>
+        <v>132.56</v>
       </c>
       <c r="L86" t="n">
-        <v>178.51</v>
+        <v>172.47</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>08:51:31</t>
+          <t>08:48:20</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -3691,34 +3691,34 @@
         <v>2</v>
       </c>
       <c r="E87" t="n">
-        <v>1.89</v>
+        <v>2.32</v>
       </c>
       <c r="F87" t="n">
-        <v>4.86</v>
+        <v>10.08</v>
       </c>
       <c r="G87" t="n">
-        <v>68.59999999999999</v>
+        <v>66.3</v>
       </c>
       <c r="H87" t="n">
-        <v>28</v>
+        <v>31.4</v>
       </c>
       <c r="I87" t="n">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="J87" t="n">
-        <v>106.05</v>
+        <v>13.15</v>
       </c>
       <c r="K87" t="n">
-        <v>161.18</v>
+        <v>-130.34</v>
       </c>
       <c r="L87" t="n">
-        <v>192.94</v>
+        <v>131</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>08:53:27</t>
+          <t>08:49:08</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -3733,28 +3733,28 @@
         <v>3</v>
       </c>
       <c r="E88" t="n">
-        <v>1.53</v>
+        <v>2.19</v>
       </c>
       <c r="F88" t="n">
-        <v>10.31</v>
+        <v>9.23</v>
       </c>
       <c r="G88" t="n">
-        <v>80.40000000000001</v>
+        <v>53.4</v>
       </c>
       <c r="H88" t="n">
-        <v>32.3</v>
+        <v>15.2</v>
       </c>
       <c r="I88" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="J88" t="n">
-        <v>202.97</v>
+        <v>291.72</v>
       </c>
       <c r="K88" t="n">
-        <v>-81.97</v>
+        <v>15.42</v>
       </c>
       <c r="L88" t="n">
-        <v>218.9</v>
+        <v>292.12</v>
       </c>
     </row>
   </sheetData>

--- a/output/2024-07-26.xlsx
+++ b/output/2024-07-26.xlsx
@@ -625,34 +625,34 @@
         <v>1</v>
       </c>
       <c r="E14" t="n">
-        <v>1.7</v>
+        <v>1.02</v>
       </c>
       <c r="F14" t="n">
-        <v>7.78</v>
+        <v>5.94</v>
       </c>
       <c r="G14" t="n">
-        <v>63.7</v>
+        <v>56</v>
       </c>
       <c r="H14" t="n">
-        <v>29.4</v>
+        <v>56</v>
       </c>
       <c r="I14" t="n">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="J14" t="n">
-        <v>-6.08</v>
+        <v>-30.68</v>
       </c>
       <c r="K14" t="n">
-        <v>-28.79</v>
+        <v>6.38</v>
       </c>
       <c r="L14" t="n">
-        <v>29.43</v>
+        <v>31.34</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>05:10:54</t>
+          <t>05:10:20</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -667,34 +667,34 @@
         <v>2</v>
       </c>
       <c r="E15" t="n">
-        <v>2.09</v>
+        <v>1.7</v>
       </c>
       <c r="F15" t="n">
         <v>10.35</v>
       </c>
       <c r="G15" t="n">
-        <v>73.90000000000001</v>
+        <v>71</v>
       </c>
       <c r="H15" t="n">
-        <v>61.4</v>
+        <v>22.6</v>
       </c>
       <c r="I15" t="n">
-        <v>19</v>
+        <v>31</v>
       </c>
       <c r="J15" t="n">
-        <v>16.24</v>
+        <v>-32.38</v>
       </c>
       <c r="K15" t="n">
-        <v>28.85</v>
+        <v>-9.449999999999999</v>
       </c>
       <c r="L15" t="n">
-        <v>33.11</v>
+        <v>33.73</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>05:11:47</t>
+          <t>05:11:49</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -709,28 +709,28 @@
         <v>3</v>
       </c>
       <c r="E16" t="n">
-        <v>1.59</v>
+        <v>1.78</v>
       </c>
       <c r="F16" t="n">
-        <v>9.6</v>
+        <v>10.35</v>
       </c>
       <c r="G16" t="n">
-        <v>51.4</v>
+        <v>83.5</v>
       </c>
       <c r="H16" t="n">
-        <v>14.9</v>
+        <v>23.5</v>
       </c>
       <c r="I16" t="n">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="J16" t="n">
-        <v>-28.58</v>
+        <v>-34.99</v>
       </c>
       <c r="K16" t="n">
-        <v>-0.9399999999999999</v>
+        <v>3.35</v>
       </c>
       <c r="L16" t="n">
-        <v>28.6</v>
+        <v>35.15</v>
       </c>
     </row>
     <row r="17">
@@ -751,34 +751,34 @@
         <v>1</v>
       </c>
       <c r="E17" t="n">
-        <v>1.78</v>
+        <v>1.92</v>
       </c>
       <c r="F17" t="n">
-        <v>5.58</v>
+        <v>5.95</v>
       </c>
       <c r="G17" t="n">
-        <v>63</v>
+        <v>74</v>
       </c>
       <c r="H17" t="n">
-        <v>37.9</v>
+        <v>28.7</v>
       </c>
       <c r="I17" t="n">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="J17" t="n">
-        <v>16.83</v>
+        <v>8.390000000000001</v>
       </c>
       <c r="K17" t="n">
-        <v>-39.26</v>
+        <v>-43.16</v>
       </c>
       <c r="L17" t="n">
-        <v>42.71</v>
+        <v>43.97</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>05:17:54</t>
+          <t>05:19:01</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -793,34 +793,34 @@
         <v>2</v>
       </c>
       <c r="E18" t="n">
-        <v>1.76</v>
+        <v>2.09</v>
       </c>
       <c r="F18" t="n">
-        <v>10.35</v>
+        <v>8.93</v>
       </c>
       <c r="G18" t="n">
-        <v>61.5</v>
+        <v>70</v>
       </c>
       <c r="H18" t="n">
-        <v>10.8</v>
+        <v>35.6</v>
       </c>
       <c r="I18" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="J18" t="n">
-        <v>-38.41</v>
+        <v>-7.34</v>
       </c>
       <c r="K18" t="n">
-        <v>31.62</v>
+        <v>53.68</v>
       </c>
       <c r="L18" t="n">
-        <v>49.75</v>
+        <v>54.18</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>05:18:56</t>
+          <t>05:21:35</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -835,34 +835,34 @@
         <v>3</v>
       </c>
       <c r="E19" t="n">
-        <v>1.87</v>
+        <v>1.82</v>
       </c>
       <c r="F19" t="n">
-        <v>6.01</v>
+        <v>6.69</v>
       </c>
       <c r="G19" t="n">
-        <v>69.59999999999999</v>
+        <v>62.4</v>
       </c>
       <c r="H19" t="n">
-        <v>16.8</v>
+        <v>22.7</v>
       </c>
       <c r="I19" t="n">
-        <v>22</v>
+        <v>32</v>
       </c>
       <c r="J19" t="n">
-        <v>43.25</v>
+        <v>-41.63</v>
       </c>
       <c r="K19" t="n">
-        <v>-29.78</v>
+        <v>-15.72</v>
       </c>
       <c r="L19" t="n">
-        <v>52.51</v>
+        <v>44.5</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>05:22:39</t>
+          <t>05:26:20</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -877,34 +877,34 @@
         <v>1</v>
       </c>
       <c r="E20" t="n">
-        <v>1.21</v>
+        <v>2.01</v>
       </c>
       <c r="F20" t="n">
-        <v>4.37</v>
+        <v>5.94</v>
       </c>
       <c r="G20" t="n">
-        <v>65.8</v>
+        <v>70.8</v>
       </c>
       <c r="H20" t="n">
-        <v>14.6</v>
+        <v>28.1</v>
       </c>
       <c r="I20" t="n">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="J20" t="n">
-        <v>-62.32</v>
+        <v>-73.44</v>
       </c>
       <c r="K20" t="n">
-        <v>26.62</v>
+        <v>14.53</v>
       </c>
       <c r="L20" t="n">
-        <v>67.77</v>
+        <v>74.87</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>05:24:07</t>
+          <t>05:28:12</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -919,34 +919,34 @@
         <v>2</v>
       </c>
       <c r="E21" t="n">
-        <v>1.58</v>
+        <v>1.29</v>
       </c>
       <c r="F21" t="n">
-        <v>8.720000000000001</v>
+        <v>3.74</v>
       </c>
       <c r="G21" t="n">
-        <v>60.2</v>
+        <v>68.2</v>
       </c>
       <c r="H21" t="n">
-        <v>60.9</v>
+        <v>66.3</v>
       </c>
       <c r="I21" t="n">
-        <v>20</v>
+        <v>32</v>
       </c>
       <c r="J21" t="n">
-        <v>-56.33</v>
+        <v>8.890000000000001</v>
       </c>
       <c r="K21" t="n">
-        <v>-10</v>
+        <v>-73</v>
       </c>
       <c r="L21" t="n">
-        <v>57.21</v>
+        <v>73.54000000000001</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>05:25:48</t>
+          <t>05:29:23</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -961,34 +961,34 @@
         <v>3</v>
       </c>
       <c r="E22" t="n">
-        <v>1.27</v>
+        <v>1.81</v>
       </c>
       <c r="F22" t="n">
-        <v>8.58</v>
+        <v>10.35</v>
       </c>
       <c r="G22" t="n">
-        <v>63.7</v>
+        <v>70.59999999999999</v>
       </c>
       <c r="H22" t="n">
-        <v>49.1</v>
+        <v>59.4</v>
       </c>
       <c r="I22" t="n">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="J22" t="n">
-        <v>7.17</v>
+        <v>-16.14</v>
       </c>
       <c r="K22" t="n">
-        <v>60.25</v>
+        <v>71.52</v>
       </c>
       <c r="L22" t="n">
-        <v>60.67</v>
+        <v>73.31999999999999</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>05:30:11</t>
+          <t>05:35:00</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1003,34 +1003,34 @@
         <v>1</v>
       </c>
       <c r="E23" t="n">
-        <v>1.82</v>
+        <v>1.6</v>
       </c>
       <c r="F23" t="n">
-        <v>7.68</v>
+        <v>6.71</v>
       </c>
       <c r="G23" t="n">
-        <v>66.3</v>
+        <v>72.3</v>
       </c>
       <c r="H23" t="n">
-        <v>38.9</v>
+        <v>57.8</v>
       </c>
       <c r="I23" t="n">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="J23" t="n">
-        <v>-98.08</v>
+        <v>114.58</v>
       </c>
       <c r="K23" t="n">
-        <v>54.64</v>
+        <v>-38.36</v>
       </c>
       <c r="L23" t="n">
-        <v>112.27</v>
+        <v>120.83</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>05:32:27</t>
+          <t>05:37:38</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1045,34 +1045,34 @@
         <v>2</v>
       </c>
       <c r="E24" t="n">
-        <v>1.75</v>
+        <v>2.08</v>
       </c>
       <c r="F24" t="n">
         <v>10.35</v>
       </c>
       <c r="G24" t="n">
-        <v>50.6</v>
+        <v>64.7</v>
       </c>
       <c r="H24" t="n">
-        <v>26.2</v>
+        <v>38.6</v>
       </c>
       <c r="I24" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="J24" t="n">
-        <v>-21.51</v>
+        <v>104.09</v>
       </c>
       <c r="K24" t="n">
-        <v>-83.84999999999999</v>
+        <v>-0.89</v>
       </c>
       <c r="L24" t="n">
-        <v>86.56999999999999</v>
+        <v>104.09</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>05:34:20</t>
+          <t>05:38:15</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1087,34 +1087,34 @@
         <v>3</v>
       </c>
       <c r="E25" t="n">
-        <v>2.36</v>
+        <v>1.75</v>
       </c>
       <c r="F25" t="n">
-        <v>9.859999999999999</v>
+        <v>4.75</v>
       </c>
       <c r="G25" t="n">
-        <v>60.5</v>
+        <v>67.7</v>
       </c>
       <c r="H25" t="n">
-        <v>50.5</v>
+        <v>24.5</v>
       </c>
       <c r="I25" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="J25" t="n">
-        <v>114.97</v>
+        <v>-118.83</v>
       </c>
       <c r="K25" t="n">
-        <v>79.39</v>
+        <v>33.12</v>
       </c>
       <c r="L25" t="n">
-        <v>139.72</v>
+        <v>123.36</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>05:39:10</t>
+          <t>05:42:13</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1129,34 +1129,34 @@
         <v>1</v>
       </c>
       <c r="E26" t="n">
-        <v>1.74</v>
+        <v>1.76</v>
       </c>
       <c r="F26" t="n">
-        <v>4.59</v>
+        <v>8.609999999999999</v>
       </c>
       <c r="G26" t="n">
-        <v>78</v>
+        <v>61.9</v>
       </c>
       <c r="H26" t="n">
-        <v>30.3</v>
+        <v>70.8</v>
       </c>
       <c r="I26" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="J26" t="n">
-        <v>149.21</v>
+        <v>80.93000000000001</v>
       </c>
       <c r="K26" t="n">
-        <v>-9.859999999999999</v>
+        <v>132.23</v>
       </c>
       <c r="L26" t="n">
-        <v>149.54</v>
+        <v>155.03</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>05:41:29</t>
+          <t>05:43:43</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1171,34 +1171,34 @@
         <v>2</v>
       </c>
       <c r="E27" t="n">
-        <v>1.87</v>
+        <v>2.08</v>
       </c>
       <c r="F27" t="n">
-        <v>7.94</v>
+        <v>7.61</v>
       </c>
       <c r="G27" t="n">
-        <v>72.5</v>
+        <v>68.7</v>
       </c>
       <c r="H27" t="n">
-        <v>44.9</v>
+        <v>50.7</v>
       </c>
       <c r="I27" t="n">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="J27" t="n">
-        <v>153.73</v>
+        <v>101.56</v>
       </c>
       <c r="K27" t="n">
-        <v>8.16</v>
+        <v>125.67</v>
       </c>
       <c r="L27" t="n">
-        <v>153.95</v>
+        <v>161.58</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>05:42:54</t>
+          <t>05:45:42</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1213,34 +1213,34 @@
         <v>3</v>
       </c>
       <c r="E28" t="n">
-        <v>1.63</v>
+        <v>1.83</v>
       </c>
       <c r="F28" t="n">
-        <v>6.63</v>
+        <v>9.48</v>
       </c>
       <c r="G28" t="n">
-        <v>77.3</v>
+        <v>63.5</v>
       </c>
       <c r="H28" t="n">
-        <v>40.6</v>
+        <v>69.5</v>
       </c>
       <c r="I28" t="n">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="J28" t="n">
-        <v>93.06</v>
+        <v>-44.27</v>
       </c>
       <c r="K28" t="n">
-        <v>111.45</v>
+        <v>44.16</v>
       </c>
       <c r="L28" t="n">
-        <v>145.2</v>
+        <v>62.53</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>05:54:13</t>
+          <t>05:56:22</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1255,34 +1255,34 @@
         <v>1</v>
       </c>
       <c r="E29" t="n">
-        <v>2.15</v>
+        <v>1.62</v>
       </c>
       <c r="F29" t="n">
-        <v>9.41</v>
+        <v>4.57</v>
       </c>
       <c r="G29" t="n">
-        <v>57</v>
+        <v>62.2</v>
       </c>
       <c r="H29" t="n">
-        <v>75.8</v>
+        <v>49.9</v>
       </c>
       <c r="I29" t="n">
-        <v>20</v>
+        <v>32</v>
       </c>
       <c r="J29" t="n">
-        <v>4.67</v>
+        <v>-27.74</v>
       </c>
       <c r="K29" t="n">
-        <v>43.34</v>
+        <v>22.55</v>
       </c>
       <c r="L29" t="n">
-        <v>43.59</v>
+        <v>35.75</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>05:55:50</t>
+          <t>05:57:51</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1297,34 +1297,34 @@
         <v>2</v>
       </c>
       <c r="E30" t="n">
-        <v>1.93</v>
+        <v>2.08</v>
       </c>
       <c r="F30" t="n">
-        <v>7.52</v>
+        <v>10.35</v>
       </c>
       <c r="G30" t="n">
-        <v>64.2</v>
+        <v>67.90000000000001</v>
       </c>
       <c r="H30" t="n">
-        <v>57.3</v>
+        <v>74.5</v>
       </c>
       <c r="I30" t="n">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="J30" t="n">
-        <v>30.18</v>
+        <v>-27.8</v>
       </c>
       <c r="K30" t="n">
-        <v>-19.92</v>
+        <v>8.449999999999999</v>
       </c>
       <c r="L30" t="n">
-        <v>36.16</v>
+        <v>29.05</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>05:57:11</t>
+          <t>05:59:22</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1339,34 +1339,34 @@
         <v>3</v>
       </c>
       <c r="E31" t="n">
-        <v>2.23</v>
+        <v>1.42</v>
       </c>
       <c r="F31" t="n">
-        <v>10.35</v>
+        <v>3.18</v>
       </c>
       <c r="G31" t="n">
-        <v>62.4</v>
+        <v>56.9</v>
       </c>
       <c r="H31" t="n">
-        <v>54.3</v>
+        <v>50.5</v>
       </c>
       <c r="I31" t="n">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="J31" t="n">
-        <v>-4.3</v>
+        <v>20.44</v>
       </c>
       <c r="K31" t="n">
-        <v>41.01</v>
+        <v>-21.24</v>
       </c>
       <c r="L31" t="n">
-        <v>41.23</v>
+        <v>29.47</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>06:00:45</t>
+          <t>06:04:49</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1381,34 +1381,34 @@
         <v>1</v>
       </c>
       <c r="E32" t="n">
-        <v>1.65</v>
+        <v>1.76</v>
       </c>
       <c r="F32" t="n">
-        <v>2.85</v>
+        <v>10.35</v>
       </c>
       <c r="G32" t="n">
-        <v>64.2</v>
+        <v>63.1</v>
       </c>
       <c r="H32" t="n">
-        <v>38.3</v>
+        <v>88</v>
       </c>
       <c r="I32" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="J32" t="n">
-        <v>-36.11</v>
+        <v>50.41</v>
       </c>
       <c r="K32" t="n">
-        <v>16.31</v>
+        <v>5.03</v>
       </c>
       <c r="L32" t="n">
-        <v>39.63</v>
+        <v>50.66</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>06:02:00</t>
+          <t>06:06:17</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1423,34 +1423,34 @@
         <v>2</v>
       </c>
       <c r="E33" t="n">
-        <v>1.4</v>
+        <v>1.37</v>
       </c>
       <c r="F33" t="n">
-        <v>7.32</v>
+        <v>10.19</v>
       </c>
       <c r="G33" t="n">
-        <v>67</v>
+        <v>70.59999999999999</v>
       </c>
       <c r="H33" t="n">
-        <v>30.5</v>
+        <v>60.9</v>
       </c>
       <c r="I33" t="n">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="J33" t="n">
-        <v>-40.45</v>
+        <v>14.54</v>
       </c>
       <c r="K33" t="n">
-        <v>18.61</v>
+        <v>-60.53</v>
       </c>
       <c r="L33" t="n">
-        <v>44.53</v>
+        <v>62.25</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>06:03:22</t>
+          <t>06:08:53</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1465,34 +1465,34 @@
         <v>3</v>
       </c>
       <c r="E34" t="n">
-        <v>1.75</v>
+        <v>1.67</v>
       </c>
       <c r="F34" t="n">
-        <v>5.41</v>
+        <v>3.45</v>
       </c>
       <c r="G34" t="n">
-        <v>67.59999999999999</v>
+        <v>45.5</v>
       </c>
       <c r="H34" t="n">
-        <v>47.9</v>
+        <v>55</v>
       </c>
       <c r="I34" t="n">
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="J34" t="n">
-        <v>1.87</v>
+        <v>-43.27</v>
       </c>
       <c r="K34" t="n">
-        <v>39.06</v>
+        <v>19.72</v>
       </c>
       <c r="L34" t="n">
-        <v>39.11</v>
+        <v>47.55</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>06:08:26</t>
+          <t>06:14:21</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1507,34 +1507,34 @@
         <v>1</v>
       </c>
       <c r="E35" t="n">
-        <v>2.11</v>
+        <v>2.08</v>
       </c>
       <c r="F35" t="n">
-        <v>4.25</v>
+        <v>4.98</v>
       </c>
       <c r="G35" t="n">
-        <v>84.90000000000001</v>
+        <v>64</v>
       </c>
       <c r="H35" t="n">
-        <v>38.9</v>
+        <v>56.7</v>
       </c>
       <c r="I35" t="n">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="J35" t="n">
-        <v>64.43000000000001</v>
+        <v>11.91</v>
       </c>
       <c r="K35" t="n">
-        <v>59.85</v>
+        <v>-72.51000000000001</v>
       </c>
       <c r="L35" t="n">
-        <v>87.94</v>
+        <v>73.48999999999999</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>06:10:49</t>
+          <t>06:15:55</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1549,34 +1549,34 @@
         <v>2</v>
       </c>
       <c r="E36" t="n">
-        <v>1.87</v>
+        <v>2.11</v>
       </c>
       <c r="F36" t="n">
-        <v>2.17</v>
+        <v>10.35</v>
       </c>
       <c r="G36" t="n">
-        <v>60.7</v>
+        <v>59.9</v>
       </c>
       <c r="H36" t="n">
-        <v>70.7</v>
+        <v>54.4</v>
       </c>
       <c r="I36" t="n">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="J36" t="n">
-        <v>-38.13</v>
+        <v>32.45</v>
       </c>
       <c r="K36" t="n">
-        <v>73.12</v>
+        <v>-94.89</v>
       </c>
       <c r="L36" t="n">
-        <v>82.47</v>
+        <v>100.29</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>06:12:32</t>
+          <t>06:17:18</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1591,34 +1591,34 @@
         <v>3</v>
       </c>
       <c r="E37" t="n">
-        <v>1.62</v>
+        <v>1.94</v>
       </c>
       <c r="F37" t="n">
-        <v>9.35</v>
+        <v>9.6</v>
       </c>
       <c r="G37" t="n">
-        <v>73.09999999999999</v>
+        <v>53.8</v>
       </c>
       <c r="H37" t="n">
-        <v>47.6</v>
+        <v>41.5</v>
       </c>
       <c r="I37" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="J37" t="n">
-        <v>72.48</v>
+        <v>-7.93</v>
       </c>
       <c r="K37" t="n">
-        <v>40.78</v>
+        <v>-79.09999999999999</v>
       </c>
       <c r="L37" t="n">
-        <v>83.17</v>
+        <v>79.5</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>06:17:08</t>
+          <t>06:21:59</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1633,34 +1633,34 @@
         <v>1</v>
       </c>
       <c r="E38" t="n">
-        <v>2.27</v>
+        <v>1.8</v>
       </c>
       <c r="F38" t="n">
-        <v>5.2</v>
+        <v>7.4</v>
       </c>
       <c r="G38" t="n">
-        <v>58.2</v>
+        <v>69.40000000000001</v>
       </c>
       <c r="H38" t="n">
-        <v>80.8</v>
+        <v>30</v>
       </c>
       <c r="I38" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="J38" t="n">
-        <v>-20.74</v>
+        <v>-94.06999999999999</v>
       </c>
       <c r="K38" t="n">
-        <v>139.46</v>
+        <v>-89.18000000000001</v>
       </c>
       <c r="L38" t="n">
-        <v>141</v>
+        <v>129.63</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>06:19:13</t>
+          <t>06:23:33</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1675,34 +1675,34 @@
         <v>2</v>
       </c>
       <c r="E39" t="n">
-        <v>2.09</v>
+        <v>1.62</v>
       </c>
       <c r="F39" t="n">
-        <v>4.25</v>
+        <v>8.67</v>
       </c>
       <c r="G39" t="n">
-        <v>73.90000000000001</v>
+        <v>72.7</v>
       </c>
       <c r="H39" t="n">
-        <v>0</v>
+        <v>23.5</v>
       </c>
       <c r="I39" t="n">
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="J39" t="n">
-        <v>-40.25</v>
+        <v>75.34999999999999</v>
       </c>
       <c r="K39" t="n">
-        <v>-125.17</v>
+        <v>122.18</v>
       </c>
       <c r="L39" t="n">
-        <v>131.48</v>
+        <v>143.55</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>06:20:46</t>
+          <t>06:24:40</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1717,34 +1717,34 @@
         <v>3</v>
       </c>
       <c r="E40" t="n">
-        <v>2.1</v>
+        <v>1.98</v>
       </c>
       <c r="F40" t="n">
-        <v>5.6</v>
+        <v>10.35</v>
       </c>
       <c r="G40" t="n">
-        <v>62.3</v>
+        <v>76.40000000000001</v>
       </c>
       <c r="H40" t="n">
-        <v>0</v>
+        <v>44.7</v>
       </c>
       <c r="I40" t="n">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="J40" t="n">
-        <v>53.06</v>
+        <v>122.18</v>
       </c>
       <c r="K40" t="n">
-        <v>-91.02</v>
+        <v>37.32</v>
       </c>
       <c r="L40" t="n">
-        <v>105.36</v>
+        <v>127.75</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>06:26:05</t>
+          <t>06:29:19</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1759,34 +1759,34 @@
         <v>1</v>
       </c>
       <c r="E41" t="n">
-        <v>2.08</v>
+        <v>1.69</v>
       </c>
       <c r="F41" t="n">
-        <v>10.35</v>
+        <v>9.42</v>
       </c>
       <c r="G41" t="n">
-        <v>62.8</v>
+        <v>49.3</v>
       </c>
       <c r="H41" t="n">
-        <v>46.1</v>
+        <v>54.5</v>
       </c>
       <c r="I41" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="J41" t="n">
-        <v>184.96</v>
+        <v>65.76000000000001</v>
       </c>
       <c r="K41" t="n">
-        <v>-18.55</v>
+        <v>144.7</v>
       </c>
       <c r="L41" t="n">
-        <v>185.88</v>
+        <v>158.94</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>06:28:20</t>
+          <t>06:30:28</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -1801,34 +1801,34 @@
         <v>2</v>
       </c>
       <c r="E42" t="n">
-        <v>2.07</v>
+        <v>1.9</v>
       </c>
       <c r="F42" t="n">
-        <v>8.42</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="G42" t="n">
-        <v>70.40000000000001</v>
+        <v>79.3</v>
       </c>
       <c r="H42" t="n">
-        <v>30.5</v>
+        <v>55.3</v>
       </c>
       <c r="I42" t="n">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="J42" t="n">
-        <v>-84.36</v>
+        <v>-2.28</v>
       </c>
       <c r="K42" t="n">
-        <v>189.31</v>
+        <v>-145.68</v>
       </c>
       <c r="L42" t="n">
-        <v>207.26</v>
+        <v>145.7</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>06:30:28</t>
+          <t>06:31:42</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -1843,34 +1843,34 @@
         <v>3</v>
       </c>
       <c r="E43" t="n">
-        <v>1.98</v>
+        <v>2.33</v>
       </c>
       <c r="F43" t="n">
-        <v>6.94</v>
+        <v>10.13</v>
       </c>
       <c r="G43" t="n">
-        <v>69.3</v>
+        <v>64.2</v>
       </c>
       <c r="H43" t="n">
-        <v>44.9</v>
+        <v>47.1</v>
       </c>
       <c r="I43" t="n">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="J43" t="n">
-        <v>-56.7</v>
+        <v>-144.38</v>
       </c>
       <c r="K43" t="n">
-        <v>-156.37</v>
+        <v>165.34</v>
       </c>
       <c r="L43" t="n">
-        <v>166.33</v>
+        <v>219.51</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>06:40:23</t>
+          <t>06:40:34</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -1885,34 +1885,34 @@
         <v>1</v>
       </c>
       <c r="E44" t="n">
-        <v>1.57</v>
+        <v>1.61</v>
       </c>
       <c r="F44" t="n">
-        <v>6.84</v>
+        <v>10.35</v>
       </c>
       <c r="G44" t="n">
-        <v>67.5</v>
+        <v>71.09999999999999</v>
       </c>
       <c r="H44" t="n">
-        <v>55.3</v>
+        <v>74.90000000000001</v>
       </c>
       <c r="I44" t="n">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="J44" t="n">
-        <v>-2.93</v>
+        <v>9.16</v>
       </c>
       <c r="K44" t="n">
-        <v>37.89</v>
+        <v>-14.71</v>
       </c>
       <c r="L44" t="n">
-        <v>38</v>
+        <v>17.33</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>06:42:39</t>
+          <t>06:42:24</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -1927,34 +1927,34 @@
         <v>2</v>
       </c>
       <c r="E45" t="n">
-        <v>1.72</v>
+        <v>2.93</v>
       </c>
       <c r="F45" t="n">
-        <v>8.44</v>
+        <v>9.76</v>
       </c>
       <c r="G45" t="n">
-        <v>62.6</v>
+        <v>63.6</v>
       </c>
       <c r="H45" t="n">
-        <v>52.8</v>
+        <v>55.4</v>
       </c>
       <c r="I45" t="n">
         <v>24</v>
       </c>
       <c r="J45" t="n">
-        <v>-26.81</v>
+        <v>1.18</v>
       </c>
       <c r="K45" t="n">
-        <v>-12.8</v>
+        <v>53.13</v>
       </c>
       <c r="L45" t="n">
-        <v>29.71</v>
+        <v>53.15</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>06:43:17</t>
+          <t>06:44:33</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -1969,34 +1969,34 @@
         <v>3</v>
       </c>
       <c r="E46" t="n">
-        <v>2.2</v>
+        <v>2.06</v>
       </c>
       <c r="F46" t="n">
-        <v>10.35</v>
+        <v>6.87</v>
       </c>
       <c r="G46" t="n">
-        <v>74.5</v>
+        <v>72.7</v>
       </c>
       <c r="H46" t="n">
-        <v>44.9</v>
+        <v>68.2</v>
       </c>
       <c r="I46" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="J46" t="n">
-        <v>25.33</v>
+        <v>18.59</v>
       </c>
       <c r="K46" t="n">
-        <v>-27.71</v>
+        <v>-17.81</v>
       </c>
       <c r="L46" t="n">
-        <v>37.54</v>
+        <v>25.75</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>06:48:42</t>
+          <t>06:48:44</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -2011,34 +2011,34 @@
         <v>1</v>
       </c>
       <c r="E47" t="n">
-        <v>2.11</v>
+        <v>1.7</v>
       </c>
       <c r="F47" t="n">
-        <v>8.529999999999999</v>
+        <v>6.7</v>
       </c>
       <c r="G47" t="n">
-        <v>68.90000000000001</v>
+        <v>67.8</v>
       </c>
       <c r="H47" t="n">
-        <v>35.7</v>
+        <v>61</v>
       </c>
       <c r="I47" t="n">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="J47" t="n">
-        <v>-52.14</v>
+        <v>42.88</v>
       </c>
       <c r="K47" t="n">
-        <v>-18.02</v>
+        <v>5.55</v>
       </c>
       <c r="L47" t="n">
-        <v>55.16</v>
+        <v>43.24</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>06:50:06</t>
+          <t>06:51:08</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2053,34 +2053,34 @@
         <v>2</v>
       </c>
       <c r="E48" t="n">
-        <v>1.32</v>
+        <v>2.07</v>
       </c>
       <c r="F48" t="n">
-        <v>6.89</v>
+        <v>7.31</v>
       </c>
       <c r="G48" t="n">
-        <v>71.90000000000001</v>
+        <v>54.6</v>
       </c>
       <c r="H48" t="n">
-        <v>16.9</v>
+        <v>48.5</v>
       </c>
       <c r="I48" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="J48" t="n">
-        <v>25.55</v>
+        <v>-39.11</v>
       </c>
       <c r="K48" t="n">
-        <v>31.01</v>
+        <v>36.77</v>
       </c>
       <c r="L48" t="n">
-        <v>40.18</v>
+        <v>53.69</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>06:51:07</t>
+          <t>06:52:36</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2095,34 +2095,34 @@
         <v>3</v>
       </c>
       <c r="E49" t="n">
-        <v>2.46</v>
+        <v>2.22</v>
       </c>
       <c r="F49" t="n">
-        <v>8.06</v>
+        <v>10.35</v>
       </c>
       <c r="G49" t="n">
-        <v>69.40000000000001</v>
+        <v>67.7</v>
       </c>
       <c r="H49" t="n">
-        <v>42.5</v>
+        <v>40.1</v>
       </c>
       <c r="I49" t="n">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="J49" t="n">
-        <v>50.6</v>
+        <v>-14</v>
       </c>
       <c r="K49" t="n">
-        <v>53.71</v>
+        <v>63.99</v>
       </c>
       <c r="L49" t="n">
-        <v>73.79000000000001</v>
+        <v>65.5</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>06:56:10</t>
+          <t>06:57:30</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -2137,34 +2137,34 @@
         <v>1</v>
       </c>
       <c r="E50" t="n">
-        <v>2.37</v>
+        <v>1.43</v>
       </c>
       <c r="F50" t="n">
-        <v>10.35</v>
+        <v>5.6</v>
       </c>
       <c r="G50" t="n">
-        <v>63.8</v>
+        <v>63.1</v>
       </c>
       <c r="H50" t="n">
-        <v>38.4</v>
+        <v>93.40000000000001</v>
       </c>
       <c r="I50" t="n">
         <v>28</v>
       </c>
       <c r="J50" t="n">
-        <v>15.39</v>
+        <v>67.81999999999999</v>
       </c>
       <c r="K50" t="n">
-        <v>135.07</v>
+        <v>7.56</v>
       </c>
       <c r="L50" t="n">
-        <v>135.94</v>
+        <v>68.23999999999999</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>06:57:36</t>
+          <t>06:59:51</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -2179,34 +2179,34 @@
         <v>2</v>
       </c>
       <c r="E51" t="n">
-        <v>2.17</v>
+        <v>1.61</v>
       </c>
       <c r="F51" t="n">
-        <v>8.77</v>
+        <v>10.35</v>
       </c>
       <c r="G51" t="n">
-        <v>56.6</v>
+        <v>69.09999999999999</v>
       </c>
       <c r="H51" t="n">
-        <v>49.1</v>
+        <v>7.7</v>
       </c>
       <c r="I51" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="J51" t="n">
-        <v>58.52</v>
+        <v>44.98</v>
       </c>
       <c r="K51" t="n">
-        <v>-83.79000000000001</v>
+        <v>63.05</v>
       </c>
       <c r="L51" t="n">
-        <v>102.21</v>
+        <v>77.45</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>06:59:52</t>
+          <t>07:02:28</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -2221,34 +2221,34 @@
         <v>3</v>
       </c>
       <c r="E52" t="n">
-        <v>2.06</v>
+        <v>2.2</v>
       </c>
       <c r="F52" t="n">
-        <v>4.31</v>
+        <v>10.29</v>
       </c>
       <c r="G52" t="n">
-        <v>69.8</v>
+        <v>72.7</v>
       </c>
       <c r="H52" t="n">
-        <v>45.3</v>
+        <v>63.7</v>
       </c>
       <c r="I52" t="n">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="J52" t="n">
-        <v>-80.47</v>
+        <v>20.72</v>
       </c>
       <c r="K52" t="n">
-        <v>3.7</v>
+        <v>-42.12</v>
       </c>
       <c r="L52" t="n">
-        <v>80.56</v>
+        <v>46.94</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>07:05:15</t>
+          <t>07:08:41</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -2263,34 +2263,34 @@
         <v>1</v>
       </c>
       <c r="E53" t="n">
-        <v>2.09</v>
+        <v>1.63</v>
       </c>
       <c r="F53" t="n">
         <v>10.35</v>
       </c>
       <c r="G53" t="n">
-        <v>67.3</v>
+        <v>69.8</v>
       </c>
       <c r="H53" t="n">
-        <v>48.8</v>
+        <v>38.9</v>
       </c>
       <c r="I53" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J53" t="n">
-        <v>135.28</v>
+        <v>48.47</v>
       </c>
       <c r="K53" t="n">
-        <v>-69.48999999999999</v>
+        <v>-97.40000000000001</v>
       </c>
       <c r="L53" t="n">
-        <v>152.09</v>
+        <v>108.79</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>07:07:32</t>
+          <t>07:10:42</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -2305,34 +2305,34 @@
         <v>2</v>
       </c>
       <c r="E54" t="n">
-        <v>1.9</v>
+        <v>1.45</v>
       </c>
       <c r="F54" t="n">
-        <v>8.44</v>
+        <v>1.75</v>
       </c>
       <c r="G54" t="n">
-        <v>79</v>
+        <v>60.5</v>
       </c>
       <c r="H54" t="n">
-        <v>30.9</v>
+        <v>65.8</v>
       </c>
       <c r="I54" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="J54" t="n">
-        <v>-42.22</v>
+        <v>-50.73</v>
       </c>
       <c r="K54" t="n">
-        <v>-72.11</v>
+        <v>87.12</v>
       </c>
       <c r="L54" t="n">
-        <v>83.56</v>
+        <v>100.81</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>07:08:25</t>
+          <t>07:11:48</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -2347,34 +2347,34 @@
         <v>3</v>
       </c>
       <c r="E55" t="n">
-        <v>2.15</v>
+        <v>2.61</v>
       </c>
       <c r="F55" t="n">
-        <v>10.35</v>
+        <v>3.16</v>
       </c>
       <c r="G55" t="n">
-        <v>54.4</v>
+        <v>62.6</v>
       </c>
       <c r="H55" t="n">
-        <v>12.3</v>
+        <v>35.4</v>
       </c>
       <c r="I55" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="J55" t="n">
-        <v>101.82</v>
+        <v>-101.67</v>
       </c>
       <c r="K55" t="n">
-        <v>13.77</v>
+        <v>37.28</v>
       </c>
       <c r="L55" t="n">
-        <v>102.75</v>
+        <v>108.29</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>07:12:57</t>
+          <t>07:15:45</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -2389,34 +2389,34 @@
         <v>1</v>
       </c>
       <c r="E56" t="n">
-        <v>1.89</v>
+        <v>2.12</v>
       </c>
       <c r="F56" t="n">
-        <v>8.34</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="G56" t="n">
-        <v>80.3</v>
+        <v>69.5</v>
       </c>
       <c r="H56" t="n">
-        <v>67.59999999999999</v>
+        <v>38.1</v>
       </c>
       <c r="I56" t="n">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="J56" t="n">
-        <v>161.78</v>
+        <v>112.14</v>
       </c>
       <c r="K56" t="n">
-        <v>-59.19</v>
+        <v>38.05</v>
       </c>
       <c r="L56" t="n">
-        <v>172.27</v>
+        <v>118.42</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>07:15:04</t>
+          <t>07:18:23</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -2431,34 +2431,34 @@
         <v>2</v>
       </c>
       <c r="E57" t="n">
-        <v>1.74</v>
+        <v>2.2</v>
       </c>
       <c r="F57" t="n">
-        <v>4.75</v>
+        <v>8.039999999999999</v>
       </c>
       <c r="G57" t="n">
-        <v>70.5</v>
+        <v>77</v>
       </c>
       <c r="H57" t="n">
-        <v>42.7</v>
+        <v>42.4</v>
       </c>
       <c r="I57" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="J57" t="n">
-        <v>14.88</v>
+        <v>167.98</v>
       </c>
       <c r="K57" t="n">
-        <v>-109.92</v>
+        <v>-12.1</v>
       </c>
       <c r="L57" t="n">
-        <v>110.92</v>
+        <v>168.42</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>07:16:57</t>
+          <t>07:19:26</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -2473,34 +2473,34 @@
         <v>3</v>
       </c>
       <c r="E58" t="n">
-        <v>1.94</v>
+        <v>1.8</v>
       </c>
       <c r="F58" t="n">
-        <v>9.210000000000001</v>
+        <v>8.19</v>
       </c>
       <c r="G58" t="n">
-        <v>59.4</v>
+        <v>54.3</v>
       </c>
       <c r="H58" t="n">
-        <v>43</v>
+        <v>54.3</v>
       </c>
       <c r="I58" t="n">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="J58" t="n">
-        <v>-158.48</v>
+        <v>51.12</v>
       </c>
       <c r="K58" t="n">
-        <v>-62.24</v>
+        <v>-154.63</v>
       </c>
       <c r="L58" t="n">
-        <v>170.26</v>
+        <v>162.86</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>07:26:43</t>
+          <t>07:30:57</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -2515,34 +2515,34 @@
         <v>1</v>
       </c>
       <c r="E59" t="n">
-        <v>1.82</v>
+        <v>1.75</v>
       </c>
       <c r="F59" t="n">
-        <v>9.44</v>
+        <v>9.42</v>
       </c>
       <c r="G59" t="n">
-        <v>58.7</v>
+        <v>63.7</v>
       </c>
       <c r="H59" t="n">
-        <v>33.3</v>
+        <v>28.1</v>
       </c>
       <c r="I59" t="n">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="J59" t="n">
-        <v>-12.54</v>
+        <v>4.76</v>
       </c>
       <c r="K59" t="n">
-        <v>29.88</v>
+        <v>31.59</v>
       </c>
       <c r="L59" t="n">
-        <v>32.4</v>
+        <v>31.95</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>07:28:34</t>
+          <t>07:31:48</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -2557,34 +2557,34 @@
         <v>2</v>
       </c>
       <c r="E60" t="n">
-        <v>2.15</v>
+        <v>2.09</v>
       </c>
       <c r="F60" t="n">
         <v>10.35</v>
       </c>
       <c r="G60" t="n">
-        <v>67.09999999999999</v>
+        <v>61.5</v>
       </c>
       <c r="H60" t="n">
-        <v>41.9</v>
+        <v>37.7</v>
       </c>
       <c r="I60" t="n">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="J60" t="n">
-        <v>5.51</v>
+        <v>2.97</v>
       </c>
       <c r="K60" t="n">
-        <v>35.76</v>
+        <v>28.85</v>
       </c>
       <c r="L60" t="n">
-        <v>36.18</v>
+        <v>29</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>07:30:03</t>
+          <t>07:33:23</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -2599,34 +2599,34 @@
         <v>3</v>
       </c>
       <c r="E61" t="n">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
       <c r="F61" t="n">
-        <v>6.36</v>
+        <v>8.48</v>
       </c>
       <c r="G61" t="n">
-        <v>59.6</v>
+        <v>59.7</v>
       </c>
       <c r="H61" t="n">
-        <v>51.8</v>
+        <v>29.9</v>
       </c>
       <c r="I61" t="n">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="J61" t="n">
-        <v>26.01</v>
+        <v>-8.43</v>
       </c>
       <c r="K61" t="n">
-        <v>6.89</v>
+        <v>-31.61</v>
       </c>
       <c r="L61" t="n">
-        <v>26.91</v>
+        <v>32.72</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>07:34:36</t>
+          <t>07:36:39</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -2641,34 +2641,34 @@
         <v>1</v>
       </c>
       <c r="E62" t="n">
-        <v>1.44</v>
+        <v>1.92</v>
       </c>
       <c r="F62" t="n">
-        <v>1.74</v>
+        <v>7.56</v>
       </c>
       <c r="G62" t="n">
-        <v>74.3</v>
+        <v>61.6</v>
       </c>
       <c r="H62" t="n">
-        <v>34.1</v>
+        <v>53.2</v>
       </c>
       <c r="I62" t="n">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="J62" t="n">
-        <v>-35.3</v>
+        <v>33.58</v>
       </c>
       <c r="K62" t="n">
-        <v>-15.49</v>
+        <v>-30.07</v>
       </c>
       <c r="L62" t="n">
-        <v>38.55</v>
+        <v>45.08</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>07:36:58</t>
+          <t>07:38:06</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -2683,34 +2683,34 @@
         <v>2</v>
       </c>
       <c r="E63" t="n">
-        <v>2.04</v>
+        <v>1.8</v>
       </c>
       <c r="F63" t="n">
-        <v>6.87</v>
+        <v>4.45</v>
       </c>
       <c r="G63" t="n">
-        <v>64.2</v>
+        <v>64.3</v>
       </c>
       <c r="H63" t="n">
-        <v>53</v>
+        <v>66.09999999999999</v>
       </c>
       <c r="I63" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="J63" t="n">
-        <v>-39.45</v>
+        <v>57.63</v>
       </c>
       <c r="K63" t="n">
-        <v>29.58</v>
+        <v>7.01</v>
       </c>
       <c r="L63" t="n">
-        <v>49.31</v>
+        <v>58.05</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>07:39:05</t>
+          <t>07:40:02</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -2725,34 +2725,34 @@
         <v>3</v>
       </c>
       <c r="E64" t="n">
-        <v>1.96</v>
+        <v>1.71</v>
       </c>
       <c r="F64" t="n">
-        <v>10.35</v>
+        <v>7.54</v>
       </c>
       <c r="G64" t="n">
-        <v>54.5</v>
+        <v>68</v>
       </c>
       <c r="H64" t="n">
-        <v>53.4</v>
+        <v>54.6</v>
       </c>
       <c r="I64" t="n">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="J64" t="n">
-        <v>37.62</v>
+        <v>-27.44</v>
       </c>
       <c r="K64" t="n">
-        <v>-8.02</v>
+        <v>-50.57</v>
       </c>
       <c r="L64" t="n">
-        <v>38.47</v>
+        <v>57.53</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>07:44:17</t>
+          <t>07:45:03</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -2767,34 +2767,34 @@
         <v>1</v>
       </c>
       <c r="E65" t="n">
-        <v>2.01</v>
+        <v>1.93</v>
       </c>
       <c r="F65" t="n">
-        <v>5.25</v>
+        <v>10.07</v>
       </c>
       <c r="G65" t="n">
-        <v>59.6</v>
+        <v>72.09999999999999</v>
       </c>
       <c r="H65" t="n">
-        <v>58.3</v>
+        <v>40.5</v>
       </c>
       <c r="I65" t="n">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="J65" t="n">
-        <v>75.43000000000001</v>
+        <v>116.72</v>
       </c>
       <c r="K65" t="n">
-        <v>-22.67</v>
+        <v>50.25</v>
       </c>
       <c r="L65" t="n">
-        <v>78.76000000000001</v>
+        <v>127.08</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>07:46:29</t>
+          <t>07:47:19</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -2809,34 +2809,34 @@
         <v>2</v>
       </c>
       <c r="E66" t="n">
-        <v>1.87</v>
+        <v>1.91</v>
       </c>
       <c r="F66" t="n">
-        <v>2.62</v>
+        <v>10.35</v>
       </c>
       <c r="G66" t="n">
-        <v>62.8</v>
+        <v>56.6</v>
       </c>
       <c r="H66" t="n">
-        <v>70</v>
+        <v>49.1</v>
       </c>
       <c r="I66" t="n">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="J66" t="n">
-        <v>-47.3</v>
+        <v>38.2</v>
       </c>
       <c r="K66" t="n">
-        <v>-41.3</v>
+        <v>-86.95</v>
       </c>
       <c r="L66" t="n">
-        <v>62.79</v>
+        <v>94.97</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>07:48:57</t>
+          <t>07:49:44</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -2851,34 +2851,34 @@
         <v>3</v>
       </c>
       <c r="E67" t="n">
-        <v>1.85</v>
+        <v>2.14</v>
       </c>
       <c r="F67" t="n">
-        <v>8.18</v>
+        <v>4.93</v>
       </c>
       <c r="G67" t="n">
-        <v>67.09999999999999</v>
+        <v>65.90000000000001</v>
       </c>
       <c r="H67" t="n">
-        <v>58.8</v>
+        <v>55.5</v>
       </c>
       <c r="I67" t="n">
         <v>24</v>
       </c>
       <c r="J67" t="n">
-        <v>-1.84</v>
+        <v>-80.45999999999999</v>
       </c>
       <c r="K67" t="n">
-        <v>78.2</v>
+        <v>49.84</v>
       </c>
       <c r="L67" t="n">
-        <v>78.22</v>
+        <v>94.65000000000001</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>07:54:13</t>
+          <t>07:54:17</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -2893,34 +2893,34 @@
         <v>1</v>
       </c>
       <c r="E68" t="n">
-        <v>1.93</v>
+        <v>2.37</v>
       </c>
       <c r="F68" t="n">
-        <v>8.289999999999999</v>
+        <v>9.98</v>
       </c>
       <c r="G68" t="n">
-        <v>84.7</v>
+        <v>67.3</v>
       </c>
       <c r="H68" t="n">
-        <v>54.3</v>
+        <v>48.8</v>
       </c>
       <c r="I68" t="n">
-        <v>20</v>
+        <v>31</v>
       </c>
       <c r="J68" t="n">
-        <v>-55.93</v>
+        <v>140.63</v>
       </c>
       <c r="K68" t="n">
-        <v>-84.16</v>
+        <v>-96.65000000000001</v>
       </c>
       <c r="L68" t="n">
-        <v>101.05</v>
+        <v>170.64</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>07:56:30</t>
+          <t>07:55:42</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -2935,34 +2935,34 @@
         <v>2</v>
       </c>
       <c r="E69" t="n">
-        <v>2.3</v>
+        <v>1.98</v>
       </c>
       <c r="F69" t="n">
-        <v>10.35</v>
+        <v>9.039999999999999</v>
       </c>
       <c r="G69" t="n">
-        <v>70.09999999999999</v>
+        <v>68.59999999999999</v>
       </c>
       <c r="H69" t="n">
-        <v>48.1</v>
+        <v>78.59999999999999</v>
       </c>
       <c r="I69" t="n">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="J69" t="n">
-        <v>96.88</v>
+        <v>137.3</v>
       </c>
       <c r="K69" t="n">
-        <v>-34.58</v>
+        <v>-23.79</v>
       </c>
       <c r="L69" t="n">
-        <v>102.87</v>
+        <v>139.35</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>07:57:32</t>
+          <t>07:57:52</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -2977,34 +2977,34 @@
         <v>3</v>
       </c>
       <c r="E70" t="n">
-        <v>2.22</v>
+        <v>1.95</v>
       </c>
       <c r="F70" t="n">
-        <v>10.31</v>
+        <v>10.35</v>
       </c>
       <c r="G70" t="n">
-        <v>63.6</v>
+        <v>54.4</v>
       </c>
       <c r="H70" t="n">
-        <v>0</v>
+        <v>12.3</v>
       </c>
       <c r="I70" t="n">
         <v>25</v>
       </c>
       <c r="J70" t="n">
-        <v>74.76000000000001</v>
+        <v>101.86</v>
       </c>
       <c r="K70" t="n">
-        <v>126.84</v>
+        <v>3.76</v>
       </c>
       <c r="L70" t="n">
-        <v>147.23</v>
+        <v>101.93</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>08:02:50</t>
+          <t>08:02:35</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -3019,34 +3019,34 @@
         <v>1</v>
       </c>
       <c r="E71" t="n">
-        <v>1.86</v>
+        <v>1.97</v>
       </c>
       <c r="F71" t="n">
-        <v>10.35</v>
+        <v>8.94</v>
       </c>
       <c r="G71" t="n">
-        <v>69.59999999999999</v>
+        <v>61.8</v>
       </c>
       <c r="H71" t="n">
-        <v>63.8</v>
+        <v>81.8</v>
       </c>
       <c r="I71" t="n">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="J71" t="n">
-        <v>126.25</v>
+        <v>-153.66</v>
       </c>
       <c r="K71" t="n">
-        <v>-149.89</v>
+        <v>-146.67</v>
       </c>
       <c r="L71" t="n">
-        <v>195.98</v>
+        <v>212.42</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>08:03:26</t>
+          <t>08:04:42</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -3061,34 +3061,34 @@
         <v>2</v>
       </c>
       <c r="E72" t="n">
-        <v>1.94</v>
+        <v>2.07</v>
       </c>
       <c r="F72" t="n">
-        <v>9.75</v>
+        <v>9.69</v>
       </c>
       <c r="G72" t="n">
-        <v>74.40000000000001</v>
+        <v>70.5</v>
       </c>
       <c r="H72" t="n">
-        <v>83.59999999999999</v>
+        <v>42.7</v>
       </c>
       <c r="I72" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="J72" t="n">
-        <v>-82.73</v>
+        <v>1.1</v>
       </c>
       <c r="K72" t="n">
-        <v>-107.82</v>
+        <v>-121.47</v>
       </c>
       <c r="L72" t="n">
-        <v>135.9</v>
+        <v>121.47</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>08:06:06</t>
+          <t>08:07:01</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -3103,34 +3103,34 @@
         <v>3</v>
       </c>
       <c r="E73" t="n">
-        <v>1.79</v>
+        <v>2.02</v>
       </c>
       <c r="F73" t="n">
-        <v>10.35</v>
+        <v>9.81</v>
       </c>
       <c r="G73" t="n">
-        <v>69.8</v>
+        <v>51.6</v>
       </c>
       <c r="H73" t="n">
-        <v>41.2</v>
+        <v>29.5</v>
       </c>
       <c r="I73" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="J73" t="n">
-        <v>109.46</v>
+        <v>144.35</v>
       </c>
       <c r="K73" t="n">
-        <v>-14.91</v>
+        <v>-6.16</v>
       </c>
       <c r="L73" t="n">
-        <v>110.47</v>
+        <v>144.48</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>08:13:25</t>
+          <t>08:16:48</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -3145,34 +3145,34 @@
         <v>1</v>
       </c>
       <c r="E74" t="n">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="F74" t="n">
-        <v>10</v>
+        <v>8.07</v>
       </c>
       <c r="G74" t="n">
-        <v>73.59999999999999</v>
+        <v>58.7</v>
       </c>
       <c r="H74" t="n">
-        <v>31.3</v>
+        <v>33.3</v>
       </c>
       <c r="I74" t="n">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="J74" t="n">
-        <v>30.94</v>
+        <v>-18.57</v>
       </c>
       <c r="K74" t="n">
-        <v>19.25</v>
+        <v>30.22</v>
       </c>
       <c r="L74" t="n">
-        <v>36.44</v>
+        <v>35.47</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>08:15:22</t>
+          <t>08:18:24</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -3187,34 +3187,34 @@
         <v>2</v>
       </c>
       <c r="E75" t="n">
-        <v>1.87</v>
+        <v>2.22</v>
       </c>
       <c r="F75" t="n">
-        <v>7.33</v>
+        <v>10.35</v>
       </c>
       <c r="G75" t="n">
-        <v>68.7</v>
+        <v>61.7</v>
       </c>
       <c r="H75" t="n">
-        <v>50.7</v>
+        <v>48.8</v>
       </c>
       <c r="I75" t="n">
-        <v>18</v>
+        <v>32</v>
       </c>
       <c r="J75" t="n">
-        <v>-30.57</v>
+        <v>20.48</v>
       </c>
       <c r="K75" t="n">
-        <v>25.53</v>
+        <v>-34.35</v>
       </c>
       <c r="L75" t="n">
-        <v>39.83</v>
+        <v>39.99</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>08:17:23</t>
+          <t>08:20:46</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -3229,34 +3229,34 @@
         <v>3</v>
       </c>
       <c r="E76" t="n">
-        <v>1.91</v>
+        <v>1.57</v>
       </c>
       <c r="F76" t="n">
-        <v>10.35</v>
+        <v>3.18</v>
       </c>
       <c r="G76" t="n">
-        <v>52.7</v>
+        <v>59.6</v>
       </c>
       <c r="H76" t="n">
-        <v>56.2</v>
+        <v>51.8</v>
       </c>
       <c r="I76" t="n">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="J76" t="n">
-        <v>-33.49</v>
+        <v>26.74</v>
       </c>
       <c r="K76" t="n">
-        <v>-2.98</v>
+        <v>5.7</v>
       </c>
       <c r="L76" t="n">
-        <v>33.62</v>
+        <v>27.34</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>08:21:12</t>
+          <t>08:24:34</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -3271,34 +3271,34 @@
         <v>1</v>
       </c>
       <c r="E77" t="n">
-        <v>1.79</v>
+        <v>1.51</v>
       </c>
       <c r="F77" t="n">
-        <v>10.09</v>
+        <v>1.81</v>
       </c>
       <c r="G77" t="n">
-        <v>62.4</v>
+        <v>89.7</v>
       </c>
       <c r="H77" t="n">
-        <v>55.1</v>
+        <v>66.90000000000001</v>
       </c>
       <c r="I77" t="n">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="J77" t="n">
-        <v>45.09</v>
+        <v>-13.68</v>
       </c>
       <c r="K77" t="n">
-        <v>0.23</v>
+        <v>40.91</v>
       </c>
       <c r="L77" t="n">
-        <v>45.09</v>
+        <v>43.14</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>08:23:45</t>
+          <t>08:26:59</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -3313,34 +3313,34 @@
         <v>2</v>
       </c>
       <c r="E78" t="n">
-        <v>2.1</v>
+        <v>1.97</v>
       </c>
       <c r="F78" t="n">
-        <v>7.76</v>
+        <v>8.83</v>
       </c>
       <c r="G78" t="n">
-        <v>77.3</v>
+        <v>60.2</v>
       </c>
       <c r="H78" t="n">
-        <v>53.8</v>
+        <v>27.4</v>
       </c>
       <c r="I78" t="n">
         <v>25</v>
       </c>
       <c r="J78" t="n">
-        <v>33.2</v>
+        <v>36.24</v>
       </c>
       <c r="K78" t="n">
-        <v>35.58</v>
+        <v>33.85</v>
       </c>
       <c r="L78" t="n">
-        <v>48.66</v>
+        <v>49.59</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>08:25:37</t>
+          <t>08:29:22</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -3355,34 +3355,34 @@
         <v>3</v>
       </c>
       <c r="E79" t="n">
-        <v>2.19</v>
+        <v>2.39</v>
       </c>
       <c r="F79" t="n">
-        <v>10.35</v>
+        <v>7.51</v>
       </c>
       <c r="G79" t="n">
-        <v>54.8</v>
+        <v>71</v>
       </c>
       <c r="H79" t="n">
-        <v>27.9</v>
+        <v>29.2</v>
       </c>
       <c r="I79" t="n">
         <v>28</v>
       </c>
       <c r="J79" t="n">
-        <v>55.88</v>
+        <v>53.08</v>
       </c>
       <c r="K79" t="n">
-        <v>3.5</v>
+        <v>31.85</v>
       </c>
       <c r="L79" t="n">
-        <v>55.99</v>
+        <v>61.9</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>08:29:28</t>
+          <t>08:34:02</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -3397,34 +3397,34 @@
         <v>1</v>
       </c>
       <c r="E80" t="n">
-        <v>2.14</v>
+        <v>3.66</v>
       </c>
       <c r="F80" t="n">
-        <v>10.15</v>
+        <v>10.35</v>
       </c>
       <c r="G80" t="n">
-        <v>69.59999999999999</v>
+        <v>88.90000000000001</v>
       </c>
       <c r="H80" t="n">
-        <v>58.8</v>
+        <v>76.2</v>
       </c>
       <c r="I80" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="J80" t="n">
-        <v>-69.09999999999999</v>
+        <v>68.76000000000001</v>
       </c>
       <c r="K80" t="n">
-        <v>-28.57</v>
+        <v>87.73999999999999</v>
       </c>
       <c r="L80" t="n">
-        <v>74.77</v>
+        <v>111.48</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>08:31:43</t>
+          <t>08:34:59</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -3439,34 +3439,34 @@
         <v>2</v>
       </c>
       <c r="E81" t="n">
-        <v>1.76</v>
+        <v>2.36</v>
       </c>
       <c r="F81" t="n">
-        <v>6.98</v>
+        <v>8.220000000000001</v>
       </c>
       <c r="G81" t="n">
-        <v>57.5</v>
+        <v>65</v>
       </c>
       <c r="H81" t="n">
-        <v>22.4</v>
+        <v>80</v>
       </c>
       <c r="I81" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="J81" t="n">
-        <v>-74.73</v>
+        <v>90.64</v>
       </c>
       <c r="K81" t="n">
-        <v>-68.27</v>
+        <v>-14.35</v>
       </c>
       <c r="L81" t="n">
-        <v>101.22</v>
+        <v>91.76000000000001</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>08:33:40</t>
+          <t>08:35:57</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -3481,34 +3481,34 @@
         <v>3</v>
       </c>
       <c r="E82" t="n">
-        <v>2.22</v>
+        <v>2.56</v>
       </c>
       <c r="F82" t="n">
         <v>10.35</v>
       </c>
       <c r="G82" t="n">
-        <v>49.7</v>
+        <v>63.6</v>
       </c>
       <c r="H82" t="n">
-        <v>50.7</v>
+        <v>100</v>
       </c>
       <c r="I82" t="n">
-        <v>18</v>
+        <v>32</v>
       </c>
       <c r="J82" t="n">
-        <v>32.92</v>
+        <v>-77.38</v>
       </c>
       <c r="K82" t="n">
-        <v>83.56</v>
+        <v>81.45999999999999</v>
       </c>
       <c r="L82" t="n">
-        <v>89.81</v>
+        <v>112.36</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>08:38:37</t>
+          <t>08:40:20</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -3523,34 +3523,34 @@
         <v>1</v>
       </c>
       <c r="E83" t="n">
-        <v>2.11</v>
+        <v>2.38</v>
       </c>
       <c r="F83" t="n">
-        <v>10.35</v>
+        <v>9.18</v>
       </c>
       <c r="G83" t="n">
-        <v>77.5</v>
+        <v>72.7</v>
       </c>
       <c r="H83" t="n">
-        <v>28.7</v>
+        <v>24.9</v>
       </c>
       <c r="I83" t="n">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="J83" t="n">
-        <v>47.66</v>
+        <v>-77.73999999999999</v>
       </c>
       <c r="K83" t="n">
-        <v>-98.34999999999999</v>
+        <v>161.16</v>
       </c>
       <c r="L83" t="n">
-        <v>109.29</v>
+        <v>178.93</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>08:39:49</t>
+          <t>08:41:34</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -3565,34 +3565,34 @@
         <v>2</v>
       </c>
       <c r="E84" t="n">
-        <v>2.34</v>
+        <v>1.94</v>
       </c>
       <c r="F84" t="n">
-        <v>9.6</v>
+        <v>6.27</v>
       </c>
       <c r="G84" t="n">
-        <v>59</v>
+        <v>64.8</v>
       </c>
       <c r="H84" t="n">
-        <v>52.2</v>
+        <v>35.5</v>
       </c>
       <c r="I84" t="n">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="J84" t="n">
-        <v>120.16</v>
+        <v>115.72</v>
       </c>
       <c r="K84" t="n">
-        <v>29.07</v>
+        <v>4.39</v>
       </c>
       <c r="L84" t="n">
-        <v>123.62</v>
+        <v>115.8</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>08:41:18</t>
+          <t>08:43:29</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -3607,34 +3607,34 @@
         <v>3</v>
       </c>
       <c r="E85" t="n">
-        <v>2.07</v>
+        <v>1.34</v>
       </c>
       <c r="F85" t="n">
-        <v>8.08</v>
+        <v>2.57</v>
       </c>
       <c r="G85" t="n">
-        <v>61.2</v>
+        <v>46.1</v>
       </c>
       <c r="H85" t="n">
-        <v>47.8</v>
+        <v>74.09999999999999</v>
       </c>
       <c r="I85" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="J85" t="n">
-        <v>69.98999999999999</v>
+        <v>-17.52</v>
       </c>
       <c r="K85" t="n">
-        <v>91.83</v>
+        <v>-100.69</v>
       </c>
       <c r="L85" t="n">
-        <v>115.47</v>
+        <v>102.2</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>08:46:41</t>
+          <t>08:46:52</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -3655,28 +3655,28 @@
         <v>10.35</v>
       </c>
       <c r="G86" t="n">
-        <v>57.8</v>
+        <v>80.8</v>
       </c>
       <c r="H86" t="n">
-        <v>1.3</v>
+        <v>70.40000000000001</v>
       </c>
       <c r="I86" t="n">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="J86" t="n">
-        <v>110.34</v>
+        <v>157.5</v>
       </c>
       <c r="K86" t="n">
-        <v>132.56</v>
+        <v>104.59</v>
       </c>
       <c r="L86" t="n">
-        <v>172.47</v>
+        <v>189.06</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>08:48:20</t>
+          <t>08:49:38</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -3691,34 +3691,34 @@
         <v>2</v>
       </c>
       <c r="E87" t="n">
-        <v>2.32</v>
+        <v>2.68</v>
       </c>
       <c r="F87" t="n">
-        <v>10.08</v>
+        <v>10.35</v>
       </c>
       <c r="G87" t="n">
-        <v>66.3</v>
+        <v>59.8</v>
       </c>
       <c r="H87" t="n">
-        <v>31.4</v>
+        <v>29</v>
       </c>
       <c r="I87" t="n">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="J87" t="n">
-        <v>13.15</v>
+        <v>-7.03</v>
       </c>
       <c r="K87" t="n">
-        <v>-130.34</v>
+        <v>-172.68</v>
       </c>
       <c r="L87" t="n">
-        <v>131</v>
+        <v>172.83</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>08:49:08</t>
+          <t>08:50:26</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -3733,28 +3733,28 @@
         <v>3</v>
       </c>
       <c r="E88" t="n">
-        <v>2.19</v>
+        <v>2.07</v>
       </c>
       <c r="F88" t="n">
-        <v>9.23</v>
+        <v>6.75</v>
       </c>
       <c r="G88" t="n">
-        <v>53.4</v>
+        <v>51.4</v>
       </c>
       <c r="H88" t="n">
-        <v>15.2</v>
+        <v>64.3</v>
       </c>
       <c r="I88" t="n">
-        <v>20</v>
+        <v>31</v>
       </c>
       <c r="J88" t="n">
-        <v>291.72</v>
+        <v>-163.45</v>
       </c>
       <c r="K88" t="n">
-        <v>15.42</v>
+        <v>-83.06</v>
       </c>
       <c r="L88" t="n">
-        <v>292.12</v>
+        <v>183.35</v>
       </c>
     </row>
   </sheetData>

--- a/output/2024-07-26.xlsx
+++ b/output/2024-07-26.xlsx
@@ -640,13 +640,13 @@
         <v>27</v>
       </c>
       <c r="J14" t="n">
-        <v>28.31</v>
+        <v>29.33</v>
       </c>
       <c r="K14" t="n">
-        <v>28.91</v>
+        <v>29.95</v>
       </c>
       <c r="L14" t="n">
-        <v>40.46</v>
+        <v>41.92</v>
       </c>
     </row>
     <row r="15">
@@ -682,13 +682,13 @@
         <v>25</v>
       </c>
       <c r="J15" t="n">
-        <v>23.7</v>
+        <v>26.26</v>
       </c>
       <c r="K15" t="n">
-        <v>-19.03</v>
+        <v>-21.08</v>
       </c>
       <c r="L15" t="n">
-        <v>30.4</v>
+        <v>33.67</v>
       </c>
     </row>
     <row r="16">
@@ -724,13 +724,13 @@
         <v>23</v>
       </c>
       <c r="J16" t="n">
-        <v>-13.81</v>
+        <v>-14.83</v>
       </c>
       <c r="K16" t="n">
-        <v>32.99</v>
+        <v>35.44</v>
       </c>
       <c r="L16" t="n">
-        <v>35.76</v>
+        <v>38.41</v>
       </c>
     </row>
     <row r="17">
@@ -766,13 +766,13 @@
         <v>22</v>
       </c>
       <c r="J17" t="n">
-        <v>-43.92</v>
+        <v>-45.61</v>
       </c>
       <c r="K17" t="n">
-        <v>38.29</v>
+        <v>39.77</v>
       </c>
       <c r="L17" t="n">
-        <v>58.27</v>
+        <v>60.52</v>
       </c>
     </row>
     <row r="18">
@@ -808,13 +808,13 @@
         <v>22</v>
       </c>
       <c r="J18" t="n">
-        <v>44.52</v>
+        <v>48.89</v>
       </c>
       <c r="K18" t="n">
-        <v>8.390000000000001</v>
+        <v>9.210000000000001</v>
       </c>
       <c r="L18" t="n">
-        <v>45.31</v>
+        <v>49.76</v>
       </c>
     </row>
     <row r="19">
@@ -850,13 +850,13 @@
         <v>25</v>
       </c>
       <c r="J19" t="n">
-        <v>69.28</v>
+        <v>67.26000000000001</v>
       </c>
       <c r="K19" t="n">
-        <v>-5.95</v>
+        <v>-5.78</v>
       </c>
       <c r="L19" t="n">
-        <v>69.53</v>
+        <v>67.51000000000001</v>
       </c>
     </row>
     <row r="20">
@@ -892,13 +892,13 @@
         <v>22</v>
       </c>
       <c r="J20" t="n">
-        <v>-18.77</v>
+        <v>-20.4</v>
       </c>
       <c r="K20" t="n">
-        <v>79.45</v>
+        <v>86.34999999999999</v>
       </c>
       <c r="L20" t="n">
-        <v>81.63</v>
+        <v>88.73</v>
       </c>
     </row>
     <row r="21">
@@ -934,13 +934,13 @@
         <v>24</v>
       </c>
       <c r="J21" t="n">
-        <v>-114.51</v>
+        <v>-118.07</v>
       </c>
       <c r="K21" t="n">
-        <v>-7.65</v>
+        <v>-7.89</v>
       </c>
       <c r="L21" t="n">
-        <v>114.76</v>
+        <v>118.34</v>
       </c>
     </row>
     <row r="22">
@@ -976,13 +976,13 @@
         <v>21</v>
       </c>
       <c r="J22" t="n">
-        <v>107.49</v>
+        <v>112.97</v>
       </c>
       <c r="K22" t="n">
-        <v>35.35</v>
+        <v>37.15</v>
       </c>
       <c r="L22" t="n">
-        <v>113.15</v>
+        <v>118.92</v>
       </c>
     </row>
     <row r="23">
@@ -1018,13 +1018,13 @@
         <v>23</v>
       </c>
       <c r="J23" t="n">
-        <v>-136.2</v>
+        <v>-143.14</v>
       </c>
       <c r="K23" t="n">
-        <v>-86.73999999999999</v>
+        <v>-91.16</v>
       </c>
       <c r="L23" t="n">
-        <v>161.47</v>
+        <v>169.71</v>
       </c>
     </row>
     <row r="24">
@@ -1060,13 +1060,13 @@
         <v>23</v>
       </c>
       <c r="J24" t="n">
-        <v>-84.09999999999999</v>
+        <v>-101.43</v>
       </c>
       <c r="K24" t="n">
-        <v>-32.54</v>
+        <v>-39.25</v>
       </c>
       <c r="L24" t="n">
-        <v>90.18000000000001</v>
+        <v>108.76</v>
       </c>
     </row>
     <row r="25">
@@ -1102,13 +1102,13 @@
         <v>27</v>
       </c>
       <c r="J25" t="n">
-        <v>44.32</v>
+        <v>50.48</v>
       </c>
       <c r="K25" t="n">
-        <v>-92.84999999999999</v>
+        <v>-105.77</v>
       </c>
       <c r="L25" t="n">
-        <v>102.89</v>
+        <v>117.2</v>
       </c>
     </row>
     <row r="26">
@@ -1144,13 +1144,13 @@
         <v>22</v>
       </c>
       <c r="J26" t="n">
-        <v>21.53</v>
+        <v>27.91</v>
       </c>
       <c r="K26" t="n">
-        <v>-127.45</v>
+        <v>-165.17</v>
       </c>
       <c r="L26" t="n">
-        <v>129.26</v>
+        <v>167.51</v>
       </c>
     </row>
     <row r="27">
@@ -1186,13 +1186,13 @@
         <v>25</v>
       </c>
       <c r="J27" t="n">
-        <v>120.54</v>
+        <v>147.06</v>
       </c>
       <c r="K27" t="n">
-        <v>-66.5</v>
+        <v>-81.13</v>
       </c>
       <c r="L27" t="n">
-        <v>137.66</v>
+        <v>167.95</v>
       </c>
     </row>
     <row r="28">
@@ -1228,13 +1228,13 @@
         <v>21</v>
       </c>
       <c r="J28" t="n">
-        <v>-315.08</v>
+        <v>-331.29</v>
       </c>
       <c r="K28" t="n">
-        <v>-29.21</v>
+        <v>-30.71</v>
       </c>
       <c r="L28" t="n">
-        <v>316.43</v>
+        <v>332.71</v>
       </c>
     </row>
     <row r="29">
@@ -1270,13 +1270,13 @@
         <v>24</v>
       </c>
       <c r="J29" t="n">
-        <v>35.19</v>
+        <v>36.53</v>
       </c>
       <c r="K29" t="n">
-        <v>18.29</v>
+        <v>18.99</v>
       </c>
       <c r="L29" t="n">
-        <v>39.66</v>
+        <v>41.17</v>
       </c>
     </row>
     <row r="30">
@@ -1312,13 +1312,13 @@
         <v>23</v>
       </c>
       <c r="J30" t="n">
-        <v>-41.7</v>
+        <v>-39.59</v>
       </c>
       <c r="K30" t="n">
-        <v>36.14</v>
+        <v>34.31</v>
       </c>
       <c r="L30" t="n">
-        <v>55.18</v>
+        <v>52.39</v>
       </c>
     </row>
     <row r="31">
@@ -1354,13 +1354,13 @@
         <v>21</v>
       </c>
       <c r="J31" t="n">
-        <v>-2.51</v>
+        <v>-2.81</v>
       </c>
       <c r="K31" t="n">
-        <v>-33.47</v>
+        <v>-37.48</v>
       </c>
       <c r="L31" t="n">
-        <v>33.56</v>
+        <v>37.59</v>
       </c>
     </row>
     <row r="32">
@@ -1396,13 +1396,13 @@
         <v>27</v>
       </c>
       <c r="J32" t="n">
-        <v>39.84</v>
+        <v>43.58</v>
       </c>
       <c r="K32" t="n">
-        <v>29.43</v>
+        <v>32.19</v>
       </c>
       <c r="L32" t="n">
-        <v>49.53</v>
+        <v>54.18</v>
       </c>
     </row>
     <row r="33">
@@ -1438,13 +1438,13 @@
         <v>25</v>
       </c>
       <c r="J33" t="n">
-        <v>32.74</v>
+        <v>34.65</v>
       </c>
       <c r="K33" t="n">
-        <v>43.81</v>
+        <v>46.36</v>
       </c>
       <c r="L33" t="n">
-        <v>54.69</v>
+        <v>57.88</v>
       </c>
     </row>
     <row r="34">
@@ -1480,13 +1480,13 @@
         <v>26</v>
       </c>
       <c r="J34" t="n">
-        <v>-52.56</v>
+        <v>-51.59</v>
       </c>
       <c r="K34" t="n">
-        <v>60.09</v>
+        <v>58.98</v>
       </c>
       <c r="L34" t="n">
-        <v>79.83</v>
+        <v>78.36</v>
       </c>
     </row>
     <row r="35">
@@ -1522,13 +1522,13 @@
         <v>22</v>
       </c>
       <c r="J35" t="n">
-        <v>86.29000000000001</v>
+        <v>94.52</v>
       </c>
       <c r="K35" t="n">
-        <v>33.22</v>
+        <v>36.39</v>
       </c>
       <c r="L35" t="n">
-        <v>92.45999999999999</v>
+        <v>101.28</v>
       </c>
     </row>
     <row r="36">
@@ -1564,13 +1564,13 @@
         <v>25</v>
       </c>
       <c r="J36" t="n">
-        <v>91.34</v>
+        <v>91.48</v>
       </c>
       <c r="K36" t="n">
-        <v>71</v>
+        <v>71.09999999999999</v>
       </c>
       <c r="L36" t="n">
-        <v>115.69</v>
+        <v>115.86</v>
       </c>
     </row>
     <row r="37">
@@ -1606,13 +1606,13 @@
         <v>23</v>
       </c>
       <c r="J37" t="n">
-        <v>55.42</v>
+        <v>56.27</v>
       </c>
       <c r="K37" t="n">
-        <v>-132.16</v>
+        <v>-134.19</v>
       </c>
       <c r="L37" t="n">
-        <v>143.31</v>
+        <v>145.51</v>
       </c>
     </row>
     <row r="38">
@@ -1648,13 +1648,13 @@
         <v>23</v>
       </c>
       <c r="J38" t="n">
-        <v>84.36</v>
+        <v>87.61</v>
       </c>
       <c r="K38" t="n">
-        <v>154.62</v>
+        <v>160.59</v>
       </c>
       <c r="L38" t="n">
-        <v>176.14</v>
+        <v>182.94</v>
       </c>
     </row>
     <row r="39">
@@ -1690,13 +1690,13 @@
         <v>24</v>
       </c>
       <c r="J39" t="n">
-        <v>-92.23</v>
+        <v>-103.7</v>
       </c>
       <c r="K39" t="n">
-        <v>70.53</v>
+        <v>79.31</v>
       </c>
       <c r="L39" t="n">
-        <v>116.11</v>
+        <v>130.55</v>
       </c>
     </row>
     <row r="40">
@@ -1732,13 +1732,13 @@
         <v>25</v>
       </c>
       <c r="J40" t="n">
-        <v>-40.86</v>
+        <v>-45.58</v>
       </c>
       <c r="K40" t="n">
-        <v>104.52</v>
+        <v>116.6</v>
       </c>
       <c r="L40" t="n">
-        <v>112.22</v>
+        <v>125.19</v>
       </c>
     </row>
     <row r="41">
@@ -1774,13 +1774,13 @@
         <v>23</v>
       </c>
       <c r="J41" t="n">
-        <v>-79.61</v>
+        <v>-95.95</v>
       </c>
       <c r="K41" t="n">
-        <v>132.85</v>
+        <v>160.11</v>
       </c>
       <c r="L41" t="n">
-        <v>154.88</v>
+        <v>186.66</v>
       </c>
     </row>
     <row r="42">
@@ -1816,13 +1816,13 @@
         <v>21</v>
       </c>
       <c r="J42" t="n">
-        <v>107.98</v>
+        <v>134.96</v>
       </c>
       <c r="K42" t="n">
-        <v>84.11</v>
+        <v>105.13</v>
       </c>
       <c r="L42" t="n">
-        <v>136.87</v>
+        <v>171.08</v>
       </c>
     </row>
     <row r="43">
@@ -1858,13 +1858,13 @@
         <v>22</v>
       </c>
       <c r="J43" t="n">
-        <v>126.45</v>
+        <v>143.4</v>
       </c>
       <c r="K43" t="n">
-        <v>-150.15</v>
+        <v>-170.29</v>
       </c>
       <c r="L43" t="n">
-        <v>196.3</v>
+        <v>222.63</v>
       </c>
     </row>
     <row r="44">
@@ -1900,13 +1900,13 @@
         <v>27</v>
       </c>
       <c r="J44" t="n">
-        <v>-12.61</v>
+        <v>-12.59</v>
       </c>
       <c r="K44" t="n">
-        <v>39.7</v>
+        <v>39.66</v>
       </c>
       <c r="L44" t="n">
-        <v>41.66</v>
+        <v>41.61</v>
       </c>
     </row>
     <row r="45">
@@ -1942,13 +1942,13 @@
         <v>26</v>
       </c>
       <c r="J45" t="n">
-        <v>40.66</v>
+        <v>41.85</v>
       </c>
       <c r="K45" t="n">
-        <v>-2.28</v>
+        <v>-2.35</v>
       </c>
       <c r="L45" t="n">
-        <v>40.72</v>
+        <v>41.92</v>
       </c>
     </row>
     <row r="46">
@@ -1984,13 +1984,13 @@
         <v>23</v>
       </c>
       <c r="J46" t="n">
-        <v>33.31</v>
+        <v>36.01</v>
       </c>
       <c r="K46" t="n">
-        <v>-5.39</v>
+        <v>-5.82</v>
       </c>
       <c r="L46" t="n">
-        <v>33.74</v>
+        <v>36.48</v>
       </c>
     </row>
     <row r="47">
@@ -2026,13 +2026,13 @@
         <v>23</v>
       </c>
       <c r="J47" t="n">
-        <v>-25.64</v>
+        <v>-27.78</v>
       </c>
       <c r="K47" t="n">
-        <v>41.97</v>
+        <v>45.48</v>
       </c>
       <c r="L47" t="n">
-        <v>49.18</v>
+        <v>53.29</v>
       </c>
     </row>
     <row r="48">
@@ -2068,13 +2068,13 @@
         <v>21</v>
       </c>
       <c r="J48" t="n">
-        <v>-35.35</v>
+        <v>-35.03</v>
       </c>
       <c r="K48" t="n">
-        <v>91.56</v>
+        <v>90.73999999999999</v>
       </c>
       <c r="L48" t="n">
-        <v>98.14</v>
+        <v>97.27</v>
       </c>
     </row>
     <row r="49">
@@ -2110,13 +2110,13 @@
         <v>22</v>
       </c>
       <c r="J49" t="n">
-        <v>76.73</v>
+        <v>76.66</v>
       </c>
       <c r="K49" t="n">
-        <v>32.8</v>
+        <v>32.77</v>
       </c>
       <c r="L49" t="n">
-        <v>83.45</v>
+        <v>83.37</v>
       </c>
     </row>
     <row r="50">
@@ -2152,13 +2152,13 @@
         <v>25</v>
       </c>
       <c r="J50" t="n">
-        <v>23.48</v>
+        <v>26.82</v>
       </c>
       <c r="K50" t="n">
-        <v>-68.56</v>
+        <v>-78.3</v>
       </c>
       <c r="L50" t="n">
-        <v>72.47</v>
+        <v>82.77</v>
       </c>
     </row>
     <row r="51">
@@ -2194,13 +2194,13 @@
         <v>24</v>
       </c>
       <c r="J51" t="n">
-        <v>-47</v>
+        <v>-51.68</v>
       </c>
       <c r="K51" t="n">
-        <v>93.97</v>
+        <v>103.33</v>
       </c>
       <c r="L51" t="n">
-        <v>105.07</v>
+        <v>115.53</v>
       </c>
     </row>
     <row r="52">
@@ -2236,13 +2236,13 @@
         <v>21</v>
       </c>
       <c r="J52" t="n">
-        <v>68.06999999999999</v>
+        <v>78.52</v>
       </c>
       <c r="K52" t="n">
-        <v>-10.26</v>
+        <v>-11.84</v>
       </c>
       <c r="L52" t="n">
-        <v>68.83</v>
+        <v>79.41</v>
       </c>
     </row>
     <row r="53">
@@ -2278,13 +2278,13 @@
         <v>23</v>
       </c>
       <c r="J53" t="n">
-        <v>-11.03</v>
+        <v>-12.33</v>
       </c>
       <c r="K53" t="n">
-        <v>127.59</v>
+        <v>142.61</v>
       </c>
       <c r="L53" t="n">
-        <v>128.06</v>
+        <v>143.14</v>
       </c>
     </row>
     <row r="54">
@@ -2320,13 +2320,13 @@
         <v>23</v>
       </c>
       <c r="J54" t="n">
-        <v>138.77</v>
+        <v>145.83</v>
       </c>
       <c r="K54" t="n">
-        <v>58.12</v>
+        <v>61.08</v>
       </c>
       <c r="L54" t="n">
-        <v>150.45</v>
+        <v>158.1</v>
       </c>
     </row>
     <row r="55">
@@ -2362,13 +2362,13 @@
         <v>21</v>
       </c>
       <c r="J55" t="n">
-        <v>177.56</v>
+        <v>185.95</v>
       </c>
       <c r="K55" t="n">
-        <v>-14.14</v>
+        <v>-14.81</v>
       </c>
       <c r="L55" t="n">
-        <v>178.12</v>
+        <v>186.54</v>
       </c>
     </row>
     <row r="56">
@@ -2404,13 +2404,13 @@
         <v>24</v>
       </c>
       <c r="J56" t="n">
-        <v>7.07</v>
+        <v>8.289999999999999</v>
       </c>
       <c r="K56" t="n">
-        <v>154.45</v>
+        <v>181.19</v>
       </c>
       <c r="L56" t="n">
-        <v>154.61</v>
+        <v>181.38</v>
       </c>
     </row>
     <row r="57">
@@ -2446,13 +2446,13 @@
         <v>24</v>
       </c>
       <c r="J57" t="n">
-        <v>160.9</v>
+        <v>193.72</v>
       </c>
       <c r="K57" t="n">
-        <v>7.11</v>
+        <v>8.56</v>
       </c>
       <c r="L57" t="n">
-        <v>161.06</v>
+        <v>193.91</v>
       </c>
     </row>
     <row r="58">
@@ -2488,13 +2488,13 @@
         <v>23</v>
       </c>
       <c r="J58" t="n">
-        <v>38.18</v>
+        <v>48.75</v>
       </c>
       <c r="K58" t="n">
-        <v>-36.07</v>
+        <v>-46.06</v>
       </c>
       <c r="L58" t="n">
-        <v>52.53</v>
+        <v>67.06999999999999</v>
       </c>
     </row>
     <row r="59">
@@ -2530,13 +2530,13 @@
         <v>24</v>
       </c>
       <c r="J59" t="n">
-        <v>3.99</v>
+        <v>3.85</v>
       </c>
       <c r="K59" t="n">
-        <v>57.23</v>
+        <v>55.32</v>
       </c>
       <c r="L59" t="n">
-        <v>57.36</v>
+        <v>55.45</v>
       </c>
     </row>
     <row r="60">
@@ -2572,13 +2572,13 @@
         <v>22</v>
       </c>
       <c r="J60" t="n">
-        <v>-38.04</v>
+        <v>-39.22</v>
       </c>
       <c r="K60" t="n">
-        <v>25.41</v>
+        <v>26.2</v>
       </c>
       <c r="L60" t="n">
-        <v>45.75</v>
+        <v>47.17</v>
       </c>
     </row>
     <row r="61">
@@ -2614,13 +2614,13 @@
         <v>21</v>
       </c>
       <c r="J61" t="n">
-        <v>-44.09</v>
+        <v>-42.81</v>
       </c>
       <c r="K61" t="n">
-        <v>38.07</v>
+        <v>36.96</v>
       </c>
       <c r="L61" t="n">
-        <v>58.25</v>
+        <v>56.56</v>
       </c>
     </row>
     <row r="62">
@@ -2656,13 +2656,13 @@
         <v>21</v>
       </c>
       <c r="J62" t="n">
-        <v>32.66</v>
+        <v>33.04</v>
       </c>
       <c r="K62" t="n">
-        <v>65.54000000000001</v>
+        <v>66.3</v>
       </c>
       <c r="L62" t="n">
-        <v>73.23</v>
+        <v>74.08</v>
       </c>
     </row>
     <row r="63">
@@ -2698,13 +2698,13 @@
         <v>26</v>
       </c>
       <c r="J63" t="n">
-        <v>62.12</v>
+        <v>62.3</v>
       </c>
       <c r="K63" t="n">
-        <v>24.95</v>
+        <v>25.03</v>
       </c>
       <c r="L63" t="n">
-        <v>66.94</v>
+        <v>67.14</v>
       </c>
     </row>
     <row r="64">
@@ -2740,13 +2740,13 @@
         <v>22</v>
       </c>
       <c r="J64" t="n">
-        <v>73.94</v>
+        <v>75.66</v>
       </c>
       <c r="K64" t="n">
-        <v>-55.61</v>
+        <v>-56.9</v>
       </c>
       <c r="L64" t="n">
-        <v>92.52</v>
+        <v>94.66</v>
       </c>
     </row>
     <row r="65">
@@ -2782,13 +2782,13 @@
         <v>23</v>
       </c>
       <c r="J65" t="n">
-        <v>115.05</v>
+        <v>117.73</v>
       </c>
       <c r="K65" t="n">
-        <v>-97.68000000000001</v>
+        <v>-99.95</v>
       </c>
       <c r="L65" t="n">
-        <v>150.92</v>
+        <v>154.44</v>
       </c>
     </row>
     <row r="66">
@@ -2824,13 +2824,13 @@
         <v>26</v>
       </c>
       <c r="J66" t="n">
-        <v>-11.43</v>
+        <v>-13.26</v>
       </c>
       <c r="K66" t="n">
-        <v>64.02</v>
+        <v>74.27</v>
       </c>
       <c r="L66" t="n">
-        <v>65.04000000000001</v>
+        <v>75.45</v>
       </c>
     </row>
     <row r="67">
@@ -2866,13 +2866,13 @@
         <v>23</v>
       </c>
       <c r="J67" t="n">
-        <v>-31.48</v>
+        <v>-38</v>
       </c>
       <c r="K67" t="n">
-        <v>32.39</v>
+        <v>39.11</v>
       </c>
       <c r="L67" t="n">
-        <v>45.17</v>
+        <v>54.53</v>
       </c>
     </row>
     <row r="68">
@@ -2908,13 +2908,13 @@
         <v>21</v>
       </c>
       <c r="J68" t="n">
-        <v>68.3</v>
+        <v>75.78</v>
       </c>
       <c r="K68" t="n">
-        <v>115.59</v>
+        <v>128.25</v>
       </c>
       <c r="L68" t="n">
-        <v>134.26</v>
+        <v>148.97</v>
       </c>
     </row>
     <row r="69">
@@ -2950,13 +2950,13 @@
         <v>27</v>
       </c>
       <c r="J69" t="n">
-        <v>58.17</v>
+        <v>59.68</v>
       </c>
       <c r="K69" t="n">
-        <v>146.16</v>
+        <v>149.96</v>
       </c>
       <c r="L69" t="n">
-        <v>157.32</v>
+        <v>161.4</v>
       </c>
     </row>
     <row r="70">
@@ -2992,13 +2992,13 @@
         <v>26</v>
       </c>
       <c r="J70" t="n">
-        <v>104.44</v>
+        <v>111.48</v>
       </c>
       <c r="K70" t="n">
-        <v>108.8</v>
+        <v>116.13</v>
       </c>
       <c r="L70" t="n">
-        <v>150.81</v>
+        <v>160.98</v>
       </c>
     </row>
     <row r="71">
@@ -3034,13 +3034,13 @@
         <v>25</v>
       </c>
       <c r="J71" t="n">
-        <v>-4.82</v>
+        <v>-5.59</v>
       </c>
       <c r="K71" t="n">
-        <v>-282.29</v>
+        <v>-327.45</v>
       </c>
       <c r="L71" t="n">
-        <v>282.33</v>
+        <v>327.5</v>
       </c>
     </row>
     <row r="72">
@@ -3076,13 +3076,13 @@
         <v>21</v>
       </c>
       <c r="J72" t="n">
-        <v>-5.94</v>
+        <v>-6.56</v>
       </c>
       <c r="K72" t="n">
-        <v>252.25</v>
+        <v>278.65</v>
       </c>
       <c r="L72" t="n">
-        <v>252.32</v>
+        <v>278.73</v>
       </c>
     </row>
     <row r="73">
@@ -3118,13 +3118,13 @@
         <v>27</v>
       </c>
       <c r="J73" t="n">
-        <v>78.68000000000001</v>
+        <v>92.78</v>
       </c>
       <c r="K73" t="n">
-        <v>-135.68</v>
+        <v>-159.99</v>
       </c>
       <c r="L73" t="n">
-        <v>156.84</v>
+        <v>184.94</v>
       </c>
     </row>
     <row r="74">
@@ -3160,13 +3160,13 @@
         <v>27</v>
       </c>
       <c r="J74" t="n">
-        <v>-51.54</v>
+        <v>-47.87</v>
       </c>
       <c r="K74" t="n">
-        <v>-24.27</v>
+        <v>-22.54</v>
       </c>
       <c r="L74" t="n">
-        <v>56.97</v>
+        <v>52.92</v>
       </c>
     </row>
     <row r="75">
@@ -3202,13 +3202,13 @@
         <v>23</v>
       </c>
       <c r="J75" t="n">
-        <v>18.15</v>
+        <v>19.63</v>
       </c>
       <c r="K75" t="n">
-        <v>-31.33</v>
+        <v>-33.88</v>
       </c>
       <c r="L75" t="n">
-        <v>36.2</v>
+        <v>39.16</v>
       </c>
     </row>
     <row r="76">
@@ -3244,13 +3244,13 @@
         <v>22</v>
       </c>
       <c r="J76" t="n">
-        <v>-43.74</v>
+        <v>-43.23</v>
       </c>
       <c r="K76" t="n">
-        <v>33.77</v>
+        <v>33.38</v>
       </c>
       <c r="L76" t="n">
-        <v>55.26</v>
+        <v>54.62</v>
       </c>
     </row>
     <row r="77">
@@ -3286,13 +3286,13 @@
         <v>22</v>
       </c>
       <c r="J77" t="n">
-        <v>-37.5</v>
+        <v>-38.11</v>
       </c>
       <c r="K77" t="n">
-        <v>63.76</v>
+        <v>64.78</v>
       </c>
       <c r="L77" t="n">
-        <v>73.97</v>
+        <v>75.16</v>
       </c>
     </row>
     <row r="78">
@@ -3328,13 +3328,13 @@
         <v>25</v>
       </c>
       <c r="J78" t="n">
-        <v>35.77</v>
+        <v>39.01</v>
       </c>
       <c r="K78" t="n">
-        <v>-31.67</v>
+        <v>-34.54</v>
       </c>
       <c r="L78" t="n">
-        <v>47.77</v>
+        <v>52.1</v>
       </c>
     </row>
     <row r="79">
@@ -3370,13 +3370,13 @@
         <v>25</v>
       </c>
       <c r="J79" t="n">
-        <v>65.28</v>
+        <v>65.12</v>
       </c>
       <c r="K79" t="n">
-        <v>44.44</v>
+        <v>44.33</v>
       </c>
       <c r="L79" t="n">
-        <v>78.97</v>
+        <v>78.78</v>
       </c>
     </row>
     <row r="80">
@@ -3412,13 +3412,13 @@
         <v>27</v>
       </c>
       <c r="J80" t="n">
-        <v>-56.41</v>
+        <v>-65.29000000000001</v>
       </c>
       <c r="K80" t="n">
-        <v>-36.39</v>
+        <v>-42.11</v>
       </c>
       <c r="L80" t="n">
-        <v>67.13</v>
+        <v>77.69</v>
       </c>
     </row>
     <row r="81">
@@ -3454,13 +3454,13 @@
         <v>21</v>
       </c>
       <c r="J81" t="n">
-        <v>-79.39</v>
+        <v>-88.81</v>
       </c>
       <c r="K81" t="n">
-        <v>27.1</v>
+        <v>30.32</v>
       </c>
       <c r="L81" t="n">
-        <v>83.89</v>
+        <v>93.84</v>
       </c>
     </row>
     <row r="82">
@@ -3496,13 +3496,13 @@
         <v>22</v>
       </c>
       <c r="J82" t="n">
-        <v>-3.88</v>
+        <v>-4.72</v>
       </c>
       <c r="K82" t="n">
-        <v>66.08</v>
+        <v>80.39</v>
       </c>
       <c r="L82" t="n">
-        <v>66.19</v>
+        <v>80.53</v>
       </c>
     </row>
     <row r="83">
@@ -3538,13 +3538,13 @@
         <v>25</v>
       </c>
       <c r="J83" t="n">
-        <v>158.52</v>
+        <v>163</v>
       </c>
       <c r="K83" t="n">
-        <v>14.38</v>
+        <v>14.78</v>
       </c>
       <c r="L83" t="n">
-        <v>159.17</v>
+        <v>163.66</v>
       </c>
     </row>
     <row r="84">
@@ -3580,13 +3580,13 @@
         <v>21</v>
       </c>
       <c r="J84" t="n">
-        <v>-13.6</v>
+        <v>-15.43</v>
       </c>
       <c r="K84" t="n">
-        <v>118.1</v>
+        <v>134.06</v>
       </c>
       <c r="L84" t="n">
-        <v>118.88</v>
+        <v>134.95</v>
       </c>
     </row>
     <row r="85">
@@ -3622,13 +3622,13 @@
         <v>22</v>
       </c>
       <c r="J85" t="n">
-        <v>-41.96</v>
+        <v>-42.94</v>
       </c>
       <c r="K85" t="n">
-        <v>-180.4</v>
+        <v>-184.6</v>
       </c>
       <c r="L85" t="n">
-        <v>185.22</v>
+        <v>189.53</v>
       </c>
     </row>
     <row r="86">
@@ -3664,13 +3664,13 @@
         <v>23</v>
       </c>
       <c r="J86" t="n">
-        <v>-254.59</v>
+        <v>-277.98</v>
       </c>
       <c r="K86" t="n">
-        <v>71.25</v>
+        <v>77.79000000000001</v>
       </c>
       <c r="L86" t="n">
-        <v>264.37</v>
+        <v>288.66</v>
       </c>
     </row>
     <row r="87">
@@ -3706,13 +3706,13 @@
         <v>26</v>
       </c>
       <c r="J87" t="n">
-        <v>-194.02</v>
+        <v>-215.47</v>
       </c>
       <c r="K87" t="n">
-        <v>-61.89</v>
+        <v>-68.73999999999999</v>
       </c>
       <c r="L87" t="n">
-        <v>203.65</v>
+        <v>226.17</v>
       </c>
     </row>
     <row r="88">
@@ -3748,13 +3748,13 @@
         <v>21</v>
       </c>
       <c r="J88" t="n">
-        <v>-156.08</v>
+        <v>-185.69</v>
       </c>
       <c r="K88" t="n">
-        <v>-51.82</v>
+        <v>-61.65</v>
       </c>
       <c r="L88" t="n">
-        <v>164.45</v>
+        <v>195.66</v>
       </c>
     </row>
   </sheetData>
